--- a/data/dati.xlsx
+++ b/data/dati.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan_\Desktop\AMI\GitHub\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD3E5617-8C1A-4865-99F2-B8F56F7C1ED8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{424C8256-A2BE-41BF-87BC-91C5A403DACC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Catalogo" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1016" uniqueCount="455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1025" uniqueCount="460">
   <si>
     <t>ID</t>
   </si>
@@ -1387,6 +1387,21 @@
   </si>
   <si>
     <t>https://archive.org/details/avanziamo-lungo-la-via/mode/2up</t>
+  </si>
+  <si>
+    <t>AMI-0093</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/ai-comunisti-ai-lavoratori/mode/2up</t>
+  </si>
+  <si>
+    <t>Firenze</t>
+  </si>
+  <si>
+    <t>Centro Karl Marx</t>
+  </si>
+  <si>
+    <t>Ai comunisti ai lavoratori</t>
   </si>
 </sst>
 </file>
@@ -1446,7 +1461,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1456,6 +1471,7 @@
     <xf numFmtId="17" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Collegamento ipertestuale" xfId="1" builtinId="8"/>
@@ -1812,7 +1828,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P93"/>
+  <dimension ref="A1:P94"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5546875" customWidth="1"/>
@@ -5018,6 +5034,38 @@
       </c>
       <c r="M93" s="3" t="s">
         <v>454</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>455</v>
+      </c>
+      <c r="B94" t="s">
+        <v>459</v>
+      </c>
+      <c r="C94" t="s">
+        <v>458</v>
+      </c>
+      <c r="D94" t="s">
+        <v>458</v>
+      </c>
+      <c r="F94" s="9">
+        <v>26085</v>
+      </c>
+      <c r="G94" t="s">
+        <v>26</v>
+      </c>
+      <c r="H94" t="s">
+        <v>457</v>
+      </c>
+      <c r="I94" t="s">
+        <v>68</v>
+      </c>
+      <c r="L94" t="s">
+        <v>314</v>
+      </c>
+      <c r="M94" s="3" t="s">
+        <v>456</v>
       </c>
     </row>
   </sheetData>
@@ -5115,10 +5163,11 @@
     <hyperlink ref="M91" r:id="rId90" xr:uid="{734F4C0D-ECE0-4D17-AED2-596C8405BA52}"/>
     <hyperlink ref="M70" r:id="rId91" xr:uid="{410C497E-B7A6-4A52-BDB5-CD7FDB43C527}"/>
     <hyperlink ref="M93" r:id="rId92" xr:uid="{A1560D73-B423-4F16-8BB5-470F2068279E}"/>
+    <hyperlink ref="M94" r:id="rId93" xr:uid="{5C1389EE-7B8E-4CE1-AD67-A06B346AE661}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart r:id="rId93"/>
+    <tablePart r:id="rId94"/>
   </tableParts>
 </worksheet>
 </file>

--- a/data/dati.xlsx
+++ b/data/dati.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan_\Desktop\AMI\GitHub\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{424C8256-A2BE-41BF-87BC-91C5A403DACC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BABC0C2-4D01-402A-A898-792DA291A622}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1025" uniqueCount="460">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1047" uniqueCount="467">
   <si>
     <t>ID</t>
   </si>
@@ -1402,6 +1402,27 @@
   </si>
   <si>
     <t>Ai comunisti ai lavoratori</t>
+  </si>
+  <si>
+    <t>06/1971</t>
+  </si>
+  <si>
+    <t>AMI-0094</t>
+  </si>
+  <si>
+    <t>AMI-0095</t>
+  </si>
+  <si>
+    <t>Contro il liberalismo</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/1968-contro-il-liberalismo/mode/2up</t>
+  </si>
+  <si>
+    <t>Presentazione della rivista Il Comunista</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/1969-presentazione-il-comunista/mode/2up</t>
   </si>
 </sst>
 </file>
@@ -1461,7 +1482,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1471,7 +1492,6 @@
     <xf numFmtId="17" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Collegamento ipertestuale" xfId="1" builtinId="8"/>
@@ -1828,7 +1848,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P94"/>
+  <dimension ref="A1:P96"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5546875" customWidth="1"/>
@@ -5049,8 +5069,8 @@
       <c r="D94" t="s">
         <v>458</v>
       </c>
-      <c r="F94" s="9">
-        <v>26085</v>
+      <c r="F94" s="5" t="s">
+        <v>460</v>
       </c>
       <c r="G94" t="s">
         <v>26</v>
@@ -5066,6 +5086,79 @@
       </c>
       <c r="M94" s="3" t="s">
         <v>456</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>461</v>
+      </c>
+      <c r="B95" t="s">
+        <v>463</v>
+      </c>
+      <c r="C95" t="s">
+        <v>17</v>
+      </c>
+      <c r="D95" t="s">
+        <v>18</v>
+      </c>
+      <c r="E95" t="s">
+        <v>19</v>
+      </c>
+      <c r="F95">
+        <v>1968</v>
+      </c>
+      <c r="G95" t="s">
+        <v>26</v>
+      </c>
+      <c r="H95" t="s">
+        <v>21</v>
+      </c>
+      <c r="I95" t="s">
+        <v>34</v>
+      </c>
+      <c r="L95" t="s">
+        <v>313</v>
+      </c>
+      <c r="M95" s="3" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>462</v>
+      </c>
+      <c r="B96" t="s">
+        <v>465</v>
+      </c>
+      <c r="C96" t="s">
+        <v>17</v>
+      </c>
+      <c r="D96" t="s">
+        <v>18</v>
+      </c>
+      <c r="E96" t="s">
+        <v>19</v>
+      </c>
+      <c r="F96">
+        <v>1969</v>
+      </c>
+      <c r="G96" t="s">
+        <v>26</v>
+      </c>
+      <c r="H96" t="s">
+        <v>21</v>
+      </c>
+      <c r="I96" t="s">
+        <v>34</v>
+      </c>
+      <c r="K96" t="s">
+        <v>196</v>
+      </c>
+      <c r="L96" t="s">
+        <v>313</v>
+      </c>
+      <c r="M96" s="3" t="s">
+        <v>466</v>
       </c>
     </row>
   </sheetData>
@@ -5164,10 +5257,12 @@
     <hyperlink ref="M70" r:id="rId91" xr:uid="{410C497E-B7A6-4A52-BDB5-CD7FDB43C527}"/>
     <hyperlink ref="M93" r:id="rId92" xr:uid="{A1560D73-B423-4F16-8BB5-470F2068279E}"/>
     <hyperlink ref="M94" r:id="rId93" xr:uid="{5C1389EE-7B8E-4CE1-AD67-A06B346AE661}"/>
+    <hyperlink ref="M95" r:id="rId94" xr:uid="{E6D09A0C-0E6C-4767-9502-C45CAD42E349}"/>
+    <hyperlink ref="M96" r:id="rId95" xr:uid="{3C030BC5-8750-46CD-A50B-E8D120B6AA4F}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart r:id="rId94"/>
+    <tablePart r:id="rId96"/>
   </tableParts>
 </worksheet>
 </file>

--- a/data/dati.xlsx
+++ b/data/dati.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan_\Desktop\AMI\GitHub\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BABC0C2-4D01-402A-A898-792DA291A622}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2282EF6-78F7-42D3-B924-6812D2FCE83D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Catalogo" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1047" uniqueCount="467">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1055" uniqueCount="471">
   <si>
     <t>ID</t>
   </si>
@@ -1423,6 +1423,18 @@
   </si>
   <si>
     <t>https://archive.org/details/1969-presentazione-il-comunista/mode/2up</t>
+  </si>
+  <si>
+    <t>AMI-0096</t>
+  </si>
+  <si>
+    <t>Pubblicità "Amaro Ramazzotti" raffigurante Mao Zedong</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/ramazzotti-1973</t>
+  </si>
+  <si>
+    <t>1973-Ramazzotti.png</t>
   </si>
 </sst>
 </file>
@@ -1848,7 +1860,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P96"/>
+  <dimension ref="A1:P97"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5546875" customWidth="1"/>
@@ -5159,6 +5171,35 @@
       </c>
       <c r="M96" s="3" t="s">
         <v>466</v>
+      </c>
+    </row>
+    <row r="97" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>467</v>
+      </c>
+      <c r="B97" t="s">
+        <v>468</v>
+      </c>
+      <c r="F97">
+        <v>1973</v>
+      </c>
+      <c r="G97" t="s">
+        <v>75</v>
+      </c>
+      <c r="I97" t="s">
+        <v>106</v>
+      </c>
+      <c r="J97" t="s">
+        <v>18</v>
+      </c>
+      <c r="L97" t="s">
+        <v>314</v>
+      </c>
+      <c r="M97" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="N97" t="s">
+        <v>470</v>
       </c>
     </row>
   </sheetData>
@@ -5259,10 +5300,11 @@
     <hyperlink ref="M94" r:id="rId93" xr:uid="{5C1389EE-7B8E-4CE1-AD67-A06B346AE661}"/>
     <hyperlink ref="M95" r:id="rId94" xr:uid="{E6D09A0C-0E6C-4767-9502-C45CAD42E349}"/>
     <hyperlink ref="M96" r:id="rId95" xr:uid="{3C030BC5-8750-46CD-A50B-E8D120B6AA4F}"/>
+    <hyperlink ref="M97" r:id="rId96" xr:uid="{CCEB970E-D5AA-46D9-977A-7634751F3020}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart r:id="rId96"/>
+    <tablePart r:id="rId97"/>
   </tableParts>
 </worksheet>
 </file>

--- a/data/dati.xlsx
+++ b/data/dati.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan_\Desktop\AMI\GitHub\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2282EF6-78F7-42D3-B924-6812D2FCE83D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3980230-5DB0-4446-9BE6-F7F54FEF0282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2550,7 +2550,7 @@
         <v>81</v>
       </c>
       <c r="F19" s="2">
-        <v>23511</v>
+        <v>23514</v>
       </c>
       <c r="G19" t="s">
         <v>75</v>

--- a/data/dati.xlsx
+++ b/data/dati.xlsx
@@ -8,21 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan_\Desktop\AMI\GitHub\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3980230-5DB0-4446-9BE6-F7F54FEF0282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AED86B4-DFDC-4228-B308-A0CDEED38F03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Catalogo" sheetId="1" r:id="rId1"/>
     <sheet name="Persone" sheetId="2" r:id="rId2"/>
     <sheet name="Organizzazioni" sheetId="3" r:id="rId3"/>
+    <sheet name="Relazioni" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1055" uniqueCount="471">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1533" uniqueCount="597">
   <si>
     <t>ID</t>
   </si>
@@ -57,6 +58,9 @@
     <t>Organizzazioni_collegate</t>
   </si>
   <si>
+    <t>Provenienza</t>
+  </si>
+  <si>
     <t>URL</t>
   </si>
   <si>
@@ -93,6 +97,9 @@
     <t>Materiali cinesi; Fondamenti del maoismo; Libretti rossi</t>
   </si>
   <si>
+    <t>Collezione personale</t>
+  </si>
+  <si>
     <t>https://archive.org/details/1967-citazioni-dalle-opere-del-presidente-mao-tse-tung-lingue-estere/mode/2up</t>
   </si>
   <si>
@@ -129,6 +136,9 @@
     <t>Materiali cinesi</t>
   </si>
   <si>
+    <t>Fondo Filippo Grossi</t>
+  </si>
+  <si>
     <t>https://archive.org/details/dichiarazione-in-supporto-degli-afroamericani/mode/2up</t>
   </si>
   <si>
@@ -363,15 +373,24 @@
     <t>Bologna</t>
   </si>
   <si>
+    <t>https://archive.org/details/ribellarsi-e-giusto/mode/2up</t>
+  </si>
+  <si>
     <t>AMI-0021</t>
   </si>
   <si>
+    <t>Lavoro Politico, no. 1</t>
+  </si>
+  <si>
     <t>Lavoro Politico</t>
   </si>
   <si>
     <t>Centro di Informazione di Verona</t>
   </si>
   <si>
+    <t>10/1967</t>
+  </si>
+  <si>
     <t>Periodico</t>
   </si>
   <si>
@@ -381,48 +400,105 @@
     <t>Riviste marxiste-leniniste</t>
   </si>
   <si>
+    <t>Archivio Storico della Nuova Sinistra "Marco Pezzi"</t>
+  </si>
+  <si>
     <t>https://archive.org/details/lavoro-politico-01/mode/2up</t>
   </si>
   <si>
     <t>AMI-0022</t>
   </si>
   <si>
+    <t>Lavoro Politico, no. 2</t>
+  </si>
+  <si>
+    <t>11/1967</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/lavoro-politico-02/mode/2up</t>
+  </si>
+  <si>
     <t>AMI-0023</t>
   </si>
   <si>
+    <t>Lavoro Politico, no. 3</t>
+  </si>
+  <si>
+    <t>01/1968</t>
+  </si>
+  <si>
     <t>https://archive.org/details/lavoro-politico-03/mode/2up</t>
   </si>
   <si>
     <t>AMI-0024</t>
   </si>
   <si>
+    <t>Lavoro Politico, no. 4</t>
+  </si>
+  <si>
+    <t>02/1968</t>
+  </si>
+  <si>
     <t>https://archive.org/details/lavoro-politico-04/mode/2up</t>
   </si>
   <si>
     <t>AMI-0025</t>
   </si>
   <si>
+    <t>Lavoro Politico, no. 5/6</t>
+  </si>
+  <si>
+    <t>03/1968</t>
+  </si>
+  <si>
     <t>https://archive.org/details/lavoro-politico-05-06/mode/2up</t>
   </si>
   <si>
     <t>AMI-0026</t>
   </si>
   <si>
+    <t>Lavoro Politico, no. 7</t>
+  </si>
+  <si>
+    <t>05/1968</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/lavoro-politico-07/mode/2up</t>
+  </si>
+  <si>
     <t>AMI-0027</t>
   </si>
   <si>
+    <t>Lavoro Politico, no. 8/9</t>
+  </si>
+  <si>
+    <t>06/1968</t>
+  </si>
+  <si>
     <t>https://archive.org/details/lavoro-politico-08-09/mode/2up</t>
   </si>
   <si>
     <t>AMI-0028</t>
   </si>
   <si>
+    <t>Lavoro Politico, no. 10</t>
+  </si>
+  <si>
+    <t>09/1968</t>
+  </si>
+  <si>
     <t>https://archive.org/details/lavoro-politico-10/mode/2up</t>
   </si>
   <si>
     <t>AMI-0029</t>
   </si>
   <si>
+    <t>Lavoro Politico, no. 11/12</t>
+  </si>
+  <si>
+    <t>12/1968</t>
+  </si>
+  <si>
     <t>Partito Comunista d'Italia (marxista-leninista); Partito Comunista d'Italia (marxista-leninista) - linea rossa</t>
   </si>
   <si>
@@ -516,6 +592,9 @@
     <t>Viva il popolo cinese</t>
   </si>
   <si>
+    <t>08/1969</t>
+  </si>
+  <si>
     <t>Milano</t>
   </si>
   <si>
@@ -741,6 +820,9 @@
     <t>Linea Proletaria</t>
   </si>
   <si>
+    <t>03/1978</t>
+  </si>
+  <si>
     <t>Manifesto</t>
   </si>
   <si>
@@ -777,12 +859,432 @@
     <t>AMI-0057</t>
   </si>
   <si>
+    <t>Congresso di fondazione del Partito Comunista Unificato d'Italia</t>
+  </si>
+  <si>
+    <t>Organizzazione dei Comunisti (marxisti-leninisti) d'Italia; Organizzazione Comunista (marxista-leninista) - Fronte Unito; Partito Comunista (marxista-leninista) d'Italia - Lotta di lunga durata; Partito Marxista-Leninista-Maoista Italiano</t>
+  </si>
+  <si>
     <t>https://archive.org/details/fondazione-pcudi-1977</t>
   </si>
   <si>
     <t>05.08.1977-fondazione-pcudi.png</t>
   </si>
   <si>
+    <t>AMI-0058</t>
+  </si>
+  <si>
+    <t>Proletari senza rivoluzione: Storia delle classi subalterne italiane dal 1860 al 1950, Vol. 1</t>
+  </si>
+  <si>
+    <t>Renzo del Carria</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/proletari-senza-rivoluzione-1/mode/2up</t>
+  </si>
+  <si>
+    <t>AMI-0059</t>
+  </si>
+  <si>
+    <t>Proletari senza rivoluzione: Storia delle classi subalterne italiane dal 1860 al 1950, Vol. 2</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/proletari-senza-rivoluzione-2/mode/2up</t>
+  </si>
+  <si>
+    <t>AMI-0060</t>
+  </si>
+  <si>
+    <t>Come diventare un buon comunista</t>
+  </si>
+  <si>
+    <t>Liu Shaoqi</t>
+  </si>
+  <si>
+    <t>Arnaldo Bressan</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/come-diventare-un-buon-comunista/mode/2up</t>
+  </si>
+  <si>
+    <t>AMI-0061</t>
+  </si>
+  <si>
+    <t>Sulla guerra di lunga durata</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/guerra-di-lunga-durata/mode/2up</t>
+  </si>
+  <si>
+    <t>AMI-0062</t>
+  </si>
+  <si>
+    <t>Delegazione del movimento studentesco dell'Università di Trieste sulla nave cinese Jinsha</t>
+  </si>
+  <si>
+    <t>Trieste</t>
+  </si>
+  <si>
+    <t>Partito Comunista d'Italia (marxista-leninista); Movimento Studentesco</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/1968-delegazione-nave-jinsha</t>
+  </si>
+  <si>
+    <t>1968-Delegazione-Nave-Jinsha.png</t>
+  </si>
+  <si>
+    <t>AMI-0063</t>
+  </si>
+  <si>
+    <t>Volantino del PC(m-l)I contro il carovita sotto il governo Rumor</t>
+  </si>
+  <si>
+    <t>01/1974</t>
+  </si>
+  <si>
+    <t>Brindisi</t>
+  </si>
+  <si>
+    <t>Archivio Storico Benedetto Petrone</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/pcmli-volantino-contro-rumor/mode/2up</t>
+  </si>
+  <si>
+    <t>AMI-0064</t>
+  </si>
+  <si>
+    <t>Volantino dell'OC(m-l) - Fronte Unito contro l'aumento del costo della benzina</t>
+  </si>
+  <si>
+    <t>Organizzazione Comunista (marxista-leninista) Fronte Unito</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/ocml-volantino-anti-rumor/mode/2up</t>
+  </si>
+  <si>
+    <t>AMI-0065</t>
+  </si>
+  <si>
+    <t>Manifestazione del Partito Comunista d'Italia (marxista-leninista)</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/1968.manifestazione.PCDI</t>
+  </si>
+  <si>
+    <t>1968.Mantifestazione.PCDI.jpg</t>
+  </si>
+  <si>
+    <t>AMI-0066</t>
+  </si>
+  <si>
+    <t>Manifestazione del Movimento Studentesco</t>
+  </si>
+  <si>
+    <t>Movimento Studentesco</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/1970-movimento-studentesco-pensierodi-mao</t>
+  </si>
+  <si>
+    <t>1970.Movimento.Studentesco.PensierodiMao.jpg</t>
+  </si>
+  <si>
+    <t>AMI-0067</t>
+  </si>
+  <si>
+    <t>Volantino del PCd'I(m-l) contro l'eccidio di Avola</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/1968-volantino-pcdi-avola/mode/2up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                                           </t>
+  </si>
+  <si>
+    <t>AMI-0068</t>
+  </si>
+  <si>
+    <t>Lotta di Classe, no. 1</t>
+  </si>
+  <si>
+    <t>Circoli Lenin dell'Emilia Romagna</t>
+  </si>
+  <si>
+    <t>05/1970</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/lotta-di-classe-1970-01/mode/2up</t>
+  </si>
+  <si>
+    <t>AMI-0069</t>
+  </si>
+  <si>
+    <t>Lotta di Classe, no. 2</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/lotta-di-classe-1970-02/mode/2up</t>
+  </si>
+  <si>
+    <t>AMI-0070</t>
+  </si>
+  <si>
+    <t>Lotta di Classe, supplemento al no. 2</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/lotta-di-classe-1970-02-suppl/mode/2up</t>
+  </si>
+  <si>
+    <t>AMI-0071</t>
+  </si>
+  <si>
+    <t>Lotta di Classe, no. 3</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/lotta-di-classe-1970-03/mode/2up</t>
+  </si>
+  <si>
+    <t>AMI-0072</t>
+  </si>
+  <si>
+    <t>Lotta di Classe, no. 4</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/lotta-di-classe-1970-04/mode/2up</t>
+  </si>
+  <si>
+    <t>AMI-0073</t>
+  </si>
+  <si>
+    <t>Lotta di Classe, no. 5/6</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/lotta-di-classe-1970-05-06/mode/2up</t>
+  </si>
+  <si>
+    <t>AMI-0074</t>
+  </si>
+  <si>
+    <t>Lotta di Classe, no. 7/8</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/lotta-di-classe-1970-07-08/mode/2up</t>
+  </si>
+  <si>
+    <t>AMI-0075</t>
+  </si>
+  <si>
+    <t>Lotta di Classe, no. 9/10</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/lotta-di-classe-1970-09-10/mode/2up</t>
+  </si>
+  <si>
+    <t>AMI-0076</t>
+  </si>
+  <si>
+    <t>Lotta di Classe, no. 11</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/lotta-di-classe-1970-11/mode/2up</t>
+  </si>
+  <si>
+    <t>AMI-0077</t>
+  </si>
+  <si>
+    <t>Lotta di Classe, no. 12</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/lotta-di-classe-1970-12/mode/2up</t>
+  </si>
+  <si>
+    <t>AMI-0078</t>
+  </si>
+  <si>
+    <t>Lotta di Classe, no. 13</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/lotta-di-classe-1971-13/mode/2up</t>
+  </si>
+  <si>
+    <t>AMI-0079</t>
+  </si>
+  <si>
+    <t>Lotta di Classe, no. 14</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/lotta-di-classe-1971-14/mode/2up</t>
+  </si>
+  <si>
+    <t>AMI-0080</t>
+  </si>
+  <si>
+    <t>Lotta di Classe, no. 15/16</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/lotta-di-classe-1971-15-16/mode/2up</t>
+  </si>
+  <si>
+    <t>AMI-0081</t>
+  </si>
+  <si>
+    <t>Lotta di Classe, no. 17/18</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/lotta-di-classe-1971-17-18/mode/2up</t>
+  </si>
+  <si>
+    <t>AMI-0082</t>
+  </si>
+  <si>
+    <t>Lotta di Classe, no. 19/20</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/lotta-di-classe-1971-19-20/mode/2up</t>
+  </si>
+  <si>
+    <t>AMI-0083</t>
+  </si>
+  <si>
+    <t>Lotta di Classe, no. 21</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/lotta-di-classe-1971-21/mode/2up</t>
+  </si>
+  <si>
+    <t>AMI-0084</t>
+  </si>
+  <si>
+    <t>Lotta di Classe, no. 22</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/lotta-di-classe-1971-22/mode/2up</t>
+  </si>
+  <si>
+    <t>AMI-0085</t>
+  </si>
+  <si>
+    <t>Lotta di Classe, no. 23</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/lotta-di-classe-1971-23/mode/2up</t>
+  </si>
+  <si>
+    <t>AMI-0086</t>
+  </si>
+  <si>
+    <t>Lotta di Classe, no. 24/25</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/lotta-di-classe-1971-24-25/mode/2up</t>
+  </si>
+  <si>
+    <t>AMI-0087</t>
+  </si>
+  <si>
+    <t>Lotta di Classe, anno III, no. 1</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/lotta-di-classe-1972-01/mode/2up</t>
+  </si>
+  <si>
+    <t>AMI-0088</t>
+  </si>
+  <si>
+    <t>Lotta di Classe, anno III, no. 2/3</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/lotta-di-classe-1972-02-03/mode/2up</t>
+  </si>
+  <si>
+    <t>AMI-0089</t>
+  </si>
+  <si>
+    <t>Lotta di Classe, anno III, no. 4/5</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/lotta-di-classe-1972-04-05/mode/2up</t>
+  </si>
+  <si>
+    <t>AMI-0090</t>
+  </si>
+  <si>
+    <t>Lotta di Classe, anno III, no. 6</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/lotta-di-classe-1972-06/mode/2up</t>
+  </si>
+  <si>
+    <t>AMI-0091</t>
+  </si>
+  <si>
+    <t>Lotta di Classe, anno IV, no. 1/2</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/lotta-di-classe-1973-01-02/mode/2up</t>
+  </si>
+  <si>
+    <t>AMI-0092</t>
+  </si>
+  <si>
+    <t>Avanziamo lungo la via aperta dalla Rivoluzione socialista d'ottobre</t>
+  </si>
+  <si>
+    <t>Edizioni Servire il Popolo</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/avanziamo-lungo-la-via/mode/2up</t>
+  </si>
+  <si>
+    <t>AMI-0093</t>
+  </si>
+  <si>
+    <t>Ai comunisti ai lavoratori</t>
+  </si>
+  <si>
+    <t>Centro Karl Marx</t>
+  </si>
+  <si>
+    <t>06/1971</t>
+  </si>
+  <si>
+    <t>Firenze</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/ai-comunisti-ai-lavoratori/mode/2up</t>
+  </si>
+  <si>
+    <t>AMI-0094</t>
+  </si>
+  <si>
+    <t>Contro il liberalismo</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/1968-contro-il-liberalismo/mode/2up</t>
+  </si>
+  <si>
+    <t>AMI-0095</t>
+  </si>
+  <si>
+    <t>Presentazione della rivista Il Comunista</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/1969-presentazione-il-comunista/mode/2up</t>
+  </si>
+  <si>
+    <t>AMI-0096</t>
+  </si>
+  <si>
+    <t>Pubblicità "Amaro Ramazzotti" raffigurante Mao Zedong</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/ramazzotti-1973</t>
+  </si>
+  <si>
+    <t>1973-Ramazzotti.png</t>
+  </si>
+  <si>
     <t>Nome</t>
   </si>
   <si>
@@ -798,12 +1300,75 @@
     <t>Immagine</t>
   </si>
   <si>
+    <t>ID_autorita</t>
+  </si>
+  <si>
+    <t>Tipo_entita</t>
+  </si>
+  <si>
+    <t>Forme_varianti</t>
+  </si>
+  <si>
+    <t>Biografia</t>
+  </si>
+  <si>
+    <t>Luoghi</t>
+  </si>
+  <si>
+    <t>Wikidata</t>
+  </si>
+  <si>
+    <t>VIAF</t>
+  </si>
+  <si>
+    <t>Stato_record</t>
+  </si>
+  <si>
+    <t>Livello_dettaglio</t>
+  </si>
+  <si>
+    <t>Data_redazione</t>
+  </si>
+  <si>
+    <t>Norme</t>
+  </si>
+  <si>
+    <t>Lingua_record</t>
+  </si>
+  <si>
+    <t>Note_redazionali</t>
+  </si>
+  <si>
     <t>Mao</t>
   </si>
   <si>
     <t>mao.webp</t>
   </si>
   <si>
+    <t>AMI-P-001</t>
+  </si>
+  <si>
+    <t>Persona</t>
+  </si>
+  <si>
+    <t>Bozza</t>
+  </si>
+  <si>
+    <t>Minimo</t>
+  </si>
+  <si>
+    <t>2026-10-02 creazione struttura ISAAR</t>
+  </si>
+  <si>
+    <t>ISAAR(CPF), 2a ed., 2004</t>
+  </si>
+  <si>
+    <t>ita</t>
+  </si>
+  <si>
+    <t>Biografia da redigere</t>
+  </si>
+  <si>
     <t>Fosco Dinucci</t>
   </si>
   <si>
@@ -813,69 +1378,135 @@
     <t>dinucci.webp</t>
   </si>
   <si>
+    <t>AMI-P-002</t>
+  </si>
+  <si>
     <t>Pesce</t>
   </si>
   <si>
     <t>pesce.webp</t>
   </si>
   <si>
+    <t>AMI-P-003</t>
+  </si>
+  <si>
     <t>Yao</t>
   </si>
   <si>
+    <t>AMI-P-004</t>
+  </si>
+  <si>
     <t>Roberto Sassi</t>
   </si>
   <si>
     <t>Sassi</t>
   </si>
   <si>
+    <t>AMI-P-005</t>
+  </si>
+  <si>
     <t>Calò</t>
   </si>
   <si>
+    <t>AMI-P-006</t>
+  </si>
+  <si>
+    <t>Date di esistenza mancanti o incomplete; Biografia da redigere</t>
+  </si>
+  <si>
     <t>Dino Dini</t>
   </si>
   <si>
     <t>Dini</t>
   </si>
   <si>
+    <t>AMI-P-007</t>
+  </si>
+  <si>
     <t>Lin Biao</t>
   </si>
   <si>
     <t>Lin</t>
   </si>
   <si>
+    <t>AMI-P-008</t>
+  </si>
+  <si>
     <t>Kang Sheng</t>
   </si>
   <si>
     <t>Kang</t>
   </si>
   <si>
+    <t>AMI-P-009</t>
+  </si>
+  <si>
     <t>Zhou Enlai</t>
   </si>
   <si>
     <t>Zhou</t>
   </si>
   <si>
+    <t>AMI-P-010</t>
+  </si>
+  <si>
     <t>Chen Boda</t>
   </si>
   <si>
     <t>Chen</t>
   </si>
   <si>
+    <t>AMI-P-011</t>
+  </si>
+  <si>
     <t>Jiang Qing</t>
   </si>
   <si>
     <t>Jiang</t>
   </si>
   <si>
+    <t>AMI-P-012</t>
+  </si>
+  <si>
     <t>Angiolo Gracci</t>
   </si>
   <si>
     <t>Gracci</t>
   </si>
   <si>
+    <t>AMI-P-013</t>
+  </si>
+  <si>
     <t>Zucchetti</t>
   </si>
   <si>
+    <t>AMI-P-014</t>
+  </si>
+  <si>
+    <t>Liu</t>
+  </si>
+  <si>
+    <t>AMI-P-015</t>
+  </si>
+  <si>
+    <t>del Carria</t>
+  </si>
+  <si>
+    <t>AMI-P-016</t>
+  </si>
+  <si>
+    <t>Date di esistenza mancanti o incomplete; Biografia da redigere; Record creato il 2026-10-02 perché il nome compare nel Catalogo senza record d'autorità; Verificare la grafia (del Carria / Del Carria)</t>
+  </si>
+  <si>
+    <t>Bressan</t>
+  </si>
+  <si>
+    <t>AMI-P-017</t>
+  </si>
+  <si>
+    <t>Date di esistenza mancanti o incomplete; Biografia da redigere; Record creato il 2026-10-02 perché il nome compare nel Catalogo senza record d'autorità</t>
+  </si>
+  <si>
     <t>Categoria</t>
   </si>
   <si>
@@ -885,563 +1516,311 @@
     <t>Scioglimento</t>
   </si>
   <si>
+    <t>Storia</t>
+  </si>
+  <si>
     <t>Associazione di massa</t>
   </si>
   <si>
     <t>201?</t>
   </si>
   <si>
+    <t>AMI-O-001</t>
+  </si>
+  <si>
+    <t>Ente</t>
+  </si>
+  <si>
+    <t>Data di scioglimento incerta ("201?"); Storia da redigere</t>
+  </si>
+  <si>
     <t>Casa editrice</t>
   </si>
   <si>
+    <t>AMI-O-002</t>
+  </si>
+  <si>
+    <t>Storia da redigere</t>
+  </si>
+  <si>
+    <t>AMI-O-003</t>
+  </si>
+  <si>
     <t>Giornale</t>
   </si>
   <si>
+    <t>AMI-O-004</t>
+  </si>
+  <si>
+    <t>Quotidiano del Popolo</t>
+  </si>
+  <si>
     <t>Hongqi</t>
   </si>
   <si>
+    <t>AMI-O-005</t>
+  </si>
+  <si>
+    <t>Bandiera Rossa</t>
+  </si>
+  <si>
+    <t>AMI-O-006</t>
+  </si>
+  <si>
     <t>Jiefangjun Bao</t>
   </si>
   <si>
+    <t>AMI-O-007</t>
+  </si>
+  <si>
+    <t>Quotidiano dell'EPL</t>
+  </si>
+  <si>
     <t>Gruppo</t>
   </si>
   <si>
+    <t>AMI-O-008</t>
+  </si>
+  <si>
+    <t>Data di fondazione mancante; Storia da redigere</t>
+  </si>
+  <si>
     <t>Organo di partito</t>
   </si>
   <si>
+    <t>AMI-O-009</t>
+  </si>
+  <si>
+    <t>AMI-O-010</t>
+  </si>
+  <si>
     <t>Unione della gioventù comunista d’Italia (marxista-leninista)</t>
   </si>
   <si>
+    <t>AMI-O-011</t>
+  </si>
+  <si>
+    <t>AMI-O-012</t>
+  </si>
+  <si>
     <t>Partito</t>
   </si>
   <si>
     <t>logo-pcdi.svg</t>
   </si>
   <si>
+    <t>AMI-O-013</t>
+  </si>
+  <si>
+    <t>PCd'I (m-l); PCd'I(m-l)</t>
+  </si>
+  <si>
     <t>logo-UCI.svg</t>
   </si>
   <si>
+    <t>AMI-O-014</t>
+  </si>
+  <si>
+    <t>UCI (m.l)</t>
+  </si>
+  <si>
     <t>logo-pcc.svg</t>
   </si>
   <si>
+    <t>AMI-O-015</t>
+  </si>
+  <si>
+    <t>PCC</t>
+  </si>
+  <si>
     <t>Partito Comunista d'Italia (marxista-leninista) - linea rossa</t>
   </si>
   <si>
+    <t>AMI-O-016</t>
+  </si>
+  <si>
+    <t>AMI-O-017</t>
+  </si>
+  <si>
     <t>????</t>
   </si>
   <si>
+    <t>AMI-O-018</t>
+  </si>
+  <si>
+    <t>Data di scioglimento incerta ("????"); Storia da redigere</t>
+  </si>
+  <si>
+    <t>AMI-O-019</t>
+  </si>
+  <si>
+    <t>PC(m-l)I</t>
+  </si>
+  <si>
     <t>Rivista</t>
   </si>
   <si>
-    <t>Congresso di fondazione del Partito Comunista Unificato d'Italia</t>
-  </si>
-  <si>
-    <t>AMI-0058</t>
-  </si>
-  <si>
-    <t>AMI-0059</t>
-  </si>
-  <si>
-    <t>Proletari senza rivoluzione: Storia delle classi subalterne italiane dal 1860 al 1950, Vol. 2</t>
-  </si>
-  <si>
-    <t>Proletari senza rivoluzione: Storia delle classi subalterne italiane dal 1860 al 1950, Vol. 1</t>
-  </si>
-  <si>
-    <t>Renzo del Carria</t>
-  </si>
-  <si>
-    <t>https://archive.org/details/proletari-senza-rivoluzione-2/mode/2up</t>
-  </si>
-  <si>
-    <t>https://archive.org/details/proletari-senza-rivoluzione-1/mode/2up</t>
-  </si>
-  <si>
-    <t>Provenienza</t>
-  </si>
-  <si>
-    <t>Archivio Storico della Nuova Sinistra "Marco Pezzi"</t>
-  </si>
-  <si>
-    <t>Fondo Filippo Grossi</t>
-  </si>
-  <si>
-    <t>Collezione personale</t>
-  </si>
-  <si>
-    <t>AMI-0060</t>
-  </si>
-  <si>
-    <t>Come diventare un buon comunista</t>
-  </si>
-  <si>
-    <t>Liu Shaoqi</t>
-  </si>
-  <si>
-    <t>Arnaldo Bressan</t>
-  </si>
-  <si>
-    <t>https://archive.org/details/come-diventare-un-buon-comunista/mode/2up</t>
-  </si>
-  <si>
-    <t>https://archive.org/details/lavoro-politico-02/mode/2up</t>
-  </si>
-  <si>
-    <t>https://archive.org/details/lavoro-politico-07/mode/2up</t>
-  </si>
-  <si>
-    <t>https://archive.org/details/ribellarsi-e-giusto/mode/2up</t>
-  </si>
-  <si>
-    <t>Liu</t>
-  </si>
-  <si>
-    <t>AMI-0061</t>
-  </si>
-  <si>
-    <t>Sulla guerra di lunga durata</t>
-  </si>
-  <si>
-    <t>https://archive.org/details/guerra-di-lunga-durata/mode/2up</t>
-  </si>
-  <si>
-    <t>AMI-0062</t>
-  </si>
-  <si>
-    <t>Delegazione del movimento studentesco dell'Università di Trieste sulla nave cinese Jinsha</t>
-  </si>
-  <si>
-    <t>Trieste</t>
-  </si>
-  <si>
-    <t>Partito Comunista d'Italia (marxista-leninista); Movimento Studentesco</t>
-  </si>
-  <si>
-    <t>https://archive.org/details/1968-delegazione-nave-jinsha</t>
-  </si>
-  <si>
-    <t>1968-Delegazione-Nave-Jinsha.png</t>
-  </si>
-  <si>
-    <t>AMI-0063</t>
-  </si>
-  <si>
-    <t>AMI-0064</t>
-  </si>
-  <si>
-    <t>Brindisi</t>
-  </si>
-  <si>
-    <t>Archivio Storico Benedetto Petrone</t>
-  </si>
-  <si>
-    <t>Organizzazione Comunista (marxista-leninista) Fronte Unito</t>
-  </si>
-  <si>
-    <t>Volantino del PC(m-l)I contro il carovita sotto il governo Rumor</t>
-  </si>
-  <si>
-    <t>Volantino dell'OC(m-l) - Fronte Unito contro l'aumento del costo della benzina</t>
-  </si>
-  <si>
-    <t>AMI-0065</t>
-  </si>
-  <si>
-    <t>Manifestazione del Partito Comunista d'Italia (marxista-leninista)</t>
-  </si>
-  <si>
-    <t>https://archive.org/details/1968.manifestazione.PCDI</t>
-  </si>
-  <si>
-    <t>AMI-0066</t>
-  </si>
-  <si>
-    <t>Manifestazione del Movimento Studentesco</t>
-  </si>
-  <si>
-    <t>Movimento Studentesco</t>
-  </si>
-  <si>
-    <t>https://archive.org/details/1970-movimento-studentesco-pensierodi-mao</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                                           </t>
-  </si>
-  <si>
-    <t>1970.Movimento.Studentesco.PensierodiMao.jpg</t>
-  </si>
-  <si>
-    <t>1968.Mantifestazione.PCDI.jpg</t>
-  </si>
-  <si>
-    <t>AMI-0067</t>
-  </si>
-  <si>
-    <t>Volantino del PCd'I(m-l) contro l'eccidio di Avola</t>
-  </si>
-  <si>
-    <t>12/1968</t>
-  </si>
-  <si>
-    <t>01/1974</t>
-  </si>
-  <si>
-    <t>03/1978</t>
-  </si>
-  <si>
-    <t>08/1969</t>
-  </si>
-  <si>
-    <t>09/1968</t>
-  </si>
-  <si>
-    <t>06/1968</t>
-  </si>
-  <si>
-    <t>05/1968</t>
-  </si>
-  <si>
-    <t>03/1968</t>
-  </si>
-  <si>
-    <t>02/1968</t>
-  </si>
-  <si>
-    <t>01/1968</t>
-  </si>
-  <si>
-    <t>11/1967</t>
-  </si>
-  <si>
-    <t>10/1967</t>
-  </si>
-  <si>
-    <t>AMI-0068</t>
-  </si>
-  <si>
-    <t>AMI-0069</t>
-  </si>
-  <si>
-    <t>AMI-0070</t>
-  </si>
-  <si>
-    <t>AMI-0071</t>
-  </si>
-  <si>
-    <t>AMI-0072</t>
-  </si>
-  <si>
-    <t>AMI-0073</t>
-  </si>
-  <si>
-    <t>AMI-0074</t>
-  </si>
-  <si>
-    <t>AMI-0075</t>
-  </si>
-  <si>
-    <t>AMI-0076</t>
-  </si>
-  <si>
-    <t>AMI-0077</t>
-  </si>
-  <si>
-    <t>AMI-0078</t>
-  </si>
-  <si>
-    <t>AMI-0079</t>
-  </si>
-  <si>
-    <t>AMI-0080</t>
-  </si>
-  <si>
-    <t>AMI-0081</t>
-  </si>
-  <si>
-    <t>AMI-0082</t>
-  </si>
-  <si>
-    <t>AMI-0083</t>
-  </si>
-  <si>
-    <t>AMI-0084</t>
-  </si>
-  <si>
-    <t>AMI-0085</t>
-  </si>
-  <si>
-    <t>AMI-0086</t>
-  </si>
-  <si>
-    <t>AMI-0087</t>
-  </si>
-  <si>
-    <t>AMI-0088</t>
-  </si>
-  <si>
-    <t>AMI-0089</t>
-  </si>
-  <si>
-    <t>AMI-0090</t>
-  </si>
-  <si>
-    <t>Lotta di Classe, anno III, no. 1</t>
-  </si>
-  <si>
-    <t>Lotta di Classe, anno III, no. 2/3</t>
-  </si>
-  <si>
-    <t>Lotta di Classe, anno III, no. 4/5</t>
-  </si>
-  <si>
-    <t>Lotta di Classe, anno III, no. 6</t>
-  </si>
-  <si>
-    <t>Circoli Lenin dell'Emilia Romagna</t>
-  </si>
-  <si>
-    <t>Lavoro Politico, no. 1</t>
-  </si>
-  <si>
-    <t>Lavoro Politico, no. 2</t>
-  </si>
-  <si>
-    <t>Lavoro Politico, no. 3</t>
-  </si>
-  <si>
-    <t>Lavoro Politico, no. 4</t>
-  </si>
-  <si>
-    <t>Lavoro Politico, no. 5/6</t>
-  </si>
-  <si>
-    <t>Lavoro Politico, no. 7</t>
-  </si>
-  <si>
-    <t>Lavoro Politico, no. 8/9</t>
-  </si>
-  <si>
-    <t>Lavoro Politico, no. 10</t>
-  </si>
-  <si>
-    <t>Lavoro Politico, no. 11/12</t>
-  </si>
-  <si>
-    <t>https://archive.org/details/lotta-di-classe-1970-01/mode/2up</t>
-  </si>
-  <si>
-    <t>https://archive.org/details/lotta-di-classe-1970-02-suppl/mode/2up</t>
-  </si>
-  <si>
-    <t>Lotta di Classe, supplemento al no. 2</t>
-  </si>
-  <si>
-    <t>Lotta di Classe, no. 1</t>
-  </si>
-  <si>
-    <t>Lotta di Classe, no. 3</t>
-  </si>
-  <si>
-    <t>Lotta di Classe, no. 4</t>
-  </si>
-  <si>
-    <t>Lotta di Classe, no. 5/6</t>
-  </si>
-  <si>
-    <t>Lotta di Classe, no. 7/8</t>
-  </si>
-  <si>
-    <t>Lotta di Classe, no. 9/10</t>
-  </si>
-  <si>
-    <t>Lotta di Classe, no. 11</t>
-  </si>
-  <si>
-    <t>Lotta di Classe, no. 12</t>
-  </si>
-  <si>
-    <t>Lotta di Classe, no. 13</t>
-  </si>
-  <si>
-    <t>Lotta di Classe, no. 14</t>
-  </si>
-  <si>
-    <t>Lotta di Classe, no. 15/16</t>
-  </si>
-  <si>
-    <t>Lotta di Classe, no. 17/18</t>
-  </si>
-  <si>
-    <t>Lotta di Classe, no. 19/20</t>
-  </si>
-  <si>
-    <t>Lotta di Classe, no. 21</t>
-  </si>
-  <si>
-    <t>Lotta di Classe, no. 22</t>
-  </si>
-  <si>
-    <t>Lotta di Classe, no. 23</t>
-  </si>
-  <si>
-    <t>Lotta di Classe, no. 24/25</t>
-  </si>
-  <si>
-    <t>05/1970</t>
-  </si>
-  <si>
-    <t>https://archive.org/details/lotta-di-classe-1972-04-05/mode/2up</t>
-  </si>
-  <si>
-    <t>https://archive.org/details/lotta-di-classe-1973-01-02/mode/2up</t>
-  </si>
-  <si>
-    <t>https://archive.org/details/lotta-di-classe-1970-03/mode/2up</t>
-  </si>
-  <si>
-    <t>https://archive.org/details/lotta-di-classe-1970-04/mode/2up</t>
-  </si>
-  <si>
-    <t>https://archive.org/details/lotta-di-classe-1970-05-06/mode/2up</t>
-  </si>
-  <si>
-    <t>https://archive.org/details/lotta-di-classe-1970-07-08/mode/2up</t>
-  </si>
-  <si>
-    <t>https://archive.org/details/lotta-di-classe-1970-09-10/mode/2up</t>
-  </si>
-  <si>
-    <t>https://archive.org/details/lotta-di-classe-1970-11/mode/2up</t>
-  </si>
-  <si>
-    <t>https://archive.org/details/lotta-di-classe-1970-12/mode/2up</t>
-  </si>
-  <si>
-    <t>https://archive.org/details/lotta-di-classe-1971-13/mode/2up</t>
-  </si>
-  <si>
-    <t>https://archive.org/details/lotta-di-classe-1971-14/mode/2up</t>
-  </si>
-  <si>
-    <t>https://archive.org/details/lotta-di-classe-1971-15-16/mode/2up</t>
-  </si>
-  <si>
-    <t>https://archive.org/details/lotta-di-classe-1971-17-18/mode/2up</t>
-  </si>
-  <si>
-    <t>https://archive.org/details/lotta-di-classe-1971-19-20/mode/2up</t>
-  </si>
-  <si>
-    <t>https://archive.org/details/lotta-di-classe-1971-21/mode/2up</t>
-  </si>
-  <si>
-    <t>https://archive.org/details/lotta-di-classe-1971-22/mode/2up</t>
-  </si>
-  <si>
-    <t>https://archive.org/details/lotta-di-classe-1971-23/mode/2up</t>
-  </si>
-  <si>
-    <t>https://archive.org/details/1968-volantino-pcdi-avola/mode/2up</t>
-  </si>
-  <si>
-    <t>https://archive.org/details/ocml-volantino-anti-rumor/mode/2up</t>
-  </si>
-  <si>
-    <t>https://archive.org/details/pcmli-volantino-contro-rumor/mode/2up</t>
-  </si>
-  <si>
-    <t>https://archive.org/details/lotta-di-classe-1971-24-25/mode/2up</t>
-  </si>
-  <si>
-    <t>https://archive.org/details/lotta-di-classe-1972-01/mode/2up</t>
-  </si>
-  <si>
-    <t>https://archive.org/details/lotta-di-classe-1972-02-03/mode/2up</t>
-  </si>
-  <si>
-    <t>https://archive.org/details/lotta-di-classe-1972-06/mode/2up</t>
-  </si>
-  <si>
-    <t>AMI-0091</t>
-  </si>
-  <si>
-    <t>Lotta di Classe, no. 2</t>
-  </si>
-  <si>
-    <t>https://archive.org/details/lotta-di-classe-1970-02/mode/2up</t>
-  </si>
-  <si>
-    <t>Lotta di Classe, anno IV, no. 1/2</t>
-  </si>
-  <si>
-    <t>Organizzazione dei Comunisti (marxisti-leninisti) d'Italia; Organizzazione Comunista (marxista-leninista) - Fronte Unito; Partito Comunista (marxista-leninista) d'Italia - Lotta di lunga durata; Partito Marxista-Leninista-Maoista Italiano</t>
-  </si>
-  <si>
-    <t>AMI-0092</t>
-  </si>
-  <si>
-    <t>Avanziamo lungo la via aperta dalla Rivoluzione socialista d'ottobre</t>
-  </si>
-  <si>
-    <t>Edizioni Servire il Popolo</t>
-  </si>
-  <si>
-    <t>https://archive.org/details/avanziamo-lungo-la-via/mode/2up</t>
-  </si>
-  <si>
-    <t>AMI-0093</t>
-  </si>
-  <si>
-    <t>https://archive.org/details/ai-comunisti-ai-lavoratori/mode/2up</t>
-  </si>
-  <si>
-    <t>Firenze</t>
-  </si>
-  <si>
-    <t>Centro Karl Marx</t>
-  </si>
-  <si>
-    <t>Ai comunisti ai lavoratori</t>
-  </si>
-  <si>
-    <t>06/1971</t>
-  </si>
-  <si>
-    <t>AMI-0094</t>
-  </si>
-  <si>
-    <t>AMI-0095</t>
-  </si>
-  <si>
-    <t>Contro il liberalismo</t>
-  </si>
-  <si>
-    <t>https://archive.org/details/1968-contro-il-liberalismo/mode/2up</t>
-  </si>
-  <si>
-    <t>Presentazione della rivista Il Comunista</t>
-  </si>
-  <si>
-    <t>https://archive.org/details/1969-presentazione-il-comunista/mode/2up</t>
-  </si>
-  <si>
-    <t>AMI-0096</t>
-  </si>
-  <si>
-    <t>Pubblicità "Amaro Ramazzotti" raffigurante Mao Zedong</t>
-  </si>
-  <si>
-    <t>https://archive.org/details/ramazzotti-1973</t>
-  </si>
-  <si>
-    <t>1973-Ramazzotti.png</t>
+    <t>AMI-O-020</t>
+  </si>
+  <si>
+    <t>AMI-O-021</t>
+  </si>
+  <si>
+    <t>AMI-O-022</t>
+  </si>
+  <si>
+    <t>AMI-O-023</t>
+  </si>
+  <si>
+    <t>Record creato il 2026-10-02 perché il nome compare nel Catalogo senza record d'autorità; categoria e date da compilare; Storia da redigere</t>
+  </si>
+  <si>
+    <t>AMI-O-024</t>
+  </si>
+  <si>
+    <t>Record creato il 2026-10-02 perché il nome compare nel Catalogo senza record d'autorità; categoria e date da compilare; Nel Catalogo il nome compare in due grafie (con e senza trattino): uniformare; Storia da redigere</t>
+  </si>
+  <si>
+    <t>AMI-O-025</t>
+  </si>
+  <si>
+    <t>Organizzazione dei Comunisti (marxisti-leninisti) d'Italia</t>
+  </si>
+  <si>
+    <t>AMI-O-026</t>
+  </si>
+  <si>
+    <t>Partito Comunista (marxista-leninista) d'Italia - Lotta di lunga durata</t>
+  </si>
+  <si>
+    <t>AMI-O-027</t>
+  </si>
+  <si>
+    <t>Partito Marxista-Leninista-Maoista Italiano</t>
+  </si>
+  <si>
+    <t>AMI-O-028</t>
+  </si>
+  <si>
+    <t>ID_relazione</t>
+  </si>
+  <si>
+    <t>ID_entita_A</t>
+  </si>
+  <si>
+    <t>Entita_A</t>
+  </si>
+  <si>
+    <t>Relazione</t>
+  </si>
+  <si>
+    <t>Categoria_ISAAR</t>
+  </si>
+  <si>
+    <t>ID_entita_B</t>
+  </si>
+  <si>
+    <t>Entita_B</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Fonte</t>
+  </si>
+  <si>
+    <t>Note</t>
+  </si>
+  <si>
+    <t>AMI-R-001</t>
+  </si>
+  <si>
+    <t>segretario di</t>
+  </si>
+  <si>
+    <t>gerarchica</t>
+  </si>
+  <si>
+    <t>attestato al 1969-10-03</t>
+  </si>
+  <si>
+    <t>Titolo di AMI-0016</t>
+  </si>
+  <si>
+    <t>AMI-R-002</t>
+  </si>
+  <si>
+    <t>membro di</t>
+  </si>
+  <si>
+    <t>associativa</t>
+  </si>
+  <si>
+    <t>attestato al 1968-08-31</t>
+  </si>
+  <si>
+    <t>Titolo di AMI-0015</t>
+  </si>
+  <si>
+    <t>Il titolo associa Pesce al partito senza indicarne la carica</t>
+  </si>
+  <si>
+    <t>AMI-R-003</t>
+  </si>
+  <si>
+    <t>presidente di</t>
+  </si>
+  <si>
+    <t>attestato al 1968</t>
+  </si>
+  <si>
+    <t>Titolo di AMI-0004</t>
+  </si>
+  <si>
+    <t>AMI-R-004</t>
+  </si>
+  <si>
+    <t>organo di</t>
+  </si>
+  <si>
+    <t>Denominazione dell'ente</t>
+  </si>
+  <si>
+    <t>AMI-R-005</t>
+  </si>
+  <si>
+    <t>articolazione locale di</t>
+  </si>
+  <si>
+    <t>AMI-R-006</t>
+  </si>
+  <si>
+    <t>AMI-R-007</t>
+  </si>
+  <si>
+    <t>da definire</t>
+  </si>
+  <si>
+    <t>Natura del rapporto (scissione, frazione, ecc.) da documentare con una fonte</t>
+  </si>
+  <si>
+    <t>Mao Tse-tung; Mao Tsetung</t>
+  </si>
+  <si>
+    <t>Lin Piao</t>
+  </si>
+  <si>
+    <t>Liu Shao-chi</t>
+  </si>
+  <si>
+    <t>Organizzazione Comunista (marxista-leninista); Organizzazione Comunista (marxista-leninista) - Fronte Unito; OC(m-l) - Fronte Unito</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1458,10 +1837,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="8"/>
+      <b/>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1492,9 +1878,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1504,6 +1890,8 @@
     <xf numFmtId="17" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Collegamento ipertestuale" xfId="1" builtinId="8"/>
@@ -1523,53 +1911,79 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C0C43707-2E5D-4FCB-B56E-4856FC4DF5B6}" name="Tabella1" displayName="Tabella1" ref="A1:P151" totalsRowShown="0">
-  <autoFilter ref="A1:P151" xr:uid="{C0C43707-2E5D-4FCB-B56E-4856FC4DF5B6}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabella1" displayName="Tabella1" ref="A1:P151" totalsRowShown="0">
+  <autoFilter ref="A1:P151" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{40EB6498-034B-4FD2-B823-BD9BDE560AB5}" name="ID"/>
-    <tableColumn id="2" xr3:uid="{E00E7517-D29A-46F7-B049-8E1F1ECC043C}" name="Titolo"/>
-    <tableColumn id="3" xr3:uid="{12EB6F9C-1D8F-4A95-872D-EB8DF3CC2DA3}" name="Organizzazione"/>
-    <tableColumn id="4" xr3:uid="{1453CAAA-C763-4A57-9337-9B188E02FD6E}" name="Autore"/>
-    <tableColumn id="5" xr3:uid="{EC137B4A-61EE-4F97-9321-CE86743D3FC4}" name="Editore"/>
-    <tableColumn id="6" xr3:uid="{CA408818-B405-48D0-A2A8-EA5E3A80BAB3}" name="Data"/>
-    <tableColumn id="7" xr3:uid="{971DF9E2-F9AA-437A-969B-F8C941329ED2}" name="Tipo"/>
-    <tableColumn id="8" xr3:uid="{EEBE2275-AF9C-4B13-AF88-5DFA3A895FDD}" name="Luogo"/>
-    <tableColumn id="9" xr3:uid="{95A8BDEE-2111-4C66-8F45-95353EF33A2F}" name="Serie"/>
-    <tableColumn id="10" xr3:uid="{90BC9D87-1BF0-48A2-868D-6C56548FCEB4}" name="Persone_collegate"/>
-    <tableColumn id="11" xr3:uid="{C8BD21B7-C8B1-4984-92F4-1D47F4D1DDE8}" name="Organizzazioni_collegate"/>
-    <tableColumn id="16" xr3:uid="{2EA96E38-185B-4190-9E45-A3915A9F5041}" name="Provenienza"/>
-    <tableColumn id="12" xr3:uid="{39126A50-DCAA-4469-B47D-EEF765E35B2A}" name="URL"/>
-    <tableColumn id="13" xr3:uid="{2CA56103-9CDF-40D7-9D80-7561D0C1F54A}" name="Nome_file"/>
-    <tableColumn id="14" xr3:uid="{031C733F-A723-4277-8E99-4BFF4677306D}" name="Nome_file_originale"/>
-    <tableColumn id="15" xr3:uid="{FE9C8AAB-B853-49B1-8952-449DEEFCD706}" name="Nome_file_traduzione"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Titolo"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Organizzazione"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Autore"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Editore"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Data"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Tipo"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Luogo"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Serie"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Persone_collegate"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Organizzazioni_collegate"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Provenienza"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="URL"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Nome_file"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Nome_file_originale"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Nome_file_traduzione"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9EF36B9C-830E-4E0F-A41F-6E8D74431EB6}" name="Tabella3" displayName="Tabella3" ref="A1:E25" totalsRowShown="0">
-  <autoFilter ref="A1:E25" xr:uid="{9EF36B9C-830E-4E0F-A41F-6E8D74431EB6}"/>
-  <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{A132190C-24DA-4CCB-B14B-610323E40AF2}" name="Nome"/>
-    <tableColumn id="2" xr3:uid="{BCF03C38-D473-4972-AEDE-C2DE7C8396EB}" name="Cognome"/>
-    <tableColumn id="3" xr3:uid="{6177FBDD-C58A-42B9-9E0F-5EC58CF0264B}" name="Nascita"/>
-    <tableColumn id="4" xr3:uid="{6E1728DF-7AAC-4726-A07C-5B9D4DEA408A}" name="Morte"/>
-    <tableColumn id="5" xr3:uid="{7D4D55C2-305A-4D45-8057-24C0FED752E2}" name="Immagine"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabella3" displayName="Tabella3" ref="A1:R25" totalsRowShown="0">
+  <autoFilter ref="A1:R25" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+  <tableColumns count="18">
+    <tableColumn id="6" xr3:uid="{3212BA2D-A712-4A4C-8E4F-C02CA96AFD1F}" name="ID_autorita"/>
+    <tableColumn id="7" xr3:uid="{15562B4C-0702-4DEF-87F7-E3BD984669EF}" name="Tipo_entita"/>
+    <tableColumn id="17" xr3:uid="{7283C6B4-B4E6-404F-92AD-8F80E7D20008}" name="Norme"/>
+    <tableColumn id="18" xr3:uid="{F4A739E8-A998-4105-A512-53005410A134}" name="Lingua_record"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Nome"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Cognome"/>
+    <tableColumn id="8" xr3:uid="{3D544CFB-2C18-49C0-8353-2E50D6C3EE44}" name="Forme_varianti"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Nascita"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Morte"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Immagine"/>
+    <tableColumn id="9" xr3:uid="{D71155FF-2283-41CA-B4BA-E37281403641}" name="Biografia"/>
+    <tableColumn id="10" xr3:uid="{013E7873-303A-4FB8-8865-E6B3DFD1AEE9}" name="Luoghi"/>
+    <tableColumn id="11" xr3:uid="{22E6E213-BB2B-4D30-8C40-F7E5D640C195}" name="Wikidata"/>
+    <tableColumn id="12" xr3:uid="{6BAB851C-A200-4855-A259-229103E48483}" name="VIAF"/>
+    <tableColumn id="14" xr3:uid="{8D2B76C7-0208-4F33-A8E7-118BFD4CAD08}" name="Stato_record"/>
+    <tableColumn id="15" xr3:uid="{116F1AD4-6283-44E1-BC3B-7194F7AF5740}" name="Livello_dettaglio"/>
+    <tableColumn id="16" xr3:uid="{61FFE37B-86B2-42F2-A68A-4D026BFFD05D}" name="Data_redazione"/>
+    <tableColumn id="19" xr3:uid="{3C7A0B86-8AF1-47EE-86F8-3A969A4DCE3F}" name="Note_redazionali"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{5CBE908E-36DF-4FAC-A0A5-2AB7F42271C9}" name="Tabella4" displayName="Tabella4" ref="A1:E54" totalsRowShown="0">
-  <autoFilter ref="A1:E54" xr:uid="{5CBE908E-36DF-4FAC-A0A5-2AB7F42271C9}"/>
-  <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{53869648-CC91-454C-84FE-E80E77CB50F3}" name="Nome"/>
-    <tableColumn id="2" xr3:uid="{571D8435-37DF-44A7-B07C-63E008584694}" name="Categoria"/>
-    <tableColumn id="3" xr3:uid="{FF2C4760-FCCE-4C5C-94AB-9EF56A7B83B2}" name="Fondazione"/>
-    <tableColumn id="4" xr3:uid="{5B08FD8D-EDC3-4ECA-8AC5-FB35EFBA2A48}" name="Scioglimento"/>
-    <tableColumn id="5" xr3:uid="{E42B4989-AC40-4D16-9DCF-2FA7F8A7878C}" name="Immagine"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Tabella4" displayName="Tabella4" ref="A1:R54" totalsRowShown="0">
+  <autoFilter ref="A1:R54" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
+  <tableColumns count="18">
+    <tableColumn id="6" xr3:uid="{4369E07F-84A8-44D8-A69E-07057DF34B9B}" name="ID_autorita"/>
+    <tableColumn id="7" xr3:uid="{FB5D02D3-DA94-4843-BABB-940A8E6F528E}" name="Tipo_entita"/>
+    <tableColumn id="17" xr3:uid="{824F81ED-99E2-4986-981B-22027E119042}" name="Norme"/>
+    <tableColumn id="18" xr3:uid="{1E915349-0311-4AF4-91C1-AD3A716F356A}" name="Lingua_record"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Nome"/>
+    <tableColumn id="8" xr3:uid="{DC922B9C-EEE2-48ED-B058-A3A0FB131D11}" name="Forme_varianti"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Categoria"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Fondazione"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Scioglimento"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Immagine"/>
+    <tableColumn id="9" xr3:uid="{0D3C4DBF-008D-4567-AD38-806BB5838BA2}" name="Storia"/>
+    <tableColumn id="10" xr3:uid="{4CA71764-7AE9-47EC-B817-04DD223E365A}" name="Luoghi"/>
+    <tableColumn id="11" xr3:uid="{E820A84A-CE7F-492F-9F18-D9BE2FB1B76A}" name="Wikidata"/>
+    <tableColumn id="12" xr3:uid="{344AA8A3-47C9-4835-AEB9-BCADD2757D98}" name="VIAF"/>
+    <tableColumn id="14" xr3:uid="{980BF526-5BC6-4DE8-9A72-0CFD571F90B2}" name="Stato_record"/>
+    <tableColumn id="15" xr3:uid="{62373511-EB64-41E7-89EC-C7497EE927C2}" name="Livello_dettaglio"/>
+    <tableColumn id="16" xr3:uid="{ADD323D5-F89C-43E4-B88D-B836E3B9D86D}" name="Data_redazione"/>
+    <tableColumn id="19" xr3:uid="{A30F4815-98AE-40F4-8467-092D97C457CF}" name="Note_redazionali"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1911,2934 +2325,2934 @@
         <v>10</v>
       </c>
       <c r="L1" t="s">
-        <v>311</v>
+        <v>11</v>
       </c>
       <c r="M1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F2" s="1">
         <v>1969</v>
       </c>
       <c r="G2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L2" t="s">
-        <v>314</v>
+        <v>24</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F3" s="1">
         <v>1967</v>
       </c>
       <c r="G3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L3" t="s">
-        <v>314</v>
+        <v>24</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F4" s="1">
         <v>1968</v>
       </c>
       <c r="G4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L4" t="s">
-        <v>314</v>
+        <v>24</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F5" s="1">
         <v>1968</v>
       </c>
       <c r="G5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L5" t="s">
-        <v>313</v>
+        <v>37</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B6" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F6" s="1">
         <v>1968</v>
       </c>
       <c r="G6" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L6" t="s">
-        <v>313</v>
+        <v>37</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F7" s="1">
         <v>1968</v>
       </c>
       <c r="G7" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I7" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L7" t="s">
-        <v>314</v>
+        <v>24</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B8" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F8" s="1">
         <v>1968</v>
       </c>
       <c r="G8" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L8" t="s">
-        <v>314</v>
+        <v>24</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B9" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F9" s="1">
         <v>1969</v>
       </c>
       <c r="G9" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L9" t="s">
-        <v>314</v>
+        <v>24</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B10" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F10" s="1">
         <v>1969</v>
       </c>
       <c r="G10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L10" t="s">
-        <v>314</v>
+        <v>24</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B11" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F11" s="1">
         <v>1970</v>
       </c>
       <c r="G11" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L11" t="s">
-        <v>314</v>
+        <v>24</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B12" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D12" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F12" s="1">
         <v>1968</v>
       </c>
       <c r="G12" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L12" t="s">
-        <v>314</v>
+        <v>24</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B13" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D13" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F13" s="1">
         <v>1968</v>
       </c>
       <c r="G13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L13" t="s">
-        <v>314</v>
+        <v>24</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B14" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C14" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D14" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E14" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F14" s="1">
         <v>1967</v>
       </c>
       <c r="G14" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H14" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="I14" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="J14" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="K14" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="L14" t="s">
-        <v>314</v>
+        <v>24</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B15" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C15" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D15" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F15" s="2">
         <v>25064</v>
       </c>
       <c r="G15" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H15" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I15" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="J15" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="L15" t="s">
-        <v>314</v>
+        <v>24</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="N15" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B16" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C16" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D16" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F16" s="2">
         <v>25081</v>
       </c>
       <c r="G16" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I16" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="J16" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="L16" t="s">
-        <v>314</v>
+        <v>24</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="N16" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B17" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C17" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D17" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F17" s="2">
         <v>25479</v>
       </c>
       <c r="G17" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I17" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="J17" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="L17" t="s">
-        <v>314</v>
+        <v>24</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="N17" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B18" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C18" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D18" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F18" s="2">
         <v>25485</v>
       </c>
       <c r="G18" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="H18" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="I18" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="L18" t="s">
-        <v>314</v>
+        <v>24</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B19" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C19" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D19" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F19" s="2">
         <v>23514</v>
       </c>
       <c r="G19" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H19" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I19" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="L19" t="s">
-        <v>314</v>
+        <v>24</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="N19" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B20" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D20" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E20" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="F20" s="1">
         <v>1969</v>
       </c>
       <c r="G20" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="I20" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="L20" t="s">
-        <v>314</v>
+        <v>24</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B21" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D21" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E21" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="F21" s="1">
         <v>1993</v>
       </c>
       <c r="G21" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H21" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="I21" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="L21" t="s">
-        <v>314</v>
+        <v>24</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>322</v>
+        <v>116</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B22" t="s">
-        <v>392</v>
+        <v>118</v>
       </c>
       <c r="C22" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="E22" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>363</v>
+        <v>121</v>
       </c>
       <c r="G22" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="H22" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="I22" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="L22" t="s">
-        <v>312</v>
+        <v>125</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>127</v>
+      </c>
+      <c r="B23" t="s">
+        <v>128</v>
+      </c>
+      <c r="C23" t="s">
+        <v>119</v>
+      </c>
+      <c r="E23" t="s">
         <v>120</v>
       </c>
-      <c r="B23" t="s">
-        <v>393</v>
-      </c>
-      <c r="C23" t="s">
-        <v>114</v>
-      </c>
-      <c r="E23" t="s">
-        <v>115</v>
-      </c>
       <c r="F23" s="6" t="s">
-        <v>362</v>
+        <v>129</v>
       </c>
       <c r="G23" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="H23" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="I23" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="L23" t="s">
-        <v>312</v>
+        <v>125</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>320</v>
+        <v>130</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="B24" t="s">
-        <v>394</v>
+        <v>132</v>
       </c>
       <c r="C24" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="E24" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>361</v>
+        <v>133</v>
       </c>
       <c r="G24" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="H24" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="I24" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="L24" t="s">
-        <v>312</v>
+        <v>125</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
+        <v>135</v>
+      </c>
+      <c r="B25" t="s">
+        <v>136</v>
+      </c>
+      <c r="C25" t="s">
+        <v>119</v>
+      </c>
+      <c r="E25" t="s">
+        <v>120</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="G25" t="s">
+        <v>122</v>
+      </c>
+      <c r="H25" t="s">
         <v>123</v>
       </c>
-      <c r="B25" t="s">
-        <v>395</v>
-      </c>
-      <c r="C25" t="s">
-        <v>114</v>
-      </c>
-      <c r="E25" t="s">
-        <v>115</v>
-      </c>
-      <c r="F25" s="6" t="s">
-        <v>360</v>
-      </c>
-      <c r="G25" t="s">
-        <v>116</v>
-      </c>
-      <c r="H25" t="s">
-        <v>117</v>
-      </c>
       <c r="I25" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="L25" t="s">
-        <v>312</v>
+        <v>125</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
+        <v>139</v>
+      </c>
+      <c r="B26" t="s">
+        <v>140</v>
+      </c>
+      <c r="C26" t="s">
+        <v>119</v>
+      </c>
+      <c r="E26" t="s">
+        <v>120</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="G26" t="s">
+        <v>122</v>
+      </c>
+      <c r="H26" t="s">
+        <v>123</v>
+      </c>
+      <c r="I26" t="s">
+        <v>124</v>
+      </c>
+      <c r="L26" t="s">
         <v>125</v>
       </c>
-      <c r="B26" t="s">
-        <v>396</v>
-      </c>
-      <c r="C26" t="s">
-        <v>114</v>
-      </c>
-      <c r="E26" t="s">
-        <v>115</v>
-      </c>
-      <c r="F26" s="6" t="s">
-        <v>359</v>
-      </c>
-      <c r="G26" t="s">
-        <v>116</v>
-      </c>
-      <c r="H26" t="s">
-        <v>117</v>
-      </c>
-      <c r="I26" t="s">
-        <v>118</v>
-      </c>
-      <c r="L26" t="s">
-        <v>312</v>
-      </c>
       <c r="M26" s="3" t="s">
-        <v>126</v>
+        <v>142</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="B27" t="s">
-        <v>397</v>
+        <v>144</v>
       </c>
       <c r="C27" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="E27" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>358</v>
+        <v>145</v>
       </c>
       <c r="G27" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="H27" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="I27" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="L27" t="s">
-        <v>312</v>
+        <v>125</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>321</v>
+        <v>146</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="B28" t="s">
-        <v>398</v>
+        <v>148</v>
       </c>
       <c r="C28" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="E28" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>357</v>
+        <v>149</v>
       </c>
       <c r="G28" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="H28" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="I28" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="L28" t="s">
-        <v>312</v>
+        <v>125</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="B29" t="s">
-        <v>399</v>
+        <v>152</v>
       </c>
       <c r="C29" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="E29" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>356</v>
+        <v>153</v>
       </c>
       <c r="G29" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="H29" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="I29" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="K29" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="L29" t="s">
-        <v>312</v>
+        <v>125</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>131</v>
+        <v>154</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>132</v>
+        <v>155</v>
       </c>
       <c r="B30" t="s">
-        <v>400</v>
+        <v>156</v>
       </c>
       <c r="C30" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="E30" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>352</v>
+        <v>157</v>
       </c>
       <c r="G30" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="H30" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="I30" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="K30" t="s">
-        <v>133</v>
+        <v>158</v>
       </c>
       <c r="L30" t="s">
-        <v>312</v>
+        <v>125</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>134</v>
+        <v>159</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>135</v>
+        <v>160</v>
       </c>
       <c r="B31" t="s">
-        <v>136</v>
+        <v>161</v>
       </c>
       <c r="C31" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D31" t="s">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="E31" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F31" s="1">
         <v>1968</v>
       </c>
       <c r="G31" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H31" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I31" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L31" t="s">
-        <v>314</v>
+        <v>24</v>
       </c>
       <c r="M31" s="3" t="s">
-        <v>138</v>
+        <v>163</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="B32" t="s">
-        <v>140</v>
+        <v>165</v>
       </c>
       <c r="C32" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D32" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E32" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F32" s="1">
         <v>1968</v>
       </c>
       <c r="G32" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H32" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I32" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L32" t="s">
-        <v>313</v>
+        <v>37</v>
       </c>
       <c r="M32" s="3" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>142</v>
+        <v>167</v>
       </c>
       <c r="B33" t="s">
-        <v>143</v>
+        <v>168</v>
       </c>
       <c r="C33" t="s">
-        <v>144</v>
+        <v>169</v>
       </c>
       <c r="F33" s="1">
         <v>1970</v>
       </c>
       <c r="G33" t="s">
-        <v>145</v>
+        <v>170</v>
       </c>
       <c r="I33" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="J33" t="s">
-        <v>146</v>
+        <v>171</v>
       </c>
       <c r="L33" t="s">
-        <v>314</v>
+        <v>24</v>
       </c>
       <c r="M33" s="3" t="s">
-        <v>147</v>
+        <v>172</v>
       </c>
       <c r="N33" t="s">
-        <v>148</v>
+        <v>173</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>149</v>
+        <v>174</v>
       </c>
       <c r="B34" t="s">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="C34" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F34" s="2">
         <v>25063</v>
       </c>
       <c r="G34" t="s">
-        <v>151</v>
+        <v>176</v>
       </c>
       <c r="H34" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I34" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="J34" t="s">
-        <v>152</v>
+        <v>177</v>
       </c>
       <c r="K34" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L34" t="s">
-        <v>314</v>
+        <v>24</v>
       </c>
       <c r="M34" s="3" t="s">
-        <v>153</v>
+        <v>178</v>
       </c>
       <c r="O34" t="s">
-        <v>154</v>
+        <v>179</v>
       </c>
       <c r="P34" t="s">
-        <v>155</v>
+        <v>180</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="B35" t="s">
-        <v>157</v>
+        <v>182</v>
       </c>
       <c r="C35" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D35" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F35" s="2">
         <v>25081</v>
       </c>
       <c r="G35" t="s">
-        <v>151</v>
+        <v>176</v>
       </c>
       <c r="H35" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I35" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="J35" t="s">
-        <v>158</v>
+        <v>183</v>
       </c>
       <c r="K35" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="L35" t="s">
-        <v>314</v>
+        <v>24</v>
       </c>
       <c r="M35" s="3" t="s">
-        <v>159</v>
+        <v>184</v>
       </c>
       <c r="O35" t="s">
-        <v>160</v>
+        <v>185</v>
       </c>
       <c r="P35" t="s">
-        <v>161</v>
+        <v>186</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>162</v>
+        <v>187</v>
       </c>
       <c r="B36" t="s">
-        <v>163</v>
+        <v>188</v>
       </c>
       <c r="C36" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>355</v>
+        <v>189</v>
       </c>
       <c r="G36" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="H36" t="s">
-        <v>164</v>
+        <v>190</v>
       </c>
       <c r="I36" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="L36" t="s">
-        <v>314</v>
+        <v>24</v>
       </c>
       <c r="M36" s="3" t="s">
-        <v>165</v>
+        <v>191</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>166</v>
+        <v>192</v>
       </c>
       <c r="B37" t="s">
-        <v>167</v>
+        <v>193</v>
       </c>
       <c r="C37" t="s">
-        <v>144</v>
+        <v>169</v>
       </c>
       <c r="D37" t="s">
-        <v>146</v>
+        <v>171</v>
       </c>
       <c r="E37" t="s">
-        <v>168</v>
+        <v>194</v>
       </c>
       <c r="F37" s="1">
         <v>1975</v>
       </c>
       <c r="G37" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H37" t="s">
+        <v>195</v>
+      </c>
+      <c r="I37" t="s">
+        <v>109</v>
+      </c>
+      <c r="K37" t="s">
         <v>169</v>
       </c>
-      <c r="I37" t="s">
-        <v>106</v>
-      </c>
-      <c r="K37" t="s">
-        <v>144</v>
-      </c>
       <c r="L37" t="s">
-        <v>314</v>
+        <v>24</v>
       </c>
       <c r="M37" s="3" t="s">
-        <v>170</v>
+        <v>196</v>
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>171</v>
+        <v>197</v>
       </c>
       <c r="B38" t="s">
-        <v>172</v>
+        <v>198</v>
       </c>
       <c r="C38" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D38" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E38" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F38" s="1">
         <v>1968</v>
       </c>
       <c r="G38" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H38" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I38" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L38" t="s">
-        <v>314</v>
+        <v>24</v>
       </c>
       <c r="M38" s="3" t="s">
-        <v>173</v>
+        <v>199</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>174</v>
+        <v>200</v>
       </c>
       <c r="B39" t="s">
-        <v>175</v>
+        <v>201</v>
       </c>
       <c r="C39" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D39" t="s">
-        <v>176</v>
+        <v>202</v>
       </c>
       <c r="E39" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F39" s="1">
         <v>1970</v>
       </c>
       <c r="G39" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H39" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I39" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J39" t="s">
-        <v>177</v>
+        <v>203</v>
       </c>
       <c r="L39" t="s">
-        <v>314</v>
+        <v>24</v>
       </c>
       <c r="M39" s="3" t="s">
-        <v>178</v>
+        <v>204</v>
       </c>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>179</v>
+        <v>205</v>
       </c>
       <c r="B40" t="s">
-        <v>180</v>
+        <v>206</v>
       </c>
       <c r="C40" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D40" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E40" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F40" s="1">
         <v>1968</v>
       </c>
       <c r="G40" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H40" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I40" t="s">
-        <v>181</v>
+        <v>207</v>
       </c>
       <c r="L40" t="s">
-        <v>314</v>
+        <v>24</v>
       </c>
       <c r="M40" s="3" t="s">
-        <v>182</v>
+        <v>208</v>
       </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>183</v>
+        <v>209</v>
       </c>
       <c r="B41" t="s">
-        <v>184</v>
+        <v>210</v>
       </c>
       <c r="C41" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D41" t="s">
-        <v>185</v>
+        <v>211</v>
       </c>
       <c r="E41" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F41" s="1">
         <v>1970</v>
       </c>
       <c r="G41" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H41" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I41" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L41" t="s">
-        <v>314</v>
+        <v>24</v>
       </c>
       <c r="M41" s="3" t="s">
-        <v>186</v>
+        <v>212</v>
       </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>187</v>
+        <v>213</v>
       </c>
       <c r="B42" t="s">
-        <v>188</v>
+        <v>214</v>
       </c>
       <c r="D42" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E42" t="s">
-        <v>189</v>
+        <v>215</v>
       </c>
       <c r="F42" s="1">
         <v>1968</v>
       </c>
       <c r="G42" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H42" t="s">
-        <v>164</v>
+        <v>190</v>
       </c>
       <c r="I42" t="s">
-        <v>190</v>
+        <v>216</v>
       </c>
       <c r="L42" t="s">
-        <v>314</v>
+        <v>24</v>
       </c>
       <c r="M42" s="3" t="s">
-        <v>191</v>
+        <v>217</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>192</v>
+        <v>218</v>
       </c>
       <c r="B43" t="s">
-        <v>193</v>
+        <v>219</v>
       </c>
       <c r="D43" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E43" t="s">
-        <v>194</v>
+        <v>220</v>
       </c>
       <c r="F43" s="1">
         <v>1967</v>
       </c>
       <c r="G43" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H43" t="s">
-        <v>164</v>
+        <v>190</v>
       </c>
       <c r="I43" t="s">
-        <v>190</v>
+        <v>216</v>
       </c>
       <c r="J43" t="s">
-        <v>195</v>
+        <v>221</v>
       </c>
       <c r="K43" t="s">
-        <v>196</v>
+        <v>222</v>
       </c>
       <c r="L43" t="s">
-        <v>314</v>
+        <v>24</v>
       </c>
       <c r="M43" s="3" t="s">
-        <v>197</v>
+        <v>223</v>
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>198</v>
+        <v>224</v>
       </c>
       <c r="B44" t="s">
-        <v>199</v>
+        <v>225</v>
       </c>
       <c r="C44" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D44" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E44" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F44" s="1">
         <v>1968</v>
       </c>
       <c r="G44" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H44" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I44" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L44" t="s">
-        <v>314</v>
+        <v>24</v>
       </c>
       <c r="M44" s="3" t="s">
-        <v>200</v>
+        <v>226</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>201</v>
+        <v>227</v>
       </c>
       <c r="B45" t="s">
-        <v>202</v>
+        <v>228</v>
       </c>
       <c r="C45" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D45" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E45" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F45" s="1">
         <v>1967</v>
       </c>
       <c r="G45" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H45" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I45" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L45" t="s">
-        <v>314</v>
+        <v>24</v>
       </c>
       <c r="M45" s="3" t="s">
-        <v>203</v>
+        <v>229</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>204</v>
+        <v>230</v>
       </c>
       <c r="B46" t="s">
-        <v>205</v>
+        <v>231</v>
       </c>
       <c r="C46" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D46" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E46" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F46" s="1">
         <v>1968</v>
       </c>
       <c r="G46" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H46" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I46" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L46" t="s">
-        <v>314</v>
+        <v>24</v>
       </c>
       <c r="M46" s="3" t="s">
-        <v>206</v>
+        <v>232</v>
       </c>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>207</v>
+        <v>233</v>
       </c>
       <c r="B47" t="s">
-        <v>208</v>
+        <v>234</v>
       </c>
       <c r="C47" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D47" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E47" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F47" s="1">
         <v>1969</v>
       </c>
       <c r="G47" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H47" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I47" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L47" t="s">
-        <v>314</v>
+        <v>24</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>209</v>
+        <v>235</v>
       </c>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>210</v>
+        <v>236</v>
       </c>
       <c r="B48" t="s">
-        <v>211</v>
+        <v>237</v>
       </c>
       <c r="C48" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D48" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E48" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F48" s="1">
         <v>1971</v>
       </c>
       <c r="G48" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H48" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I48" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L48" t="s">
-        <v>314</v>
+        <v>24</v>
       </c>
       <c r="M48" s="3" t="s">
-        <v>212</v>
+        <v>238</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>213</v>
+        <v>239</v>
       </c>
       <c r="B49" t="s">
-        <v>214</v>
+        <v>240</v>
       </c>
       <c r="C49" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D49" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E49" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F49" s="1">
         <v>1968</v>
       </c>
       <c r="G49" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H49" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I49" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L49" t="s">
-        <v>314</v>
+        <v>24</v>
       </c>
       <c r="M49" s="3" t="s">
-        <v>215</v>
+        <v>241</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>216</v>
+        <v>242</v>
       </c>
       <c r="B50" t="s">
-        <v>217</v>
+        <v>243</v>
       </c>
       <c r="C50" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D50" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E50" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F50" s="1">
         <v>1968</v>
       </c>
       <c r="G50" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H50" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I50" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L50" t="s">
-        <v>314</v>
+        <v>24</v>
       </c>
       <c r="M50" s="3" t="s">
-        <v>218</v>
+        <v>244</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>219</v>
+        <v>245</v>
       </c>
       <c r="B51" t="s">
-        <v>220</v>
+        <v>246</v>
       </c>
       <c r="C51" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D51" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E51" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F51" s="1">
         <v>1968</v>
       </c>
       <c r="G51" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H51" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I51" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L51" t="s">
-        <v>314</v>
+        <v>24</v>
       </c>
       <c r="M51" s="3" t="s">
-        <v>221</v>
+        <v>247</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>222</v>
+        <v>248</v>
       </c>
       <c r="B52" t="s">
-        <v>223</v>
+        <v>249</v>
       </c>
       <c r="C52" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D52" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E52" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F52" s="1">
         <v>1968</v>
       </c>
       <c r="G52" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H52" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I52" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L52" t="s">
-        <v>314</v>
+        <v>24</v>
       </c>
       <c r="M52" s="3" t="s">
-        <v>224</v>
+        <v>250</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="B53" t="s">
-        <v>226</v>
+        <v>252</v>
       </c>
       <c r="C53" t="s">
-        <v>227</v>
+        <v>253</v>
       </c>
       <c r="D53" t="s">
-        <v>227</v>
+        <v>253</v>
       </c>
       <c r="E53" t="s">
-        <v>228</v>
+        <v>254</v>
       </c>
       <c r="F53" s="1">
         <v>1969</v>
       </c>
       <c r="G53" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H53" t="s">
-        <v>164</v>
+        <v>190</v>
       </c>
       <c r="I53" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="L53" t="s">
-        <v>314</v>
+        <v>24</v>
       </c>
       <c r="M53" s="3" t="s">
-        <v>229</v>
+        <v>255</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>230</v>
+        <v>256</v>
       </c>
       <c r="B54" t="s">
-        <v>231</v>
+        <v>257</v>
       </c>
       <c r="C54" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="F54" s="1">
         <v>1972</v>
       </c>
       <c r="G54" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="H54" t="s">
-        <v>232</v>
+        <v>258</v>
       </c>
       <c r="I54" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="K54" t="s">
-        <v>233</v>
+        <v>259</v>
       </c>
       <c r="L54" t="s">
-        <v>314</v>
+        <v>24</v>
       </c>
       <c r="M54" s="3" t="s">
-        <v>234</v>
+        <v>260</v>
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>235</v>
+        <v>261</v>
       </c>
       <c r="B55" t="s">
-        <v>236</v>
+        <v>262</v>
       </c>
       <c r="C55" t="s">
-        <v>237</v>
+        <v>263</v>
       </c>
       <c r="D55" t="s">
-        <v>237</v>
+        <v>263</v>
       </c>
       <c r="E55" t="s">
-        <v>238</v>
+        <v>264</v>
       </c>
       <c r="F55" s="6" t="s">
-        <v>354</v>
+        <v>265</v>
       </c>
       <c r="G55" t="s">
-        <v>239</v>
+        <v>266</v>
       </c>
       <c r="H55" t="s">
-        <v>164</v>
+        <v>190</v>
       </c>
       <c r="I55" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="J55" t="s">
-        <v>240</v>
+        <v>267</v>
       </c>
       <c r="L55" t="s">
-        <v>314</v>
+        <v>24</v>
       </c>
       <c r="M55" s="3" t="s">
-        <v>241</v>
+        <v>268</v>
       </c>
       <c r="N55" t="s">
-        <v>242</v>
+        <v>269</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>243</v>
+        <v>270</v>
       </c>
       <c r="B56" t="s">
-        <v>244</v>
+        <v>271</v>
       </c>
       <c r="C56" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D56" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E56" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F56" s="1">
         <v>1967</v>
       </c>
       <c r="G56" t="s">
-        <v>239</v>
+        <v>266</v>
       </c>
       <c r="I56" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="L56" t="s">
-        <v>314</v>
+        <v>24</v>
       </c>
       <c r="M56" s="3" t="s">
-        <v>245</v>
+        <v>272</v>
       </c>
       <c r="N56" t="s">
-        <v>246</v>
+        <v>273</v>
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>247</v>
+        <v>274</v>
       </c>
       <c r="B57" t="s">
-        <v>248</v>
+        <v>275</v>
       </c>
       <c r="C57" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D57" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E57" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="F57" s="1">
         <v>1967</v>
       </c>
       <c r="G57" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H57" t="s">
-        <v>164</v>
+        <v>190</v>
       </c>
       <c r="I57" t="s">
-        <v>190</v>
+        <v>216</v>
       </c>
       <c r="L57" t="s">
-        <v>314</v>
+        <v>24</v>
       </c>
       <c r="M57" s="3" t="s">
-        <v>249</v>
+        <v>276</v>
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>250</v>
+        <v>277</v>
       </c>
       <c r="B58" t="s">
-        <v>303</v>
+        <v>278</v>
       </c>
       <c r="C58" t="s">
-        <v>237</v>
+        <v>263</v>
       </c>
       <c r="D58" t="s">
-        <v>237</v>
+        <v>263</v>
       </c>
       <c r="E58" t="s">
-        <v>238</v>
+        <v>264</v>
       </c>
       <c r="F58" s="2">
         <v>28253</v>
       </c>
       <c r="G58" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H58" t="s">
-        <v>169</v>
+        <v>195</v>
       </c>
       <c r="I58" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="J58" t="s">
-        <v>240</v>
+        <v>267</v>
       </c>
       <c r="K58" t="s">
-        <v>450</v>
+        <v>279</v>
       </c>
       <c r="L58" t="s">
-        <v>314</v>
+        <v>24</v>
       </c>
       <c r="M58" s="3" t="s">
-        <v>251</v>
+        <v>280</v>
       </c>
       <c r="N58" t="s">
-        <v>252</v>
+        <v>281</v>
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>304</v>
+        <v>282</v>
       </c>
       <c r="B59" t="s">
-        <v>307</v>
+        <v>283</v>
       </c>
       <c r="C59" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D59" t="s">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="E59" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="F59">
         <v>1970</v>
       </c>
       <c r="G59" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H59" t="s">
-        <v>164</v>
+        <v>190</v>
       </c>
       <c r="I59" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="L59" t="s">
-        <v>314</v>
+        <v>24</v>
       </c>
       <c r="M59" s="3" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>305</v>
+        <v>286</v>
       </c>
       <c r="B60" t="s">
-        <v>306</v>
+        <v>287</v>
       </c>
       <c r="C60" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D60" t="s">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="E60" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="F60">
         <v>1970</v>
       </c>
       <c r="G60" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H60" t="s">
-        <v>164</v>
+        <v>190</v>
       </c>
       <c r="I60" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="L60" t="s">
-        <v>314</v>
+        <v>24</v>
       </c>
       <c r="M60" s="3" t="s">
-        <v>309</v>
+        <v>288</v>
       </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>315</v>
+        <v>289</v>
       </c>
       <c r="B61" t="s">
-        <v>316</v>
+        <v>290</v>
       </c>
       <c r="C61" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D61" t="s">
-        <v>317</v>
+        <v>291</v>
       </c>
       <c r="E61" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="F61">
         <v>1965</v>
       </c>
       <c r="G61" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H61" t="s">
-        <v>164</v>
+        <v>190</v>
       </c>
       <c r="I61" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="J61" t="s">
-        <v>318</v>
+        <v>292</v>
       </c>
       <c r="L61" t="s">
-        <v>314</v>
+        <v>24</v>
       </c>
       <c r="M61" s="3" t="s">
-        <v>319</v>
+        <v>293</v>
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>324</v>
+        <v>294</v>
       </c>
       <c r="B62" t="s">
-        <v>325</v>
+        <v>295</v>
       </c>
       <c r="C62" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D62" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E62" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F62" s="1">
         <v>1971</v>
       </c>
       <c r="G62" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H62" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I62" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L62" t="s">
-        <v>314</v>
+        <v>24</v>
       </c>
       <c r="M62" s="3" t="s">
-        <v>326</v>
+        <v>296</v>
       </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>327</v>
+        <v>297</v>
       </c>
       <c r="B63" t="s">
-        <v>328</v>
+        <v>298</v>
       </c>
       <c r="F63" s="4">
         <v>24917</v>
       </c>
       <c r="G63" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H63" t="s">
-        <v>329</v>
+        <v>299</v>
       </c>
       <c r="I63" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="K63" t="s">
-        <v>330</v>
+        <v>300</v>
       </c>
       <c r="L63" t="s">
-        <v>314</v>
+        <v>24</v>
       </c>
       <c r="M63" s="3" t="s">
-        <v>331</v>
+        <v>301</v>
       </c>
       <c r="N63" t="s">
-        <v>332</v>
+        <v>302</v>
       </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>333</v>
+        <v>303</v>
       </c>
       <c r="B64" t="s">
-        <v>338</v>
+        <v>304</v>
       </c>
       <c r="C64" t="s">
-        <v>233</v>
+        <v>259</v>
       </c>
       <c r="D64" t="s">
-        <v>233</v>
+        <v>259</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>353</v>
+        <v>305</v>
       </c>
       <c r="G64" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="H64" t="s">
-        <v>335</v>
+        <v>306</v>
       </c>
       <c r="I64" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="L64" t="s">
-        <v>336</v>
+        <v>307</v>
       </c>
       <c r="M64" s="3" t="s">
-        <v>441</v>
+        <v>308</v>
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>334</v>
+        <v>309</v>
       </c>
       <c r="B65" t="s">
-        <v>339</v>
+        <v>310</v>
       </c>
       <c r="C65" t="s">
-        <v>337</v>
+        <v>311</v>
       </c>
       <c r="D65" t="s">
-        <v>337</v>
+        <v>311</v>
       </c>
       <c r="F65" s="4">
         <v>26956</v>
       </c>
       <c r="G65" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="H65" t="s">
-        <v>335</v>
+        <v>306</v>
       </c>
       <c r="I65" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="L65" t="s">
-        <v>336</v>
+        <v>307</v>
       </c>
       <c r="M65" s="3" t="s">
-        <v>440</v>
+        <v>312</v>
       </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>340</v>
+        <v>313</v>
       </c>
       <c r="B66" t="s">
-        <v>341</v>
+        <v>314</v>
       </c>
       <c r="C66" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F66">
         <v>1968</v>
       </c>
       <c r="G66" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H66" t="s">
-        <v>164</v>
+        <v>190</v>
       </c>
       <c r="I66" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="L66" t="s">
-        <v>314</v>
+        <v>24</v>
       </c>
       <c r="M66" s="3" t="s">
-        <v>342</v>
+        <v>315</v>
       </c>
       <c r="N66" t="s">
-        <v>349</v>
+        <v>316</v>
       </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>343</v>
+        <v>317</v>
       </c>
       <c r="B67" t="s">
-        <v>344</v>
+        <v>318</v>
       </c>
       <c r="C67" t="s">
-        <v>345</v>
+        <v>319</v>
       </c>
       <c r="F67">
         <v>1970</v>
       </c>
       <c r="G67" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H67" t="s">
-        <v>164</v>
+        <v>190</v>
       </c>
       <c r="I67" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="L67" t="s">
-        <v>314</v>
+        <v>24</v>
       </c>
       <c r="M67" s="3" t="s">
-        <v>346</v>
+        <v>320</v>
       </c>
       <c r="N67" t="s">
-        <v>348</v>
+        <v>321</v>
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>350</v>
+        <v>322</v>
       </c>
       <c r="B68" t="s">
-        <v>351</v>
+        <v>323</v>
       </c>
       <c r="C68" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>352</v>
+        <v>157</v>
       </c>
       <c r="G68" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="H68" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="I68" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="L68" t="s">
-        <v>314</v>
+        <v>24</v>
       </c>
       <c r="M68" s="3" t="s">
-        <v>439</v>
+        <v>324</v>
       </c>
       <c r="N68" t="s">
-        <v>347</v>
+        <v>325</v>
       </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>364</v>
+        <v>326</v>
       </c>
       <c r="B69" t="s">
-        <v>404</v>
+        <v>327</v>
       </c>
       <c r="C69" t="s">
-        <v>391</v>
+        <v>328</v>
       </c>
       <c r="D69" t="s">
-        <v>391</v>
+        <v>328</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>421</v>
+        <v>329</v>
       </c>
       <c r="G69" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="H69" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="I69" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="L69" t="s">
-        <v>312</v>
+        <v>125</v>
       </c>
       <c r="M69" s="3" t="s">
-        <v>401</v>
+        <v>330</v>
       </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>365</v>
+        <v>331</v>
       </c>
       <c r="B70" t="s">
-        <v>447</v>
+        <v>332</v>
       </c>
       <c r="C70" t="s">
-        <v>391</v>
+        <v>328</v>
       </c>
       <c r="D70" t="s">
-        <v>391</v>
+        <v>328</v>
       </c>
       <c r="F70" s="8">
         <v>25704</v>
       </c>
       <c r="G70" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="H70" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="I70" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="L70" t="s">
-        <v>312</v>
+        <v>125</v>
       </c>
       <c r="M70" s="3" t="s">
-        <v>448</v>
+        <v>333</v>
       </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>366</v>
+        <v>334</v>
       </c>
       <c r="B71" t="s">
-        <v>403</v>
+        <v>335</v>
       </c>
       <c r="C71" t="s">
-        <v>391</v>
+        <v>328</v>
       </c>
       <c r="D71" t="s">
-        <v>391</v>
+        <v>328</v>
       </c>
       <c r="F71" s="4">
         <v>25718</v>
       </c>
       <c r="G71" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="H71" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="I71" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="L71" t="s">
-        <v>312</v>
+        <v>125</v>
       </c>
       <c r="M71" s="3" t="s">
-        <v>402</v>
+        <v>336</v>
       </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>367</v>
+        <v>337</v>
       </c>
       <c r="B72" t="s">
-        <v>405</v>
+        <v>338</v>
       </c>
       <c r="C72" t="s">
-        <v>391</v>
+        <v>328</v>
       </c>
       <c r="D72" t="s">
-        <v>391</v>
+        <v>328</v>
       </c>
       <c r="F72" s="4">
         <v>25719</v>
       </c>
       <c r="G72" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="H72" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="I72" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="L72" t="s">
-        <v>312</v>
+        <v>125</v>
       </c>
       <c r="M72" s="3" t="s">
-        <v>424</v>
+        <v>339</v>
       </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>368</v>
+        <v>340</v>
       </c>
       <c r="B73" t="s">
-        <v>406</v>
+        <v>341</v>
       </c>
       <c r="C73" t="s">
-        <v>391</v>
+        <v>328</v>
       </c>
       <c r="D73" t="s">
-        <v>391</v>
+        <v>328</v>
       </c>
       <c r="F73" s="4">
         <v>25740</v>
       </c>
       <c r="G73" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="H73" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="I73" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="L73" t="s">
-        <v>312</v>
+        <v>125</v>
       </c>
       <c r="M73" s="3" t="s">
-        <v>425</v>
+        <v>342</v>
       </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>369</v>
+        <v>343</v>
       </c>
       <c r="B74" t="s">
-        <v>407</v>
+        <v>344</v>
       </c>
       <c r="C74" t="s">
-        <v>391</v>
+        <v>328</v>
       </c>
       <c r="D74" t="s">
-        <v>391</v>
+        <v>328</v>
       </c>
       <c r="F74" s="4">
         <v>25765</v>
       </c>
       <c r="G74" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="H74" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="I74" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="L74" t="s">
-        <v>312</v>
+        <v>125</v>
       </c>
       <c r="M74" s="3" t="s">
-        <v>426</v>
+        <v>345</v>
       </c>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>370</v>
+        <v>346</v>
       </c>
       <c r="B75" t="s">
-        <v>408</v>
+        <v>347</v>
       </c>
       <c r="C75" t="s">
-        <v>391</v>
+        <v>328</v>
       </c>
       <c r="D75" t="s">
-        <v>391</v>
+        <v>328</v>
       </c>
       <c r="F75" s="4">
         <v>25824</v>
       </c>
       <c r="G75" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="H75" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="I75" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="L75" t="s">
-        <v>312</v>
+        <v>125</v>
       </c>
       <c r="M75" s="3" t="s">
-        <v>427</v>
+        <v>348</v>
       </c>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>371</v>
+        <v>349</v>
       </c>
       <c r="B76" t="s">
-        <v>409</v>
+        <v>350</v>
       </c>
       <c r="C76" t="s">
-        <v>391</v>
+        <v>328</v>
       </c>
       <c r="D76" t="s">
-        <v>391</v>
+        <v>328</v>
       </c>
       <c r="F76" s="4">
         <v>25866</v>
       </c>
       <c r="G76" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="H76" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="I76" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="L76" t="s">
-        <v>312</v>
+        <v>125</v>
       </c>
       <c r="M76" s="3" t="s">
-        <v>428</v>
+        <v>351</v>
       </c>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>372</v>
+        <v>352</v>
       </c>
       <c r="B77" t="s">
-        <v>410</v>
+        <v>353</v>
       </c>
       <c r="C77" t="s">
-        <v>391</v>
+        <v>328</v>
       </c>
       <c r="D77" t="s">
-        <v>391</v>
+        <v>328</v>
       </c>
       <c r="F77" s="4">
         <v>25887</v>
       </c>
       <c r="G77" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="H77" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="I77" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="L77" t="s">
-        <v>312</v>
+        <v>125</v>
       </c>
       <c r="M77" s="3" t="s">
-        <v>429</v>
+        <v>354</v>
       </c>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>373</v>
+        <v>355</v>
       </c>
       <c r="B78" t="s">
-        <v>411</v>
+        <v>356</v>
       </c>
       <c r="C78" t="s">
-        <v>391</v>
+        <v>328</v>
       </c>
       <c r="D78" t="s">
-        <v>391</v>
+        <v>328</v>
       </c>
       <c r="F78" s="4">
         <v>25915</v>
       </c>
       <c r="G78" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="H78" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="I78" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="L78" t="s">
-        <v>312</v>
+        <v>125</v>
       </c>
       <c r="M78" s="3" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>374</v>
+        <v>358</v>
       </c>
       <c r="B79" t="s">
-        <v>412</v>
+        <v>359</v>
       </c>
       <c r="C79" t="s">
-        <v>391</v>
+        <v>328</v>
       </c>
       <c r="D79" t="s">
-        <v>391</v>
+        <v>328</v>
       </c>
       <c r="F79" s="4">
         <v>25950</v>
       </c>
       <c r="G79" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="H79" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="I79" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="L79" t="s">
-        <v>312</v>
+        <v>125</v>
       </c>
       <c r="M79" s="3" t="s">
-        <v>431</v>
+        <v>360</v>
       </c>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>375</v>
+        <v>361</v>
       </c>
       <c r="B80" t="s">
-        <v>413</v>
+        <v>362</v>
       </c>
       <c r="C80" t="s">
-        <v>391</v>
+        <v>328</v>
       </c>
       <c r="D80" t="s">
-        <v>391</v>
+        <v>328</v>
       </c>
       <c r="F80" s="4">
         <v>25971</v>
       </c>
       <c r="G80" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="H80" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="I80" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="L80" t="s">
-        <v>312</v>
+        <v>125</v>
       </c>
       <c r="M80" s="3" t="s">
-        <v>432</v>
+        <v>363</v>
       </c>
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="B81" t="s">
-        <v>414</v>
+        <v>365</v>
       </c>
       <c r="C81" t="s">
-        <v>391</v>
+        <v>328</v>
       </c>
       <c r="D81" t="s">
-        <v>391</v>
+        <v>328</v>
       </c>
       <c r="F81" s="4">
         <v>25999</v>
       </c>
       <c r="G81" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="H81" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="I81" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="L81" t="s">
-        <v>312</v>
+        <v>125</v>
       </c>
       <c r="M81" s="3" t="s">
-        <v>433</v>
+        <v>366</v>
       </c>
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="B82" t="s">
-        <v>415</v>
+        <v>368</v>
       </c>
       <c r="C82" t="s">
-        <v>391</v>
+        <v>328</v>
       </c>
       <c r="D82" t="s">
-        <v>391</v>
+        <v>328</v>
       </c>
       <c r="F82" s="4">
         <v>26027</v>
       </c>
       <c r="G82" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="H82" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="I82" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="L82" t="s">
-        <v>312</v>
+        <v>125</v>
       </c>
       <c r="M82" s="3" t="s">
-        <v>434</v>
+        <v>369</v>
       </c>
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="B83" t="s">
-        <v>416</v>
+        <v>371</v>
       </c>
       <c r="C83" t="s">
-        <v>391</v>
+        <v>328</v>
       </c>
       <c r="D83" t="s">
-        <v>391</v>
+        <v>328</v>
       </c>
       <c r="F83" s="4">
         <v>26054</v>
       </c>
       <c r="G83" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="H83" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="I83" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="L83" t="s">
-        <v>312</v>
+        <v>125</v>
       </c>
       <c r="M83" s="3" t="s">
-        <v>435</v>
+        <v>372</v>
       </c>
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="B84" t="s">
-        <v>417</v>
+        <v>374</v>
       </c>
       <c r="C84" t="s">
-        <v>391</v>
+        <v>328</v>
       </c>
       <c r="D84" t="s">
-        <v>391</v>
+        <v>328</v>
       </c>
       <c r="F84" s="4">
         <v>26076</v>
       </c>
       <c r="G84" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="H84" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="I84" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="L84" t="s">
-        <v>312</v>
+        <v>125</v>
       </c>
       <c r="M84" s="3" t="s">
-        <v>436</v>
+        <v>375</v>
       </c>
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="B85" t="s">
-        <v>418</v>
+        <v>377</v>
       </c>
       <c r="C85" t="s">
-        <v>391</v>
+        <v>328</v>
       </c>
       <c r="D85" t="s">
-        <v>391</v>
+        <v>328</v>
       </c>
       <c r="F85" s="4">
         <v>26104</v>
       </c>
       <c r="G85" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="H85" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="I85" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="L85" t="s">
-        <v>312</v>
+        <v>125</v>
       </c>
       <c r="M85" s="3" t="s">
-        <v>437</v>
+        <v>378</v>
       </c>
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B86" t="s">
-        <v>419</v>
+        <v>380</v>
       </c>
       <c r="C86" t="s">
-        <v>391</v>
+        <v>328</v>
       </c>
       <c r="D86" t="s">
-        <v>391</v>
+        <v>328</v>
       </c>
       <c r="F86" s="4">
         <v>26139</v>
       </c>
       <c r="G86" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="H86" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="I86" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="L86" t="s">
-        <v>312</v>
+        <v>125</v>
       </c>
       <c r="M86" s="3" t="s">
-        <v>438</v>
+        <v>381</v>
       </c>
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.3">
@@ -4846,461 +5260,460 @@
         <v>382</v>
       </c>
       <c r="B87" t="s">
-        <v>420</v>
+        <v>383</v>
       </c>
       <c r="C87" t="s">
-        <v>391</v>
+        <v>328</v>
       </c>
       <c r="D87" t="s">
-        <v>391</v>
+        <v>328</v>
       </c>
       <c r="F87" s="4">
         <v>26265</v>
       </c>
       <c r="G87" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="H87" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="I87" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="L87" t="s">
-        <v>312</v>
+        <v>125</v>
       </c>
       <c r="M87" s="3" t="s">
-        <v>442</v>
+        <v>384</v>
       </c>
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B88" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C88" t="s">
-        <v>391</v>
+        <v>328</v>
       </c>
       <c r="D88" t="s">
-        <v>391</v>
+        <v>328</v>
       </c>
       <c r="F88" s="4">
         <v>26307</v>
       </c>
       <c r="G88" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="H88" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="I88" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="L88" t="s">
-        <v>312</v>
+        <v>125</v>
       </c>
       <c r="M88" s="3" t="s">
-        <v>443</v>
+        <v>387</v>
       </c>
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="B89" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C89" t="s">
-        <v>391</v>
+        <v>328</v>
       </c>
       <c r="D89" t="s">
-        <v>391</v>
+        <v>328</v>
       </c>
       <c r="F89" s="4">
         <v>26370</v>
       </c>
       <c r="G89" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="H89" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="I89" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="L89" t="s">
-        <v>312</v>
+        <v>125</v>
       </c>
       <c r="M89" s="3" t="s">
-        <v>444</v>
+        <v>390</v>
       </c>
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="B90" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="C90" t="s">
-        <v>391</v>
+        <v>328</v>
       </c>
       <c r="D90" t="s">
-        <v>391</v>
+        <v>328</v>
       </c>
       <c r="F90" s="4">
         <v>26420</v>
       </c>
       <c r="G90" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="H90" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="I90" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="L90" t="s">
-        <v>312</v>
+        <v>125</v>
       </c>
       <c r="M90" s="3" t="s">
-        <v>422</v>
+        <v>393</v>
       </c>
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="B91" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="C91" t="s">
-        <v>391</v>
+        <v>328</v>
       </c>
       <c r="D91" t="s">
-        <v>391</v>
+        <v>328</v>
       </c>
       <c r="F91" s="4">
         <v>26608</v>
       </c>
       <c r="G91" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="H91" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="I91" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="L91" t="s">
-        <v>312</v>
+        <v>125</v>
       </c>
       <c r="M91" s="3" t="s">
-        <v>445</v>
+        <v>396</v>
       </c>
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>446</v>
+        <v>397</v>
       </c>
       <c r="B92" t="s">
-        <v>449</v>
+        <v>398</v>
       </c>
       <c r="C92" t="s">
-        <v>391</v>
+        <v>328</v>
       </c>
       <c r="D92" t="s">
-        <v>391</v>
+        <v>328</v>
       </c>
       <c r="F92" s="4">
         <v>26785</v>
       </c>
       <c r="G92" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="H92" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="I92" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="L92" t="s">
-        <v>312</v>
+        <v>125</v>
       </c>
       <c r="M92" s="3" t="s">
-        <v>423</v>
+        <v>399</v>
       </c>
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>451</v>
+        <v>400</v>
       </c>
       <c r="B93" t="s">
-        <v>452</v>
+        <v>401</v>
       </c>
       <c r="C93" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E93" t="s">
-        <v>453</v>
+        <v>402</v>
       </c>
       <c r="F93">
         <v>1969</v>
       </c>
       <c r="G93" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H93" t="s">
-        <v>164</v>
+        <v>190</v>
       </c>
       <c r="I93" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K93" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L93" t="s">
-        <v>314</v>
+        <v>24</v>
       </c>
       <c r="M93" s="3" t="s">
-        <v>454</v>
+        <v>403</v>
       </c>
     </row>
     <row r="94" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>455</v>
+        <v>404</v>
       </c>
       <c r="B94" t="s">
-        <v>459</v>
+        <v>405</v>
       </c>
       <c r="C94" t="s">
-        <v>458</v>
+        <v>406</v>
       </c>
       <c r="D94" t="s">
-        <v>458</v>
+        <v>406</v>
       </c>
       <c r="F94" s="5" t="s">
-        <v>460</v>
+        <v>407</v>
       </c>
       <c r="G94" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H94" t="s">
-        <v>457</v>
+        <v>408</v>
       </c>
       <c r="I94" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="L94" t="s">
-        <v>314</v>
+        <v>24</v>
       </c>
       <c r="M94" s="3" t="s">
-        <v>456</v>
+        <v>409</v>
       </c>
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>461</v>
+        <v>410</v>
       </c>
       <c r="B95" t="s">
-        <v>463</v>
+        <v>411</v>
       </c>
       <c r="C95" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D95" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E95" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F95">
         <v>1968</v>
       </c>
       <c r="G95" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H95" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I95" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L95" t="s">
-        <v>313</v>
+        <v>37</v>
       </c>
       <c r="M95" s="3" t="s">
-        <v>464</v>
+        <v>412</v>
       </c>
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>462</v>
+        <v>413</v>
       </c>
       <c r="B96" t="s">
-        <v>465</v>
+        <v>414</v>
       </c>
       <c r="C96" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D96" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E96" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F96">
         <v>1969</v>
       </c>
       <c r="G96" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H96" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I96" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K96" t="s">
-        <v>196</v>
+        <v>222</v>
       </c>
       <c r="L96" t="s">
-        <v>313</v>
+        <v>37</v>
       </c>
       <c r="M96" s="3" t="s">
-        <v>466</v>
+        <v>415</v>
       </c>
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>467</v>
+        <v>416</v>
       </c>
       <c r="B97" t="s">
-        <v>468</v>
+        <v>417</v>
       </c>
       <c r="F97">
         <v>1973</v>
       </c>
       <c r="G97" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I97" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="J97" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L97" t="s">
-        <v>314</v>
+        <v>24</v>
       </c>
       <c r="M97" s="3" t="s">
-        <v>469</v>
+        <v>418</v>
       </c>
       <c r="N97" t="s">
-        <v>470</v>
+        <v>419</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="M15" r:id="rId1" xr:uid="{070CD713-285D-499E-AAF3-CA6E04F2E67D}"/>
-    <hyperlink ref="M16" r:id="rId2" xr:uid="{84CDC93C-1C17-4B8A-99AF-92002F858E35}"/>
-    <hyperlink ref="M17" r:id="rId3" xr:uid="{D28CC0D1-FF9B-45E5-8C06-32AA0A3E53A9}"/>
-    <hyperlink ref="M18" r:id="rId4" xr:uid="{B48EE935-D4BB-42A2-BD03-F7462BDAA973}"/>
-    <hyperlink ref="M19" r:id="rId5" xr:uid="{FC1907F3-06C3-44E2-85AA-D0706308A852}"/>
-    <hyperlink ref="M20" r:id="rId6" xr:uid="{FDA55CF4-B32E-4DB1-9DD2-2EFA7CF0ABA3}"/>
-    <hyperlink ref="M21" r:id="rId7" xr:uid="{7D576BEC-A372-4CAE-BF84-2F0963043CDC}"/>
-    <hyperlink ref="M22" r:id="rId8" xr:uid="{F23954CB-9B25-4B73-8617-4ADD50A0FE7D}"/>
-    <hyperlink ref="M24" r:id="rId9" xr:uid="{7A4658DA-5DD5-47F2-85C1-73F1BDE8C8F1}"/>
-    <hyperlink ref="M3" r:id="rId10" xr:uid="{049E9471-667A-44C7-B555-6B41CDEA4334}"/>
-    <hyperlink ref="M2" r:id="rId11" xr:uid="{A94FBB18-F767-4034-AB25-89E99187EDC8}"/>
-    <hyperlink ref="M4" r:id="rId12" xr:uid="{90B8B390-068D-4C88-BDE5-E99B638462B8}"/>
-    <hyperlink ref="M5" r:id="rId13" xr:uid="{01D903FA-154C-4673-BAA8-E8DA92B9B8EF}"/>
-    <hyperlink ref="M6" r:id="rId14" xr:uid="{682D036E-FC9A-4F6A-98CD-4CC91B1FB74F}"/>
-    <hyperlink ref="M7" r:id="rId15" xr:uid="{3F4DD620-2B56-494F-A792-A22FC9B8558D}"/>
-    <hyperlink ref="M8" r:id="rId16" xr:uid="{98CD4C7F-B63B-4FF7-9B9D-848EB9126C18}"/>
-    <hyperlink ref="M9" r:id="rId17" xr:uid="{21EFE2D2-97B6-4C85-A920-0CB2A7EC194D}"/>
-    <hyperlink ref="M10" r:id="rId18" xr:uid="{243006E2-0318-4FEE-83E6-AE585C338675}"/>
-    <hyperlink ref="M11" r:id="rId19" xr:uid="{1C7440C2-41CA-429B-80DC-4C69183A7CB9}"/>
-    <hyperlink ref="M12" r:id="rId20" xr:uid="{02E0AD7E-CEF6-4B6C-AB17-6CFDCF494509}"/>
-    <hyperlink ref="M13" r:id="rId21" xr:uid="{ABEF46E4-5EAF-4B10-9C40-A0B5F240E5BE}"/>
-    <hyperlink ref="M14" r:id="rId22" xr:uid="{B047393B-2E22-4ABF-A937-7D3E0B2FACB6}"/>
-    <hyperlink ref="M23" r:id="rId23" xr:uid="{A4B37D7B-D4FE-4B50-A01A-19BC8F084672}"/>
-    <hyperlink ref="M25" r:id="rId24" xr:uid="{46495F89-39F5-46CA-B3F0-960411F5BC3C}"/>
-    <hyperlink ref="M26" r:id="rId25" xr:uid="{5AD82D9D-0E76-446D-9312-7E6628A684B1}"/>
-    <hyperlink ref="M27" r:id="rId26" xr:uid="{C2001CED-BED9-4C03-B640-920A41146810}"/>
-    <hyperlink ref="M29" r:id="rId27" xr:uid="{DA89E417-4E4A-4547-B9AE-B031E332AA2A}"/>
-    <hyperlink ref="M28" r:id="rId28" xr:uid="{A051F0A1-FCEF-4CBB-9900-7D1A10FDEAE5}"/>
-    <hyperlink ref="M30" r:id="rId29" xr:uid="{D3924AA9-86C0-4DF6-B403-67F371618448}"/>
-    <hyperlink ref="M31" r:id="rId30" xr:uid="{FBF9CB2D-4BDE-4C09-A9B9-E188D6960A6D}"/>
-    <hyperlink ref="M32" r:id="rId31" xr:uid="{4BE15358-8230-40C1-9063-AA9B0E3B3CD2}"/>
-    <hyperlink ref="M33" r:id="rId32" xr:uid="{1F894DFD-3BA6-465A-AF03-CDD08322754B}"/>
-    <hyperlink ref="M34" r:id="rId33" xr:uid="{581D5573-91DC-48B0-B727-966BB2028F03}"/>
-    <hyperlink ref="M35" r:id="rId34" xr:uid="{A2BF5663-A951-44D0-8055-DEB448E680FA}"/>
-    <hyperlink ref="M36" r:id="rId35" xr:uid="{617F5B23-3270-413A-A61D-68FDD54E7A5D}"/>
-    <hyperlink ref="M58" r:id="rId36" xr:uid="{51AC1783-6AF1-44A4-B660-485062AF29AC}"/>
-    <hyperlink ref="M57" r:id="rId37" xr:uid="{FB7BD1A0-AC49-43FC-854E-AC6789AE027F}"/>
-    <hyperlink ref="M56" r:id="rId38" xr:uid="{39FD45C0-8BE5-49BB-820B-F4B1C9541F87}"/>
-    <hyperlink ref="M55" r:id="rId39" xr:uid="{7E342A29-2423-4FDD-810C-FE73FAB7AE34}"/>
-    <hyperlink ref="M54" r:id="rId40" xr:uid="{1E92ED11-F3F3-4DA7-9D48-EE7BC4656DBE}"/>
-    <hyperlink ref="M53" r:id="rId41" xr:uid="{23968C0E-AA65-46EC-BCA7-5E09457FFE21}"/>
-    <hyperlink ref="M52" r:id="rId42" xr:uid="{ECC4B67E-553A-48BB-AA46-D6D3B7E711A3}"/>
-    <hyperlink ref="M51" r:id="rId43" xr:uid="{EE7680E7-C97C-4D61-BAA2-B6338763FDC4}"/>
-    <hyperlink ref="M50" r:id="rId44" xr:uid="{F5DF849D-6410-4191-95D4-230AC66C7CA4}"/>
-    <hyperlink ref="M49" r:id="rId45" xr:uid="{503C1BAA-9ECB-4C41-80ED-8DC52510E0A4}"/>
-    <hyperlink ref="M48" r:id="rId46" xr:uid="{E8C1A178-DA4F-4B05-A76D-351144E0C9EE}"/>
-    <hyperlink ref="M47" r:id="rId47" xr:uid="{A39623B0-D279-45D6-85E1-31AB955D11CE}"/>
-    <hyperlink ref="M46" r:id="rId48" xr:uid="{83AE49A5-F427-4C3C-8E4E-242DC5D2A5AF}"/>
-    <hyperlink ref="M45" r:id="rId49" xr:uid="{EC0B0B03-23A7-4F85-9ED1-54CB0A297766}"/>
-    <hyperlink ref="M44" r:id="rId50" xr:uid="{31DB0E58-E325-4889-9CE7-6655563392AD}"/>
-    <hyperlink ref="M43" r:id="rId51" xr:uid="{7885CACE-875F-47AD-A333-D5F2BE7CB53A}"/>
-    <hyperlink ref="M42" r:id="rId52" xr:uid="{B6324CEB-644A-4010-9BEB-3901A9D50E96}"/>
-    <hyperlink ref="M41" r:id="rId53" xr:uid="{934B93F5-8138-42E6-80D5-481369F37014}"/>
-    <hyperlink ref="M40" r:id="rId54" xr:uid="{35BD77ED-E319-4F1A-A811-144D37AAB8D6}"/>
-    <hyperlink ref="M39" r:id="rId55" xr:uid="{AC96C58D-63A8-4720-903B-4B77FAE765E0}"/>
-    <hyperlink ref="M38" r:id="rId56" xr:uid="{AE5C737D-7C90-4D7C-873F-3C60101D039A}"/>
-    <hyperlink ref="M37" r:id="rId57" xr:uid="{B05C7093-7AA4-486E-ABD2-DF7A65B8D535}"/>
-    <hyperlink ref="M60" r:id="rId58" xr:uid="{C5EB4BB3-59E1-4C20-A245-98D06E913CD4}"/>
-    <hyperlink ref="M59" r:id="rId59" xr:uid="{FE9971B9-AD52-4DFF-86F3-668D687F4985}"/>
-    <hyperlink ref="M61" r:id="rId60" xr:uid="{84225D9C-CA52-466B-B2BD-B20C11AFA762}"/>
-    <hyperlink ref="M62" r:id="rId61" xr:uid="{7C0E21C7-5F11-4346-9647-7720BC7FADE0}"/>
-    <hyperlink ref="M63" r:id="rId62" xr:uid="{5EE44639-4FF3-43AB-A33E-7E859265AB4E}"/>
-    <hyperlink ref="M64" r:id="rId63" xr:uid="{5D3389C0-C71F-4CF3-93D8-DFF5AF7892D2}"/>
-    <hyperlink ref="M65" r:id="rId64" xr:uid="{705AEFBC-C508-48F1-BEC0-89DB7C3BD430}"/>
-    <hyperlink ref="M66" r:id="rId65" xr:uid="{8365E924-D46C-4D93-9FDD-E2A533CDCEF8}"/>
-    <hyperlink ref="M67" r:id="rId66" xr:uid="{9E0E6191-2474-42FA-BA40-68DA6CAC11D8}"/>
-    <hyperlink ref="M68" r:id="rId67" xr:uid="{7538D10C-1B89-41F2-8EF8-6C51156B9F3D}"/>
-    <hyperlink ref="M71" r:id="rId68" xr:uid="{992A5A10-6FA8-441D-9D96-1910EB939BD3}"/>
-    <hyperlink ref="M69" r:id="rId69" xr:uid="{006EA408-C0A6-4811-B052-83CF129EA2C0}"/>
-    <hyperlink ref="M90" r:id="rId70" xr:uid="{928D77CC-3AAA-4B77-AC03-61D687FF16B3}"/>
-    <hyperlink ref="M92" r:id="rId71" xr:uid="{45AC23F1-4EC4-4BAF-8049-0EFBB684BA5C}"/>
-    <hyperlink ref="M72" r:id="rId72" xr:uid="{C7350187-B80D-4F0F-9164-990486FA3ADE}"/>
-    <hyperlink ref="M73" r:id="rId73" xr:uid="{4AD25FBC-7B54-479D-8684-9ED95A508D3C}"/>
-    <hyperlink ref="M74" r:id="rId74" xr:uid="{6422EBC7-589E-44E2-96BD-306A215E30A6}"/>
-    <hyperlink ref="M75" r:id="rId75" xr:uid="{A3070D3B-90C9-499E-BD98-EACA481ED14E}"/>
-    <hyperlink ref="M76" r:id="rId76" xr:uid="{808FAF65-7C15-4E6A-9F54-14CA6A450A96}"/>
-    <hyperlink ref="M77" r:id="rId77" xr:uid="{1DCE5792-408E-469A-8742-17FE6E620712}"/>
-    <hyperlink ref="M78" r:id="rId78" xr:uid="{E33F0CDF-648A-446F-970E-C441D4A5FA6B}"/>
-    <hyperlink ref="M79" r:id="rId79" xr:uid="{FDF98D3A-2BDF-4222-9515-D396FE754728}"/>
-    <hyperlink ref="M80" r:id="rId80" xr:uid="{09F70555-E46E-46FA-8E11-BD505AFF380C}"/>
-    <hyperlink ref="M81" r:id="rId81" xr:uid="{B1CF9F07-1CC5-482D-9B20-938BDAE84FC4}"/>
-    <hyperlink ref="M82" r:id="rId82" xr:uid="{9B9C0FBA-9DA3-44F6-B651-2C6DEE7D8C97}"/>
-    <hyperlink ref="M83" r:id="rId83" xr:uid="{90142248-2915-4038-B9C7-282968CDDAD5}"/>
-    <hyperlink ref="M84" r:id="rId84" xr:uid="{095EBA0A-5F28-4E5A-AF60-AC6DAD8CC4E1}"/>
-    <hyperlink ref="M85" r:id="rId85" xr:uid="{91F4EEAE-C2CF-4DCA-BCB5-FF47689B42B2}"/>
-    <hyperlink ref="M86" r:id="rId86" xr:uid="{C98C421D-3FFF-4959-B494-99F2D5BF189F}"/>
-    <hyperlink ref="M87" r:id="rId87" xr:uid="{2DCC8DBF-33F4-4246-9B50-8489F6E17A99}"/>
-    <hyperlink ref="M88" r:id="rId88" xr:uid="{4D72D9B5-0915-4B7E-9F96-6275A944EE54}"/>
-    <hyperlink ref="M89" r:id="rId89" xr:uid="{8D9593CC-1AC6-4151-A7F0-9E914C39EEA1}"/>
-    <hyperlink ref="M91" r:id="rId90" xr:uid="{734F4C0D-ECE0-4D17-AED2-596C8405BA52}"/>
-    <hyperlink ref="M70" r:id="rId91" xr:uid="{410C497E-B7A6-4A52-BDB5-CD7FDB43C527}"/>
-    <hyperlink ref="M93" r:id="rId92" xr:uid="{A1560D73-B423-4F16-8BB5-470F2068279E}"/>
-    <hyperlink ref="M94" r:id="rId93" xr:uid="{5C1389EE-7B8E-4CE1-AD67-A06B346AE661}"/>
-    <hyperlink ref="M95" r:id="rId94" xr:uid="{E6D09A0C-0E6C-4767-9502-C45CAD42E349}"/>
-    <hyperlink ref="M96" r:id="rId95" xr:uid="{3C030BC5-8750-46CD-A50B-E8D120B6AA4F}"/>
-    <hyperlink ref="M97" r:id="rId96" xr:uid="{CCEB970E-D5AA-46D9-977A-7634751F3020}"/>
+    <hyperlink ref="M2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="M3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="M4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="M5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="M6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="M7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="M8" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="M9" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="M10" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="M11" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="M12" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="M13" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="M14" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="M15" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="M16" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="M17" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="M18" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="M19" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="M20" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="M21" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="M22" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="M23" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="M24" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="M25" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="M26" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="M27" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="M28" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="M29" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="M30" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="M31" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="M32" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="M33" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="M34" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="M35" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="M36" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="M37" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="M38" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="M39" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="M40" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="M41" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="M42" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="M43" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="M44" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="M45" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="M46" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="M47" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="M48" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="M49" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="M50" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="M51" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="M52" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="M53" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="M54" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="M55" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="M56" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="M57" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="M58" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="M59" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="M60" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="M61" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="M62" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="M63" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="M64" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="M65" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="M66" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="M67" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="M68" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="M69" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="M70" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="M71" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="M72" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="M73" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
+    <hyperlink ref="M74" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="M75" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="M76" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="M77" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="M78" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="M79" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
+    <hyperlink ref="M80" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="M81" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="M82" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="M83" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
+    <hyperlink ref="M84" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="M85" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
+    <hyperlink ref="M86" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="M87" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="M88" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="M89" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
+    <hyperlink ref="M90" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="M91" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
+    <hyperlink ref="M92" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="M93" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
+    <hyperlink ref="M94" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="M95" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
+    <hyperlink ref="M96" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
+    <hyperlink ref="M97" r:id="rId96" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -5311,235 +5724,718 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:R18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.6640625" customWidth="1"/>
-    <col min="2" max="5" width="10.6640625" customWidth="1"/>
+    <col min="1" max="1" width="12.77734375" customWidth="1"/>
+    <col min="3" max="3" width="13.5546875" customWidth="1"/>
+    <col min="4" max="4" width="4.21875" customWidth="1"/>
+    <col min="5" max="5" width="16.6640625" customWidth="1"/>
+    <col min="6" max="6" width="10.6640625" customWidth="1"/>
+    <col min="8" max="10" width="10.6640625" customWidth="1"/>
+    <col min="12" max="12" width="15" customWidth="1"/>
+    <col min="13" max="13" width="18" customWidth="1"/>
+    <col min="14" max="18" width="14" customWidth="1"/>
+    <col min="21" max="21" width="18" customWidth="1"/>
+    <col min="22" max="22" width="14" customWidth="1"/>
+    <col min="23" max="23" width="17" customWidth="1"/>
+    <col min="24" max="24" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>253</v>
-      </c>
-      <c r="B1" t="s">
-        <v>254</v>
-      </c>
-      <c r="C1" t="s">
-        <v>255</v>
-      </c>
-      <c r="D1" t="s">
-        <v>256</v>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A1" s="10" t="s">
+        <v>425</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>426</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>435</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>436</v>
       </c>
       <c r="E1" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+        <v>420</v>
+      </c>
+      <c r="F1" t="s">
+        <v>421</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>427</v>
+      </c>
+      <c r="H1" t="s">
+        <v>422</v>
+      </c>
+      <c r="I1" t="s">
+        <v>423</v>
+      </c>
+      <c r="J1" t="s">
+        <v>424</v>
+      </c>
+      <c r="K1" s="10" t="s">
+        <v>428</v>
+      </c>
+      <c r="L1" s="10" t="s">
+        <v>429</v>
+      </c>
+      <c r="M1" s="10" t="s">
+        <v>430</v>
+      </c>
+      <c r="N1" s="10" t="s">
+        <v>431</v>
+      </c>
+      <c r="O1" s="10" t="s">
+        <v>432</v>
+      </c>
+      <c r="P1" s="10" t="s">
+        <v>433</v>
+      </c>
+      <c r="Q1" s="10" t="s">
+        <v>434</v>
+      </c>
+      <c r="R1" s="10" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>440</v>
       </c>
       <c r="B2" t="s">
-        <v>258</v>
-      </c>
-      <c r="C2">
+        <v>441</v>
+      </c>
+      <c r="C2" t="s">
+        <v>445</v>
+      </c>
+      <c r="D2" t="s">
+        <v>446</v>
+      </c>
+      <c r="E2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" t="s">
+        <v>438</v>
+      </c>
+      <c r="G2" t="s">
+        <v>593</v>
+      </c>
+      <c r="H2">
         <v>1893</v>
       </c>
-      <c r="D2">
+      <c r="I2">
         <v>1976</v>
       </c>
-      <c r="E2" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="J2" t="s">
+        <v>439</v>
+      </c>
+      <c r="O2" t="s">
+        <v>442</v>
+      </c>
+      <c r="P2" t="s">
+        <v>443</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>444</v>
+      </c>
+      <c r="R2" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>260</v>
+        <v>451</v>
       </c>
       <c r="B3" t="s">
-        <v>261</v>
-      </c>
-      <c r="C3">
+        <v>441</v>
+      </c>
+      <c r="C3" t="s">
+        <v>445</v>
+      </c>
+      <c r="D3" t="s">
+        <v>446</v>
+      </c>
+      <c r="E3" t="s">
+        <v>448</v>
+      </c>
+      <c r="F3" t="s">
+        <v>449</v>
+      </c>
+      <c r="H3">
         <v>1921</v>
       </c>
-      <c r="D3">
+      <c r="I3">
         <v>1993</v>
       </c>
-      <c r="E3" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="J3" t="s">
+        <v>450</v>
+      </c>
+      <c r="O3" t="s">
+        <v>442</v>
+      </c>
+      <c r="P3" t="s">
+        <v>443</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>444</v>
+      </c>
+      <c r="R3" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>240</v>
+        <v>454</v>
       </c>
       <c r="B4" t="s">
-        <v>263</v>
-      </c>
-      <c r="C4">
+        <v>441</v>
+      </c>
+      <c r="C4" t="s">
+        <v>445</v>
+      </c>
+      <c r="D4" t="s">
+        <v>446</v>
+      </c>
+      <c r="E4" t="s">
+        <v>267</v>
+      </c>
+      <c r="F4" t="s">
+        <v>452</v>
+      </c>
+      <c r="H4">
         <v>1938</v>
       </c>
-      <c r="D4">
+      <c r="I4">
         <v>2021</v>
       </c>
-      <c r="E4" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="J4" t="s">
+        <v>453</v>
+      </c>
+      <c r="O4" t="s">
+        <v>442</v>
+      </c>
+      <c r="P4" t="s">
+        <v>443</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>444</v>
+      </c>
+      <c r="R4" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>60</v>
+        <v>456</v>
       </c>
       <c r="B5" t="s">
-        <v>265</v>
-      </c>
-      <c r="C5">
+        <v>441</v>
+      </c>
+      <c r="C5" t="s">
+        <v>445</v>
+      </c>
+      <c r="D5" t="s">
+        <v>446</v>
+      </c>
+      <c r="E5" t="s">
+        <v>63</v>
+      </c>
+      <c r="F5" t="s">
+        <v>455</v>
+      </c>
+      <c r="H5">
         <v>1931</v>
       </c>
-      <c r="D5">
+      <c r="I5">
         <v>2005</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="O5" t="s">
+        <v>442</v>
+      </c>
+      <c r="P5" t="s">
+        <v>443</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>444</v>
+      </c>
+      <c r="R5" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>266</v>
+        <v>459</v>
       </c>
       <c r="B6" t="s">
-        <v>267</v>
-      </c>
-      <c r="C6">
+        <v>441</v>
+      </c>
+      <c r="C6" t="s">
+        <v>445</v>
+      </c>
+      <c r="D6" t="s">
+        <v>446</v>
+      </c>
+      <c r="E6" t="s">
+        <v>457</v>
+      </c>
+      <c r="F6" t="s">
+        <v>458</v>
+      </c>
+      <c r="H6">
         <v>1960</v>
       </c>
-      <c r="D6">
+      <c r="I6">
         <v>2023</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="O6" t="s">
+        <v>442</v>
+      </c>
+      <c r="P6" t="s">
+        <v>443</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>444</v>
+      </c>
+      <c r="R6" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>146</v>
+        <v>461</v>
       </c>
       <c r="B7" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+        <v>441</v>
+      </c>
+      <c r="C7" t="s">
+        <v>445</v>
+      </c>
+      <c r="D7" t="s">
+        <v>446</v>
+      </c>
+      <c r="E7" t="s">
+        <v>171</v>
+      </c>
+      <c r="F7" t="s">
+        <v>460</v>
+      </c>
+      <c r="O7" t="s">
+        <v>442</v>
+      </c>
+      <c r="P7" t="s">
+        <v>443</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>444</v>
+      </c>
+      <c r="R7" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>269</v>
+        <v>465</v>
       </c>
       <c r="B8" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+        <v>441</v>
+      </c>
+      <c r="C8" t="s">
+        <v>445</v>
+      </c>
+      <c r="D8" t="s">
+        <v>446</v>
+      </c>
+      <c r="E8" t="s">
+        <v>463</v>
+      </c>
+      <c r="F8" t="s">
+        <v>464</v>
+      </c>
+      <c r="O8" t="s">
+        <v>442</v>
+      </c>
+      <c r="P8" t="s">
+        <v>443</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>444</v>
+      </c>
+      <c r="R8" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>271</v>
+        <v>468</v>
       </c>
       <c r="B9" t="s">
-        <v>272</v>
-      </c>
-      <c r="C9">
+        <v>441</v>
+      </c>
+      <c r="C9" t="s">
+        <v>445</v>
+      </c>
+      <c r="D9" t="s">
+        <v>446</v>
+      </c>
+      <c r="E9" t="s">
+        <v>466</v>
+      </c>
+      <c r="F9" t="s">
+        <v>467</v>
+      </c>
+      <c r="G9" t="s">
+        <v>594</v>
+      </c>
+      <c r="H9">
         <v>1907</v>
       </c>
-      <c r="D9">
+      <c r="I9">
         <v>1971</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="O9" t="s">
+        <v>442</v>
+      </c>
+      <c r="P9" t="s">
+        <v>443</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>444</v>
+      </c>
+      <c r="R9" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>273</v>
+        <v>471</v>
       </c>
       <c r="B10" t="s">
-        <v>274</v>
-      </c>
-      <c r="C10">
+        <v>441</v>
+      </c>
+      <c r="C10" t="s">
+        <v>445</v>
+      </c>
+      <c r="D10" t="s">
+        <v>446</v>
+      </c>
+      <c r="E10" t="s">
+        <v>469</v>
+      </c>
+      <c r="F10" t="s">
+        <v>470</v>
+      </c>
+      <c r="H10">
         <v>1898</v>
       </c>
-      <c r="D10">
+      <c r="I10">
         <v>1975</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="O10" t="s">
+        <v>442</v>
+      </c>
+      <c r="P10" t="s">
+        <v>443</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>444</v>
+      </c>
+      <c r="R10" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>275</v>
+        <v>474</v>
       </c>
       <c r="B11" t="s">
-        <v>276</v>
-      </c>
-      <c r="C11">
+        <v>441</v>
+      </c>
+      <c r="C11" t="s">
+        <v>445</v>
+      </c>
+      <c r="D11" t="s">
+        <v>446</v>
+      </c>
+      <c r="E11" t="s">
+        <v>472</v>
+      </c>
+      <c r="F11" t="s">
+        <v>473</v>
+      </c>
+      <c r="H11">
         <v>1898</v>
       </c>
-      <c r="D11">
+      <c r="I11">
         <v>1976</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="O11" t="s">
+        <v>442</v>
+      </c>
+      <c r="P11" t="s">
+        <v>443</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>444</v>
+      </c>
+      <c r="R11" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>277</v>
+        <v>477</v>
       </c>
       <c r="B12" t="s">
-        <v>278</v>
-      </c>
-      <c r="C12">
+        <v>441</v>
+      </c>
+      <c r="C12" t="s">
+        <v>445</v>
+      </c>
+      <c r="D12" t="s">
+        <v>446</v>
+      </c>
+      <c r="E12" t="s">
+        <v>475</v>
+      </c>
+      <c r="F12" t="s">
+        <v>476</v>
+      </c>
+      <c r="H12">
         <v>1904</v>
       </c>
-      <c r="D12">
+      <c r="I12">
         <v>1989</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="O12" t="s">
+        <v>442</v>
+      </c>
+      <c r="P12" t="s">
+        <v>443</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>444</v>
+      </c>
+      <c r="R12" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>279</v>
+        <v>480</v>
       </c>
       <c r="B13" t="s">
-        <v>280</v>
-      </c>
-      <c r="C13">
+        <v>441</v>
+      </c>
+      <c r="C13" t="s">
+        <v>445</v>
+      </c>
+      <c r="D13" t="s">
+        <v>446</v>
+      </c>
+      <c r="E13" t="s">
+        <v>478</v>
+      </c>
+      <c r="F13" t="s">
+        <v>479</v>
+      </c>
+      <c r="H13">
         <v>1914</v>
       </c>
-      <c r="D13">
+      <c r="I13">
         <v>1991</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="O13" t="s">
+        <v>442</v>
+      </c>
+      <c r="P13" t="s">
+        <v>443</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>444</v>
+      </c>
+      <c r="R13" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>281</v>
+        <v>483</v>
       </c>
       <c r="B14" t="s">
-        <v>282</v>
-      </c>
-      <c r="C14">
+        <v>441</v>
+      </c>
+      <c r="C14" t="s">
+        <v>445</v>
+      </c>
+      <c r="D14" t="s">
+        <v>446</v>
+      </c>
+      <c r="E14" t="s">
+        <v>481</v>
+      </c>
+      <c r="F14" t="s">
+        <v>482</v>
+      </c>
+      <c r="H14">
         <v>1920</v>
       </c>
-      <c r="D14">
+      <c r="I14">
         <v>2004</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="O14" t="s">
+        <v>442</v>
+      </c>
+      <c r="P14" t="s">
+        <v>443</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>444</v>
+      </c>
+      <c r="R14" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>195</v>
+        <v>485</v>
       </c>
       <c r="B15" t="s">
-        <v>283</v>
-      </c>
-      <c r="C15">
+        <v>441</v>
+      </c>
+      <c r="C15" t="s">
+        <v>445</v>
+      </c>
+      <c r="D15" t="s">
+        <v>446</v>
+      </c>
+      <c r="E15" t="s">
+        <v>221</v>
+      </c>
+      <c r="F15" t="s">
+        <v>484</v>
+      </c>
+      <c r="H15">
         <v>1920</v>
       </c>
-      <c r="D15">
+      <c r="I15">
         <v>1997</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="O15" t="s">
+        <v>442</v>
+      </c>
+      <c r="P15" t="s">
+        <v>443</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>444</v>
+      </c>
+      <c r="R15" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>317</v>
+        <v>487</v>
       </c>
       <c r="B16" t="s">
-        <v>323</v>
-      </c>
-      <c r="C16">
+        <v>441</v>
+      </c>
+      <c r="C16" t="s">
+        <v>445</v>
+      </c>
+      <c r="D16" t="s">
+        <v>446</v>
+      </c>
+      <c r="E16" t="s">
+        <v>291</v>
+      </c>
+      <c r="F16" t="s">
+        <v>486</v>
+      </c>
+      <c r="G16" t="s">
+        <v>595</v>
+      </c>
+      <c r="H16">
         <v>1898</v>
       </c>
-      <c r="D16">
+      <c r="I16">
         <v>1969</v>
+      </c>
+      <c r="O16" t="s">
+        <v>442</v>
+      </c>
+      <c r="P16" t="s">
+        <v>443</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>444</v>
+      </c>
+      <c r="R16" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>489</v>
+      </c>
+      <c r="B17" t="s">
+        <v>441</v>
+      </c>
+      <c r="C17" t="s">
+        <v>445</v>
+      </c>
+      <c r="D17" t="s">
+        <v>446</v>
+      </c>
+      <c r="E17" t="s">
+        <v>284</v>
+      </c>
+      <c r="F17" t="s">
+        <v>488</v>
+      </c>
+      <c r="O17" t="s">
+        <v>442</v>
+      </c>
+      <c r="P17" t="s">
+        <v>443</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>444</v>
+      </c>
+      <c r="R17" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>492</v>
+      </c>
+      <c r="B18" t="s">
+        <v>441</v>
+      </c>
+      <c r="C18" t="s">
+        <v>445</v>
+      </c>
+      <c r="D18" t="s">
+        <v>446</v>
+      </c>
+      <c r="E18" t="s">
+        <v>292</v>
+      </c>
+      <c r="F18" t="s">
+        <v>491</v>
+      </c>
+      <c r="O18" t="s">
+        <v>442</v>
+      </c>
+      <c r="P18" t="s">
+        <v>443</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>444</v>
+      </c>
+      <c r="R18" t="s">
+        <v>493</v>
       </c>
     </row>
   </sheetData>
@@ -5552,324 +6448,1101 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:R29"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="50.33203125" customWidth="1"/>
-    <col min="2" max="5" width="10.6640625" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" customWidth="1"/>
+    <col min="2" max="2" width="6.33203125" customWidth="1"/>
+    <col min="3" max="3" width="12.88671875" customWidth="1"/>
+    <col min="4" max="4" width="4.109375" customWidth="1"/>
+    <col min="5" max="5" width="50.33203125" customWidth="1"/>
+    <col min="6" max="6" width="10.6640625" customWidth="1"/>
+    <col min="9" max="10" width="10.6640625" customWidth="1"/>
+    <col min="12" max="12" width="10.6640625" customWidth="1"/>
+    <col min="15" max="15" width="18" customWidth="1"/>
+    <col min="16" max="20" width="14" customWidth="1"/>
+    <col min="21" max="21" width="16" customWidth="1"/>
+    <col min="24" max="24" width="14" customWidth="1"/>
+    <col min="25" max="25" width="17" customWidth="1"/>
+    <col min="26" max="26" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A1" s="10" t="s">
+        <v>425</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>426</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>435</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>436</v>
+      </c>
+      <c r="E1" t="s">
+        <v>420</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>427</v>
+      </c>
+      <c r="G1" t="s">
+        <v>494</v>
+      </c>
+      <c r="H1" t="s">
+        <v>495</v>
+      </c>
+      <c r="I1" t="s">
+        <v>496</v>
+      </c>
+      <c r="J1" t="s">
+        <v>424</v>
+      </c>
+      <c r="K1" s="10" t="s">
+        <v>497</v>
+      </c>
+      <c r="L1" s="10" t="s">
+        <v>429</v>
+      </c>
+      <c r="M1" s="10" t="s">
+        <v>430</v>
+      </c>
+      <c r="N1" s="10" t="s">
+        <v>431</v>
+      </c>
+      <c r="O1" s="10" t="s">
+        <v>432</v>
+      </c>
+      <c r="P1" s="10" t="s">
+        <v>433</v>
+      </c>
+      <c r="Q1" s="10" t="s">
+        <v>434</v>
+      </c>
+      <c r="R1" s="10" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>500</v>
+      </c>
+      <c r="B2" t="s">
+        <v>501</v>
+      </c>
+      <c r="C2" t="s">
+        <v>445</v>
+      </c>
+      <c r="D2" t="s">
+        <v>446</v>
+      </c>
+      <c r="E2" t="s">
+        <v>222</v>
+      </c>
+      <c r="G2" t="s">
+        <v>498</v>
+      </c>
+      <c r="H2">
+        <v>1962</v>
+      </c>
+      <c r="I2" t="s">
+        <v>499</v>
+      </c>
+      <c r="O2" t="s">
+        <v>442</v>
+      </c>
+      <c r="P2" t="s">
+        <v>443</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>444</v>
+      </c>
+      <c r="R2" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>504</v>
+      </c>
+      <c r="B3" t="s">
+        <v>501</v>
+      </c>
+      <c r="C3" t="s">
+        <v>445</v>
+      </c>
+      <c r="D3" t="s">
+        <v>446</v>
+      </c>
+      <c r="E3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" t="s">
+        <v>503</v>
+      </c>
+      <c r="H3">
+        <v>1952</v>
+      </c>
+      <c r="O3" t="s">
+        <v>442</v>
+      </c>
+      <c r="P3" t="s">
+        <v>443</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>444</v>
+      </c>
+      <c r="R3" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>506</v>
+      </c>
+      <c r="B4" t="s">
+        <v>501</v>
+      </c>
+      <c r="C4" t="s">
+        <v>445</v>
+      </c>
+      <c r="D4" t="s">
+        <v>446</v>
+      </c>
+      <c r="E4" t="s">
+        <v>102</v>
+      </c>
+      <c r="G4" t="s">
+        <v>503</v>
+      </c>
+      <c r="H4">
+        <v>1963</v>
+      </c>
+      <c r="I4">
+        <v>1979</v>
+      </c>
+      <c r="O4" t="s">
+        <v>442</v>
+      </c>
+      <c r="P4" t="s">
+        <v>443</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>444</v>
+      </c>
+      <c r="R4" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>508</v>
+      </c>
+      <c r="B5" t="s">
+        <v>501</v>
+      </c>
+      <c r="C5" t="s">
+        <v>445</v>
+      </c>
+      <c r="D5" t="s">
+        <v>446</v>
+      </c>
+      <c r="E5" t="s">
+        <v>77</v>
+      </c>
+      <c r="F5" t="s">
+        <v>509</v>
+      </c>
+      <c r="G5" t="s">
+        <v>507</v>
+      </c>
+      <c r="H5">
+        <v>1948</v>
+      </c>
+      <c r="O5" t="s">
+        <v>442</v>
+      </c>
+      <c r="P5" t="s">
+        <v>443</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>444</v>
+      </c>
+      <c r="R5" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>511</v>
+      </c>
+      <c r="B6" t="s">
+        <v>501</v>
+      </c>
+      <c r="C6" t="s">
+        <v>445</v>
+      </c>
+      <c r="D6" t="s">
+        <v>446</v>
+      </c>
+      <c r="E6" t="s">
+        <v>510</v>
+      </c>
+      <c r="F6" t="s">
+        <v>512</v>
+      </c>
+      <c r="G6" t="s">
+        <v>507</v>
+      </c>
+      <c r="H6">
+        <v>1958</v>
+      </c>
+      <c r="I6">
+        <v>1998</v>
+      </c>
+      <c r="O6" t="s">
+        <v>442</v>
+      </c>
+      <c r="P6" t="s">
+        <v>443</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>444</v>
+      </c>
+      <c r="R6" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>513</v>
+      </c>
+      <c r="B7" t="s">
+        <v>501</v>
+      </c>
+      <c r="C7" t="s">
+        <v>445</v>
+      </c>
+      <c r="D7" t="s">
+        <v>446</v>
+      </c>
+      <c r="E7" t="s">
+        <v>84</v>
+      </c>
+      <c r="G7" t="s">
+        <v>507</v>
+      </c>
+      <c r="H7">
+        <v>1964</v>
+      </c>
+      <c r="I7">
+        <v>1991</v>
+      </c>
+      <c r="O7" t="s">
+        <v>442</v>
+      </c>
+      <c r="P7" t="s">
+        <v>443</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>444</v>
+      </c>
+      <c r="R7" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>515</v>
+      </c>
+      <c r="B8" t="s">
+        <v>501</v>
+      </c>
+      <c r="C8" t="s">
+        <v>445</v>
+      </c>
+      <c r="D8" t="s">
+        <v>446</v>
+      </c>
+      <c r="E8" t="s">
+        <v>514</v>
+      </c>
+      <c r="F8" t="s">
+        <v>516</v>
+      </c>
+      <c r="G8" t="s">
+        <v>507</v>
+      </c>
+      <c r="H8">
+        <v>1956</v>
+      </c>
+      <c r="O8" t="s">
+        <v>442</v>
+      </c>
+      <c r="P8" t="s">
+        <v>443</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>444</v>
+      </c>
+      <c r="R8" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>518</v>
+      </c>
+      <c r="B9" t="s">
+        <v>501</v>
+      </c>
+      <c r="C9" t="s">
+        <v>445</v>
+      </c>
+      <c r="D9" t="s">
+        <v>446</v>
+      </c>
+      <c r="E9" t="s">
+        <v>120</v>
+      </c>
+      <c r="G9" t="s">
+        <v>517</v>
+      </c>
+      <c r="O9" t="s">
+        <v>442</v>
+      </c>
+      <c r="P9" t="s">
+        <v>443</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>444</v>
+      </c>
+      <c r="R9" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>521</v>
+      </c>
+      <c r="B10" t="s">
+        <v>501</v>
+      </c>
+      <c r="C10" t="s">
+        <v>445</v>
+      </c>
+      <c r="D10" t="s">
+        <v>446</v>
+      </c>
+      <c r="E10" t="s">
+        <v>68</v>
+      </c>
+      <c r="G10" t="s">
+        <v>520</v>
+      </c>
+      <c r="H10">
+        <v>1966</v>
+      </c>
+      <c r="I10">
+        <v>1991</v>
+      </c>
+      <c r="O10" t="s">
+        <v>442</v>
+      </c>
+      <c r="P10" t="s">
+        <v>443</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>444</v>
+      </c>
+      <c r="R10" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>522</v>
+      </c>
+      <c r="B11" t="s">
+        <v>501</v>
+      </c>
+      <c r="C11" t="s">
+        <v>445</v>
+      </c>
+      <c r="D11" t="s">
+        <v>446</v>
+      </c>
+      <c r="E11" t="s">
+        <v>96</v>
+      </c>
+      <c r="G11" t="s">
+        <v>520</v>
+      </c>
+      <c r="H11">
+        <v>1968</v>
+      </c>
+      <c r="I11">
+        <v>1972</v>
+      </c>
+      <c r="O11" t="s">
+        <v>442</v>
+      </c>
+      <c r="P11" t="s">
+        <v>443</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>444</v>
+      </c>
+      <c r="R11" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>524</v>
+      </c>
+      <c r="B12" t="s">
+        <v>501</v>
+      </c>
+      <c r="C12" t="s">
+        <v>445</v>
+      </c>
+      <c r="D12" t="s">
+        <v>446</v>
+      </c>
+      <c r="E12" t="s">
+        <v>523</v>
+      </c>
+      <c r="G12" t="s">
+        <v>520</v>
+      </c>
+      <c r="H12">
+        <v>1966</v>
+      </c>
+      <c r="I12">
+        <v>1991</v>
+      </c>
+      <c r="O12" t="s">
+        <v>442</v>
+      </c>
+      <c r="P12" t="s">
+        <v>443</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>444</v>
+      </c>
+      <c r="R12" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>525</v>
+      </c>
+      <c r="B13" t="s">
+        <v>501</v>
+      </c>
+      <c r="C13" t="s">
+        <v>445</v>
+      </c>
+      <c r="D13" t="s">
+        <v>446</v>
+      </c>
+      <c r="E13" t="s">
+        <v>202</v>
+      </c>
+      <c r="G13" t="s">
+        <v>520</v>
+      </c>
+      <c r="H13">
+        <v>1921</v>
+      </c>
+      <c r="O13" t="s">
+        <v>442</v>
+      </c>
+      <c r="P13" t="s">
+        <v>443</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>444</v>
+      </c>
+      <c r="R13" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>528</v>
+      </c>
+      <c r="B14" t="s">
+        <v>501</v>
+      </c>
+      <c r="C14" t="s">
+        <v>445</v>
+      </c>
+      <c r="D14" t="s">
+        <v>446</v>
+      </c>
+      <c r="E14" t="s">
+        <v>67</v>
+      </c>
+      <c r="F14" t="s">
+        <v>529</v>
+      </c>
+      <c r="G14" t="s">
+        <v>526</v>
+      </c>
+      <c r="H14">
+        <v>1966</v>
+      </c>
+      <c r="I14">
+        <v>1991</v>
+      </c>
+      <c r="J14" t="s">
+        <v>527</v>
+      </c>
+      <c r="O14" t="s">
+        <v>442</v>
+      </c>
+      <c r="P14" t="s">
+        <v>443</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>444</v>
+      </c>
+      <c r="R14" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>531</v>
+      </c>
+      <c r="B15" t="s">
+        <v>501</v>
+      </c>
+      <c r="C15" t="s">
+        <v>445</v>
+      </c>
+      <c r="D15" t="s">
+        <v>446</v>
+      </c>
+      <c r="E15" t="s">
+        <v>95</v>
+      </c>
+      <c r="F15" t="s">
+        <v>532</v>
+      </c>
+      <c r="G15" t="s">
+        <v>526</v>
+      </c>
+      <c r="H15">
+        <v>1968</v>
+      </c>
+      <c r="I15">
+        <v>1972</v>
+      </c>
+      <c r="J15" t="s">
+        <v>530</v>
+      </c>
+      <c r="O15" t="s">
+        <v>442</v>
+      </c>
+      <c r="P15" t="s">
+        <v>443</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>444</v>
+      </c>
+      <c r="R15" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>534</v>
+      </c>
+      <c r="B16" t="s">
+        <v>501</v>
+      </c>
+      <c r="C16" t="s">
+        <v>445</v>
+      </c>
+      <c r="D16" t="s">
+        <v>446</v>
+      </c>
+      <c r="E16" t="s">
+        <v>18</v>
+      </c>
+      <c r="F16" t="s">
+        <v>535</v>
+      </c>
+      <c r="G16" t="s">
+        <v>526</v>
+      </c>
+      <c r="H16">
+        <v>1921</v>
+      </c>
+      <c r="J16" t="s">
+        <v>533</v>
+      </c>
+      <c r="O16" t="s">
+        <v>442</v>
+      </c>
+      <c r="P16" t="s">
+        <v>443</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>444</v>
+      </c>
+      <c r="R16" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>537</v>
+      </c>
+      <c r="B17" t="s">
+        <v>501</v>
+      </c>
+      <c r="C17" t="s">
+        <v>445</v>
+      </c>
+      <c r="D17" t="s">
+        <v>446</v>
+      </c>
+      <c r="E17" t="s">
+        <v>536</v>
+      </c>
+      <c r="G17" t="s">
+        <v>526</v>
+      </c>
+      <c r="H17">
+        <v>1968</v>
+      </c>
+      <c r="I17">
+        <v>1969</v>
+      </c>
+      <c r="O17" t="s">
+        <v>442</v>
+      </c>
+      <c r="P17" t="s">
+        <v>443</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>444</v>
+      </c>
+      <c r="R17" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>538</v>
+      </c>
+      <c r="B18" t="s">
+        <v>501</v>
+      </c>
+      <c r="C18" t="s">
+        <v>445</v>
+      </c>
+      <c r="D18" t="s">
+        <v>446</v>
+      </c>
+      <c r="E18" t="s">
+        <v>169</v>
+      </c>
+      <c r="G18" t="s">
+        <v>526</v>
+      </c>
+      <c r="H18">
+        <v>1969</v>
+      </c>
+      <c r="I18">
+        <v>1976</v>
+      </c>
+      <c r="O18" t="s">
+        <v>442</v>
+      </c>
+      <c r="P18" t="s">
+        <v>443</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>444</v>
+      </c>
+      <c r="R18" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>540</v>
+      </c>
+      <c r="B19" t="s">
+        <v>501</v>
+      </c>
+      <c r="C19" t="s">
+        <v>445</v>
+      </c>
+      <c r="D19" t="s">
+        <v>446</v>
+      </c>
+      <c r="E19" t="s">
         <v>253</v>
       </c>
-      <c r="B1" t="s">
-        <v>284</v>
-      </c>
-      <c r="C1" t="s">
-        <v>285</v>
-      </c>
-      <c r="D1" t="s">
-        <v>286</v>
-      </c>
-      <c r="E1" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>196</v>
-      </c>
-      <c r="B2" t="s">
-        <v>287</v>
-      </c>
-      <c r="C2">
-        <v>1962</v>
-      </c>
-      <c r="D2" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" t="s">
-        <v>289</v>
-      </c>
-      <c r="C3">
-        <v>1952</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>99</v>
-      </c>
-      <c r="B4" t="s">
-        <v>289</v>
-      </c>
-      <c r="C4">
-        <v>1963</v>
-      </c>
-      <c r="D4">
-        <v>1979</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>74</v>
-      </c>
-      <c r="B5" t="s">
-        <v>290</v>
-      </c>
-      <c r="C5">
-        <v>1948</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>291</v>
-      </c>
-      <c r="B6" t="s">
-        <v>290</v>
-      </c>
-      <c r="C6">
-        <v>1958</v>
-      </c>
-      <c r="D6">
-        <v>1998</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>81</v>
-      </c>
-      <c r="B7" t="s">
-        <v>290</v>
-      </c>
-      <c r="C7">
-        <v>1964</v>
-      </c>
-      <c r="D7">
-        <v>1991</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>292</v>
-      </c>
-      <c r="B8" t="s">
-        <v>290</v>
-      </c>
-      <c r="C8">
-        <v>1956</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>115</v>
-      </c>
-      <c r="B9" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>65</v>
-      </c>
-      <c r="B10" t="s">
-        <v>294</v>
-      </c>
-      <c r="C10">
-        <v>1966</v>
-      </c>
-      <c r="D10">
-        <v>1991</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>93</v>
-      </c>
-      <c r="B11" t="s">
-        <v>294</v>
-      </c>
-      <c r="C11">
+      <c r="G19" t="s">
+        <v>526</v>
+      </c>
+      <c r="H19">
         <v>1968</v>
       </c>
-      <c r="D11">
+      <c r="I19" t="s">
+        <v>539</v>
+      </c>
+      <c r="O19" t="s">
+        <v>442</v>
+      </c>
+      <c r="P19" t="s">
+        <v>443</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>444</v>
+      </c>
+      <c r="R19" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>542</v>
+      </c>
+      <c r="B20" t="s">
+        <v>501</v>
+      </c>
+      <c r="C20" t="s">
+        <v>445</v>
+      </c>
+      <c r="D20" t="s">
+        <v>446</v>
+      </c>
+      <c r="E20" t="s">
+        <v>259</v>
+      </c>
+      <c r="F20" t="s">
+        <v>543</v>
+      </c>
+      <c r="G20" t="s">
+        <v>526</v>
+      </c>
+      <c r="H20">
         <v>1972</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>295</v>
-      </c>
-      <c r="B12" t="s">
-        <v>294</v>
-      </c>
-      <c r="C12">
-        <v>1966</v>
-      </c>
-      <c r="D12">
-        <v>1991</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>176</v>
-      </c>
-      <c r="B13" t="s">
-        <v>294</v>
-      </c>
-      <c r="C13">
-        <v>1921</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>64</v>
-      </c>
-      <c r="B14" t="s">
-        <v>296</v>
-      </c>
-      <c r="C14">
-        <v>1966</v>
-      </c>
-      <c r="D14">
-        <v>1991</v>
-      </c>
-      <c r="E14" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>92</v>
-      </c>
-      <c r="B15" t="s">
-        <v>296</v>
-      </c>
-      <c r="C15">
-        <v>1968</v>
-      </c>
-      <c r="D15">
-        <v>1972</v>
-      </c>
-      <c r="E15" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" t="s">
-        <v>296</v>
-      </c>
-      <c r="C16">
-        <v>1921</v>
-      </c>
-      <c r="E16" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>300</v>
-      </c>
-      <c r="B17" t="s">
-        <v>296</v>
-      </c>
-      <c r="C17">
-        <v>1968</v>
-      </c>
-      <c r="D17">
+      <c r="I20">
+        <v>1977</v>
+      </c>
+      <c r="O20" t="s">
+        <v>442</v>
+      </c>
+      <c r="P20" t="s">
+        <v>443</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>444</v>
+      </c>
+      <c r="R20" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>545</v>
+      </c>
+      <c r="B21" t="s">
+        <v>501</v>
+      </c>
+      <c r="C21" t="s">
+        <v>445</v>
+      </c>
+      <c r="D21" t="s">
+        <v>446</v>
+      </c>
+      <c r="E21" t="s">
+        <v>119</v>
+      </c>
+      <c r="G21" t="s">
+        <v>544</v>
+      </c>
+      <c r="H21">
+        <v>1967</v>
+      </c>
+      <c r="I21">
         <v>1969</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>144</v>
-      </c>
-      <c r="B18" t="s">
-        <v>296</v>
-      </c>
-      <c r="C18">
-        <v>1969</v>
-      </c>
-      <c r="D18">
-        <v>1976</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>227</v>
-      </c>
-      <c r="B19" t="s">
-        <v>296</v>
-      </c>
-      <c r="C19">
-        <v>1968</v>
-      </c>
-      <c r="D19" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>233</v>
-      </c>
-      <c r="B20" t="s">
-        <v>296</v>
-      </c>
-      <c r="C20">
-        <v>1972</v>
-      </c>
-      <c r="D20">
+      <c r="O21" t="s">
+        <v>442</v>
+      </c>
+      <c r="P21" t="s">
+        <v>443</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>444</v>
+      </c>
+      <c r="R21" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>546</v>
+      </c>
+      <c r="B22" t="s">
+        <v>501</v>
+      </c>
+      <c r="C22" t="s">
+        <v>445</v>
+      </c>
+      <c r="D22" t="s">
+        <v>446</v>
+      </c>
+      <c r="E22" t="s">
+        <v>263</v>
+      </c>
+      <c r="G22" t="s">
+        <v>526</v>
+      </c>
+      <c r="H22">
         <v>1977</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>114</v>
-      </c>
-      <c r="B21" t="s">
-        <v>302</v>
-      </c>
-      <c r="C21">
-        <v>1967</v>
-      </c>
-      <c r="D21">
-        <v>1969</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>237</v>
-      </c>
-      <c r="B22" t="s">
-        <v>296</v>
-      </c>
-      <c r="C22">
-        <v>1977</v>
-      </c>
-      <c r="D22">
+      <c r="I22">
         <v>1984</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="O22" t="s">
+        <v>442</v>
+      </c>
+      <c r="P22" t="s">
+        <v>443</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>444</v>
+      </c>
+      <c r="R22" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>391</v>
+        <v>547</v>
       </c>
       <c r="B23" t="s">
-        <v>293</v>
-      </c>
-      <c r="C23">
+        <v>501</v>
+      </c>
+      <c r="C23" t="s">
+        <v>445</v>
+      </c>
+      <c r="D23" t="s">
+        <v>446</v>
+      </c>
+      <c r="E23" t="s">
+        <v>328</v>
+      </c>
+      <c r="G23" t="s">
+        <v>517</v>
+      </c>
+      <c r="H23">
         <v>1970</v>
       </c>
-      <c r="D23">
+      <c r="I23">
         <v>1973</v>
+      </c>
+      <c r="O23" t="s">
+        <v>442</v>
+      </c>
+      <c r="P23" t="s">
+        <v>443</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>444</v>
+      </c>
+      <c r="R23" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>548</v>
+      </c>
+      <c r="B24" t="s">
+        <v>501</v>
+      </c>
+      <c r="C24" t="s">
+        <v>445</v>
+      </c>
+      <c r="D24" t="s">
+        <v>446</v>
+      </c>
+      <c r="E24" t="s">
+        <v>406</v>
+      </c>
+      <c r="O24" t="s">
+        <v>442</v>
+      </c>
+      <c r="P24" t="s">
+        <v>443</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>444</v>
+      </c>
+      <c r="R24" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>550</v>
+      </c>
+      <c r="B25" t="s">
+        <v>501</v>
+      </c>
+      <c r="C25" t="s">
+        <v>445</v>
+      </c>
+      <c r="D25" t="s">
+        <v>446</v>
+      </c>
+      <c r="E25" t="s">
+        <v>311</v>
+      </c>
+      <c r="F25" t="s">
+        <v>596</v>
+      </c>
+      <c r="O25" t="s">
+        <v>442</v>
+      </c>
+      <c r="P25" t="s">
+        <v>443</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>444</v>
+      </c>
+      <c r="R25" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>552</v>
+      </c>
+      <c r="B26" t="s">
+        <v>501</v>
+      </c>
+      <c r="C26" t="s">
+        <v>445</v>
+      </c>
+      <c r="D26" t="s">
+        <v>446</v>
+      </c>
+      <c r="E26" t="s">
+        <v>319</v>
+      </c>
+      <c r="O26" t="s">
+        <v>442</v>
+      </c>
+      <c r="P26" t="s">
+        <v>443</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>444</v>
+      </c>
+      <c r="R26" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>554</v>
+      </c>
+      <c r="B27" t="s">
+        <v>501</v>
+      </c>
+      <c r="C27" t="s">
+        <v>445</v>
+      </c>
+      <c r="D27" t="s">
+        <v>446</v>
+      </c>
+      <c r="E27" t="s">
+        <v>553</v>
+      </c>
+      <c r="O27" t="s">
+        <v>442</v>
+      </c>
+      <c r="P27" t="s">
+        <v>443</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>444</v>
+      </c>
+      <c r="R27" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>556</v>
+      </c>
+      <c r="B28" t="s">
+        <v>501</v>
+      </c>
+      <c r="C28" t="s">
+        <v>445</v>
+      </c>
+      <c r="D28" t="s">
+        <v>446</v>
+      </c>
+      <c r="E28" t="s">
+        <v>555</v>
+      </c>
+      <c r="O28" t="s">
+        <v>442</v>
+      </c>
+      <c r="P28" t="s">
+        <v>443</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>444</v>
+      </c>
+      <c r="R28" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>558</v>
+      </c>
+      <c r="B29" t="s">
+        <v>501</v>
+      </c>
+      <c r="C29" t="s">
+        <v>445</v>
+      </c>
+      <c r="D29" t="s">
+        <v>446</v>
+      </c>
+      <c r="E29" t="s">
+        <v>557</v>
+      </c>
+      <c r="O29" t="s">
+        <v>442</v>
+      </c>
+      <c r="P29" t="s">
+        <v>443</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>444</v>
+      </c>
+      <c r="R29" t="s">
+        <v>549</v>
       </c>
     </row>
   </sheetData>
@@ -5878,4 +7551,254 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:J8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="13" customWidth="1"/>
+    <col min="3" max="3" width="45" customWidth="1"/>
+    <col min="4" max="4" width="22" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="7" max="7" width="45" customWidth="1"/>
+    <col min="8" max="8" width="22" customWidth="1"/>
+    <col min="9" max="9" width="38" customWidth="1"/>
+    <col min="10" max="10" width="55" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" s="9" t="s">
+        <v>559</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>560</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>561</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>562</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>563</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>564</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>565</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>566</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>567</v>
+      </c>
+      <c r="J1" s="9" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>569</v>
+      </c>
+      <c r="B2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C2" t="s">
+        <v>448</v>
+      </c>
+      <c r="D2" t="s">
+        <v>570</v>
+      </c>
+      <c r="E2" t="s">
+        <v>571</v>
+      </c>
+      <c r="F2" t="s">
+        <v>528</v>
+      </c>
+      <c r="G2" t="s">
+        <v>67</v>
+      </c>
+      <c r="H2" t="s">
+        <v>572</v>
+      </c>
+      <c r="I2" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>574</v>
+      </c>
+      <c r="B3" t="s">
+        <v>454</v>
+      </c>
+      <c r="C3" t="s">
+        <v>267</v>
+      </c>
+      <c r="D3" t="s">
+        <v>575</v>
+      </c>
+      <c r="E3" t="s">
+        <v>576</v>
+      </c>
+      <c r="F3" t="s">
+        <v>528</v>
+      </c>
+      <c r="G3" t="s">
+        <v>67</v>
+      </c>
+      <c r="H3" t="s">
+        <v>577</v>
+      </c>
+      <c r="I3" t="s">
+        <v>578</v>
+      </c>
+      <c r="J3" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>580</v>
+      </c>
+      <c r="B4" t="s">
+        <v>440</v>
+      </c>
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" t="s">
+        <v>581</v>
+      </c>
+      <c r="E4" t="s">
+        <v>571</v>
+      </c>
+      <c r="F4" t="s">
+        <v>525</v>
+      </c>
+      <c r="G4" t="s">
+        <v>202</v>
+      </c>
+      <c r="H4" t="s">
+        <v>582</v>
+      </c>
+      <c r="I4" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>584</v>
+      </c>
+      <c r="B5" t="s">
+        <v>521</v>
+      </c>
+      <c r="C5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" t="s">
+        <v>585</v>
+      </c>
+      <c r="E5" t="s">
+        <v>571</v>
+      </c>
+      <c r="F5" t="s">
+        <v>528</v>
+      </c>
+      <c r="G5" t="s">
+        <v>67</v>
+      </c>
+      <c r="I5" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>587</v>
+      </c>
+      <c r="B6" t="s">
+        <v>522</v>
+      </c>
+      <c r="C6" t="s">
+        <v>96</v>
+      </c>
+      <c r="D6" t="s">
+        <v>588</v>
+      </c>
+      <c r="E6" t="s">
+        <v>571</v>
+      </c>
+      <c r="F6" t="s">
+        <v>531</v>
+      </c>
+      <c r="G6" t="s">
+        <v>95</v>
+      </c>
+      <c r="I6" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>589</v>
+      </c>
+      <c r="B7" t="s">
+        <v>525</v>
+      </c>
+      <c r="C7" t="s">
+        <v>202</v>
+      </c>
+      <c r="D7" t="s">
+        <v>585</v>
+      </c>
+      <c r="E7" t="s">
+        <v>571</v>
+      </c>
+      <c r="F7" t="s">
+        <v>534</v>
+      </c>
+      <c r="G7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I7" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>590</v>
+      </c>
+      <c r="B8" t="s">
+        <v>537</v>
+      </c>
+      <c r="C8" t="s">
+        <v>536</v>
+      </c>
+      <c r="D8" t="s">
+        <v>591</v>
+      </c>
+      <c r="E8" t="s">
+        <v>591</v>
+      </c>
+      <c r="F8" t="s">
+        <v>528</v>
+      </c>
+      <c r="G8" t="s">
+        <v>67</v>
+      </c>
+      <c r="I8" t="s">
+        <v>586</v>
+      </c>
+      <c r="J8" t="s">
+        <v>592</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/dati.xlsx
+++ b/data/dati.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan_\Desktop\AMI\GitHub\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AED86B4-DFDC-4228-B308-A0CDEED38F03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E302D8AB-518E-4E36-99EA-1D0B0B656F2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Catalogo" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,262 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1533" uniqueCount="597">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1511" uniqueCount="600">
+  <si>
+    <t>ID_autorita</t>
+  </si>
+  <si>
+    <t>Tipo_entita</t>
+  </si>
+  <si>
+    <t>Norme</t>
+  </si>
+  <si>
+    <t>Lingua_record</t>
+  </si>
+  <si>
+    <t>Nome</t>
+  </si>
+  <si>
+    <t>Cognome</t>
+  </si>
+  <si>
+    <t>Forme_varianti</t>
+  </si>
+  <si>
+    <t>Nascita</t>
+  </si>
+  <si>
+    <t>Morte</t>
+  </si>
+  <si>
+    <t>Immagine</t>
+  </si>
+  <si>
+    <t>Biografia</t>
+  </si>
+  <si>
+    <t>Luoghi</t>
+  </si>
+  <si>
+    <t>Wikidata</t>
+  </si>
+  <si>
+    <t>VIAF</t>
+  </si>
+  <si>
+    <t>Stato_record</t>
+  </si>
+  <si>
+    <t>Livello_dettaglio</t>
+  </si>
+  <si>
+    <t>Data_redazione</t>
+  </si>
+  <si>
+    <t>Note_redazionali</t>
+  </si>
+  <si>
+    <t>AMI-P-001</t>
+  </si>
+  <si>
+    <t>Persona</t>
+  </si>
+  <si>
+    <t>ISAAR(CPF), 2a ed., 2004</t>
+  </si>
+  <si>
+    <t>ita</t>
+  </si>
+  <si>
+    <t>Mao Zedong</t>
+  </si>
+  <si>
+    <t>Mao</t>
+  </si>
+  <si>
+    <t>Mao Tse-tung; Mao Tsetung</t>
+  </si>
+  <si>
+    <t>mao.webp</t>
+  </si>
+  <si>
+    <t>Bozza</t>
+  </si>
+  <si>
+    <t>Minimo</t>
+  </si>
+  <si>
+    <t>Biografia da redigere</t>
+  </si>
+  <si>
+    <t>AMI-P-002</t>
+  </si>
+  <si>
+    <t>Fosco Dinucci</t>
+  </si>
+  <si>
+    <t>Dinucci</t>
+  </si>
+  <si>
+    <t>dinucci.webp</t>
+  </si>
+  <si>
+    <t>AMI-P-003</t>
+  </si>
+  <si>
+    <t>Osvaldo Pesce</t>
+  </si>
+  <si>
+    <t>Pesce</t>
+  </si>
+  <si>
+    <t>pesce.webp</t>
+  </si>
+  <si>
+    <t>AMI-P-004</t>
+  </si>
+  <si>
+    <t>Yao Wenyuan</t>
+  </si>
+  <si>
+    <t>Yao</t>
+  </si>
+  <si>
+    <t>AMI-P-005</t>
+  </si>
+  <si>
+    <t>Roberto Sassi</t>
+  </si>
+  <si>
+    <t>Sassi</t>
+  </si>
+  <si>
+    <t>AMI-P-006</t>
+  </si>
+  <si>
+    <t>Vincenzo Calò</t>
+  </si>
+  <si>
+    <t>Calò</t>
+  </si>
+  <si>
+    <t>????</t>
+  </si>
+  <si>
+    <t>AMI-P-007</t>
+  </si>
+  <si>
+    <t>Dino Dini</t>
+  </si>
+  <si>
+    <t>Dini</t>
+  </si>
+  <si>
+    <t>AMI-P-008</t>
+  </si>
+  <si>
+    <t>Lin Biao</t>
+  </si>
+  <si>
+    <t>Lin</t>
+  </si>
+  <si>
+    <t>Lin Piao</t>
+  </si>
+  <si>
+    <t>AMI-P-009</t>
+  </si>
+  <si>
+    <t>Kang Sheng</t>
+  </si>
+  <si>
+    <t>Kang</t>
+  </si>
+  <si>
+    <t>AMI-P-010</t>
+  </si>
+  <si>
+    <t>Zhou Enlai</t>
+  </si>
+  <si>
+    <t>Zhou</t>
+  </si>
+  <si>
+    <t>Chou En-lai; Chou Enlai</t>
+  </si>
+  <si>
+    <t>AMI-P-011</t>
+  </si>
+  <si>
+    <t>Chen Boda</t>
+  </si>
+  <si>
+    <t>Chen</t>
+  </si>
+  <si>
+    <t>Chen Po-ta; Chen Pota</t>
+  </si>
+  <si>
+    <t>AMI-P-012</t>
+  </si>
+  <si>
+    <t>Jiang Qing</t>
+  </si>
+  <si>
+    <t>Jiang</t>
+  </si>
+  <si>
+    <t>Chiang Ching</t>
+  </si>
+  <si>
+    <t>AMI-P-013</t>
+  </si>
+  <si>
+    <t>Angiolo Gracci</t>
+  </si>
+  <si>
+    <t>Gracci</t>
+  </si>
+  <si>
+    <t>AMI-P-014</t>
+  </si>
+  <si>
+    <t>Giorgio Zucchetti</t>
+  </si>
+  <si>
+    <t>Zucchetti</t>
+  </si>
+  <si>
+    <t>AMI-P-015</t>
+  </si>
+  <si>
+    <t>Liu Shaoqi</t>
+  </si>
+  <si>
+    <t>Liu</t>
+  </si>
+  <si>
+    <t>Liu Shao-chi</t>
+  </si>
+  <si>
+    <t>AMI-P-016</t>
+  </si>
+  <si>
+    <t>Renzo Del Carria</t>
+  </si>
+  <si>
+    <t>Del Carria</t>
+  </si>
+  <si>
+    <t>AMI-P-017</t>
+  </si>
+  <si>
+    <t>Arnaldo Bressan</t>
+  </si>
+  <si>
+    <t>Bressan</t>
+  </si>
   <si>
     <t>ID</t>
   </si>
@@ -82,9 +337,6 @@
     <t>Partito Comunista Cinese</t>
   </si>
   <si>
-    <t>Mao Zedong</t>
-  </si>
-  <si>
     <t>Casa editrice in lingue estere</t>
   </si>
   <si>
@@ -214,9 +466,6 @@
     <t>La classe operaia deve esercitare la sua direzione in ogni campo</t>
   </si>
   <si>
-    <t>Yao Wenyuan</t>
-  </si>
-  <si>
     <t>https://archive.org/details/la-classe-operai-deve-esercitare-la-sua-direzione-in-ogni-cam/mode/2up</t>
   </si>
   <si>
@@ -313,7 +562,7 @@
     <t>Unione dei Comunisti Italiani (marxisti-leninisti)</t>
   </si>
   <si>
-    <t>Comitato di Partito di Catania (UCI-m.l)</t>
+    <t>Comitato di Partito di Catania (UCI m-l)</t>
   </si>
   <si>
     <t>Volantino</t>
@@ -499,7 +748,7 @@
     <t>12/1968</t>
   </si>
   <si>
-    <t>Partito Comunista d'Italia (marxista-leninista); Partito Comunista d'Italia (marxista-leninista) - linea rossa</t>
+    <t>Partito Comunista d'Italia (marxista-leninista); Partito Comunista d'Italia (marxista-leninista) - Linea rossa</t>
   </si>
   <si>
     <t>https://archive.org/details/lavoro-politico-11-12/mode/2up</t>
@@ -538,9 +787,6 @@
     <t>Testo</t>
   </si>
   <si>
-    <t>Vincenzo Calò</t>
-  </si>
-  <si>
     <t>https://archive.org/details/statuto-stella-rossa</t>
   </si>
   <si>
@@ -688,9 +934,6 @@
     <t>Longanesi &amp; C.</t>
   </si>
   <si>
-    <t>Giorgio Zucchetti</t>
-  </si>
-  <si>
     <t>Associazione Italia-Cina</t>
   </si>
   <si>
@@ -826,9 +1069,6 @@
     <t>Manifesto</t>
   </si>
   <si>
-    <t>Osvaldo Pesce</t>
-  </si>
-  <si>
     <t>https://archive.org/details/manifesto-pcudi-breznev</t>
   </si>
   <si>
@@ -862,7 +1102,7 @@
     <t>Congresso di fondazione del Partito Comunista Unificato d'Italia</t>
   </si>
   <si>
-    <t>Organizzazione dei Comunisti (marxisti-leninisti) d'Italia; Organizzazione Comunista (marxista-leninista) - Fronte Unito; Partito Comunista (marxista-leninista) d'Italia - Lotta di lunga durata; Partito Marxista-Leninista-Maoista Italiano</t>
+    <t>Organizzazione dei Comunisti (marxisti-leninisti) d'Italia; Organizzazione Comunista (marxista-leninista) Fronte Unito; Partito Comunista (marxista-leninista) d'Italia - Lotta di lunga durata; Partito Comunista Marxista-Leninista-Maoista Italiano</t>
   </si>
   <si>
     <t>https://archive.org/details/fondazione-pcudi-1977</t>
@@ -877,9 +1117,6 @@
     <t>Proletari senza rivoluzione: Storia delle classi subalterne italiane dal 1860 al 1950, Vol. 1</t>
   </si>
   <si>
-    <t>Renzo del Carria</t>
-  </si>
-  <si>
     <t>https://archive.org/details/proletari-senza-rivoluzione-1/mode/2up</t>
   </si>
   <si>
@@ -898,12 +1135,6 @@
     <t>Come diventare un buon comunista</t>
   </si>
   <si>
-    <t>Liu Shaoqi</t>
-  </si>
-  <si>
-    <t>Arnaldo Bressan</t>
-  </si>
-  <si>
     <t>https://archive.org/details/come-diventare-un-buon-comunista/mode/2up</t>
   </si>
   <si>
@@ -1285,228 +1516,6 @@
     <t>1973-Ramazzotti.png</t>
   </si>
   <si>
-    <t>Nome</t>
-  </si>
-  <si>
-    <t>Cognome</t>
-  </si>
-  <si>
-    <t>Nascita</t>
-  </si>
-  <si>
-    <t>Morte</t>
-  </si>
-  <si>
-    <t>Immagine</t>
-  </si>
-  <si>
-    <t>ID_autorita</t>
-  </si>
-  <si>
-    <t>Tipo_entita</t>
-  </si>
-  <si>
-    <t>Forme_varianti</t>
-  </si>
-  <si>
-    <t>Biografia</t>
-  </si>
-  <si>
-    <t>Luoghi</t>
-  </si>
-  <si>
-    <t>Wikidata</t>
-  </si>
-  <si>
-    <t>VIAF</t>
-  </si>
-  <si>
-    <t>Stato_record</t>
-  </si>
-  <si>
-    <t>Livello_dettaglio</t>
-  </si>
-  <si>
-    <t>Data_redazione</t>
-  </si>
-  <si>
-    <t>Norme</t>
-  </si>
-  <si>
-    <t>Lingua_record</t>
-  </si>
-  <si>
-    <t>Note_redazionali</t>
-  </si>
-  <si>
-    <t>Mao</t>
-  </si>
-  <si>
-    <t>mao.webp</t>
-  </si>
-  <si>
-    <t>AMI-P-001</t>
-  </si>
-  <si>
-    <t>Persona</t>
-  </si>
-  <si>
-    <t>Bozza</t>
-  </si>
-  <si>
-    <t>Minimo</t>
-  </si>
-  <si>
-    <t>2026-10-02 creazione struttura ISAAR</t>
-  </si>
-  <si>
-    <t>ISAAR(CPF), 2a ed., 2004</t>
-  </si>
-  <si>
-    <t>ita</t>
-  </si>
-  <si>
-    <t>Biografia da redigere</t>
-  </si>
-  <si>
-    <t>Fosco Dinucci</t>
-  </si>
-  <si>
-    <t>Dinucci</t>
-  </si>
-  <si>
-    <t>dinucci.webp</t>
-  </si>
-  <si>
-    <t>AMI-P-002</t>
-  </si>
-  <si>
-    <t>Pesce</t>
-  </si>
-  <si>
-    <t>pesce.webp</t>
-  </si>
-  <si>
-    <t>AMI-P-003</t>
-  </si>
-  <si>
-    <t>Yao</t>
-  </si>
-  <si>
-    <t>AMI-P-004</t>
-  </si>
-  <si>
-    <t>Roberto Sassi</t>
-  </si>
-  <si>
-    <t>Sassi</t>
-  </si>
-  <si>
-    <t>AMI-P-005</t>
-  </si>
-  <si>
-    <t>Calò</t>
-  </si>
-  <si>
-    <t>AMI-P-006</t>
-  </si>
-  <si>
-    <t>Date di esistenza mancanti o incomplete; Biografia da redigere</t>
-  </si>
-  <si>
-    <t>Dino Dini</t>
-  </si>
-  <si>
-    <t>Dini</t>
-  </si>
-  <si>
-    <t>AMI-P-007</t>
-  </si>
-  <si>
-    <t>Lin Biao</t>
-  </si>
-  <si>
-    <t>Lin</t>
-  </si>
-  <si>
-    <t>AMI-P-008</t>
-  </si>
-  <si>
-    <t>Kang Sheng</t>
-  </si>
-  <si>
-    <t>Kang</t>
-  </si>
-  <si>
-    <t>AMI-P-009</t>
-  </si>
-  <si>
-    <t>Zhou Enlai</t>
-  </si>
-  <si>
-    <t>Zhou</t>
-  </si>
-  <si>
-    <t>AMI-P-010</t>
-  </si>
-  <si>
-    <t>Chen Boda</t>
-  </si>
-  <si>
-    <t>Chen</t>
-  </si>
-  <si>
-    <t>AMI-P-011</t>
-  </si>
-  <si>
-    <t>Jiang Qing</t>
-  </si>
-  <si>
-    <t>Jiang</t>
-  </si>
-  <si>
-    <t>AMI-P-012</t>
-  </si>
-  <si>
-    <t>Angiolo Gracci</t>
-  </si>
-  <si>
-    <t>Gracci</t>
-  </si>
-  <si>
-    <t>AMI-P-013</t>
-  </si>
-  <si>
-    <t>Zucchetti</t>
-  </si>
-  <si>
-    <t>AMI-P-014</t>
-  </si>
-  <si>
-    <t>Liu</t>
-  </si>
-  <si>
-    <t>AMI-P-015</t>
-  </si>
-  <si>
-    <t>del Carria</t>
-  </si>
-  <si>
-    <t>AMI-P-016</t>
-  </si>
-  <si>
-    <t>Date di esistenza mancanti o incomplete; Biografia da redigere; Record creato il 2026-10-02 perché il nome compare nel Catalogo senza record d'autorità; Verificare la grafia (del Carria / Del Carria)</t>
-  </si>
-  <si>
-    <t>Bressan</t>
-  </si>
-  <si>
-    <t>AMI-P-017</t>
-  </si>
-  <si>
-    <t>Date di esistenza mancanti o incomplete; Biografia da redigere; Record creato il 2026-10-02 perché il nome compare nel Catalogo senza record d'autorità</t>
-  </si>
-  <si>
     <t>Categoria</t>
   </si>
   <si>
@@ -1519,189 +1528,198 @@
     <t>Storia</t>
   </si>
   <si>
+    <t>AMI-O-001</t>
+  </si>
+  <si>
+    <t>Ente</t>
+  </si>
+  <si>
     <t>Associazione di massa</t>
   </si>
   <si>
     <t>201?</t>
   </si>
   <si>
-    <t>AMI-O-001</t>
-  </si>
-  <si>
-    <t>Ente</t>
-  </si>
-  <si>
-    <t>Data di scioglimento incerta ("201?"); Storia da redigere</t>
+    <t>Storia da redigere</t>
+  </si>
+  <si>
+    <t>AMI-O-002</t>
   </si>
   <si>
     <t>Casa editrice</t>
   </si>
   <si>
-    <t>AMI-O-002</t>
-  </si>
-  <si>
-    <t>Storia da redigere</t>
-  </si>
-  <si>
     <t>AMI-O-003</t>
   </si>
   <si>
+    <t>AMI-O-004</t>
+  </si>
+  <si>
+    <t>Quotidiano del Popolo</t>
+  </si>
+  <si>
     <t>Giornale</t>
   </si>
   <si>
-    <t>AMI-O-004</t>
-  </si>
-  <si>
-    <t>Quotidiano del Popolo</t>
+    <t>AMI-O-005</t>
   </si>
   <si>
     <t>Hongqi</t>
   </si>
   <si>
-    <t>AMI-O-005</t>
-  </si>
-  <si>
     <t>Bandiera Rossa</t>
   </si>
   <si>
     <t>AMI-O-006</t>
   </si>
   <si>
+    <t>AMI-O-007</t>
+  </si>
+  <si>
     <t>Jiefangjun Bao</t>
   </si>
   <si>
-    <t>AMI-O-007</t>
-  </si>
-  <si>
-    <t>Quotidiano dell'EPL</t>
+    <t>Quotidiano dell'EPL; Quotidiano dell'Esercito Popolare di Liberazione</t>
+  </si>
+  <si>
+    <t>AMI-O-008</t>
   </si>
   <si>
     <t>Gruppo</t>
   </si>
   <si>
-    <t>AMI-O-008</t>
-  </si>
-  <si>
-    <t>Data di fondazione mancante; Storia da redigere</t>
+    <t>196?</t>
+  </si>
+  <si>
+    <t>197?</t>
+  </si>
+  <si>
+    <t>AMI-O-009</t>
   </si>
   <si>
     <t>Organo di partito</t>
   </si>
   <si>
-    <t>AMI-O-009</t>
-  </si>
-  <si>
     <t>AMI-O-010</t>
   </si>
   <si>
+    <t>AMI-O-011</t>
+  </si>
+  <si>
     <t>Unione della gioventù comunista d’Italia (marxista-leninista)</t>
   </si>
   <si>
-    <t>AMI-O-011</t>
-  </si>
-  <si>
     <t>AMI-O-012</t>
   </si>
   <si>
+    <t>AMI-O-013</t>
+  </si>
+  <si>
+    <t>PCd'I (m-l); PCd'I(m-l)</t>
+  </si>
+  <si>
     <t>Partito</t>
   </si>
   <si>
     <t>logo-pcdi.svg</t>
   </si>
   <si>
-    <t>AMI-O-013</t>
-  </si>
-  <si>
-    <t>PCd'I (m-l); PCd'I(m-l)</t>
+    <t>AMI-O-014</t>
+  </si>
+  <si>
+    <t>UCI (m-l); UCI(m-l)</t>
   </si>
   <si>
     <t>logo-UCI.svg</t>
   </si>
   <si>
-    <t>AMI-O-014</t>
-  </si>
-  <si>
-    <t>UCI (m.l)</t>
+    <t>AMI-O-015</t>
+  </si>
+  <si>
+    <t>PCC</t>
   </si>
   <si>
     <t>logo-pcc.svg</t>
   </si>
   <si>
-    <t>AMI-O-015</t>
-  </si>
-  <si>
-    <t>PCC</t>
-  </si>
-  <si>
-    <t>Partito Comunista d'Italia (marxista-leninista) - linea rossa</t>
-  </si>
-  <si>
     <t>AMI-O-016</t>
   </si>
   <si>
+    <t>Partito Comunista d'Italia (marxista-leninista) - Linea rossa</t>
+  </si>
+  <si>
+    <t>PCd'I(m-l) - Linea rossa; Partito Comunista d'Italia (marxista-leninista) - Il Partito; PCd'I(m-l) - Il Partito</t>
+  </si>
+  <si>
     <t>AMI-O-017</t>
   </si>
   <si>
-    <t>????</t>
+    <t>Stella Rossa</t>
   </si>
   <si>
     <t>AMI-O-018</t>
   </si>
   <si>
-    <t>Data di scioglimento incerta ("????"); Storia da redigere</t>
-  </si>
-  <si>
     <t>AMI-O-019</t>
   </si>
   <si>
     <t>PC(m-l)I</t>
   </si>
   <si>
+    <t>AMI-O-020</t>
+  </si>
+  <si>
     <t>Rivista</t>
   </si>
   <si>
-    <t>AMI-O-020</t>
-  </si>
-  <si>
     <t>AMI-O-021</t>
   </si>
   <si>
+    <t>PCUd'I</t>
+  </si>
+  <si>
     <t>AMI-O-022</t>
   </si>
   <si>
     <t>AMI-O-023</t>
   </si>
   <si>
-    <t>Record creato il 2026-10-02 perché il nome compare nel Catalogo senza record d'autorità; categoria e date da compilare; Storia da redigere</t>
-  </si>
-  <si>
     <t>AMI-O-024</t>
   </si>
   <si>
-    <t>Record creato il 2026-10-02 perché il nome compare nel Catalogo senza record d'autorità; categoria e date da compilare; Nel Catalogo il nome compare in due grafie (con e senza trattino): uniformare; Storia da redigere</t>
+    <t>Organizzazione Comunista (marxista-leninista); Organizzazione Comunista (marxista-leninista) - Fronte Unito; OC(m-l) - Fronte Unito</t>
   </si>
   <si>
     <t>AMI-O-025</t>
   </si>
   <si>
+    <t>AMI-O-026</t>
+  </si>
+  <si>
     <t>Organizzazione dei Comunisti (marxisti-leninisti) d'Italia</t>
   </si>
   <si>
-    <t>AMI-O-026</t>
+    <t>OC(m-l)d'I</t>
+  </si>
+  <si>
+    <t>AMI-O-027</t>
   </si>
   <si>
     <t>Partito Comunista (marxista-leninista) d'Italia - Lotta di lunga durata</t>
   </si>
   <si>
-    <t>AMI-O-027</t>
-  </si>
-  <si>
-    <t>Partito Marxista-Leninista-Maoista Italiano</t>
+    <t>PC(m-l)d'I; PC(m-l)d'I - Lotta di lunga durata</t>
   </si>
   <si>
     <t>AMI-O-028</t>
   </si>
   <si>
+    <t>Partito Comunista Marxista-Leninista-Maoista Italiano</t>
+  </si>
+  <si>
+    <t>PC(m-l-m)I</t>
+  </si>
+  <si>
     <t>ID_relazione</t>
   </si>
   <si>
@@ -1804,23 +1822,14 @@
     <t>Natura del rapporto (scissione, frazione, ecc.) da documentare con una fonte</t>
   </si>
   <si>
-    <t>Mao Tse-tung; Mao Tsetung</t>
-  </si>
-  <si>
-    <t>Lin Piao</t>
-  </si>
-  <si>
-    <t>Liu Shao-chi</t>
-  </si>
-  <si>
-    <t>Organizzazione Comunista (marxista-leninista); Organizzazione Comunista (marxista-leninista) - Fronte Unito; OC(m-l) - Fronte Unito</t>
+    <t>Movimento</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1835,12 +1844,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -1880,7 +1883,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1891,13 +1894,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Collegamento ipertestuale" xfId="1" builtinId="8"/>
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1939,24 +1960,24 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabella3" displayName="Tabella3" ref="A1:R25" totalsRowShown="0">
   <autoFilter ref="A1:R25" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="18">
-    <tableColumn id="6" xr3:uid="{3212BA2D-A712-4A4C-8E4F-C02CA96AFD1F}" name="ID_autorita"/>
-    <tableColumn id="7" xr3:uid="{15562B4C-0702-4DEF-87F7-E3BD984669EF}" name="Tipo_entita"/>
-    <tableColumn id="17" xr3:uid="{7283C6B4-B4E6-404F-92AD-8F80E7D20008}" name="Norme"/>
-    <tableColumn id="18" xr3:uid="{F4A739E8-A998-4105-A512-53005410A134}" name="Lingua_record"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="ID_autorita"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Tipo_entita"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0100-000011000000}" name="Norme"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0100-000012000000}" name="Lingua_record"/>
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Nome"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Cognome"/>
-    <tableColumn id="8" xr3:uid="{3D544CFB-2C18-49C0-8353-2E50D6C3EE44}" name="Forme_varianti"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Forme_varianti"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Nascita"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Morte"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Immagine"/>
-    <tableColumn id="9" xr3:uid="{D71155FF-2283-41CA-B4BA-E37281403641}" name="Biografia"/>
-    <tableColumn id="10" xr3:uid="{013E7873-303A-4FB8-8865-E6B3DFD1AEE9}" name="Luoghi"/>
-    <tableColumn id="11" xr3:uid="{22E6E213-BB2B-4D30-8C40-F7E5D640C195}" name="Wikidata"/>
-    <tableColumn id="12" xr3:uid="{6BAB851C-A200-4855-A259-229103E48483}" name="VIAF"/>
-    <tableColumn id="14" xr3:uid="{8D2B76C7-0208-4F33-A8E7-118BFD4CAD08}" name="Stato_record"/>
-    <tableColumn id="15" xr3:uid="{116F1AD4-6283-44E1-BC3B-7194F7AF5740}" name="Livello_dettaglio"/>
-    <tableColumn id="16" xr3:uid="{61FFE37B-86B2-42F2-A68A-4D026BFFD05D}" name="Data_redazione"/>
-    <tableColumn id="19" xr3:uid="{3C7A0B86-8AF1-47EE-86F8-3A969A4DCE3F}" name="Note_redazionali"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Biografia"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Luoghi"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="Wikidata"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="VIAF"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="Stato_record"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0100-00000F000000}" name="Livello_dettaglio"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0100-000010000000}" name="Data_redazione"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0100-000013000000}" name="Note_redazionali"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1966,24 +1987,43 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Tabella4" displayName="Tabella4" ref="A1:R54" totalsRowShown="0">
   <autoFilter ref="A1:R54" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="18">
-    <tableColumn id="6" xr3:uid="{4369E07F-84A8-44D8-A69E-07057DF34B9B}" name="ID_autorita"/>
-    <tableColumn id="7" xr3:uid="{FB5D02D3-DA94-4843-BABB-940A8E6F528E}" name="Tipo_entita"/>
-    <tableColumn id="17" xr3:uid="{824F81ED-99E2-4986-981B-22027E119042}" name="Norme"/>
-    <tableColumn id="18" xr3:uid="{1E915349-0311-4AF4-91C1-AD3A716F356A}" name="Lingua_record"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="ID_autorita"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="Tipo_entita"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0200-000011000000}" name="Norme"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0200-000012000000}" name="Lingua_record"/>
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Nome"/>
-    <tableColumn id="8" xr3:uid="{DC922B9C-EEE2-48ED-B058-A3A0FB131D11}" name="Forme_varianti"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="Forme_varianti"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Categoria"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Fondazione"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Scioglimento"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Immagine"/>
-    <tableColumn id="9" xr3:uid="{0D3C4DBF-008D-4567-AD38-806BB5838BA2}" name="Storia"/>
-    <tableColumn id="10" xr3:uid="{4CA71764-7AE9-47EC-B817-04DD223E365A}" name="Luoghi"/>
-    <tableColumn id="11" xr3:uid="{E820A84A-CE7F-492F-9F18-D9BE2FB1B76A}" name="Wikidata"/>
-    <tableColumn id="12" xr3:uid="{344AA8A3-47C9-4835-AEB9-BCADD2757D98}" name="VIAF"/>
-    <tableColumn id="14" xr3:uid="{980BF526-5BC6-4DE8-9A72-0CFD571F90B2}" name="Stato_record"/>
-    <tableColumn id="15" xr3:uid="{62373511-EB64-41E7-89EC-C7497EE927C2}" name="Livello_dettaglio"/>
-    <tableColumn id="16" xr3:uid="{ADD323D5-F89C-43E4-B88D-B836E3B9D86D}" name="Data_redazione"/>
-    <tableColumn id="19" xr3:uid="{A30F4815-98AE-40F4-8467-092D97C457CF}" name="Note_redazionali"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="Storia"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0200-00000A000000}" name="Luoghi"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0200-00000B000000}" name="Wikidata"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0200-00000C000000}" name="VIAF"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0200-00000E000000}" name="Stato_record"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0200-00000F000000}" name="Livello_dettaglio"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0200-000010000000}" name="Data_redazione"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0200-000013000000}" name="Note_redazionali"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{4895E276-9036-4388-B350-F25B94D00A98}" name="Tabella5" displayName="Tabella5" ref="A1:J8" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A1:J8" xr:uid="{4895E276-9036-4388-B350-F25B94D00A98}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{681E8224-5D12-4699-8FCD-F6D6D65EDFAF}" name="ID_relazione"/>
+    <tableColumn id="2" xr3:uid="{ABB6B5F5-BCC1-4479-A7C9-B3517A2E96E9}" name="ID_entita_A"/>
+    <tableColumn id="3" xr3:uid="{3F668034-0278-4DA2-A935-859974F314BD}" name="Entita_A"/>
+    <tableColumn id="6" xr3:uid="{42A1CA9B-CDB3-4B11-A772-F6671E7361A4}" name="ID_entita_B"/>
+    <tableColumn id="7" xr3:uid="{CE848972-8DB1-45ED-A2B3-0089F3F245F8}" name="Entita_B"/>
+    <tableColumn id="4" xr3:uid="{B95E7709-F734-4C56-AC55-9D28675CC09C}" name="Relazione"/>
+    <tableColumn id="5" xr3:uid="{80228F24-50C6-4B25-A089-9A91E2D1B5BE}" name="Categoria_ISAAR"/>
+    <tableColumn id="8" xr3:uid="{212F0BDC-21F6-48DB-B68E-85FA962B2DE9}" name="Date"/>
+    <tableColumn id="9" xr3:uid="{FD3B0224-7FC7-44A7-82B2-2BB98B63F4B0}" name="Fonte"/>
+    <tableColumn id="10" xr3:uid="{8504BE3C-9F3E-4F81-B091-E402614DD122}" name="Note"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2292,3328 +2332,3328 @@
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>86</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>87</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>88</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>89</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
+        <v>90</v>
       </c>
       <c r="G1" t="s">
-        <v>6</v>
+        <v>91</v>
       </c>
       <c r="H1" t="s">
-        <v>7</v>
+        <v>92</v>
       </c>
       <c r="I1" t="s">
-        <v>8</v>
+        <v>93</v>
       </c>
       <c r="J1" t="s">
-        <v>9</v>
+        <v>94</v>
       </c>
       <c r="K1" t="s">
-        <v>10</v>
+        <v>95</v>
       </c>
       <c r="L1" t="s">
-        <v>11</v>
+        <v>96</v>
       </c>
       <c r="M1" t="s">
-        <v>12</v>
+        <v>97</v>
       </c>
       <c r="N1" t="s">
-        <v>13</v>
+        <v>98</v>
       </c>
       <c r="O1" t="s">
-        <v>14</v>
+        <v>99</v>
       </c>
       <c r="P1" t="s">
-        <v>15</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>101</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>102</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>103</v>
       </c>
       <c r="D2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E2" t="s">
-        <v>20</v>
+        <v>104</v>
       </c>
       <c r="F2" s="1">
         <v>1969</v>
       </c>
       <c r="G2" t="s">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="H2" t="s">
-        <v>22</v>
+        <v>106</v>
       </c>
       <c r="I2" t="s">
-        <v>23</v>
+        <v>107</v>
       </c>
       <c r="L2" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>25</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>110</v>
       </c>
       <c r="B3" t="s">
-        <v>27</v>
+        <v>111</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>103</v>
       </c>
       <c r="D3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E3" t="s">
-        <v>20</v>
+        <v>104</v>
       </c>
       <c r="F3" s="1">
         <v>1967</v>
       </c>
       <c r="G3" t="s">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="H3" t="s">
-        <v>22</v>
+        <v>106</v>
       </c>
       <c r="I3" t="s">
-        <v>29</v>
+        <v>113</v>
       </c>
       <c r="L3" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>30</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>31</v>
+        <v>115</v>
       </c>
       <c r="B4" t="s">
-        <v>32</v>
+        <v>116</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>103</v>
       </c>
       <c r="D4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E4" t="s">
-        <v>20</v>
+        <v>104</v>
       </c>
       <c r="F4" s="1">
         <v>1968</v>
       </c>
       <c r="G4" t="s">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="H4" t="s">
-        <v>22</v>
+        <v>106</v>
       </c>
       <c r="I4" t="s">
-        <v>29</v>
+        <v>113</v>
       </c>
       <c r="L4" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>33</v>
+        <v>117</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>34</v>
+        <v>118</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>119</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>103</v>
       </c>
       <c r="D5" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E5" t="s">
-        <v>20</v>
+        <v>104</v>
       </c>
       <c r="F5" s="1">
         <v>1968</v>
       </c>
       <c r="G5" t="s">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="H5" t="s">
-        <v>22</v>
+        <v>106</v>
       </c>
       <c r="I5" t="s">
-        <v>36</v>
+        <v>120</v>
       </c>
       <c r="L5" t="s">
-        <v>37</v>
+        <v>121</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>38</v>
+        <v>122</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>39</v>
+        <v>123</v>
       </c>
       <c r="B6" t="s">
-        <v>40</v>
+        <v>124</v>
       </c>
       <c r="C6" t="s">
-        <v>18</v>
+        <v>103</v>
       </c>
       <c r="D6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E6" t="s">
-        <v>20</v>
+        <v>104</v>
       </c>
       <c r="F6" s="1">
         <v>1968</v>
       </c>
       <c r="G6" t="s">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="H6" t="s">
-        <v>22</v>
+        <v>106</v>
       </c>
       <c r="I6" t="s">
-        <v>36</v>
+        <v>120</v>
       </c>
       <c r="L6" t="s">
-        <v>37</v>
+        <v>121</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>41</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>42</v>
+        <v>126</v>
       </c>
       <c r="B7" t="s">
-        <v>43</v>
+        <v>127</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>103</v>
       </c>
       <c r="D7" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E7" t="s">
-        <v>20</v>
+        <v>104</v>
       </c>
       <c r="F7" s="1">
         <v>1968</v>
       </c>
       <c r="G7" t="s">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="H7" t="s">
-        <v>22</v>
+        <v>106</v>
       </c>
       <c r="I7" t="s">
-        <v>29</v>
+        <v>113</v>
       </c>
       <c r="L7" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>44</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>45</v>
+        <v>129</v>
       </c>
       <c r="B8" t="s">
-        <v>46</v>
+        <v>130</v>
       </c>
       <c r="C8" t="s">
-        <v>18</v>
+        <v>103</v>
       </c>
       <c r="D8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E8" t="s">
-        <v>20</v>
+        <v>104</v>
       </c>
       <c r="F8" s="1">
         <v>1968</v>
       </c>
       <c r="G8" t="s">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="H8" t="s">
-        <v>22</v>
+        <v>106</v>
       </c>
       <c r="I8" t="s">
-        <v>36</v>
+        <v>120</v>
       </c>
       <c r="L8" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>47</v>
+        <v>131</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>48</v>
+        <v>132</v>
       </c>
       <c r="B9" t="s">
-        <v>49</v>
+        <v>133</v>
       </c>
       <c r="C9" t="s">
-        <v>18</v>
+        <v>103</v>
       </c>
       <c r="D9" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E9" t="s">
-        <v>20</v>
+        <v>104</v>
       </c>
       <c r="F9" s="1">
         <v>1969</v>
       </c>
       <c r="G9" t="s">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="H9" t="s">
-        <v>22</v>
+        <v>106</v>
       </c>
       <c r="I9" t="s">
-        <v>36</v>
+        <v>120</v>
       </c>
       <c r="L9" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>50</v>
+        <v>134</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>51</v>
+        <v>135</v>
       </c>
       <c r="B10" t="s">
-        <v>52</v>
+        <v>136</v>
       </c>
       <c r="C10" t="s">
-        <v>18</v>
+        <v>103</v>
       </c>
       <c r="D10" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E10" t="s">
-        <v>20</v>
+        <v>104</v>
       </c>
       <c r="F10" s="1">
         <v>1969</v>
       </c>
       <c r="G10" t="s">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="H10" t="s">
-        <v>22</v>
+        <v>106</v>
       </c>
       <c r="I10" t="s">
-        <v>36</v>
+        <v>120</v>
       </c>
       <c r="L10" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>53</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>54</v>
+        <v>138</v>
       </c>
       <c r="B11" t="s">
-        <v>55</v>
+        <v>139</v>
       </c>
       <c r="C11" t="s">
-        <v>18</v>
+        <v>103</v>
       </c>
       <c r="D11" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E11" t="s">
-        <v>20</v>
+        <v>104</v>
       </c>
       <c r="F11" s="1">
         <v>1970</v>
       </c>
       <c r="G11" t="s">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="H11" t="s">
-        <v>22</v>
+        <v>106</v>
       </c>
       <c r="I11" t="s">
-        <v>36</v>
+        <v>120</v>
       </c>
       <c r="L11" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>56</v>
+        <v>140</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>57</v>
+        <v>141</v>
       </c>
       <c r="B12" t="s">
-        <v>58</v>
+        <v>142</v>
       </c>
       <c r="C12" t="s">
-        <v>18</v>
+        <v>103</v>
       </c>
       <c r="D12" t="s">
-        <v>59</v>
+        <v>143</v>
       </c>
       <c r="E12" t="s">
-        <v>20</v>
+        <v>104</v>
       </c>
       <c r="F12" s="1">
         <v>1968</v>
       </c>
       <c r="G12" t="s">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="H12" t="s">
-        <v>22</v>
+        <v>106</v>
       </c>
       <c r="I12" t="s">
-        <v>36</v>
+        <v>120</v>
       </c>
       <c r="K12" t="s">
-        <v>18</v>
+        <v>103</v>
       </c>
       <c r="L12" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>60</v>
+        <v>144</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>61</v>
+        <v>145</v>
       </c>
       <c r="B13" t="s">
-        <v>62</v>
+        <v>146</v>
       </c>
       <c r="C13" t="s">
-        <v>18</v>
+        <v>103</v>
       </c>
       <c r="D13" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="E13" t="s">
-        <v>20</v>
+        <v>104</v>
       </c>
       <c r="F13" s="1">
         <v>1968</v>
       </c>
       <c r="G13" t="s">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="H13" t="s">
-        <v>22</v>
+        <v>106</v>
       </c>
       <c r="I13" t="s">
-        <v>36</v>
+        <v>120</v>
       </c>
       <c r="L13" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>64</v>
+        <v>147</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>65</v>
+        <v>148</v>
       </c>
       <c r="B14" t="s">
-        <v>66</v>
+        <v>149</v>
       </c>
       <c r="C14" t="s">
-        <v>67</v>
+        <v>150</v>
       </c>
       <c r="D14" t="s">
-        <v>68</v>
+        <v>151</v>
       </c>
       <c r="E14" t="s">
-        <v>69</v>
+        <v>152</v>
       </c>
       <c r="F14" s="1">
         <v>1967</v>
       </c>
       <c r="G14" t="s">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="H14" t="s">
-        <v>70</v>
+        <v>153</v>
       </c>
       <c r="I14" t="s">
-        <v>71</v>
+        <v>154</v>
       </c>
       <c r="J14" t="s">
-        <v>72</v>
+        <v>155</v>
       </c>
       <c r="K14" t="s">
-        <v>73</v>
+        <v>156</v>
       </c>
       <c r="L14" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>74</v>
+        <v>157</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>75</v>
+        <v>158</v>
       </c>
       <c r="B15" t="s">
-        <v>76</v>
+        <v>159</v>
       </c>
       <c r="C15" t="s">
-        <v>67</v>
+        <v>150</v>
       </c>
       <c r="D15" t="s">
-        <v>77</v>
+        <v>160</v>
       </c>
       <c r="F15" s="2">
         <v>25064</v>
       </c>
       <c r="G15" t="s">
-        <v>78</v>
+        <v>161</v>
       </c>
       <c r="H15" t="s">
-        <v>22</v>
+        <v>106</v>
       </c>
       <c r="I15" t="s">
-        <v>71</v>
+        <v>154</v>
       </c>
       <c r="J15" t="s">
-        <v>79</v>
+        <v>162</v>
       </c>
       <c r="L15" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>80</v>
+        <v>163</v>
       </c>
       <c r="N15" t="s">
-        <v>81</v>
+        <v>164</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>82</v>
+        <v>165</v>
       </c>
       <c r="B16" t="s">
-        <v>83</v>
+        <v>166</v>
       </c>
       <c r="C16" t="s">
-        <v>67</v>
+        <v>150</v>
       </c>
       <c r="D16" t="s">
-        <v>84</v>
+        <v>167</v>
       </c>
       <c r="F16" s="2">
         <v>25081</v>
       </c>
       <c r="G16" t="s">
-        <v>78</v>
+        <v>161</v>
       </c>
       <c r="H16" t="s">
-        <v>22</v>
+        <v>106</v>
       </c>
       <c r="I16" t="s">
-        <v>71</v>
+        <v>154</v>
       </c>
       <c r="J16" t="s">
-        <v>85</v>
+        <v>168</v>
       </c>
       <c r="L16" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>86</v>
+        <v>169</v>
       </c>
       <c r="N16" t="s">
-        <v>87</v>
+        <v>170</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>88</v>
+        <v>171</v>
       </c>
       <c r="B17" t="s">
-        <v>89</v>
+        <v>172</v>
       </c>
       <c r="C17" t="s">
-        <v>67</v>
+        <v>150</v>
       </c>
       <c r="D17" t="s">
-        <v>77</v>
+        <v>160</v>
       </c>
       <c r="F17" s="2">
         <v>25479</v>
       </c>
       <c r="G17" t="s">
-        <v>78</v>
+        <v>161</v>
       </c>
       <c r="H17" t="s">
-        <v>22</v>
+        <v>106</v>
       </c>
       <c r="I17" t="s">
-        <v>71</v>
+        <v>154</v>
       </c>
       <c r="J17" t="s">
-        <v>90</v>
+        <v>173</v>
       </c>
       <c r="L17" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>91</v>
+        <v>174</v>
       </c>
       <c r="N17" t="s">
-        <v>92</v>
+        <v>175</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>93</v>
+        <v>176</v>
       </c>
       <c r="B18" t="s">
-        <v>94</v>
+        <v>177</v>
       </c>
       <c r="C18" t="s">
-        <v>95</v>
+        <v>178</v>
       </c>
       <c r="D18" t="s">
-        <v>96</v>
+        <v>179</v>
       </c>
       <c r="F18" s="2">
         <v>25485</v>
       </c>
       <c r="G18" t="s">
-        <v>97</v>
+        <v>180</v>
       </c>
       <c r="H18" t="s">
-        <v>98</v>
+        <v>181</v>
       </c>
       <c r="I18" t="s">
-        <v>71</v>
+        <v>154</v>
       </c>
       <c r="L18" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>99</v>
+        <v>182</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>100</v>
+        <v>183</v>
       </c>
       <c r="B19" t="s">
-        <v>101</v>
+        <v>184</v>
       </c>
       <c r="C19" t="s">
-        <v>102</v>
+        <v>185</v>
       </c>
       <c r="D19" t="s">
-        <v>84</v>
+        <v>167</v>
       </c>
       <c r="F19" s="2">
         <v>23514</v>
       </c>
       <c r="G19" t="s">
-        <v>78</v>
+        <v>161</v>
       </c>
       <c r="H19" t="s">
-        <v>22</v>
+        <v>106</v>
       </c>
       <c r="I19" t="s">
-        <v>71</v>
+        <v>154</v>
       </c>
       <c r="L19" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>103</v>
+        <v>186</v>
       </c>
       <c r="N19" t="s">
-        <v>104</v>
+        <v>187</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>105</v>
+        <v>188</v>
       </c>
       <c r="B20" t="s">
-        <v>106</v>
+        <v>189</v>
       </c>
       <c r="D20" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E20" t="s">
-        <v>107</v>
+        <v>190</v>
       </c>
       <c r="F20" s="1">
         <v>1969</v>
       </c>
       <c r="G20" t="s">
+        <v>191</v>
+      </c>
+      <c r="I20" t="s">
+        <v>192</v>
+      </c>
+      <c r="L20" t="s">
         <v>108</v>
       </c>
-      <c r="I20" t="s">
-        <v>109</v>
-      </c>
-      <c r="L20" t="s">
-        <v>24</v>
-      </c>
       <c r="M20" s="3" t="s">
-        <v>110</v>
+        <v>193</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>111</v>
+        <v>194</v>
       </c>
       <c r="B21" t="s">
-        <v>112</v>
+        <v>195</v>
       </c>
       <c r="D21" t="s">
-        <v>113</v>
+        <v>196</v>
       </c>
       <c r="E21" t="s">
-        <v>114</v>
+        <v>197</v>
       </c>
       <c r="F21" s="1">
         <v>1993</v>
       </c>
       <c r="G21" t="s">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="H21" t="s">
-        <v>115</v>
+        <v>198</v>
       </c>
       <c r="I21" t="s">
-        <v>109</v>
+        <v>192</v>
       </c>
       <c r="L21" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>116</v>
+        <v>199</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>117</v>
+        <v>200</v>
       </c>
       <c r="B22" t="s">
-        <v>118</v>
+        <v>201</v>
       </c>
       <c r="C22" t="s">
-        <v>119</v>
+        <v>202</v>
       </c>
       <c r="E22" t="s">
-        <v>120</v>
+        <v>203</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>121</v>
+        <v>204</v>
       </c>
       <c r="G22" t="s">
-        <v>122</v>
+        <v>205</v>
       </c>
       <c r="H22" t="s">
-        <v>123</v>
+        <v>206</v>
       </c>
       <c r="I22" t="s">
-        <v>124</v>
+        <v>207</v>
       </c>
       <c r="L22" t="s">
-        <v>125</v>
+        <v>208</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>126</v>
+        <v>209</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>127</v>
+        <v>210</v>
       </c>
       <c r="B23" t="s">
-        <v>128</v>
+        <v>211</v>
       </c>
       <c r="C23" t="s">
-        <v>119</v>
+        <v>202</v>
       </c>
       <c r="E23" t="s">
-        <v>120</v>
+        <v>203</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>129</v>
+        <v>212</v>
       </c>
       <c r="G23" t="s">
-        <v>122</v>
+        <v>205</v>
       </c>
       <c r="H23" t="s">
-        <v>123</v>
+        <v>206</v>
       </c>
       <c r="I23" t="s">
-        <v>124</v>
+        <v>207</v>
       </c>
       <c r="L23" t="s">
-        <v>125</v>
+        <v>208</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>130</v>
+        <v>213</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>131</v>
+        <v>214</v>
       </c>
       <c r="B24" t="s">
-        <v>132</v>
+        <v>215</v>
       </c>
       <c r="C24" t="s">
-        <v>119</v>
+        <v>202</v>
       </c>
       <c r="E24" t="s">
-        <v>120</v>
+        <v>203</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>133</v>
+        <v>216</v>
       </c>
       <c r="G24" t="s">
-        <v>122</v>
+        <v>205</v>
       </c>
       <c r="H24" t="s">
-        <v>123</v>
+        <v>206</v>
       </c>
       <c r="I24" t="s">
-        <v>124</v>
+        <v>207</v>
       </c>
       <c r="L24" t="s">
-        <v>125</v>
+        <v>208</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>134</v>
+        <v>217</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>135</v>
+        <v>218</v>
       </c>
       <c r="B25" t="s">
-        <v>136</v>
+        <v>219</v>
       </c>
       <c r="C25" t="s">
-        <v>119</v>
+        <v>202</v>
       </c>
       <c r="E25" t="s">
-        <v>120</v>
+        <v>203</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>137</v>
+        <v>220</v>
       </c>
       <c r="G25" t="s">
-        <v>122</v>
+        <v>205</v>
       </c>
       <c r="H25" t="s">
-        <v>123</v>
+        <v>206</v>
       </c>
       <c r="I25" t="s">
-        <v>124</v>
+        <v>207</v>
       </c>
       <c r="L25" t="s">
-        <v>125</v>
+        <v>208</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>139</v>
+        <v>222</v>
       </c>
       <c r="B26" t="s">
-        <v>140</v>
+        <v>223</v>
       </c>
       <c r="C26" t="s">
-        <v>119</v>
+        <v>202</v>
       </c>
       <c r="E26" t="s">
-        <v>120</v>
+        <v>203</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>141</v>
+        <v>224</v>
       </c>
       <c r="G26" t="s">
-        <v>122</v>
+        <v>205</v>
       </c>
       <c r="H26" t="s">
-        <v>123</v>
+        <v>206</v>
       </c>
       <c r="I26" t="s">
-        <v>124</v>
+        <v>207</v>
       </c>
       <c r="L26" t="s">
-        <v>125</v>
+        <v>208</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>142</v>
+        <v>225</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>143</v>
+        <v>226</v>
       </c>
       <c r="B27" t="s">
-        <v>144</v>
+        <v>227</v>
       </c>
       <c r="C27" t="s">
-        <v>119</v>
+        <v>202</v>
       </c>
       <c r="E27" t="s">
-        <v>120</v>
+        <v>203</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>145</v>
+        <v>228</v>
       </c>
       <c r="G27" t="s">
-        <v>122</v>
+        <v>205</v>
       </c>
       <c r="H27" t="s">
-        <v>123</v>
+        <v>206</v>
       </c>
       <c r="I27" t="s">
-        <v>124</v>
+        <v>207</v>
       </c>
       <c r="L27" t="s">
-        <v>125</v>
+        <v>208</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>146</v>
+        <v>229</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>147</v>
+        <v>230</v>
       </c>
       <c r="B28" t="s">
-        <v>148</v>
+        <v>231</v>
       </c>
       <c r="C28" t="s">
-        <v>119</v>
+        <v>202</v>
       </c>
       <c r="E28" t="s">
-        <v>120</v>
+        <v>203</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>149</v>
+        <v>232</v>
       </c>
       <c r="G28" t="s">
-        <v>122</v>
+        <v>205</v>
       </c>
       <c r="H28" t="s">
-        <v>123</v>
+        <v>206</v>
       </c>
       <c r="I28" t="s">
-        <v>124</v>
+        <v>207</v>
       </c>
       <c r="L28" t="s">
-        <v>125</v>
+        <v>208</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>150</v>
+        <v>233</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>151</v>
+        <v>234</v>
       </c>
       <c r="B29" t="s">
-        <v>152</v>
+        <v>235</v>
       </c>
       <c r="C29" t="s">
-        <v>119</v>
+        <v>202</v>
       </c>
       <c r="E29" t="s">
-        <v>120</v>
+        <v>203</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>153</v>
+        <v>236</v>
       </c>
       <c r="G29" t="s">
-        <v>122</v>
+        <v>205</v>
       </c>
       <c r="H29" t="s">
-        <v>123</v>
+        <v>206</v>
       </c>
       <c r="I29" t="s">
-        <v>124</v>
+        <v>207</v>
       </c>
       <c r="K29" t="s">
-        <v>67</v>
+        <v>150</v>
       </c>
       <c r="L29" t="s">
-        <v>125</v>
+        <v>208</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>154</v>
+        <v>237</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>155</v>
+        <v>238</v>
       </c>
       <c r="B30" t="s">
-        <v>156</v>
+        <v>239</v>
       </c>
       <c r="C30" t="s">
-        <v>119</v>
+        <v>202</v>
       </c>
       <c r="E30" t="s">
-        <v>120</v>
+        <v>203</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>157</v>
+        <v>240</v>
       </c>
       <c r="G30" t="s">
-        <v>122</v>
+        <v>205</v>
       </c>
       <c r="H30" t="s">
-        <v>123</v>
+        <v>206</v>
       </c>
       <c r="I30" t="s">
-        <v>124</v>
+        <v>207</v>
       </c>
       <c r="K30" t="s">
-        <v>158</v>
+        <v>241</v>
       </c>
       <c r="L30" t="s">
-        <v>125</v>
+        <v>208</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>159</v>
+        <v>242</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>160</v>
+        <v>243</v>
       </c>
       <c r="B31" t="s">
-        <v>161</v>
+        <v>244</v>
       </c>
       <c r="C31" t="s">
-        <v>18</v>
+        <v>103</v>
       </c>
       <c r="D31" t="s">
-        <v>162</v>
+        <v>245</v>
       </c>
       <c r="E31" t="s">
-        <v>20</v>
+        <v>104</v>
       </c>
       <c r="F31" s="1">
         <v>1968</v>
       </c>
       <c r="G31" t="s">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="H31" t="s">
-        <v>22</v>
+        <v>106</v>
       </c>
       <c r="I31" t="s">
-        <v>36</v>
+        <v>120</v>
       </c>
       <c r="L31" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="M31" s="3" t="s">
-        <v>163</v>
+        <v>246</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>164</v>
+        <v>247</v>
       </c>
       <c r="B32" t="s">
-        <v>165</v>
+        <v>248</v>
       </c>
       <c r="C32" t="s">
-        <v>18</v>
+        <v>103</v>
       </c>
       <c r="D32" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E32" t="s">
-        <v>20</v>
+        <v>104</v>
       </c>
       <c r="F32" s="1">
         <v>1968</v>
       </c>
       <c r="G32" t="s">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="H32" t="s">
-        <v>22</v>
+        <v>106</v>
       </c>
       <c r="I32" t="s">
-        <v>36</v>
+        <v>120</v>
       </c>
       <c r="L32" t="s">
-        <v>37</v>
+        <v>121</v>
       </c>
       <c r="M32" s="3" t="s">
-        <v>166</v>
+        <v>249</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>167</v>
+        <v>250</v>
       </c>
       <c r="B33" t="s">
-        <v>168</v>
+        <v>251</v>
       </c>
       <c r="C33" t="s">
-        <v>169</v>
+        <v>252</v>
       </c>
       <c r="F33" s="1">
         <v>1970</v>
       </c>
       <c r="G33" t="s">
-        <v>170</v>
+        <v>253</v>
       </c>
       <c r="I33" t="s">
-        <v>71</v>
+        <v>154</v>
       </c>
       <c r="J33" t="s">
-        <v>171</v>
+        <v>44</v>
       </c>
       <c r="L33" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="M33" s="3" t="s">
-        <v>172</v>
+        <v>254</v>
       </c>
       <c r="N33" t="s">
-        <v>173</v>
+        <v>255</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>174</v>
+        <v>256</v>
       </c>
       <c r="B34" t="s">
-        <v>175</v>
+        <v>257</v>
       </c>
       <c r="C34" t="s">
-        <v>67</v>
+        <v>150</v>
       </c>
       <c r="F34" s="2">
         <v>25063</v>
       </c>
       <c r="G34" t="s">
-        <v>176</v>
+        <v>258</v>
       </c>
       <c r="H34" t="s">
-        <v>22</v>
+        <v>106</v>
       </c>
       <c r="I34" t="s">
-        <v>71</v>
+        <v>154</v>
       </c>
       <c r="J34" t="s">
-        <v>177</v>
+        <v>259</v>
       </c>
       <c r="K34" t="s">
-        <v>18</v>
+        <v>103</v>
       </c>
       <c r="L34" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="M34" s="3" t="s">
-        <v>178</v>
+        <v>260</v>
       </c>
       <c r="O34" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
       <c r="P34" t="s">
-        <v>180</v>
+        <v>262</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>181</v>
+        <v>263</v>
       </c>
       <c r="B35" t="s">
-        <v>182</v>
+        <v>264</v>
       </c>
       <c r="C35" t="s">
-        <v>18</v>
+        <v>103</v>
       </c>
       <c r="D35" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F35" s="2">
         <v>25081</v>
       </c>
       <c r="G35" t="s">
-        <v>176</v>
+        <v>258</v>
       </c>
       <c r="H35" t="s">
-        <v>22</v>
+        <v>106</v>
       </c>
       <c r="I35" t="s">
-        <v>71</v>
+        <v>154</v>
       </c>
       <c r="J35" t="s">
-        <v>183</v>
+        <v>265</v>
       </c>
       <c r="K35" t="s">
-        <v>67</v>
+        <v>150</v>
       </c>
       <c r="L35" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="M35" s="3" t="s">
-        <v>184</v>
+        <v>266</v>
       </c>
       <c r="O35" t="s">
-        <v>185</v>
+        <v>267</v>
       </c>
       <c r="P35" t="s">
-        <v>186</v>
+        <v>268</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>187</v>
+        <v>269</v>
       </c>
       <c r="B36" t="s">
-        <v>188</v>
+        <v>270</v>
       </c>
       <c r="C36" t="s">
-        <v>95</v>
+        <v>178</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>189</v>
+        <v>271</v>
       </c>
       <c r="G36" t="s">
-        <v>122</v>
+        <v>205</v>
       </c>
       <c r="H36" t="s">
-        <v>190</v>
+        <v>272</v>
       </c>
       <c r="I36" t="s">
-        <v>71</v>
+        <v>154</v>
       </c>
       <c r="L36" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="M36" s="3" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>192</v>
+        <v>274</v>
       </c>
       <c r="B37" t="s">
-        <v>193</v>
+        <v>275</v>
       </c>
       <c r="C37" t="s">
-        <v>169</v>
+        <v>252</v>
       </c>
       <c r="D37" t="s">
-        <v>171</v>
+        <v>44</v>
       </c>
       <c r="E37" t="s">
-        <v>194</v>
+        <v>276</v>
       </c>
       <c r="F37" s="1">
         <v>1975</v>
       </c>
       <c r="G37" t="s">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="H37" t="s">
-        <v>195</v>
+        <v>277</v>
       </c>
       <c r="I37" t="s">
-        <v>109</v>
+        <v>192</v>
       </c>
       <c r="K37" t="s">
-        <v>169</v>
+        <v>252</v>
       </c>
       <c r="L37" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="M37" s="3" t="s">
-        <v>196</v>
+        <v>278</v>
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>197</v>
+        <v>279</v>
       </c>
       <c r="B38" t="s">
-        <v>198</v>
+        <v>280</v>
       </c>
       <c r="C38" t="s">
-        <v>18</v>
+        <v>103</v>
       </c>
       <c r="D38" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E38" t="s">
-        <v>20</v>
+        <v>104</v>
       </c>
       <c r="F38" s="1">
         <v>1968</v>
       </c>
       <c r="G38" t="s">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="H38" t="s">
-        <v>22</v>
+        <v>106</v>
       </c>
       <c r="I38" t="s">
-        <v>36</v>
+        <v>120</v>
       </c>
       <c r="L38" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="M38" s="3" t="s">
-        <v>199</v>
+        <v>281</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>200</v>
+        <v>282</v>
       </c>
       <c r="B39" t="s">
-        <v>201</v>
+        <v>283</v>
       </c>
       <c r="C39" t="s">
-        <v>18</v>
+        <v>103</v>
       </c>
       <c r="D39" t="s">
-        <v>202</v>
+        <v>284</v>
       </c>
       <c r="E39" t="s">
-        <v>20</v>
+        <v>104</v>
       </c>
       <c r="F39" s="1">
         <v>1970</v>
       </c>
       <c r="G39" t="s">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="H39" t="s">
-        <v>22</v>
+        <v>106</v>
       </c>
       <c r="I39" t="s">
-        <v>36</v>
+        <v>120</v>
       </c>
       <c r="J39" t="s">
-        <v>203</v>
+        <v>285</v>
       </c>
       <c r="L39" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="M39" s="3" t="s">
-        <v>204</v>
+        <v>286</v>
       </c>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>205</v>
+        <v>287</v>
       </c>
       <c r="B40" t="s">
-        <v>206</v>
+        <v>288</v>
       </c>
       <c r="C40" t="s">
-        <v>18</v>
+        <v>103</v>
       </c>
       <c r="D40" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E40" t="s">
-        <v>20</v>
+        <v>104</v>
       </c>
       <c r="F40" s="1">
         <v>1968</v>
       </c>
       <c r="G40" t="s">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="H40" t="s">
-        <v>22</v>
+        <v>106</v>
       </c>
       <c r="I40" t="s">
-        <v>207</v>
+        <v>289</v>
       </c>
       <c r="L40" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="M40" s="3" t="s">
-        <v>208</v>
+        <v>290</v>
       </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>209</v>
+        <v>291</v>
       </c>
       <c r="B41" t="s">
-        <v>210</v>
+        <v>292</v>
       </c>
       <c r="C41" t="s">
-        <v>18</v>
+        <v>103</v>
       </c>
       <c r="D41" t="s">
-        <v>211</v>
+        <v>293</v>
       </c>
       <c r="E41" t="s">
-        <v>20</v>
+        <v>104</v>
       </c>
       <c r="F41" s="1">
         <v>1970</v>
       </c>
       <c r="G41" t="s">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="H41" t="s">
-        <v>22</v>
+        <v>106</v>
       </c>
       <c r="I41" t="s">
-        <v>36</v>
+        <v>120</v>
       </c>
       <c r="L41" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="M41" s="3" t="s">
-        <v>212</v>
+        <v>294</v>
       </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>213</v>
+        <v>295</v>
       </c>
       <c r="B42" t="s">
-        <v>214</v>
+        <v>296</v>
       </c>
       <c r="D42" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E42" t="s">
-        <v>215</v>
+        <v>297</v>
       </c>
       <c r="F42" s="1">
         <v>1968</v>
       </c>
       <c r="G42" t="s">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="H42" t="s">
-        <v>190</v>
+        <v>272</v>
       </c>
       <c r="I42" t="s">
-        <v>216</v>
+        <v>298</v>
       </c>
       <c r="L42" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="M42" s="3" t="s">
-        <v>217</v>
+        <v>299</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>218</v>
+        <v>300</v>
       </c>
       <c r="B43" t="s">
-        <v>219</v>
+        <v>301</v>
       </c>
       <c r="D43" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E43" t="s">
-        <v>220</v>
+        <v>302</v>
       </c>
       <c r="F43" s="1">
         <v>1967</v>
       </c>
       <c r="G43" t="s">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="H43" t="s">
-        <v>190</v>
+        <v>272</v>
       </c>
       <c r="I43" t="s">
-        <v>216</v>
+        <v>298</v>
       </c>
       <c r="J43" t="s">
-        <v>221</v>
+        <v>73</v>
       </c>
       <c r="K43" t="s">
-        <v>222</v>
+        <v>303</v>
       </c>
       <c r="L43" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="M43" s="3" t="s">
-        <v>223</v>
+        <v>304</v>
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>224</v>
+        <v>305</v>
       </c>
       <c r="B44" t="s">
-        <v>225</v>
+        <v>306</v>
       </c>
       <c r="C44" t="s">
-        <v>18</v>
+        <v>103</v>
       </c>
       <c r="D44" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E44" t="s">
-        <v>20</v>
+        <v>104</v>
       </c>
       <c r="F44" s="1">
         <v>1968</v>
       </c>
       <c r="G44" t="s">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="H44" t="s">
-        <v>22</v>
+        <v>106</v>
       </c>
       <c r="I44" t="s">
-        <v>29</v>
+        <v>113</v>
       </c>
       <c r="L44" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="M44" s="3" t="s">
-        <v>226</v>
+        <v>307</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>227</v>
+        <v>308</v>
       </c>
       <c r="B45" t="s">
-        <v>228</v>
+        <v>309</v>
       </c>
       <c r="C45" t="s">
-        <v>18</v>
+        <v>103</v>
       </c>
       <c r="D45" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E45" t="s">
-        <v>20</v>
+        <v>104</v>
       </c>
       <c r="F45" s="1">
         <v>1967</v>
       </c>
       <c r="G45" t="s">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="H45" t="s">
-        <v>22</v>
+        <v>106</v>
       </c>
       <c r="I45" t="s">
-        <v>29</v>
+        <v>113</v>
       </c>
       <c r="L45" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="M45" s="3" t="s">
-        <v>229</v>
+        <v>310</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>230</v>
+        <v>311</v>
       </c>
       <c r="B46" t="s">
-        <v>231</v>
+        <v>312</v>
       </c>
       <c r="C46" t="s">
-        <v>18</v>
+        <v>103</v>
       </c>
       <c r="D46" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E46" t="s">
-        <v>20</v>
+        <v>104</v>
       </c>
       <c r="F46" s="1">
         <v>1968</v>
       </c>
       <c r="G46" t="s">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="H46" t="s">
-        <v>22</v>
+        <v>106</v>
       </c>
       <c r="I46" t="s">
-        <v>29</v>
+        <v>113</v>
       </c>
       <c r="L46" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="M46" s="3" t="s">
-        <v>232</v>
+        <v>313</v>
       </c>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>233</v>
+        <v>314</v>
       </c>
       <c r="B47" t="s">
-        <v>234</v>
+        <v>315</v>
       </c>
       <c r="C47" t="s">
-        <v>18</v>
+        <v>103</v>
       </c>
       <c r="D47" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E47" t="s">
-        <v>20</v>
+        <v>104</v>
       </c>
       <c r="F47" s="1">
         <v>1969</v>
       </c>
       <c r="G47" t="s">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="H47" t="s">
-        <v>22</v>
+        <v>106</v>
       </c>
       <c r="I47" t="s">
-        <v>36</v>
+        <v>120</v>
       </c>
       <c r="L47" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>235</v>
+        <v>316</v>
       </c>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>236</v>
+        <v>317</v>
       </c>
       <c r="B48" t="s">
-        <v>237</v>
+        <v>318</v>
       </c>
       <c r="C48" t="s">
-        <v>18</v>
+        <v>103</v>
       </c>
       <c r="D48" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E48" t="s">
-        <v>20</v>
+        <v>104</v>
       </c>
       <c r="F48" s="1">
         <v>1971</v>
       </c>
       <c r="G48" t="s">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="H48" t="s">
-        <v>22</v>
+        <v>106</v>
       </c>
       <c r="I48" t="s">
-        <v>36</v>
+        <v>120</v>
       </c>
       <c r="L48" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="M48" s="3" t="s">
-        <v>238</v>
+        <v>319</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>239</v>
+        <v>320</v>
       </c>
       <c r="B49" t="s">
-        <v>240</v>
+        <v>321</v>
       </c>
       <c r="C49" t="s">
-        <v>18</v>
+        <v>103</v>
       </c>
       <c r="D49" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E49" t="s">
-        <v>20</v>
+        <v>104</v>
       </c>
       <c r="F49" s="1">
         <v>1968</v>
       </c>
       <c r="G49" t="s">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="H49" t="s">
-        <v>22</v>
+        <v>106</v>
       </c>
       <c r="I49" t="s">
-        <v>29</v>
+        <v>113</v>
       </c>
       <c r="L49" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="M49" s="3" t="s">
-        <v>241</v>
+        <v>322</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>242</v>
+        <v>323</v>
       </c>
       <c r="B50" t="s">
-        <v>243</v>
+        <v>324</v>
       </c>
       <c r="C50" t="s">
-        <v>18</v>
+        <v>103</v>
       </c>
       <c r="D50" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E50" t="s">
-        <v>20</v>
+        <v>104</v>
       </c>
       <c r="F50" s="1">
         <v>1968</v>
       </c>
       <c r="G50" t="s">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="H50" t="s">
-        <v>22</v>
+        <v>106</v>
       </c>
       <c r="I50" t="s">
-        <v>29</v>
+        <v>113</v>
       </c>
       <c r="L50" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="M50" s="3" t="s">
-        <v>244</v>
+        <v>325</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>245</v>
+        <v>326</v>
       </c>
       <c r="B51" t="s">
-        <v>246</v>
+        <v>327</v>
       </c>
       <c r="C51" t="s">
-        <v>18</v>
+        <v>103</v>
       </c>
       <c r="D51" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E51" t="s">
-        <v>20</v>
+        <v>104</v>
       </c>
       <c r="F51" s="1">
         <v>1968</v>
       </c>
       <c r="G51" t="s">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="H51" t="s">
-        <v>22</v>
+        <v>106</v>
       </c>
       <c r="I51" t="s">
-        <v>29</v>
+        <v>113</v>
       </c>
       <c r="L51" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="M51" s="3" t="s">
-        <v>247</v>
+        <v>328</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>248</v>
+        <v>329</v>
       </c>
       <c r="B52" t="s">
-        <v>249</v>
+        <v>330</v>
       </c>
       <c r="C52" t="s">
-        <v>18</v>
+        <v>103</v>
       </c>
       <c r="D52" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E52" t="s">
-        <v>20</v>
+        <v>104</v>
       </c>
       <c r="F52" s="1">
         <v>1968</v>
       </c>
       <c r="G52" t="s">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="H52" t="s">
-        <v>22</v>
+        <v>106</v>
       </c>
       <c r="I52" t="s">
-        <v>36</v>
+        <v>120</v>
       </c>
       <c r="L52" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="M52" s="3" t="s">
-        <v>250</v>
+        <v>331</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>251</v>
+        <v>332</v>
       </c>
       <c r="B53" t="s">
-        <v>252</v>
+        <v>333</v>
       </c>
       <c r="C53" t="s">
-        <v>253</v>
+        <v>334</v>
       </c>
       <c r="D53" t="s">
-        <v>253</v>
+        <v>334</v>
       </c>
       <c r="E53" t="s">
-        <v>254</v>
+        <v>335</v>
       </c>
       <c r="F53" s="1">
         <v>1969</v>
       </c>
       <c r="G53" t="s">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="H53" t="s">
-        <v>190</v>
+        <v>272</v>
       </c>
       <c r="I53" t="s">
-        <v>71</v>
+        <v>154</v>
       </c>
       <c r="L53" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="M53" s="3" t="s">
-        <v>255</v>
+        <v>336</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>256</v>
+        <v>337</v>
       </c>
       <c r="B54" t="s">
-        <v>257</v>
+        <v>338</v>
       </c>
       <c r="C54" t="s">
-        <v>95</v>
+        <v>178</v>
       </c>
       <c r="F54" s="1">
         <v>1972</v>
       </c>
       <c r="G54" t="s">
-        <v>97</v>
+        <v>180</v>
       </c>
       <c r="H54" t="s">
-        <v>258</v>
+        <v>339</v>
       </c>
       <c r="I54" t="s">
-        <v>71</v>
+        <v>154</v>
       </c>
       <c r="K54" t="s">
-        <v>259</v>
+        <v>340</v>
       </c>
       <c r="L54" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="M54" s="3" t="s">
-        <v>260</v>
+        <v>341</v>
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>261</v>
+        <v>342</v>
       </c>
       <c r="B55" t="s">
-        <v>262</v>
+        <v>343</v>
       </c>
       <c r="C55" t="s">
-        <v>263</v>
+        <v>344</v>
       </c>
       <c r="D55" t="s">
-        <v>263</v>
+        <v>344</v>
       </c>
       <c r="E55" t="s">
-        <v>264</v>
+        <v>345</v>
       </c>
       <c r="F55" s="6" t="s">
-        <v>265</v>
+        <v>346</v>
       </c>
       <c r="G55" t="s">
-        <v>266</v>
+        <v>347</v>
       </c>
       <c r="H55" t="s">
-        <v>190</v>
+        <v>272</v>
       </c>
       <c r="I55" t="s">
-        <v>71</v>
+        <v>154</v>
       </c>
       <c r="J55" t="s">
-        <v>267</v>
+        <v>34</v>
       </c>
       <c r="L55" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="M55" s="3" t="s">
-        <v>268</v>
+        <v>348</v>
       </c>
       <c r="N55" t="s">
-        <v>269</v>
+        <v>349</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>270</v>
+        <v>350</v>
       </c>
       <c r="B56" t="s">
-        <v>271</v>
+        <v>351</v>
       </c>
       <c r="C56" t="s">
-        <v>67</v>
+        <v>150</v>
       </c>
       <c r="D56" t="s">
-        <v>67</v>
+        <v>150</v>
       </c>
       <c r="E56" t="s">
-        <v>84</v>
+        <v>167</v>
       </c>
       <c r="F56" s="1">
         <v>1967</v>
       </c>
       <c r="G56" t="s">
-        <v>266</v>
+        <v>347</v>
       </c>
       <c r="I56" t="s">
-        <v>71</v>
+        <v>154</v>
       </c>
       <c r="L56" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="M56" s="3" t="s">
-        <v>272</v>
+        <v>352</v>
       </c>
       <c r="N56" t="s">
-        <v>273</v>
+        <v>353</v>
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>274</v>
+        <v>354</v>
       </c>
       <c r="B57" t="s">
-        <v>275</v>
+        <v>355</v>
       </c>
       <c r="C57" t="s">
-        <v>102</v>
+        <v>185</v>
       </c>
       <c r="D57" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E57" t="s">
-        <v>102</v>
+        <v>185</v>
       </c>
       <c r="F57" s="1">
         <v>1967</v>
       </c>
       <c r="G57" t="s">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="H57" t="s">
-        <v>190</v>
+        <v>272</v>
       </c>
       <c r="I57" t="s">
-        <v>216</v>
+        <v>298</v>
       </c>
       <c r="L57" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="M57" s="3" t="s">
-        <v>276</v>
+        <v>356</v>
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>277</v>
+        <v>357</v>
       </c>
       <c r="B58" t="s">
-        <v>278</v>
+        <v>358</v>
       </c>
       <c r="C58" t="s">
-        <v>263</v>
+        <v>344</v>
       </c>
       <c r="D58" t="s">
-        <v>263</v>
+        <v>344</v>
       </c>
       <c r="E58" t="s">
-        <v>264</v>
+        <v>345</v>
       </c>
       <c r="F58" s="2">
         <v>28253</v>
       </c>
       <c r="G58" t="s">
-        <v>78</v>
+        <v>161</v>
       </c>
       <c r="H58" t="s">
-        <v>195</v>
+        <v>277</v>
       </c>
       <c r="I58" t="s">
-        <v>71</v>
+        <v>154</v>
       </c>
       <c r="J58" t="s">
-        <v>267</v>
+        <v>34</v>
       </c>
       <c r="K58" t="s">
-        <v>279</v>
+        <v>359</v>
       </c>
       <c r="L58" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="M58" s="3" t="s">
-        <v>280</v>
+        <v>360</v>
       </c>
       <c r="N58" t="s">
-        <v>281</v>
+        <v>361</v>
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>282</v>
+        <v>362</v>
       </c>
       <c r="B59" t="s">
-        <v>283</v>
+        <v>363</v>
       </c>
       <c r="C59" t="s">
-        <v>102</v>
+        <v>185</v>
       </c>
       <c r="D59" t="s">
-        <v>284</v>
+        <v>80</v>
       </c>
       <c r="E59" t="s">
-        <v>102</v>
+        <v>185</v>
       </c>
       <c r="F59">
         <v>1970</v>
       </c>
       <c r="G59" t="s">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="H59" t="s">
-        <v>190</v>
+        <v>272</v>
       </c>
       <c r="I59" t="s">
-        <v>109</v>
+        <v>192</v>
       </c>
       <c r="L59" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="M59" s="3" t="s">
-        <v>285</v>
+        <v>364</v>
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>286</v>
+        <v>365</v>
       </c>
       <c r="B60" t="s">
-        <v>287</v>
+        <v>366</v>
       </c>
       <c r="C60" t="s">
-        <v>102</v>
+        <v>185</v>
       </c>
       <c r="D60" t="s">
-        <v>284</v>
+        <v>80</v>
       </c>
       <c r="E60" t="s">
-        <v>102</v>
+        <v>185</v>
       </c>
       <c r="F60">
         <v>1970</v>
       </c>
       <c r="G60" t="s">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="H60" t="s">
-        <v>190</v>
+        <v>272</v>
       </c>
       <c r="I60" t="s">
-        <v>109</v>
+        <v>192</v>
       </c>
       <c r="L60" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="M60" s="3" t="s">
-        <v>288</v>
+        <v>367</v>
       </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>289</v>
+        <v>368</v>
       </c>
       <c r="B61" t="s">
-        <v>290</v>
+        <v>369</v>
       </c>
       <c r="C61" t="s">
-        <v>102</v>
+        <v>185</v>
       </c>
       <c r="D61" t="s">
-        <v>291</v>
+        <v>76</v>
       </c>
       <c r="E61" t="s">
-        <v>102</v>
+        <v>185</v>
       </c>
       <c r="F61">
         <v>1965</v>
       </c>
       <c r="G61" t="s">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="H61" t="s">
-        <v>190</v>
+        <v>272</v>
       </c>
       <c r="I61" t="s">
-        <v>109</v>
+        <v>192</v>
       </c>
       <c r="J61" t="s">
-        <v>292</v>
+        <v>83</v>
       </c>
       <c r="L61" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="M61" s="3" t="s">
-        <v>293</v>
+        <v>370</v>
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>294</v>
+        <v>371</v>
       </c>
       <c r="B62" t="s">
-        <v>295</v>
+        <v>372</v>
       </c>
       <c r="C62" t="s">
-        <v>18</v>
+        <v>103</v>
       </c>
       <c r="D62" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E62" t="s">
-        <v>20</v>
+        <v>104</v>
       </c>
       <c r="F62" s="1">
         <v>1971</v>
       </c>
       <c r="G62" t="s">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="H62" t="s">
-        <v>22</v>
+        <v>106</v>
       </c>
       <c r="I62" t="s">
-        <v>29</v>
+        <v>113</v>
       </c>
       <c r="L62" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="M62" s="3" t="s">
-        <v>296</v>
+        <v>373</v>
       </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>297</v>
+        <v>374</v>
       </c>
       <c r="B63" t="s">
-        <v>298</v>
+        <v>375</v>
       </c>
       <c r="F63" s="4">
         <v>24917</v>
       </c>
       <c r="G63" t="s">
-        <v>78</v>
+        <v>161</v>
       </c>
       <c r="H63" t="s">
-        <v>299</v>
+        <v>376</v>
       </c>
       <c r="I63" t="s">
-        <v>109</v>
+        <v>192</v>
       </c>
       <c r="K63" t="s">
-        <v>300</v>
+        <v>377</v>
       </c>
       <c r="L63" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="M63" s="3" t="s">
-        <v>301</v>
+        <v>378</v>
       </c>
       <c r="N63" t="s">
-        <v>302</v>
+        <v>379</v>
       </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>303</v>
+        <v>380</v>
       </c>
       <c r="B64" t="s">
-        <v>304</v>
+        <v>381</v>
       </c>
       <c r="C64" t="s">
-        <v>259</v>
+        <v>340</v>
       </c>
       <c r="D64" t="s">
-        <v>259</v>
+        <v>340</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>305</v>
+        <v>382</v>
       </c>
       <c r="G64" t="s">
-        <v>97</v>
+        <v>180</v>
       </c>
       <c r="H64" t="s">
-        <v>306</v>
+        <v>383</v>
       </c>
       <c r="I64" t="s">
-        <v>71</v>
+        <v>154</v>
       </c>
       <c r="L64" t="s">
-        <v>307</v>
+        <v>384</v>
       </c>
       <c r="M64" s="3" t="s">
-        <v>308</v>
+        <v>385</v>
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>309</v>
+        <v>386</v>
       </c>
       <c r="B65" t="s">
-        <v>310</v>
+        <v>387</v>
       </c>
       <c r="C65" t="s">
-        <v>311</v>
+        <v>388</v>
       </c>
       <c r="D65" t="s">
-        <v>311</v>
+        <v>388</v>
       </c>
       <c r="F65" s="4">
         <v>26956</v>
       </c>
       <c r="G65" t="s">
-        <v>97</v>
+        <v>180</v>
       </c>
       <c r="H65" t="s">
-        <v>306</v>
+        <v>383</v>
       </c>
       <c r="I65" t="s">
-        <v>71</v>
+        <v>154</v>
       </c>
       <c r="L65" t="s">
-        <v>307</v>
+        <v>384</v>
       </c>
       <c r="M65" s="3" t="s">
-        <v>312</v>
+        <v>389</v>
       </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>313</v>
+        <v>390</v>
       </c>
       <c r="B66" t="s">
-        <v>314</v>
+        <v>391</v>
       </c>
       <c r="C66" t="s">
-        <v>67</v>
+        <v>150</v>
       </c>
       <c r="F66">
         <v>1968</v>
       </c>
       <c r="G66" t="s">
-        <v>78</v>
+        <v>161</v>
       </c>
       <c r="H66" t="s">
-        <v>190</v>
+        <v>272</v>
       </c>
       <c r="I66" t="s">
-        <v>71</v>
+        <v>154</v>
       </c>
       <c r="L66" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="M66" s="3" t="s">
-        <v>315</v>
+        <v>392</v>
       </c>
       <c r="N66" t="s">
-        <v>316</v>
+        <v>393</v>
       </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>317</v>
+        <v>394</v>
       </c>
       <c r="B67" t="s">
-        <v>318</v>
+        <v>395</v>
       </c>
       <c r="C67" t="s">
-        <v>319</v>
+        <v>396</v>
       </c>
       <c r="F67">
         <v>1970</v>
       </c>
       <c r="G67" t="s">
-        <v>78</v>
+        <v>161</v>
       </c>
       <c r="H67" t="s">
-        <v>190</v>
+        <v>272</v>
       </c>
       <c r="I67" t="s">
-        <v>71</v>
+        <v>154</v>
       </c>
       <c r="L67" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="M67" s="3" t="s">
-        <v>320</v>
+        <v>397</v>
       </c>
       <c r="N67" t="s">
-        <v>321</v>
+        <v>398</v>
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>322</v>
+        <v>399</v>
       </c>
       <c r="B68" t="s">
-        <v>323</v>
+        <v>400</v>
       </c>
       <c r="C68" t="s">
-        <v>67</v>
+        <v>150</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>157</v>
+        <v>240</v>
       </c>
       <c r="G68" t="s">
-        <v>97</v>
+        <v>180</v>
       </c>
       <c r="H68" t="s">
-        <v>70</v>
+        <v>153</v>
       </c>
       <c r="I68" t="s">
-        <v>71</v>
+        <v>154</v>
       </c>
       <c r="L68" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="M68" s="3" t="s">
-        <v>324</v>
+        <v>401</v>
       </c>
       <c r="N68" t="s">
-        <v>325</v>
+        <v>402</v>
       </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>326</v>
+        <v>403</v>
       </c>
       <c r="B69" t="s">
-        <v>327</v>
+        <v>404</v>
       </c>
       <c r="C69" t="s">
-        <v>328</v>
+        <v>405</v>
       </c>
       <c r="D69" t="s">
-        <v>328</v>
+        <v>405</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>329</v>
+        <v>406</v>
       </c>
       <c r="G69" t="s">
-        <v>122</v>
+        <v>205</v>
       </c>
       <c r="H69" t="s">
-        <v>115</v>
+        <v>198</v>
       </c>
       <c r="I69" t="s">
-        <v>124</v>
+        <v>207</v>
       </c>
       <c r="L69" t="s">
-        <v>125</v>
+        <v>208</v>
       </c>
       <c r="M69" s="3" t="s">
-        <v>330</v>
+        <v>407</v>
       </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>331</v>
+        <v>408</v>
       </c>
       <c r="B70" t="s">
-        <v>332</v>
+        <v>409</v>
       </c>
       <c r="C70" t="s">
-        <v>328</v>
+        <v>405</v>
       </c>
       <c r="D70" t="s">
-        <v>328</v>
+        <v>405</v>
       </c>
       <c r="F70" s="8">
         <v>25704</v>
       </c>
       <c r="G70" t="s">
-        <v>122</v>
+        <v>205</v>
       </c>
       <c r="H70" t="s">
-        <v>115</v>
+        <v>198</v>
       </c>
       <c r="I70" t="s">
-        <v>124</v>
+        <v>207</v>
       </c>
       <c r="L70" t="s">
-        <v>125</v>
+        <v>208</v>
       </c>
       <c r="M70" s="3" t="s">
-        <v>333</v>
+        <v>410</v>
       </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>334</v>
+        <v>411</v>
       </c>
       <c r="B71" t="s">
-        <v>335</v>
+        <v>412</v>
       </c>
       <c r="C71" t="s">
-        <v>328</v>
+        <v>405</v>
       </c>
       <c r="D71" t="s">
-        <v>328</v>
+        <v>405</v>
       </c>
       <c r="F71" s="4">
         <v>25718</v>
       </c>
       <c r="G71" t="s">
-        <v>122</v>
+        <v>205</v>
       </c>
       <c r="H71" t="s">
-        <v>115</v>
+        <v>198</v>
       </c>
       <c r="I71" t="s">
-        <v>124</v>
+        <v>207</v>
       </c>
       <c r="L71" t="s">
-        <v>125</v>
+        <v>208</v>
       </c>
       <c r="M71" s="3" t="s">
-        <v>336</v>
+        <v>413</v>
       </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>337</v>
+        <v>414</v>
       </c>
       <c r="B72" t="s">
-        <v>338</v>
+        <v>415</v>
       </c>
       <c r="C72" t="s">
-        <v>328</v>
+        <v>405</v>
       </c>
       <c r="D72" t="s">
-        <v>328</v>
+        <v>405</v>
       </c>
       <c r="F72" s="4">
         <v>25719</v>
       </c>
       <c r="G72" t="s">
-        <v>122</v>
+        <v>205</v>
       </c>
       <c r="H72" t="s">
-        <v>115</v>
+        <v>198</v>
       </c>
       <c r="I72" t="s">
-        <v>124</v>
+        <v>207</v>
       </c>
       <c r="L72" t="s">
-        <v>125</v>
+        <v>208</v>
       </c>
       <c r="M72" s="3" t="s">
-        <v>339</v>
+        <v>416</v>
       </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>340</v>
+        <v>417</v>
       </c>
       <c r="B73" t="s">
-        <v>341</v>
+        <v>418</v>
       </c>
       <c r="C73" t="s">
-        <v>328</v>
+        <v>405</v>
       </c>
       <c r="D73" t="s">
-        <v>328</v>
+        <v>405</v>
       </c>
       <c r="F73" s="4">
         <v>25740</v>
       </c>
       <c r="G73" t="s">
-        <v>122</v>
+        <v>205</v>
       </c>
       <c r="H73" t="s">
-        <v>115</v>
+        <v>198</v>
       </c>
       <c r="I73" t="s">
-        <v>124</v>
+        <v>207</v>
       </c>
       <c r="L73" t="s">
-        <v>125</v>
+        <v>208</v>
       </c>
       <c r="M73" s="3" t="s">
-        <v>342</v>
+        <v>419</v>
       </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>343</v>
+        <v>420</v>
       </c>
       <c r="B74" t="s">
-        <v>344</v>
+        <v>421</v>
       </c>
       <c r="C74" t="s">
-        <v>328</v>
+        <v>405</v>
       </c>
       <c r="D74" t="s">
-        <v>328</v>
+        <v>405</v>
       </c>
       <c r="F74" s="4">
         <v>25765</v>
       </c>
       <c r="G74" t="s">
-        <v>122</v>
+        <v>205</v>
       </c>
       <c r="H74" t="s">
-        <v>115</v>
+        <v>198</v>
       </c>
       <c r="I74" t="s">
-        <v>124</v>
+        <v>207</v>
       </c>
       <c r="L74" t="s">
-        <v>125</v>
+        <v>208</v>
       </c>
       <c r="M74" s="3" t="s">
-        <v>345</v>
+        <v>422</v>
       </c>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>346</v>
+        <v>423</v>
       </c>
       <c r="B75" t="s">
-        <v>347</v>
+        <v>424</v>
       </c>
       <c r="C75" t="s">
-        <v>328</v>
+        <v>405</v>
       </c>
       <c r="D75" t="s">
-        <v>328</v>
+        <v>405</v>
       </c>
       <c r="F75" s="4">
         <v>25824</v>
       </c>
       <c r="G75" t="s">
-        <v>122</v>
+        <v>205</v>
       </c>
       <c r="H75" t="s">
-        <v>115</v>
+        <v>198</v>
       </c>
       <c r="I75" t="s">
-        <v>124</v>
+        <v>207</v>
       </c>
       <c r="L75" t="s">
-        <v>125</v>
+        <v>208</v>
       </c>
       <c r="M75" s="3" t="s">
-        <v>348</v>
+        <v>425</v>
       </c>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>349</v>
+        <v>426</v>
       </c>
       <c r="B76" t="s">
-        <v>350</v>
+        <v>427</v>
       </c>
       <c r="C76" t="s">
-        <v>328</v>
+        <v>405</v>
       </c>
       <c r="D76" t="s">
-        <v>328</v>
+        <v>405</v>
       </c>
       <c r="F76" s="4">
         <v>25866</v>
       </c>
       <c r="G76" t="s">
-        <v>122</v>
+        <v>205</v>
       </c>
       <c r="H76" t="s">
-        <v>115</v>
+        <v>198</v>
       </c>
       <c r="I76" t="s">
-        <v>124</v>
+        <v>207</v>
       </c>
       <c r="L76" t="s">
-        <v>125</v>
+        <v>208</v>
       </c>
       <c r="M76" s="3" t="s">
-        <v>351</v>
+        <v>428</v>
       </c>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>352</v>
+        <v>429</v>
       </c>
       <c r="B77" t="s">
-        <v>353</v>
+        <v>430</v>
       </c>
       <c r="C77" t="s">
-        <v>328</v>
+        <v>405</v>
       </c>
       <c r="D77" t="s">
-        <v>328</v>
+        <v>405</v>
       </c>
       <c r="F77" s="4">
         <v>25887</v>
       </c>
       <c r="G77" t="s">
-        <v>122</v>
+        <v>205</v>
       </c>
       <c r="H77" t="s">
-        <v>115</v>
+        <v>198</v>
       </c>
       <c r="I77" t="s">
-        <v>124</v>
+        <v>207</v>
       </c>
       <c r="L77" t="s">
-        <v>125</v>
+        <v>208</v>
       </c>
       <c r="M77" s="3" t="s">
-        <v>354</v>
+        <v>431</v>
       </c>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>355</v>
+        <v>432</v>
       </c>
       <c r="B78" t="s">
-        <v>356</v>
+        <v>433</v>
       </c>
       <c r="C78" t="s">
-        <v>328</v>
+        <v>405</v>
       </c>
       <c r="D78" t="s">
-        <v>328</v>
+        <v>405</v>
       </c>
       <c r="F78" s="4">
         <v>25915</v>
       </c>
       <c r="G78" t="s">
-        <v>122</v>
+        <v>205</v>
       </c>
       <c r="H78" t="s">
-        <v>115</v>
+        <v>198</v>
       </c>
       <c r="I78" t="s">
-        <v>124</v>
+        <v>207</v>
       </c>
       <c r="L78" t="s">
-        <v>125</v>
+        <v>208</v>
       </c>
       <c r="M78" s="3" t="s">
-        <v>357</v>
+        <v>434</v>
       </c>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>358</v>
+        <v>435</v>
       </c>
       <c r="B79" t="s">
-        <v>359</v>
+        <v>436</v>
       </c>
       <c r="C79" t="s">
-        <v>328</v>
+        <v>405</v>
       </c>
       <c r="D79" t="s">
-        <v>328</v>
+        <v>405</v>
       </c>
       <c r="F79" s="4">
         <v>25950</v>
       </c>
       <c r="G79" t="s">
-        <v>122</v>
+        <v>205</v>
       </c>
       <c r="H79" t="s">
-        <v>115</v>
+        <v>198</v>
       </c>
       <c r="I79" t="s">
-        <v>124</v>
+        <v>207</v>
       </c>
       <c r="L79" t="s">
-        <v>125</v>
+        <v>208</v>
       </c>
       <c r="M79" s="3" t="s">
-        <v>360</v>
+        <v>437</v>
       </c>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>361</v>
+        <v>438</v>
       </c>
       <c r="B80" t="s">
-        <v>362</v>
+        <v>439</v>
       </c>
       <c r="C80" t="s">
-        <v>328</v>
+        <v>405</v>
       </c>
       <c r="D80" t="s">
-        <v>328</v>
+        <v>405</v>
       </c>
       <c r="F80" s="4">
         <v>25971</v>
       </c>
       <c r="G80" t="s">
-        <v>122</v>
+        <v>205</v>
       </c>
       <c r="H80" t="s">
-        <v>115</v>
+        <v>198</v>
       </c>
       <c r="I80" t="s">
-        <v>124</v>
+        <v>207</v>
       </c>
       <c r="L80" t="s">
-        <v>125</v>
+        <v>208</v>
       </c>
       <c r="M80" s="3" t="s">
-        <v>363</v>
+        <v>440</v>
       </c>
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>364</v>
+        <v>441</v>
       </c>
       <c r="B81" t="s">
-        <v>365</v>
+        <v>442</v>
       </c>
       <c r="C81" t="s">
-        <v>328</v>
+        <v>405</v>
       </c>
       <c r="D81" t="s">
-        <v>328</v>
+        <v>405</v>
       </c>
       <c r="F81" s="4">
         <v>25999</v>
       </c>
       <c r="G81" t="s">
-        <v>122</v>
+        <v>205</v>
       </c>
       <c r="H81" t="s">
-        <v>115</v>
+        <v>198</v>
       </c>
       <c r="I81" t="s">
-        <v>124</v>
+        <v>207</v>
       </c>
       <c r="L81" t="s">
-        <v>125</v>
+        <v>208</v>
       </c>
       <c r="M81" s="3" t="s">
-        <v>366</v>
+        <v>443</v>
       </c>
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>367</v>
+        <v>444</v>
       </c>
       <c r="B82" t="s">
-        <v>368</v>
+        <v>445</v>
       </c>
       <c r="C82" t="s">
-        <v>328</v>
+        <v>405</v>
       </c>
       <c r="D82" t="s">
-        <v>328</v>
+        <v>405</v>
       </c>
       <c r="F82" s="4">
         <v>26027</v>
       </c>
       <c r="G82" t="s">
-        <v>122</v>
+        <v>205</v>
       </c>
       <c r="H82" t="s">
-        <v>115</v>
+        <v>198</v>
       </c>
       <c r="I82" t="s">
-        <v>124</v>
+        <v>207</v>
       </c>
       <c r="L82" t="s">
-        <v>125</v>
+        <v>208</v>
       </c>
       <c r="M82" s="3" t="s">
-        <v>369</v>
+        <v>446</v>
       </c>
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>370</v>
+        <v>447</v>
       </c>
       <c r="B83" t="s">
-        <v>371</v>
+        <v>448</v>
       </c>
       <c r="C83" t="s">
-        <v>328</v>
+        <v>405</v>
       </c>
       <c r="D83" t="s">
-        <v>328</v>
+        <v>405</v>
       </c>
       <c r="F83" s="4">
         <v>26054</v>
       </c>
       <c r="G83" t="s">
-        <v>122</v>
+        <v>205</v>
       </c>
       <c r="H83" t="s">
-        <v>115</v>
+        <v>198</v>
       </c>
       <c r="I83" t="s">
-        <v>124</v>
+        <v>207</v>
       </c>
       <c r="L83" t="s">
-        <v>125</v>
+        <v>208</v>
       </c>
       <c r="M83" s="3" t="s">
-        <v>372</v>
+        <v>449</v>
       </c>
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>373</v>
+        <v>450</v>
       </c>
       <c r="B84" t="s">
-        <v>374</v>
+        <v>451</v>
       </c>
       <c r="C84" t="s">
-        <v>328</v>
+        <v>405</v>
       </c>
       <c r="D84" t="s">
-        <v>328</v>
+        <v>405</v>
       </c>
       <c r="F84" s="4">
         <v>26076</v>
       </c>
       <c r="G84" t="s">
-        <v>122</v>
+        <v>205</v>
       </c>
       <c r="H84" t="s">
-        <v>115</v>
+        <v>198</v>
       </c>
       <c r="I84" t="s">
-        <v>124</v>
+        <v>207</v>
       </c>
       <c r="L84" t="s">
-        <v>125</v>
+        <v>208</v>
       </c>
       <c r="M84" s="3" t="s">
-        <v>375</v>
+        <v>452</v>
       </c>
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>376</v>
+        <v>453</v>
       </c>
       <c r="B85" t="s">
-        <v>377</v>
+        <v>454</v>
       </c>
       <c r="C85" t="s">
-        <v>328</v>
+        <v>405</v>
       </c>
       <c r="D85" t="s">
-        <v>328</v>
+        <v>405</v>
       </c>
       <c r="F85" s="4">
         <v>26104</v>
       </c>
       <c r="G85" t="s">
-        <v>122</v>
+        <v>205</v>
       </c>
       <c r="H85" t="s">
-        <v>115</v>
+        <v>198</v>
       </c>
       <c r="I85" t="s">
-        <v>124</v>
+        <v>207</v>
       </c>
       <c r="L85" t="s">
-        <v>125</v>
+        <v>208</v>
       </c>
       <c r="M85" s="3" t="s">
-        <v>378</v>
+        <v>455</v>
       </c>
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>379</v>
+        <v>456</v>
       </c>
       <c r="B86" t="s">
-        <v>380</v>
+        <v>457</v>
       </c>
       <c r="C86" t="s">
-        <v>328</v>
+        <v>405</v>
       </c>
       <c r="D86" t="s">
-        <v>328</v>
+        <v>405</v>
       </c>
       <c r="F86" s="4">
         <v>26139</v>
       </c>
       <c r="G86" t="s">
-        <v>122</v>
+        <v>205</v>
       </c>
       <c r="H86" t="s">
-        <v>115</v>
+        <v>198</v>
       </c>
       <c r="I86" t="s">
-        <v>124</v>
+        <v>207</v>
       </c>
       <c r="L86" t="s">
-        <v>125</v>
+        <v>208</v>
       </c>
       <c r="M86" s="3" t="s">
-        <v>381</v>
+        <v>458</v>
       </c>
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>382</v>
+        <v>459</v>
       </c>
       <c r="B87" t="s">
-        <v>383</v>
+        <v>460</v>
       </c>
       <c r="C87" t="s">
-        <v>328</v>
+        <v>405</v>
       </c>
       <c r="D87" t="s">
-        <v>328</v>
+        <v>405</v>
       </c>
       <c r="F87" s="4">
         <v>26265</v>
       </c>
       <c r="G87" t="s">
-        <v>122</v>
+        <v>205</v>
       </c>
       <c r="H87" t="s">
-        <v>115</v>
+        <v>198</v>
       </c>
       <c r="I87" t="s">
-        <v>124</v>
+        <v>207</v>
       </c>
       <c r="L87" t="s">
-        <v>125</v>
+        <v>208</v>
       </c>
       <c r="M87" s="3" t="s">
-        <v>384</v>
+        <v>461</v>
       </c>
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>385</v>
+        <v>462</v>
       </c>
       <c r="B88" t="s">
-        <v>386</v>
+        <v>463</v>
       </c>
       <c r="C88" t="s">
-        <v>328</v>
+        <v>405</v>
       </c>
       <c r="D88" t="s">
-        <v>328</v>
+        <v>405</v>
       </c>
       <c r="F88" s="4">
         <v>26307</v>
       </c>
       <c r="G88" t="s">
-        <v>122</v>
+        <v>205</v>
       </c>
       <c r="H88" t="s">
-        <v>115</v>
+        <v>198</v>
       </c>
       <c r="I88" t="s">
-        <v>124</v>
+        <v>207</v>
       </c>
       <c r="L88" t="s">
-        <v>125</v>
+        <v>208</v>
       </c>
       <c r="M88" s="3" t="s">
-        <v>387</v>
+        <v>464</v>
       </c>
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>388</v>
+        <v>465</v>
       </c>
       <c r="B89" t="s">
-        <v>389</v>
+        <v>466</v>
       </c>
       <c r="C89" t="s">
-        <v>328</v>
+        <v>405</v>
       </c>
       <c r="D89" t="s">
-        <v>328</v>
+        <v>405</v>
       </c>
       <c r="F89" s="4">
         <v>26370</v>
       </c>
       <c r="G89" t="s">
-        <v>122</v>
+        <v>205</v>
       </c>
       <c r="H89" t="s">
-        <v>115</v>
+        <v>198</v>
       </c>
       <c r="I89" t="s">
-        <v>124</v>
+        <v>207</v>
       </c>
       <c r="L89" t="s">
-        <v>125</v>
+        <v>208</v>
       </c>
       <c r="M89" s="3" t="s">
-        <v>390</v>
+        <v>467</v>
       </c>
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>391</v>
+        <v>468</v>
       </c>
       <c r="B90" t="s">
-        <v>392</v>
+        <v>469</v>
       </c>
       <c r="C90" t="s">
-        <v>328</v>
+        <v>405</v>
       </c>
       <c r="D90" t="s">
-        <v>328</v>
+        <v>405</v>
       </c>
       <c r="F90" s="4">
         <v>26420</v>
       </c>
       <c r="G90" t="s">
-        <v>122</v>
+        <v>205</v>
       </c>
       <c r="H90" t="s">
-        <v>115</v>
+        <v>198</v>
       </c>
       <c r="I90" t="s">
-        <v>124</v>
+        <v>207</v>
       </c>
       <c r="L90" t="s">
-        <v>125</v>
+        <v>208</v>
       </c>
       <c r="M90" s="3" t="s">
-        <v>393</v>
+        <v>470</v>
       </c>
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>394</v>
+        <v>471</v>
       </c>
       <c r="B91" t="s">
-        <v>395</v>
+        <v>472</v>
       </c>
       <c r="C91" t="s">
-        <v>328</v>
+        <v>405</v>
       </c>
       <c r="D91" t="s">
-        <v>328</v>
+        <v>405</v>
       </c>
       <c r="F91" s="4">
         <v>26608</v>
       </c>
       <c r="G91" t="s">
-        <v>122</v>
+        <v>205</v>
       </c>
       <c r="H91" t="s">
-        <v>115</v>
+        <v>198</v>
       </c>
       <c r="I91" t="s">
-        <v>124</v>
+        <v>207</v>
       </c>
       <c r="L91" t="s">
-        <v>125</v>
+        <v>208</v>
       </c>
       <c r="M91" s="3" t="s">
-        <v>396</v>
+        <v>473</v>
       </c>
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>397</v>
+        <v>474</v>
       </c>
       <c r="B92" t="s">
-        <v>398</v>
+        <v>475</v>
       </c>
       <c r="C92" t="s">
-        <v>328</v>
+        <v>405</v>
       </c>
       <c r="D92" t="s">
-        <v>328</v>
+        <v>405</v>
       </c>
       <c r="F92" s="4">
         <v>26785</v>
       </c>
       <c r="G92" t="s">
-        <v>122</v>
+        <v>205</v>
       </c>
       <c r="H92" t="s">
-        <v>115</v>
+        <v>198</v>
       </c>
       <c r="I92" t="s">
-        <v>124</v>
+        <v>207</v>
       </c>
       <c r="L92" t="s">
-        <v>125</v>
+        <v>208</v>
       </c>
       <c r="M92" s="3" t="s">
-        <v>399</v>
+        <v>476</v>
       </c>
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>400</v>
+        <v>477</v>
       </c>
       <c r="B93" t="s">
-        <v>401</v>
+        <v>478</v>
       </c>
       <c r="C93" t="s">
-        <v>95</v>
+        <v>178</v>
       </c>
       <c r="E93" t="s">
-        <v>402</v>
+        <v>479</v>
       </c>
       <c r="F93">
         <v>1969</v>
       </c>
       <c r="G93" t="s">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="H93" t="s">
-        <v>190</v>
+        <v>272</v>
       </c>
       <c r="I93" t="s">
-        <v>36</v>
+        <v>120</v>
       </c>
       <c r="K93" t="s">
-        <v>18</v>
+        <v>103</v>
       </c>
       <c r="L93" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="M93" s="3" t="s">
-        <v>403</v>
+        <v>480</v>
       </c>
     </row>
     <row r="94" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>404</v>
+        <v>481</v>
       </c>
       <c r="B94" t="s">
-        <v>405</v>
+        <v>482</v>
       </c>
       <c r="C94" t="s">
-        <v>406</v>
+        <v>483</v>
       </c>
       <c r="D94" t="s">
-        <v>406</v>
+        <v>483</v>
       </c>
       <c r="F94" s="5" t="s">
-        <v>407</v>
+        <v>484</v>
       </c>
       <c r="G94" t="s">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="H94" t="s">
-        <v>408</v>
+        <v>485</v>
       </c>
       <c r="I94" t="s">
-        <v>71</v>
+        <v>154</v>
       </c>
       <c r="L94" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="M94" s="3" t="s">
-        <v>409</v>
+        <v>486</v>
       </c>
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>410</v>
+        <v>487</v>
       </c>
       <c r="B95" t="s">
-        <v>411</v>
+        <v>488</v>
       </c>
       <c r="C95" t="s">
-        <v>18</v>
+        <v>103</v>
       </c>
       <c r="D95" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E95" t="s">
-        <v>20</v>
+        <v>104</v>
       </c>
       <c r="F95">
         <v>1968</v>
       </c>
       <c r="G95" t="s">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="H95" t="s">
-        <v>22</v>
+        <v>106</v>
       </c>
       <c r="I95" t="s">
-        <v>36</v>
+        <v>120</v>
       </c>
       <c r="L95" t="s">
-        <v>37</v>
+        <v>121</v>
       </c>
       <c r="M95" s="3" t="s">
-        <v>412</v>
+        <v>489</v>
       </c>
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>413</v>
+        <v>490</v>
       </c>
       <c r="B96" t="s">
-        <v>414</v>
+        <v>491</v>
       </c>
       <c r="C96" t="s">
-        <v>18</v>
+        <v>103</v>
       </c>
       <c r="D96" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E96" t="s">
-        <v>20</v>
+        <v>104</v>
       </c>
       <c r="F96">
         <v>1969</v>
       </c>
       <c r="G96" t="s">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="H96" t="s">
-        <v>22</v>
+        <v>106</v>
       </c>
       <c r="I96" t="s">
-        <v>36</v>
+        <v>120</v>
       </c>
       <c r="K96" t="s">
-        <v>222</v>
+        <v>303</v>
       </c>
       <c r="L96" t="s">
-        <v>37</v>
+        <v>121</v>
       </c>
       <c r="M96" s="3" t="s">
-        <v>415</v>
+        <v>492</v>
       </c>
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>416</v>
+        <v>493</v>
       </c>
       <c r="B97" t="s">
-        <v>417</v>
+        <v>494</v>
       </c>
       <c r="F97">
         <v>1973</v>
       </c>
       <c r="G97" t="s">
-        <v>78</v>
+        <v>161</v>
       </c>
       <c r="I97" t="s">
-        <v>109</v>
+        <v>192</v>
       </c>
       <c r="J97" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="L97" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="M97" s="3" t="s">
-        <v>418</v>
+        <v>495</v>
       </c>
       <c r="N97" t="s">
-        <v>419</v>
+        <v>496</v>
       </c>
     </row>
   </sheetData>
@@ -5743,82 +5783,82 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A1" s="10" t="s">
-        <v>425</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>426</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>435</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>436</v>
+      <c r="A1" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>420</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>421</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>427</v>
+        <v>5</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>422</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>423</v>
+        <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>424</v>
-      </c>
-      <c r="K1" s="10" t="s">
-        <v>428</v>
-      </c>
-      <c r="L1" s="10" t="s">
-        <v>429</v>
-      </c>
-      <c r="M1" s="10" t="s">
-        <v>430</v>
-      </c>
-      <c r="N1" s="10" t="s">
-        <v>431</v>
-      </c>
-      <c r="O1" s="10" t="s">
-        <v>432</v>
-      </c>
-      <c r="P1" s="10" t="s">
-        <v>433</v>
-      </c>
-      <c r="Q1" s="10" t="s">
-        <v>434</v>
-      </c>
-      <c r="R1" s="10" t="s">
-        <v>437</v>
+        <v>9</v>
+      </c>
+      <c r="K1" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>440</v>
+        <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>441</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>445</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>446</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F2" t="s">
-        <v>438</v>
+        <v>23</v>
       </c>
       <c r="G2" t="s">
-        <v>593</v>
+        <v>24</v>
       </c>
       <c r="H2">
         <v>1893</v>
@@ -5827,39 +5867,39 @@
         <v>1976</v>
       </c>
       <c r="J2" t="s">
-        <v>439</v>
+        <v>25</v>
       </c>
       <c r="O2" t="s">
-        <v>442</v>
+        <v>26</v>
       </c>
       <c r="P2" t="s">
-        <v>443</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>444</v>
+        <v>27</v>
+      </c>
+      <c r="Q2" s="4">
+        <v>46297</v>
       </c>
       <c r="R2" t="s">
-        <v>447</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>451</v>
+        <v>29</v>
       </c>
       <c r="B3" t="s">
-        <v>441</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>445</v>
+        <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>446</v>
+        <v>21</v>
       </c>
       <c r="E3" t="s">
-        <v>448</v>
+        <v>30</v>
       </c>
       <c r="F3" t="s">
-        <v>449</v>
+        <v>31</v>
       </c>
       <c r="H3">
         <v>1921</v>
@@ -5868,39 +5908,39 @@
         <v>1993</v>
       </c>
       <c r="J3" t="s">
-        <v>450</v>
+        <v>32</v>
       </c>
       <c r="O3" t="s">
-        <v>442</v>
+        <v>26</v>
       </c>
       <c r="P3" t="s">
-        <v>443</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>444</v>
+        <v>27</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>46297</v>
       </c>
       <c r="R3" t="s">
-        <v>447</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>454</v>
+        <v>33</v>
       </c>
       <c r="B4" t="s">
-        <v>441</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>445</v>
+        <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>446</v>
+        <v>21</v>
       </c>
       <c r="E4" t="s">
-        <v>267</v>
+        <v>34</v>
       </c>
       <c r="F4" t="s">
-        <v>452</v>
+        <v>35</v>
       </c>
       <c r="H4">
         <v>1938</v>
@@ -5909,39 +5949,39 @@
         <v>2021</v>
       </c>
       <c r="J4" t="s">
-        <v>453</v>
+        <v>36</v>
       </c>
       <c r="O4" t="s">
-        <v>442</v>
+        <v>26</v>
       </c>
       <c r="P4" t="s">
-        <v>443</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>444</v>
+        <v>27</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>46297</v>
       </c>
       <c r="R4" t="s">
-        <v>447</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>456</v>
+        <v>37</v>
       </c>
       <c r="B5" t="s">
-        <v>441</v>
+        <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>445</v>
+        <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>446</v>
+        <v>21</v>
       </c>
       <c r="E5" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="F5" t="s">
-        <v>455</v>
+        <v>39</v>
       </c>
       <c r="H5">
         <v>1931</v>
@@ -5950,36 +5990,36 @@
         <v>2005</v>
       </c>
       <c r="O5" t="s">
-        <v>442</v>
+        <v>26</v>
       </c>
       <c r="P5" t="s">
-        <v>443</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>444</v>
+        <v>27</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>46297</v>
       </c>
       <c r="R5" t="s">
-        <v>447</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>459</v>
+        <v>40</v>
       </c>
       <c r="B6" t="s">
-        <v>441</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>445</v>
+        <v>20</v>
       </c>
       <c r="D6" t="s">
-        <v>446</v>
+        <v>21</v>
       </c>
       <c r="E6" t="s">
-        <v>457</v>
+        <v>41</v>
       </c>
       <c r="F6" t="s">
-        <v>458</v>
+        <v>42</v>
       </c>
       <c r="H6">
         <v>1960</v>
@@ -5988,103 +6028,115 @@
         <v>2023</v>
       </c>
       <c r="O6" t="s">
-        <v>442</v>
+        <v>26</v>
       </c>
       <c r="P6" t="s">
-        <v>443</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>444</v>
+        <v>27</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>46297</v>
       </c>
       <c r="R6" t="s">
-        <v>447</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>461</v>
+        <v>43</v>
       </c>
       <c r="B7" t="s">
-        <v>441</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>445</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>446</v>
+        <v>21</v>
       </c>
       <c r="E7" t="s">
-        <v>171</v>
+        <v>44</v>
       </c>
       <c r="F7" t="s">
-        <v>460</v>
+        <v>45</v>
+      </c>
+      <c r="H7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I7" t="s">
+        <v>46</v>
       </c>
       <c r="O7" t="s">
-        <v>442</v>
+        <v>26</v>
       </c>
       <c r="P7" t="s">
-        <v>443</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>444</v>
+        <v>27</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>46297</v>
       </c>
       <c r="R7" t="s">
-        <v>462</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>465</v>
+        <v>47</v>
       </c>
       <c r="B8" t="s">
-        <v>441</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>445</v>
+        <v>20</v>
       </c>
       <c r="D8" t="s">
-        <v>446</v>
+        <v>21</v>
       </c>
       <c r="E8" t="s">
-        <v>463</v>
+        <v>48</v>
       </c>
       <c r="F8" t="s">
-        <v>464</v>
+        <v>49</v>
+      </c>
+      <c r="H8" t="s">
+        <v>46</v>
+      </c>
+      <c r="I8" t="s">
+        <v>46</v>
       </c>
       <c r="O8" t="s">
-        <v>442</v>
+        <v>26</v>
       </c>
       <c r="P8" t="s">
-        <v>443</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>444</v>
+        <v>27</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>46297</v>
       </c>
       <c r="R8" t="s">
-        <v>462</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>468</v>
+        <v>50</v>
       </c>
       <c r="B9" t="s">
-        <v>441</v>
+        <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>445</v>
+        <v>20</v>
       </c>
       <c r="D9" t="s">
-        <v>446</v>
+        <v>21</v>
       </c>
       <c r="E9" t="s">
-        <v>466</v>
+        <v>51</v>
       </c>
       <c r="F9" t="s">
-        <v>467</v>
+        <v>52</v>
       </c>
       <c r="G9" t="s">
-        <v>594</v>
+        <v>53</v>
       </c>
       <c r="H9">
         <v>1907</v>
@@ -6093,36 +6145,36 @@
         <v>1971</v>
       </c>
       <c r="O9" t="s">
-        <v>442</v>
+        <v>26</v>
       </c>
       <c r="P9" t="s">
-        <v>443</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>444</v>
+        <v>27</v>
+      </c>
+      <c r="Q9" s="4">
+        <v>46297</v>
       </c>
       <c r="R9" t="s">
-        <v>447</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>471</v>
+        <v>54</v>
       </c>
       <c r="B10" t="s">
-        <v>441</v>
+        <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>445</v>
+        <v>20</v>
       </c>
       <c r="D10" t="s">
-        <v>446</v>
+        <v>21</v>
       </c>
       <c r="E10" t="s">
-        <v>469</v>
+        <v>55</v>
       </c>
       <c r="F10" t="s">
-        <v>470</v>
+        <v>56</v>
       </c>
       <c r="H10">
         <v>1898</v>
@@ -6131,36 +6183,39 @@
         <v>1975</v>
       </c>
       <c r="O10" t="s">
-        <v>442</v>
+        <v>26</v>
       </c>
       <c r="P10" t="s">
-        <v>443</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>444</v>
+        <v>27</v>
+      </c>
+      <c r="Q10" s="4">
+        <v>46297</v>
       </c>
       <c r="R10" t="s">
-        <v>447</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>474</v>
+        <v>57</v>
       </c>
       <c r="B11" t="s">
-        <v>441</v>
+        <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>445</v>
+        <v>20</v>
       </c>
       <c r="D11" t="s">
-        <v>446</v>
+        <v>21</v>
       </c>
       <c r="E11" t="s">
-        <v>472</v>
+        <v>58</v>
       </c>
       <c r="F11" t="s">
-        <v>473</v>
+        <v>59</v>
+      </c>
+      <c r="G11" t="s">
+        <v>60</v>
       </c>
       <c r="H11">
         <v>1898</v>
@@ -6169,36 +6224,39 @@
         <v>1976</v>
       </c>
       <c r="O11" t="s">
-        <v>442</v>
+        <v>26</v>
       </c>
       <c r="P11" t="s">
-        <v>443</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>444</v>
+        <v>27</v>
+      </c>
+      <c r="Q11" s="4">
+        <v>46297</v>
       </c>
       <c r="R11" t="s">
-        <v>447</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>477</v>
+        <v>61</v>
       </c>
       <c r="B12" t="s">
-        <v>441</v>
+        <v>19</v>
       </c>
       <c r="C12" t="s">
-        <v>445</v>
+        <v>20</v>
       </c>
       <c r="D12" t="s">
-        <v>446</v>
+        <v>21</v>
       </c>
       <c r="E12" t="s">
-        <v>475</v>
+        <v>62</v>
       </c>
       <c r="F12" t="s">
-        <v>476</v>
+        <v>63</v>
+      </c>
+      <c r="G12" t="s">
+        <v>64</v>
       </c>
       <c r="H12">
         <v>1904</v>
@@ -6207,36 +6265,39 @@
         <v>1989</v>
       </c>
       <c r="O12" t="s">
-        <v>442</v>
+        <v>26</v>
       </c>
       <c r="P12" t="s">
-        <v>443</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>444</v>
+        <v>27</v>
+      </c>
+      <c r="Q12" s="4">
+        <v>46297</v>
       </c>
       <c r="R12" t="s">
-        <v>447</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>480</v>
+        <v>65</v>
       </c>
       <c r="B13" t="s">
-        <v>441</v>
+        <v>19</v>
       </c>
       <c r="C13" t="s">
-        <v>445</v>
+        <v>20</v>
       </c>
       <c r="D13" t="s">
-        <v>446</v>
+        <v>21</v>
       </c>
       <c r="E13" t="s">
-        <v>478</v>
+        <v>66</v>
       </c>
       <c r="F13" t="s">
-        <v>479</v>
+        <v>67</v>
+      </c>
+      <c r="G13" t="s">
+        <v>68</v>
       </c>
       <c r="H13">
         <v>1914</v>
@@ -6245,36 +6306,36 @@
         <v>1991</v>
       </c>
       <c r="O13" t="s">
-        <v>442</v>
+        <v>26</v>
       </c>
       <c r="P13" t="s">
-        <v>443</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>444</v>
+        <v>27</v>
+      </c>
+      <c r="Q13" s="4">
+        <v>46297</v>
       </c>
       <c r="R13" t="s">
-        <v>447</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>483</v>
+        <v>69</v>
       </c>
       <c r="B14" t="s">
-        <v>441</v>
+        <v>19</v>
       </c>
       <c r="C14" t="s">
-        <v>445</v>
+        <v>20</v>
       </c>
       <c r="D14" t="s">
-        <v>446</v>
+        <v>21</v>
       </c>
       <c r="E14" t="s">
-        <v>481</v>
+        <v>70</v>
       </c>
       <c r="F14" t="s">
-        <v>482</v>
+        <v>71</v>
       </c>
       <c r="H14">
         <v>1920</v>
@@ -6283,36 +6344,36 @@
         <v>2004</v>
       </c>
       <c r="O14" t="s">
-        <v>442</v>
+        <v>26</v>
       </c>
       <c r="P14" t="s">
-        <v>443</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>444</v>
+        <v>27</v>
+      </c>
+      <c r="Q14" s="4">
+        <v>46297</v>
       </c>
       <c r="R14" t="s">
-        <v>447</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>485</v>
+        <v>72</v>
       </c>
       <c r="B15" t="s">
-        <v>441</v>
+        <v>19</v>
       </c>
       <c r="C15" t="s">
-        <v>445</v>
+        <v>20</v>
       </c>
       <c r="D15" t="s">
-        <v>446</v>
+        <v>21</v>
       </c>
       <c r="E15" t="s">
-        <v>221</v>
+        <v>73</v>
       </c>
       <c r="F15" t="s">
-        <v>484</v>
+        <v>74</v>
       </c>
       <c r="H15">
         <v>1920</v>
@@ -6321,39 +6382,39 @@
         <v>1997</v>
       </c>
       <c r="O15" t="s">
-        <v>442</v>
+        <v>26</v>
       </c>
       <c r="P15" t="s">
-        <v>443</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>444</v>
+        <v>27</v>
+      </c>
+      <c r="Q15" s="4">
+        <v>46297</v>
       </c>
       <c r="R15" t="s">
-        <v>447</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>487</v>
+        <v>75</v>
       </c>
       <c r="B16" t="s">
-        <v>441</v>
+        <v>19</v>
       </c>
       <c r="C16" t="s">
-        <v>445</v>
+        <v>20</v>
       </c>
       <c r="D16" t="s">
-        <v>446</v>
+        <v>21</v>
       </c>
       <c r="E16" t="s">
-        <v>291</v>
+        <v>76</v>
       </c>
       <c r="F16" t="s">
-        <v>486</v>
+        <v>77</v>
       </c>
       <c r="G16" t="s">
-        <v>595</v>
+        <v>78</v>
       </c>
       <c r="H16">
         <v>1898</v>
@@ -6362,80 +6423,92 @@
         <v>1969</v>
       </c>
       <c r="O16" t="s">
-        <v>442</v>
+        <v>26</v>
       </c>
       <c r="P16" t="s">
-        <v>443</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>444</v>
+        <v>27</v>
+      </c>
+      <c r="Q16" s="4">
+        <v>46297</v>
       </c>
       <c r="R16" t="s">
-        <v>447</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>489</v>
+        <v>79</v>
       </c>
       <c r="B17" t="s">
-        <v>441</v>
+        <v>19</v>
       </c>
       <c r="C17" t="s">
-        <v>445</v>
+        <v>20</v>
       </c>
       <c r="D17" t="s">
-        <v>446</v>
+        <v>21</v>
       </c>
       <c r="E17" t="s">
-        <v>284</v>
+        <v>80</v>
       </c>
       <c r="F17" t="s">
-        <v>488</v>
+        <v>81</v>
+      </c>
+      <c r="H17">
+        <v>1924</v>
+      </c>
+      <c r="I17">
+        <v>2010</v>
       </c>
       <c r="O17" t="s">
-        <v>442</v>
+        <v>26</v>
       </c>
       <c r="P17" t="s">
-        <v>443</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>444</v>
+        <v>27</v>
+      </c>
+      <c r="Q17" s="4">
+        <v>46297</v>
       </c>
       <c r="R17" t="s">
-        <v>490</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>492</v>
+        <v>82</v>
       </c>
       <c r="B18" t="s">
-        <v>441</v>
+        <v>19</v>
       </c>
       <c r="C18" t="s">
-        <v>445</v>
+        <v>20</v>
       </c>
       <c r="D18" t="s">
-        <v>446</v>
+        <v>21</v>
       </c>
       <c r="E18" t="s">
-        <v>292</v>
+        <v>83</v>
       </c>
       <c r="F18" t="s">
-        <v>491</v>
+        <v>84</v>
+      </c>
+      <c r="H18">
+        <v>1933</v>
+      </c>
+      <c r="I18">
+        <v>1996</v>
       </c>
       <c r="O18" t="s">
-        <v>442</v>
+        <v>26</v>
       </c>
       <c r="P18" t="s">
-        <v>443</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>444</v>
+        <v>27</v>
+      </c>
+      <c r="Q18" s="4">
+        <v>46297</v>
       </c>
       <c r="R18" t="s">
-        <v>493</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -6468,129 +6541,129 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A1" s="10" t="s">
-        <v>425</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>426</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>435</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>436</v>
+      <c r="A1" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>420</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>427</v>
+        <v>4</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>6</v>
       </c>
       <c r="G1" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="H1" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="I1" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="J1" t="s">
-        <v>424</v>
-      </c>
-      <c r="K1" s="10" t="s">
-        <v>497</v>
-      </c>
-      <c r="L1" s="10" t="s">
-        <v>429</v>
-      </c>
-      <c r="M1" s="10" t="s">
-        <v>430</v>
-      </c>
-      <c r="N1" s="10" t="s">
-        <v>431</v>
-      </c>
-      <c r="O1" s="10" t="s">
-        <v>432</v>
-      </c>
-      <c r="P1" s="10" t="s">
-        <v>433</v>
-      </c>
-      <c r="Q1" s="10" t="s">
-        <v>434</v>
-      </c>
-      <c r="R1" s="10" t="s">
-        <v>437</v>
+        <v>9</v>
+      </c>
+      <c r="K1" s="9" t="s">
+        <v>500</v>
+      </c>
+      <c r="L1" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C2" t="s">
-        <v>445</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>446</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
-        <v>222</v>
+        <v>303</v>
       </c>
       <c r="G2" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="H2">
         <v>1962</v>
       </c>
       <c r="I2" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="O2" t="s">
-        <v>442</v>
+        <v>26</v>
       </c>
       <c r="P2" t="s">
-        <v>443</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>444</v>
+        <v>27</v>
+      </c>
+      <c r="Q2" s="4">
+        <v>46297</v>
       </c>
       <c r="R2" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="B3" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C3" t="s">
-        <v>445</v>
+        <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>446</v>
+        <v>21</v>
       </c>
       <c r="E3" t="s">
-        <v>20</v>
+        <v>104</v>
       </c>
       <c r="G3" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="H3">
         <v>1952</v>
       </c>
       <c r="O3" t="s">
-        <v>442</v>
+        <v>26</v>
       </c>
       <c r="P3" t="s">
-        <v>443</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>444</v>
+        <v>27</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>46297</v>
       </c>
       <c r="R3" t="s">
         <v>505</v>
@@ -6598,22 +6671,22 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B4" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C4" t="s">
-        <v>445</v>
+        <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>446</v>
+        <v>21</v>
       </c>
       <c r="E4" t="s">
-        <v>102</v>
+        <v>185</v>
       </c>
       <c r="G4" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="H4">
         <v>1963</v>
@@ -6622,13 +6695,13 @@
         <v>1979</v>
       </c>
       <c r="O4" t="s">
-        <v>442</v>
+        <v>26</v>
       </c>
       <c r="P4" t="s">
-        <v>443</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>444</v>
+        <v>27</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>46297</v>
       </c>
       <c r="R4" t="s">
         <v>505</v>
@@ -6636,37 +6709,37 @@
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B5" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C5" t="s">
-        <v>445</v>
+        <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>446</v>
+        <v>21</v>
       </c>
       <c r="E5" t="s">
-        <v>77</v>
+        <v>160</v>
       </c>
       <c r="F5" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="G5" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="H5">
         <v>1948</v>
       </c>
       <c r="O5" t="s">
-        <v>442</v>
+        <v>26</v>
       </c>
       <c r="P5" t="s">
-        <v>443</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>444</v>
+        <v>27</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>46297</v>
       </c>
       <c r="R5" t="s">
         <v>505</v>
@@ -6674,25 +6747,25 @@
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B6" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C6" t="s">
-        <v>445</v>
+        <v>20</v>
       </c>
       <c r="D6" t="s">
-        <v>446</v>
+        <v>21</v>
       </c>
       <c r="E6" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="F6" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="G6" t="s">
-        <v>507</v>
+        <v>548</v>
       </c>
       <c r="H6">
         <v>1958</v>
@@ -6701,13 +6774,13 @@
         <v>1998</v>
       </c>
       <c r="O6" t="s">
-        <v>442</v>
+        <v>26</v>
       </c>
       <c r="P6" t="s">
-        <v>443</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>444</v>
+        <v>27</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>46297</v>
       </c>
       <c r="R6" t="s">
         <v>505</v>
@@ -6715,22 +6788,22 @@
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B7" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C7" t="s">
-        <v>445</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>446</v>
+        <v>21</v>
       </c>
       <c r="E7" t="s">
-        <v>84</v>
+        <v>167</v>
       </c>
       <c r="G7" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="H7">
         <v>1964</v>
@@ -6739,13 +6812,13 @@
         <v>1991</v>
       </c>
       <c r="O7" t="s">
-        <v>442</v>
+        <v>26</v>
       </c>
       <c r="P7" t="s">
-        <v>443</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>444</v>
+        <v>27</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>46297</v>
       </c>
       <c r="R7" t="s">
         <v>505</v>
@@ -6753,37 +6826,37 @@
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B8" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C8" t="s">
-        <v>445</v>
+        <v>20</v>
       </c>
       <c r="D8" t="s">
-        <v>446</v>
+        <v>21</v>
       </c>
       <c r="E8" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="F8" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="G8" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="H8">
         <v>1956</v>
       </c>
       <c r="O8" t="s">
-        <v>442</v>
+        <v>26</v>
       </c>
       <c r="P8" t="s">
-        <v>443</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>444</v>
+        <v>27</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>46297</v>
       </c>
       <c r="R8" t="s">
         <v>505</v>
@@ -6791,54 +6864,60 @@
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B9" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C9" t="s">
-        <v>445</v>
+        <v>20</v>
       </c>
       <c r="D9" t="s">
-        <v>446</v>
+        <v>21</v>
       </c>
       <c r="E9" t="s">
-        <v>120</v>
+        <v>203</v>
       </c>
       <c r="G9" t="s">
-        <v>517</v>
+        <v>520</v>
+      </c>
+      <c r="H9" t="s">
+        <v>521</v>
+      </c>
+      <c r="I9" t="s">
+        <v>522</v>
       </c>
       <c r="O9" t="s">
-        <v>442</v>
+        <v>26</v>
       </c>
       <c r="P9" t="s">
-        <v>443</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>444</v>
+        <v>27</v>
+      </c>
+      <c r="Q9" s="4">
+        <v>46297</v>
       </c>
       <c r="R9" t="s">
-        <v>519</v>
+        <v>505</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B10" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C10" t="s">
-        <v>445</v>
+        <v>20</v>
       </c>
       <c r="D10" t="s">
-        <v>446</v>
+        <v>21</v>
       </c>
       <c r="E10" t="s">
-        <v>68</v>
+        <v>151</v>
       </c>
       <c r="G10" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="H10">
         <v>1966</v>
@@ -6847,13 +6926,13 @@
         <v>1991</v>
       </c>
       <c r="O10" t="s">
-        <v>442</v>
+        <v>26</v>
       </c>
       <c r="P10" t="s">
-        <v>443</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>444</v>
+        <v>27</v>
+      </c>
+      <c r="Q10" s="4">
+        <v>46297</v>
       </c>
       <c r="R10" t="s">
         <v>505</v>
@@ -6861,22 +6940,22 @@
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="B11" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C11" t="s">
-        <v>445</v>
+        <v>20</v>
       </c>
       <c r="D11" t="s">
-        <v>446</v>
+        <v>21</v>
       </c>
       <c r="E11" t="s">
-        <v>96</v>
+        <v>179</v>
       </c>
       <c r="G11" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="H11">
         <v>1968</v>
@@ -6885,13 +6964,13 @@
         <v>1972</v>
       </c>
       <c r="O11" t="s">
-        <v>442</v>
+        <v>26</v>
       </c>
       <c r="P11" t="s">
-        <v>443</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>444</v>
+        <v>27</v>
+      </c>
+      <c r="Q11" s="4">
+        <v>46297</v>
       </c>
       <c r="R11" t="s">
         <v>505</v>
@@ -6899,22 +6978,22 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>526</v>
+      </c>
+      <c r="B12" t="s">
+        <v>502</v>
+      </c>
+      <c r="C12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" t="s">
+        <v>527</v>
+      </c>
+      <c r="G12" t="s">
         <v>524</v>
-      </c>
-      <c r="B12" t="s">
-        <v>501</v>
-      </c>
-      <c r="C12" t="s">
-        <v>445</v>
-      </c>
-      <c r="D12" t="s">
-        <v>446</v>
-      </c>
-      <c r="E12" t="s">
-        <v>523</v>
-      </c>
-      <c r="G12" t="s">
-        <v>520</v>
       </c>
       <c r="H12">
         <v>1966</v>
@@ -6923,13 +7002,13 @@
         <v>1991</v>
       </c>
       <c r="O12" t="s">
-        <v>442</v>
+        <v>26</v>
       </c>
       <c r="P12" t="s">
-        <v>443</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>444</v>
+        <v>27</v>
+      </c>
+      <c r="Q12" s="4">
+        <v>46297</v>
       </c>
       <c r="R12" t="s">
         <v>505</v>
@@ -6937,34 +7016,34 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B13" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C13" t="s">
-        <v>445</v>
+        <v>20</v>
       </c>
       <c r="D13" t="s">
-        <v>446</v>
+        <v>21</v>
       </c>
       <c r="E13" t="s">
-        <v>202</v>
+        <v>284</v>
       </c>
       <c r="G13" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="H13">
         <v>1921</v>
       </c>
       <c r="O13" t="s">
-        <v>442</v>
+        <v>26</v>
       </c>
       <c r="P13" t="s">
-        <v>443</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>444</v>
+        <v>27</v>
+      </c>
+      <c r="Q13" s="4">
+        <v>46297</v>
       </c>
       <c r="R13" t="s">
         <v>505</v>
@@ -6972,25 +7051,25 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B14" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C14" t="s">
-        <v>445</v>
+        <v>20</v>
       </c>
       <c r="D14" t="s">
-        <v>446</v>
+        <v>21</v>
       </c>
       <c r="E14" t="s">
-        <v>67</v>
+        <v>150</v>
       </c>
       <c r="F14" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="G14" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="H14">
         <v>1966</v>
@@ -6999,16 +7078,16 @@
         <v>1991</v>
       </c>
       <c r="J14" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="O14" t="s">
-        <v>442</v>
+        <v>26</v>
       </c>
       <c r="P14" t="s">
-        <v>443</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>444</v>
+        <v>27</v>
+      </c>
+      <c r="Q14" s="4">
+        <v>46297</v>
       </c>
       <c r="R14" t="s">
         <v>505</v>
@@ -7016,25 +7095,25 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>533</v>
+      </c>
+      <c r="B15" t="s">
+        <v>502</v>
+      </c>
+      <c r="C15" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" t="s">
+        <v>21</v>
+      </c>
+      <c r="E15" t="s">
+        <v>178</v>
+      </c>
+      <c r="F15" t="s">
+        <v>534</v>
+      </c>
+      <c r="G15" t="s">
         <v>531</v>
-      </c>
-      <c r="B15" t="s">
-        <v>501</v>
-      </c>
-      <c r="C15" t="s">
-        <v>445</v>
-      </c>
-      <c r="D15" t="s">
-        <v>446</v>
-      </c>
-      <c r="E15" t="s">
-        <v>95</v>
-      </c>
-      <c r="F15" t="s">
-        <v>532</v>
-      </c>
-      <c r="G15" t="s">
-        <v>526</v>
       </c>
       <c r="H15">
         <v>1968</v>
@@ -7043,16 +7122,16 @@
         <v>1972</v>
       </c>
       <c r="J15" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="O15" t="s">
-        <v>442</v>
+        <v>26</v>
       </c>
       <c r="P15" t="s">
-        <v>443</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>444</v>
+        <v>27</v>
+      </c>
+      <c r="Q15" s="4">
+        <v>46297</v>
       </c>
       <c r="R15" t="s">
         <v>505</v>
@@ -7060,40 +7139,40 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="B16" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C16" t="s">
-        <v>445</v>
+        <v>20</v>
       </c>
       <c r="D16" t="s">
-        <v>446</v>
+        <v>21</v>
       </c>
       <c r="E16" t="s">
-        <v>18</v>
+        <v>103</v>
       </c>
       <c r="F16" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="G16" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="H16">
         <v>1921</v>
       </c>
       <c r="J16" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="O16" t="s">
-        <v>442</v>
+        <v>26</v>
       </c>
       <c r="P16" t="s">
-        <v>443</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>444</v>
+        <v>27</v>
+      </c>
+      <c r="Q16" s="4">
+        <v>46297</v>
       </c>
       <c r="R16" t="s">
         <v>505</v>
@@ -7101,22 +7180,25 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="B17" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C17" t="s">
-        <v>445</v>
+        <v>20</v>
       </c>
       <c r="D17" t="s">
-        <v>446</v>
+        <v>21</v>
       </c>
       <c r="E17" t="s">
-        <v>536</v>
+        <v>540</v>
+      </c>
+      <c r="F17" t="s">
+        <v>541</v>
       </c>
       <c r="G17" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="H17">
         <v>1968</v>
@@ -7125,13 +7207,13 @@
         <v>1969</v>
       </c>
       <c r="O17" t="s">
-        <v>442</v>
+        <v>26</v>
       </c>
       <c r="P17" t="s">
-        <v>443</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>444</v>
+        <v>27</v>
+      </c>
+      <c r="Q17" s="4">
+        <v>46297</v>
       </c>
       <c r="R17" t="s">
         <v>505</v>
@@ -7139,22 +7221,25 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="B18" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C18" t="s">
-        <v>445</v>
+        <v>20</v>
       </c>
       <c r="D18" t="s">
-        <v>446</v>
+        <v>21</v>
       </c>
       <c r="E18" t="s">
-        <v>169</v>
+        <v>252</v>
+      </c>
+      <c r="F18" t="s">
+        <v>543</v>
       </c>
       <c r="G18" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="H18">
         <v>1969</v>
@@ -7163,13 +7248,13 @@
         <v>1976</v>
       </c>
       <c r="O18" t="s">
-        <v>442</v>
+        <v>26</v>
       </c>
       <c r="P18" t="s">
-        <v>443</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>444</v>
+        <v>27</v>
+      </c>
+      <c r="Q18" s="4">
+        <v>46297</v>
       </c>
       <c r="R18" t="s">
         <v>505</v>
@@ -7177,63 +7262,63 @@
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="B19" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C19" t="s">
-        <v>445</v>
+        <v>20</v>
       </c>
       <c r="D19" t="s">
-        <v>446</v>
+        <v>21</v>
       </c>
       <c r="E19" t="s">
-        <v>253</v>
+        <v>334</v>
       </c>
       <c r="G19" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="H19">
         <v>1968</v>
       </c>
       <c r="I19" t="s">
-        <v>539</v>
+        <v>46</v>
       </c>
       <c r="O19" t="s">
-        <v>442</v>
+        <v>26</v>
       </c>
       <c r="P19" t="s">
-        <v>443</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>444</v>
+        <v>27</v>
+      </c>
+      <c r="Q19" s="4">
+        <v>46297</v>
       </c>
       <c r="R19" t="s">
-        <v>541</v>
+        <v>505</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="B20" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C20" t="s">
-        <v>445</v>
+        <v>20</v>
       </c>
       <c r="D20" t="s">
-        <v>446</v>
+        <v>21</v>
       </c>
       <c r="E20" t="s">
-        <v>259</v>
+        <v>340</v>
       </c>
       <c r="F20" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="G20" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="H20">
         <v>1972</v>
@@ -7242,13 +7327,13 @@
         <v>1977</v>
       </c>
       <c r="O20" t="s">
-        <v>442</v>
+        <v>26</v>
       </c>
       <c r="P20" t="s">
-        <v>443</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>444</v>
+        <v>27</v>
+      </c>
+      <c r="Q20" s="4">
+        <v>46297</v>
       </c>
       <c r="R20" t="s">
         <v>505</v>
@@ -7256,22 +7341,22 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="B21" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C21" t="s">
-        <v>445</v>
+        <v>20</v>
       </c>
       <c r="D21" t="s">
-        <v>446</v>
+        <v>21</v>
       </c>
       <c r="E21" t="s">
-        <v>119</v>
+        <v>202</v>
       </c>
       <c r="G21" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="H21">
         <v>1967</v>
@@ -7280,13 +7365,13 @@
         <v>1969</v>
       </c>
       <c r="O21" t="s">
-        <v>442</v>
+        <v>26</v>
       </c>
       <c r="P21" t="s">
-        <v>443</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>444</v>
+        <v>27</v>
+      </c>
+      <c r="Q21" s="4">
+        <v>46297</v>
       </c>
       <c r="R21" t="s">
         <v>505</v>
@@ -7294,22 +7379,25 @@
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="B22" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C22" t="s">
-        <v>445</v>
+        <v>20</v>
       </c>
       <c r="D22" t="s">
-        <v>446</v>
+        <v>21</v>
       </c>
       <c r="E22" t="s">
-        <v>263</v>
+        <v>344</v>
+      </c>
+      <c r="F22" t="s">
+        <v>550</v>
       </c>
       <c r="G22" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="H22">
         <v>1977</v>
@@ -7318,13 +7406,13 @@
         <v>1984</v>
       </c>
       <c r="O22" t="s">
-        <v>442</v>
+        <v>26</v>
       </c>
       <c r="P22" t="s">
-        <v>443</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>444</v>
+        <v>27</v>
+      </c>
+      <c r="Q22" s="4">
+        <v>46297</v>
       </c>
       <c r="R22" t="s">
         <v>505</v>
@@ -7332,22 +7420,22 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="B23" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C23" t="s">
-        <v>445</v>
+        <v>20</v>
       </c>
       <c r="D23" t="s">
-        <v>446</v>
+        <v>21</v>
       </c>
       <c r="E23" t="s">
-        <v>328</v>
+        <v>405</v>
       </c>
       <c r="G23" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="H23">
         <v>1970</v>
@@ -7356,13 +7444,13 @@
         <v>1973</v>
       </c>
       <c r="O23" t="s">
-        <v>442</v>
+        <v>26</v>
       </c>
       <c r="P23" t="s">
-        <v>443</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>444</v>
+        <v>27</v>
+      </c>
+      <c r="Q23" s="4">
+        <v>46297</v>
       </c>
       <c r="R23" t="s">
         <v>505</v>
@@ -7370,179 +7458,242 @@
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="B24" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C24" t="s">
-        <v>445</v>
+        <v>20</v>
       </c>
       <c r="D24" t="s">
-        <v>446</v>
+        <v>21</v>
       </c>
       <c r="E24" t="s">
-        <v>406</v>
+        <v>483</v>
+      </c>
+      <c r="G24" t="s">
+        <v>520</v>
+      </c>
+      <c r="H24">
+        <v>1969</v>
+      </c>
+      <c r="I24">
+        <v>1972</v>
       </c>
       <c r="O24" t="s">
-        <v>442</v>
+        <v>26</v>
       </c>
       <c r="P24" t="s">
-        <v>443</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>444</v>
+        <v>27</v>
+      </c>
+      <c r="Q24" s="4">
+        <v>46297</v>
       </c>
       <c r="R24" t="s">
-        <v>549</v>
+        <v>505</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="B25" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C25" t="s">
-        <v>445</v>
+        <v>20</v>
       </c>
       <c r="D25" t="s">
-        <v>446</v>
+        <v>21</v>
       </c>
       <c r="E25" t="s">
-        <v>311</v>
+        <v>388</v>
       </c>
       <c r="F25" t="s">
-        <v>596</v>
+        <v>554</v>
+      </c>
+      <c r="G25" t="s">
+        <v>531</v>
+      </c>
+      <c r="H25">
+        <v>1973</v>
+      </c>
+      <c r="I25">
+        <v>1977</v>
       </c>
       <c r="O25" t="s">
-        <v>442</v>
+        <v>26</v>
       </c>
       <c r="P25" t="s">
-        <v>443</v>
-      </c>
-      <c r="Q25" t="s">
-        <v>444</v>
+        <v>27</v>
+      </c>
+      <c r="Q25" s="4">
+        <v>46297</v>
       </c>
       <c r="R25" t="s">
-        <v>551</v>
+        <v>505</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="B26" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C26" t="s">
-        <v>445</v>
+        <v>20</v>
       </c>
       <c r="D26" t="s">
-        <v>446</v>
+        <v>21</v>
       </c>
       <c r="E26" t="s">
-        <v>319</v>
+        <v>396</v>
+      </c>
+      <c r="G26" t="s">
+        <v>599</v>
+      </c>
+      <c r="H26" t="s">
+        <v>46</v>
+      </c>
+      <c r="I26" t="s">
+        <v>46</v>
       </c>
       <c r="O26" t="s">
-        <v>442</v>
+        <v>26</v>
       </c>
       <c r="P26" t="s">
-        <v>443</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>444</v>
+        <v>27</v>
+      </c>
+      <c r="Q26" s="4">
+        <v>46297</v>
       </c>
       <c r="R26" t="s">
-        <v>549</v>
+        <v>505</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="B27" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C27" t="s">
-        <v>445</v>
+        <v>20</v>
       </c>
       <c r="D27" t="s">
-        <v>446</v>
+        <v>21</v>
       </c>
       <c r="E27" t="s">
-        <v>553</v>
+        <v>557</v>
+      </c>
+      <c r="F27" t="s">
+        <v>558</v>
+      </c>
+      <c r="G27" t="s">
+        <v>531</v>
+      </c>
+      <c r="H27">
+        <v>1970</v>
+      </c>
+      <c r="I27">
+        <v>1977</v>
       </c>
       <c r="O27" t="s">
-        <v>442</v>
+        <v>26</v>
       </c>
       <c r="P27" t="s">
-        <v>443</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>444</v>
+        <v>27</v>
+      </c>
+      <c r="Q27" s="4">
+        <v>46297</v>
       </c>
       <c r="R27" t="s">
-        <v>549</v>
+        <v>505</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="B28" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C28" t="s">
-        <v>445</v>
+        <v>20</v>
       </c>
       <c r="D28" t="s">
-        <v>446</v>
+        <v>21</v>
       </c>
       <c r="E28" t="s">
-        <v>555</v>
+        <v>560</v>
+      </c>
+      <c r="F28" t="s">
+        <v>561</v>
+      </c>
+      <c r="G28" t="s">
+        <v>531</v>
+      </c>
+      <c r="H28">
+        <v>1969</v>
+      </c>
+      <c r="I28">
+        <v>1977</v>
       </c>
       <c r="O28" t="s">
-        <v>442</v>
+        <v>26</v>
       </c>
       <c r="P28" t="s">
-        <v>443</v>
-      </c>
-      <c r="Q28" t="s">
-        <v>444</v>
+        <v>27</v>
+      </c>
+      <c r="Q28" s="4">
+        <v>46297</v>
       </c>
       <c r="R28" t="s">
-        <v>549</v>
+        <v>505</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="B29" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C29" t="s">
-        <v>445</v>
+        <v>20</v>
       </c>
       <c r="D29" t="s">
-        <v>446</v>
+        <v>21</v>
       </c>
       <c r="E29" t="s">
-        <v>557</v>
+        <v>563</v>
+      </c>
+      <c r="F29" t="s">
+        <v>564</v>
+      </c>
+      <c r="G29" t="s">
+        <v>531</v>
+      </c>
+      <c r="H29">
+        <v>1969</v>
+      </c>
+      <c r="I29">
+        <v>1977</v>
       </c>
       <c r="O29" t="s">
-        <v>442</v>
+        <v>26</v>
       </c>
       <c r="P29" t="s">
-        <v>443</v>
-      </c>
-      <c r="Q29" t="s">
-        <v>444</v>
+        <v>27</v>
+      </c>
+      <c r="Q29" s="4">
+        <v>46297</v>
       </c>
       <c r="R29" t="s">
-        <v>549</v>
+        <v>505</v>
       </c>
     </row>
   </sheetData>
@@ -7558,247 +7709,253 @@
   <dimension ref="A1:J8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="13" customWidth="1"/>
-    <col min="3" max="3" width="45" customWidth="1"/>
-    <col min="4" max="4" width="22" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
-    <col min="7" max="7" width="45" customWidth="1"/>
-    <col min="8" max="8" width="22" customWidth="1"/>
-    <col min="9" max="9" width="38" customWidth="1"/>
-    <col min="10" max="10" width="55" customWidth="1"/>
+    <col min="1" max="1" width="13.21875" customWidth="1"/>
+    <col min="2" max="2" width="11.33203125" customWidth="1"/>
+    <col min="3" max="3" width="29.5546875" customWidth="1"/>
+    <col min="4" max="4" width="11.33203125" customWidth="1"/>
+    <col min="5" max="5" width="43.109375" customWidth="1"/>
+    <col min="6" max="6" width="22.44140625" customWidth="1"/>
+    <col min="7" max="7" width="22" customWidth="1"/>
+    <col min="8" max="8" width="16.77734375" customWidth="1"/>
+    <col min="10" max="10" width="45" customWidth="1"/>
+    <col min="11" max="11" width="22" customWidth="1"/>
+    <col min="12" max="12" width="38" customWidth="1"/>
+    <col min="13" max="13" width="55" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
-        <v>559</v>
+        <v>565</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>560</v>
+        <v>566</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>562</v>
+        <v>570</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>563</v>
+        <v>571</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>566</v>
+        <v>572</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="J1" s="9" t="s">
-        <v>568</v>
+        <v>574</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="B2" t="s">
-        <v>451</v>
+        <v>29</v>
       </c>
       <c r="C2" t="s">
-        <v>448</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>570</v>
+        <v>529</v>
       </c>
       <c r="E2" t="s">
-        <v>571</v>
+        <v>150</v>
       </c>
       <c r="F2" t="s">
-        <v>528</v>
+        <v>576</v>
       </c>
       <c r="G2" t="s">
-        <v>67</v>
+        <v>577</v>
       </c>
       <c r="H2" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="I2" t="s">
-        <v>573</v>
+        <v>579</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="B3" t="s">
-        <v>454</v>
+        <v>33</v>
       </c>
       <c r="C3" t="s">
-        <v>267</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s">
-        <v>575</v>
+        <v>529</v>
       </c>
       <c r="E3" t="s">
-        <v>576</v>
+        <v>150</v>
       </c>
       <c r="F3" t="s">
-        <v>528</v>
+        <v>581</v>
       </c>
       <c r="G3" t="s">
-        <v>67</v>
+        <v>582</v>
       </c>
       <c r="H3" t="s">
-        <v>577</v>
+        <v>583</v>
       </c>
       <c r="I3" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="J3" t="s">
-        <v>579</v>
+        <v>585</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
       <c r="B4" t="s">
-        <v>440</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>581</v>
+        <v>528</v>
       </c>
       <c r="E4" t="s">
-        <v>571</v>
+        <v>284</v>
       </c>
       <c r="F4" t="s">
-        <v>525</v>
+        <v>587</v>
       </c>
       <c r="G4" t="s">
-        <v>202</v>
+        <v>577</v>
       </c>
       <c r="H4" t="s">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="I4" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="B5" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C5" t="s">
-        <v>68</v>
+        <v>151</v>
       </c>
       <c r="D5" t="s">
-        <v>585</v>
+        <v>529</v>
       </c>
       <c r="E5" t="s">
-        <v>571</v>
+        <v>150</v>
       </c>
       <c r="F5" t="s">
-        <v>528</v>
+        <v>591</v>
       </c>
       <c r="G5" t="s">
-        <v>67</v>
+        <v>577</v>
       </c>
       <c r="I5" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="B6" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="C6" t="s">
-        <v>96</v>
+        <v>179</v>
       </c>
       <c r="D6" t="s">
-        <v>588</v>
+        <v>533</v>
       </c>
       <c r="E6" t="s">
-        <v>571</v>
+        <v>178</v>
       </c>
       <c r="F6" t="s">
-        <v>531</v>
+        <v>594</v>
       </c>
       <c r="G6" t="s">
-        <v>95</v>
+        <v>577</v>
       </c>
       <c r="I6" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>589</v>
+        <v>595</v>
       </c>
       <c r="B7" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="C7" t="s">
-        <v>202</v>
+        <v>284</v>
       </c>
       <c r="D7" t="s">
-        <v>585</v>
+        <v>536</v>
       </c>
       <c r="E7" t="s">
-        <v>571</v>
+        <v>103</v>
       </c>
       <c r="F7" t="s">
-        <v>534</v>
+        <v>591</v>
       </c>
       <c r="G7" t="s">
-        <v>18</v>
+        <v>577</v>
       </c>
       <c r="I7" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="B8" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C8" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="D8" t="s">
-        <v>591</v>
+        <v>529</v>
       </c>
       <c r="E8" t="s">
-        <v>591</v>
+        <v>150</v>
       </c>
       <c r="F8" t="s">
-        <v>528</v>
+        <v>597</v>
       </c>
       <c r="G8" t="s">
-        <v>67</v>
+        <v>597</v>
       </c>
       <c r="I8" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
       <c r="J8" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/data/dati.xlsx
+++ b/data/dati.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan_\Desktop\AMI\GitHub\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E302D8AB-518E-4E36-99EA-1D0B0B656F2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A23F9D1C-20F8-49EF-97F1-AC53AA9177E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Catalogo" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1511" uniqueCount="600">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1518" uniqueCount="598">
   <si>
     <t>ID_autorita</t>
   </si>
@@ -1759,12 +1759,6 @@
     <t>gerarchica</t>
   </si>
   <si>
-    <t>attestato al 1969-10-03</t>
-  </si>
-  <si>
-    <t>Titolo di AMI-0016</t>
-  </si>
-  <si>
     <t>AMI-R-002</t>
   </si>
   <si>
@@ -1774,15 +1768,6 @@
     <t>associativa</t>
   </si>
   <si>
-    <t>attestato al 1968-08-31</t>
-  </si>
-  <si>
-    <t>Titolo di AMI-0015</t>
-  </si>
-  <si>
-    <t>Il titolo associa Pesce al partito senza indicarne la carica</t>
-  </si>
-  <si>
     <t>AMI-R-003</t>
   </si>
   <si>
@@ -1792,18 +1777,12 @@
     <t>attestato al 1968</t>
   </si>
   <si>
-    <t>Titolo di AMI-0004</t>
-  </si>
-  <si>
     <t>AMI-R-004</t>
   </si>
   <si>
     <t>organo di</t>
   </si>
   <si>
-    <t>Denominazione dell'ente</t>
-  </si>
-  <si>
     <t>AMI-R-005</t>
   </si>
   <si>
@@ -1819,17 +1798,32 @@
     <t>da definire</t>
   </si>
   <si>
-    <t>Natura del rapporto (scissione, frazione, ecc.) da documentare con una fonte</t>
-  </si>
-  <si>
     <t>Movimento</t>
+  </si>
+  <si>
+    <t>1966-1991</t>
+  </si>
+  <si>
+    <t>1966-1970</t>
+  </si>
+  <si>
+    <t>AMI-R-008</t>
+  </si>
+  <si>
+    <t>AMI-R-009</t>
+  </si>
+  <si>
+    <t>1970-1977</t>
+  </si>
+  <si>
+    <t>1977-1984</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1851,6 +1845,12 @@
       <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -2011,8 +2011,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{4895E276-9036-4388-B350-F25B94D00A98}" name="Tabella5" displayName="Tabella5" ref="A1:J8" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A1:J8" xr:uid="{4895E276-9036-4388-B350-F25B94D00A98}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{4895E276-9036-4388-B350-F25B94D00A98}" name="Tabella5" displayName="Tabella5" ref="A1:J10" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A1:J10" xr:uid="{4895E276-9036-4388-B350-F25B94D00A98}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{681E8224-5D12-4699-8FCD-F6D6D65EDFAF}" name="ID_relazione"/>
     <tableColumn id="2" xr3:uid="{ABB6B5F5-BCC1-4479-A7C9-B3517A2E96E9}" name="ID_entita_A"/>
@@ -7552,7 +7552,7 @@
         <v>396</v>
       </c>
       <c r="G26" t="s">
-        <v>599</v>
+        <v>591</v>
       </c>
       <c r="H26" t="s">
         <v>46</v>
@@ -7706,7 +7706,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.21875" customWidth="1"/>
@@ -7778,15 +7778,12 @@
         <v>577</v>
       </c>
       <c r="H2" t="s">
-        <v>578</v>
-      </c>
-      <c r="I2" t="s">
-        <v>579</v>
+        <v>592</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="B3" t="s">
         <v>33</v>
@@ -7801,158 +7798,187 @@
         <v>150</v>
       </c>
       <c r="F3" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="G3" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="H3" t="s">
-        <v>583</v>
-      </c>
-      <c r="I3" t="s">
-        <v>584</v>
-      </c>
-      <c r="J3" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s">
-        <v>528</v>
+        <v>556</v>
       </c>
       <c r="E4" t="s">
-        <v>284</v>
+        <v>557</v>
       </c>
       <c r="F4" t="s">
-        <v>587</v>
+        <v>576</v>
       </c>
       <c r="G4" t="s">
         <v>577</v>
       </c>
       <c r="H4" t="s">
-        <v>588</v>
-      </c>
-      <c r="I4" t="s">
-        <v>589</v>
+        <v>596</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="B5" t="s">
-        <v>523</v>
+        <v>33</v>
       </c>
       <c r="C5" t="s">
-        <v>151</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s">
-        <v>529</v>
+        <v>549</v>
       </c>
       <c r="E5" t="s">
-        <v>150</v>
+        <v>344</v>
       </c>
       <c r="F5" t="s">
-        <v>591</v>
+        <v>576</v>
       </c>
       <c r="G5" t="s">
         <v>577</v>
       </c>
-      <c r="I5" t="s">
-        <v>592</v>
+      <c r="H5" t="s">
+        <v>597</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>593</v>
+        <v>586</v>
       </c>
       <c r="B6" t="s">
-        <v>525</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>179</v>
+        <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="E6" t="s">
-        <v>178</v>
+        <v>284</v>
       </c>
       <c r="F6" t="s">
-        <v>594</v>
+        <v>582</v>
       </c>
       <c r="G6" t="s">
         <v>577</v>
       </c>
-      <c r="I6" t="s">
-        <v>592</v>
+      <c r="H6" t="s">
+        <v>583</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>595</v>
+        <v>588</v>
       </c>
       <c r="B7" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="C7" t="s">
-        <v>284</v>
+        <v>151</v>
       </c>
       <c r="D7" t="s">
-        <v>536</v>
+        <v>529</v>
       </c>
       <c r="E7" t="s">
-        <v>103</v>
+        <v>150</v>
       </c>
       <c r="F7" t="s">
-        <v>591</v>
+        <v>585</v>
       </c>
       <c r="G7" t="s">
         <v>577</v>
       </c>
-      <c r="I7" t="s">
-        <v>592</v>
-      </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>596</v>
+        <v>589</v>
       </c>
       <c r="B8" t="s">
+        <v>525</v>
+      </c>
+      <c r="C8" t="s">
+        <v>179</v>
+      </c>
+      <c r="D8" t="s">
+        <v>533</v>
+      </c>
+      <c r="E8" t="s">
+        <v>178</v>
+      </c>
+      <c r="F8" t="s">
+        <v>587</v>
+      </c>
+      <c r="G8" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>594</v>
+      </c>
+      <c r="B9" t="s">
+        <v>528</v>
+      </c>
+      <c r="C9" t="s">
+        <v>284</v>
+      </c>
+      <c r="D9" t="s">
+        <v>536</v>
+      </c>
+      <c r="E9" t="s">
+        <v>103</v>
+      </c>
+      <c r="F9" t="s">
+        <v>585</v>
+      </c>
+      <c r="G9" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>595</v>
+      </c>
+      <c r="B10" t="s">
         <v>539</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C10" t="s">
         <v>540</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D10" t="s">
         <v>529</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E10" t="s">
         <v>150</v>
       </c>
-      <c r="F8" t="s">
-        <v>597</v>
-      </c>
-      <c r="G8" t="s">
-        <v>597</v>
-      </c>
-      <c r="I8" t="s">
-        <v>592</v>
-      </c>
-      <c r="J8" t="s">
-        <v>598</v>
+      <c r="F10" t="s">
+        <v>590</v>
+      </c>
+      <c r="G10" t="s">
+        <v>590</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/data/dati.xlsx
+++ b/data/dati.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan_\Desktop\AMI\GitHub\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A23F9D1C-20F8-49EF-97F1-AC53AA9177E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5363FD37-321D-479C-89BE-B0C14E4CF565}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1518" uniqueCount="598">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1542" uniqueCount="603">
   <si>
     <t>ID_autorita</t>
   </si>
@@ -1774,9 +1774,6 @@
     <t>presidente di</t>
   </si>
   <si>
-    <t>attestato al 1968</t>
-  </si>
-  <si>
     <t>AMI-R-004</t>
   </si>
   <si>
@@ -1817,6 +1814,24 @@
   </si>
   <si>
     <t>1977-1984</t>
+  </si>
+  <si>
+    <t>1943-1976</t>
+  </si>
+  <si>
+    <t>AMI-R-010</t>
+  </si>
+  <si>
+    <t>AMI-R-011</t>
+  </si>
+  <si>
+    <t>AMI-R-012</t>
+  </si>
+  <si>
+    <t>1966-1968</t>
+  </si>
+  <si>
+    <t>1968-????</t>
   </si>
 </sst>
 </file>
@@ -2011,8 +2026,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{4895E276-9036-4388-B350-F25B94D00A98}" name="Tabella5" displayName="Tabella5" ref="A1:J10" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A1:J10" xr:uid="{4895E276-9036-4388-B350-F25B94D00A98}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{4895E276-9036-4388-B350-F25B94D00A98}" name="Tabella5" displayName="Tabella5" ref="A1:J13" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A1:J13" xr:uid="{4895E276-9036-4388-B350-F25B94D00A98}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{681E8224-5D12-4699-8FCD-F6D6D65EDFAF}" name="ID_relazione"/>
     <tableColumn id="2" xr3:uid="{ABB6B5F5-BCC1-4479-A7C9-B3517A2E96E9}" name="ID_entita_A"/>
@@ -7552,7 +7567,7 @@
         <v>396</v>
       </c>
       <c r="G26" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H26" t="s">
         <v>46</v>
@@ -7706,7 +7721,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.21875" customWidth="1"/>
@@ -7778,7 +7793,7 @@
         <v>577</v>
       </c>
       <c r="H2" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -7804,7 +7819,7 @@
         <v>580</v>
       </c>
       <c r="H3" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
@@ -7830,12 +7845,12 @@
         <v>577</v>
       </c>
       <c r="H4" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B5" t="s">
         <v>33</v>
@@ -7856,12 +7871,12 @@
         <v>577</v>
       </c>
       <c r="H5" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B6" t="s">
         <v>18</v>
@@ -7870,10 +7885,10 @@
         <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="E6" t="s">
-        <v>284</v>
+        <v>103</v>
       </c>
       <c r="F6" t="s">
         <v>582</v>
@@ -7882,87 +7897,96 @@
         <v>577</v>
       </c>
       <c r="H6" t="s">
-        <v>583</v>
+        <v>597</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B7" t="s">
-        <v>523</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>151</v>
+        <v>22</v>
       </c>
       <c r="D7" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="E7" t="s">
-        <v>150</v>
+        <v>284</v>
       </c>
       <c r="F7" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="G7" t="s">
         <v>577</v>
       </c>
+      <c r="H7" t="s">
+        <v>597</v>
+      </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B8" t="s">
-        <v>525</v>
+        <v>47</v>
       </c>
       <c r="C8" t="s">
-        <v>179</v>
+        <v>48</v>
       </c>
       <c r="D8" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="E8" t="s">
-        <v>178</v>
+        <v>150</v>
       </c>
       <c r="F8" t="s">
-        <v>587</v>
+        <v>579</v>
       </c>
       <c r="G8" t="s">
-        <v>577</v>
+        <v>580</v>
+      </c>
+      <c r="H8" t="s">
+        <v>601</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B9" t="s">
-        <v>528</v>
+        <v>47</v>
       </c>
       <c r="C9" t="s">
-        <v>284</v>
+        <v>48</v>
       </c>
       <c r="D9" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="E9" t="s">
-        <v>103</v>
+        <v>540</v>
       </c>
       <c r="F9" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="G9" t="s">
-        <v>577</v>
+        <v>580</v>
+      </c>
+      <c r="H9" t="s">
+        <v>602</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B10" t="s">
-        <v>539</v>
+        <v>523</v>
       </c>
       <c r="C10" t="s">
-        <v>540</v>
+        <v>151</v>
       </c>
       <c r="D10" t="s">
         <v>529</v>
@@ -7971,10 +7995,79 @@
         <v>150</v>
       </c>
       <c r="F10" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="G10" t="s">
-        <v>590</v>
+        <v>577</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>598</v>
+      </c>
+      <c r="B11" t="s">
+        <v>525</v>
+      </c>
+      <c r="C11" t="s">
+        <v>179</v>
+      </c>
+      <c r="D11" t="s">
+        <v>533</v>
+      </c>
+      <c r="E11" t="s">
+        <v>178</v>
+      </c>
+      <c r="F11" t="s">
+        <v>586</v>
+      </c>
+      <c r="G11" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>599</v>
+      </c>
+      <c r="B12" t="s">
+        <v>528</v>
+      </c>
+      <c r="C12" t="s">
+        <v>284</v>
+      </c>
+      <c r="D12" t="s">
+        <v>536</v>
+      </c>
+      <c r="E12" t="s">
+        <v>103</v>
+      </c>
+      <c r="F12" t="s">
+        <v>584</v>
+      </c>
+      <c r="G12" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>600</v>
+      </c>
+      <c r="B13" t="s">
+        <v>539</v>
+      </c>
+      <c r="C13" t="s">
+        <v>540</v>
+      </c>
+      <c r="D13" t="s">
+        <v>529</v>
+      </c>
+      <c r="E13" t="s">
+        <v>150</v>
+      </c>
+      <c r="F13" t="s">
+        <v>589</v>
+      </c>
+      <c r="G13" t="s">
+        <v>589</v>
       </c>
     </row>
   </sheetData>

--- a/data/dati.xlsx
+++ b/data/dati.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan_\Desktop\AMI\GitHub\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{085BA701-ABC8-4E9F-89CC-9271D8166F7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{702E570B-72D1-497A-8918-4A2BA64DC487}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Catalogo" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2096" uniqueCount="829">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2096" uniqueCount="830">
   <si>
     <t>ID_autorita</t>
   </si>
@@ -2589,6 +2589,9 @@
   </si>
   <si>
     <t>Calcolato automaticamente dal Catalogo</t>
+  </si>
+  <si>
+    <t>Organizzazione giovanile</t>
   </si>
 </sst>
 </file>
@@ -2676,6 +2679,21 @@
   </cellStyles>
   <dxfs count="7">
     <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2705,21 +2723,6 @@
         <color auto="1"/>
         <name val="Calibri"/>
         <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
       </font>
     </dxf>
   </dxfs>
@@ -2767,13 +2770,13 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{59486A48-317F-495A-B99D-8ACD5E099451}" name="Tabella6" displayName="Tabella6" ref="A1:D23" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{59486A48-317F-495A-B99D-8ACD5E099451}" name="Tabella6" displayName="Tabella6" ref="A1:D23" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
   <autoFilter ref="A1:D23" xr:uid="{59486A48-317F-495A-B99D-8ACD5E099451}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{A3615604-3D84-4F13-9671-EE093887D056}" name="Codice_ISAD" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{87E4C644-3EDF-4F45-A996-E7FF26FD6973}" name="Elemento" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{EF41A2A2-7B60-47CB-A566-55A8E2A526B2}" name="Valore" dataDxfId="1"/>
-    <tableColumn id="4" xr3:uid="{874121B5-A104-47D1-92CD-91A39F52BF80}" name="Note" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{A3615604-3D84-4F13-9671-EE093887D056}" name="Codice_ISAD" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{87E4C644-3EDF-4F45-A996-E7FF26FD6973}" name="Elemento" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{EF41A2A2-7B60-47CB-A566-55A8E2A526B2}" name="Valore" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{874121B5-A104-47D1-92CD-91A39F52BF80}" name="Note" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2834,7 +2837,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="Tabella5" displayName="Tabella5" ref="A1:J13" totalsRowShown="0" headerRowDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="Tabella5" displayName="Tabella5" ref="A1:J13" totalsRowShown="0" headerRowDxfId="0">
   <autoFilter ref="A1:J13" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="ID_relazione"/>
@@ -9349,7 +9352,7 @@
         <v>1958</v>
       </c>
       <c r="I6">
-        <v>1998</v>
+        <v>1988</v>
       </c>
       <c r="O6" t="s">
         <v>25</v>
@@ -9571,7 +9574,7 @@
         <v>57</v>
       </c>
       <c r="G12" t="s">
-        <v>53</v>
+        <v>829</v>
       </c>
       <c r="H12">
         <v>1966</v>

--- a/data/dati.xlsx
+++ b/data/dati.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan_\Desktop\AMI\GitHub\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{702E570B-72D1-497A-8918-4A2BA64DC487}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1936FDB-C378-4CD5-AA5D-73DEC29EC3DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Catalogo" sheetId="1" r:id="rId1"/>
@@ -1085,9 +1085,6 @@
     <t>Nota del Presidente Mao sulla relazione di Kang Sheng riguardante la raccolta di materiale sulle elezioni parlamentari nei paesi capitalisti</t>
   </si>
   <si>
-    <t>Osvaldo Pesce; Mao Zedong; Dino Dini</t>
-  </si>
-  <si>
     <t>https://archive.org/details/istruzioni-mao-italiano</t>
   </si>
   <si>
@@ -2592,6 +2589,9 @@
   </si>
   <si>
     <t>Organizzazione giovanile</t>
+  </si>
+  <si>
+    <t>Osvaldo Pesce; Dino Dini</t>
   </si>
 </sst>
 </file>
@@ -4904,7 +4904,7 @@
         <v>201</v>
       </c>
       <c r="N35" t="s">
-        <v>344</v>
+        <v>829</v>
       </c>
       <c r="O35" t="s">
         <v>61</v>
@@ -4913,21 +4913,21 @@
         <v>137</v>
       </c>
       <c r="Q35" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="S35" t="s">
         <v>345</v>
       </c>
-      <c r="S35" t="s">
+      <c r="T35" t="s">
         <v>346</v>
       </c>
-      <c r="T35" t="s">
+      <c r="V35" t="s">
         <v>347</v>
-      </c>
-      <c r="V35" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B36" t="s">
         <v>139</v>
@@ -4936,7 +4936,7 @@
         <v>142</v>
       </c>
       <c r="D36" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E36" t="s">
         <v>140</v>
@@ -4945,16 +4945,16 @@
         <v>66</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="J36" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="K36" t="s">
         <v>260</v>
       </c>
       <c r="L36" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="M36" t="s">
         <v>201</v>
@@ -4963,15 +4963,15 @@
         <v>137</v>
       </c>
       <c r="Q36" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="V36" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B37" t="s">
         <v>139</v>
@@ -4980,7 +4980,7 @@
         <v>142</v>
       </c>
       <c r="D37" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E37" t="s">
         <v>140</v>
@@ -4992,19 +4992,19 @@
         <v>328</v>
       </c>
       <c r="H37" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="I37" s="1">
         <v>1975</v>
       </c>
       <c r="J37" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="K37" t="s">
         <v>134</v>
       </c>
       <c r="L37" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="M37" t="s">
         <v>246</v>
@@ -5016,15 +5016,15 @@
         <v>137</v>
       </c>
       <c r="Q37" s="3" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="V37" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="38" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B38" t="s">
         <v>139</v>
@@ -5033,7 +5033,7 @@
         <v>142</v>
       </c>
       <c r="D38" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E38" t="s">
         <v>140</v>
@@ -5066,15 +5066,15 @@
         <v>137</v>
       </c>
       <c r="Q38" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="V38" t="s">
         <v>365</v>
-      </c>
-      <c r="V38" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="39" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B39" t="s">
         <v>139</v>
@@ -5083,7 +5083,7 @@
         <v>142</v>
       </c>
       <c r="D39" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E39" t="s">
         <v>140</v>
@@ -5113,21 +5113,21 @@
         <v>158</v>
       </c>
       <c r="N39" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="P39" t="s">
         <v>137</v>
       </c>
       <c r="Q39" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="V39" t="s">
         <v>370</v>
-      </c>
-      <c r="V39" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B40" t="s">
         <v>139</v>
@@ -5136,7 +5136,7 @@
         <v>142</v>
       </c>
       <c r="D40" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E40" t="s">
         <v>140</v>
@@ -5163,21 +5163,21 @@
         <v>135</v>
       </c>
       <c r="M40" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="P40" t="s">
         <v>137</v>
       </c>
       <c r="Q40" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="V40" t="s">
         <v>375</v>
-      </c>
-      <c r="V40" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B41" t="s">
         <v>139</v>
@@ -5186,7 +5186,7 @@
         <v>142</v>
       </c>
       <c r="D41" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E41" t="s">
         <v>140</v>
@@ -5195,7 +5195,7 @@
         <v>70</v>
       </c>
       <c r="G41" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H41" t="s">
         <v>29</v>
@@ -5219,15 +5219,15 @@
         <v>137</v>
       </c>
       <c r="Q41" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="V41" t="s">
         <v>380</v>
-      </c>
-      <c r="V41" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="42" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B42" t="s">
         <v>139</v>
@@ -5236,7 +5236,7 @@
         <v>142</v>
       </c>
       <c r="D42" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="E42" t="s">
         <v>140</v>
@@ -5245,7 +5245,7 @@
         <v>133</v>
       </c>
       <c r="H42" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="I42" s="1">
         <v>1968</v>
@@ -5257,24 +5257,24 @@
         <v>134</v>
       </c>
       <c r="L42" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="M42" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="P42" t="s">
         <v>137</v>
       </c>
       <c r="Q42" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="V42" t="s">
         <v>386</v>
-      </c>
-      <c r="V42" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="43" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B43" t="s">
         <v>139</v>
@@ -5283,7 +5283,7 @@
         <v>142</v>
       </c>
       <c r="D43" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E43" t="s">
         <v>140</v>
@@ -5292,7 +5292,7 @@
         <v>133</v>
       </c>
       <c r="H43" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="I43" s="1">
         <v>1967</v>
@@ -5304,13 +5304,13 @@
         <v>134</v>
       </c>
       <c r="L43" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="M43" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="N43" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="O43" t="s">
         <v>22</v>
@@ -5319,15 +5319,15 @@
         <v>137</v>
       </c>
       <c r="Q43" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="V43" t="s">
         <v>392</v>
-      </c>
-      <c r="V43" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B44" t="s">
         <v>139</v>
@@ -5336,7 +5336,7 @@
         <v>142</v>
       </c>
       <c r="D44" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E44" t="s">
         <v>140</v>
@@ -5369,15 +5369,15 @@
         <v>137</v>
       </c>
       <c r="Q44" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="V44" t="s">
         <v>396</v>
-      </c>
-      <c r="V44" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="45" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B45" t="s">
         <v>139</v>
@@ -5386,7 +5386,7 @@
         <v>142</v>
       </c>
       <c r="D45" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E45" t="s">
         <v>140</v>
@@ -5419,15 +5419,15 @@
         <v>137</v>
       </c>
       <c r="Q45" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="V45" t="s">
         <v>400</v>
-      </c>
-      <c r="V45" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="46" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B46" t="s">
         <v>139</v>
@@ -5436,7 +5436,7 @@
         <v>142</v>
       </c>
       <c r="D46" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E46" t="s">
         <v>140</v>
@@ -5469,15 +5469,15 @@
         <v>137</v>
       </c>
       <c r="Q46" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="V46" t="s">
         <v>404</v>
-      </c>
-      <c r="V46" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="47" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B47" t="s">
         <v>139</v>
@@ -5486,7 +5486,7 @@
         <v>142</v>
       </c>
       <c r="D47" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E47" t="s">
         <v>140</v>
@@ -5519,15 +5519,15 @@
         <v>137</v>
       </c>
       <c r="Q47" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="V47" t="s">
         <v>408</v>
-      </c>
-      <c r="V47" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="48" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B48" t="s">
         <v>139</v>
@@ -5536,7 +5536,7 @@
         <v>142</v>
       </c>
       <c r="D48" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E48" t="s">
         <v>140</v>
@@ -5554,7 +5554,7 @@
         <v>1971</v>
       </c>
       <c r="J48" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="K48" t="s">
         <v>146</v>
@@ -5569,15 +5569,15 @@
         <v>137</v>
       </c>
       <c r="Q48" s="3" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="V48" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B49" t="s">
         <v>139</v>
@@ -5586,7 +5586,7 @@
         <v>142</v>
       </c>
       <c r="D49" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E49" t="s">
         <v>140</v>
@@ -5619,15 +5619,15 @@
         <v>137</v>
       </c>
       <c r="Q49" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="V49" t="s">
         <v>417</v>
-      </c>
-      <c r="V49" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="50" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B50" t="s">
         <v>139</v>
@@ -5636,7 +5636,7 @@
         <v>142</v>
       </c>
       <c r="D50" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E50" t="s">
         <v>140</v>
@@ -5669,15 +5669,15 @@
         <v>137</v>
       </c>
       <c r="Q50" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="V50" t="s">
         <v>421</v>
-      </c>
-      <c r="V50" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="51" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B51" t="s">
         <v>139</v>
@@ -5686,7 +5686,7 @@
         <v>142</v>
       </c>
       <c r="D51" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E51" t="s">
         <v>140</v>
@@ -5719,15 +5719,15 @@
         <v>137</v>
       </c>
       <c r="Q51" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="V51" t="s">
         <v>425</v>
-      </c>
-      <c r="V51" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B52" t="s">
         <v>139</v>
@@ -5736,7 +5736,7 @@
         <v>142</v>
       </c>
       <c r="D52" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E52" t="s">
         <v>140</v>
@@ -5769,15 +5769,15 @@
         <v>137</v>
       </c>
       <c r="Q52" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="V52" t="s">
         <v>429</v>
-      </c>
-      <c r="V52" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="53" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B53" t="s">
         <v>139</v>
@@ -5786,7 +5786,7 @@
         <v>142</v>
       </c>
       <c r="D53" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E53" t="s">
         <v>140</v>
@@ -5798,7 +5798,7 @@
         <v>80</v>
       </c>
       <c r="H53" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="I53" s="1">
         <v>1969</v>
@@ -5810,7 +5810,7 @@
         <v>134</v>
       </c>
       <c r="L53" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="M53" t="s">
         <v>201</v>
@@ -5819,15 +5819,15 @@
         <v>137</v>
       </c>
       <c r="Q53" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="V53" t="s">
         <v>434</v>
-      </c>
-      <c r="V53" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B54" t="s">
         <v>139</v>
@@ -5836,7 +5836,7 @@
         <v>142</v>
       </c>
       <c r="D54" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E54" t="s">
         <v>140</v>
@@ -5848,13 +5848,13 @@
         <v>1972</v>
       </c>
       <c r="J54" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="K54" t="s">
         <v>231</v>
       </c>
       <c r="L54" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="M54" t="s">
         <v>201</v>
@@ -5866,15 +5866,15 @@
         <v>137</v>
       </c>
       <c r="Q54" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="V54" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="55" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B55" t="s">
         <v>139</v>
@@ -5883,7 +5883,7 @@
         <v>142</v>
       </c>
       <c r="D55" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E55" t="s">
         <v>140</v>
@@ -5895,42 +5895,42 @@
         <v>88</v>
       </c>
       <c r="H55" t="s">
+        <v>443</v>
+      </c>
+      <c r="I55" s="6" t="s">
         <v>444</v>
       </c>
-      <c r="I55" s="6" t="s">
+      <c r="J55" t="s">
+        <v>449</v>
+      </c>
+      <c r="K55" t="s">
         <v>445</v>
       </c>
-      <c r="J55" t="s">
-        <v>450</v>
-      </c>
-      <c r="K55" t="s">
-        <v>446</v>
-      </c>
       <c r="L55" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="M55" t="s">
         <v>201</v>
       </c>
       <c r="N55" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="P55" t="s">
         <v>137</v>
       </c>
       <c r="Q55" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="R55" t="s">
         <v>448</v>
       </c>
-      <c r="R55" t="s">
-        <v>449</v>
-      </c>
       <c r="V55" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="56" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B56" t="s">
         <v>139</v>
@@ -5939,7 +5939,7 @@
         <v>142</v>
       </c>
       <c r="D56" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E56" t="s">
         <v>140</v>
@@ -5960,7 +5960,7 @@
         <v>149</v>
       </c>
       <c r="K56" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="M56" t="s">
         <v>201</v>
@@ -5969,18 +5969,18 @@
         <v>137</v>
       </c>
       <c r="Q56" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="R56" t="s">
         <v>454</v>
       </c>
-      <c r="R56" t="s">
+      <c r="V56" t="s">
         <v>455</v>
-      </c>
-      <c r="V56" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="57" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B57" t="s">
         <v>139</v>
@@ -5989,7 +5989,7 @@
         <v>142</v>
       </c>
       <c r="D57" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="E57" t="s">
         <v>140</v>
@@ -6013,24 +6013,24 @@
         <v>134</v>
       </c>
       <c r="L57" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="M57" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="P57" t="s">
         <v>137</v>
       </c>
       <c r="Q57" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="V57" t="s">
         <v>459</v>
-      </c>
-      <c r="V57" t="s">
-        <v>460</v>
       </c>
     </row>
     <row r="58" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B58" t="s">
         <v>139</v>
@@ -6039,7 +6039,7 @@
         <v>142</v>
       </c>
       <c r="D58" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E58" t="s">
         <v>212</v>
@@ -6051,45 +6051,45 @@
         <v>88</v>
       </c>
       <c r="H58" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="I58" s="2">
         <v>28253</v>
       </c>
       <c r="J58" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="K58" t="s">
         <v>208</v>
       </c>
       <c r="L58" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="M58" t="s">
         <v>201</v>
       </c>
       <c r="N58" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="O58" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="P58" t="s">
         <v>137</v>
       </c>
       <c r="Q58" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="R58" t="s">
         <v>464</v>
       </c>
-      <c r="R58" t="s">
-        <v>465</v>
-      </c>
       <c r="V58" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="59" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B59" t="s">
         <v>139</v>
@@ -6098,7 +6098,7 @@
         <v>142</v>
       </c>
       <c r="D59" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E59" t="s">
         <v>140</v>
@@ -6107,7 +6107,7 @@
         <v>32</v>
       </c>
       <c r="G59" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H59" t="s">
         <v>32</v>
@@ -6122,7 +6122,7 @@
         <v>134</v>
       </c>
       <c r="L59" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="M59" t="s">
         <v>246</v>
@@ -6131,15 +6131,15 @@
         <v>137</v>
       </c>
       <c r="Q59" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="V59" t="s">
         <v>471</v>
-      </c>
-      <c r="V59" t="s">
-        <v>472</v>
       </c>
     </row>
     <row r="60" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B60" t="s">
         <v>139</v>
@@ -6148,7 +6148,7 @@
         <v>142</v>
       </c>
       <c r="D60" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E60" t="s">
         <v>140</v>
@@ -6157,7 +6157,7 @@
         <v>32</v>
       </c>
       <c r="G60" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H60" t="s">
         <v>32</v>
@@ -6172,7 +6172,7 @@
         <v>134</v>
       </c>
       <c r="L60" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="M60" t="s">
         <v>246</v>
@@ -6181,15 +6181,15 @@
         <v>137</v>
       </c>
       <c r="Q60" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="V60" t="s">
         <v>475</v>
-      </c>
-      <c r="V60" t="s">
-        <v>476</v>
       </c>
     </row>
     <row r="61" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B61" t="s">
         <v>139</v>
@@ -6198,7 +6198,7 @@
         <v>142</v>
       </c>
       <c r="D61" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E61" t="s">
         <v>140</v>
@@ -6207,7 +6207,7 @@
         <v>32</v>
       </c>
       <c r="G61" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H61" t="s">
         <v>32</v>
@@ -6216,33 +6216,33 @@
         <v>1965</v>
       </c>
       <c r="J61" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="K61" t="s">
         <v>134</v>
       </c>
       <c r="L61" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="M61" t="s">
         <v>246</v>
       </c>
       <c r="N61" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="P61" t="s">
         <v>137</v>
       </c>
       <c r="Q61" s="3" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="V61" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="62" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B62" t="s">
         <v>139</v>
@@ -6251,7 +6251,7 @@
         <v>142</v>
       </c>
       <c r="D62" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E62" t="s">
         <v>140</v>
@@ -6269,7 +6269,7 @@
         <v>1971</v>
       </c>
       <c r="J62" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="K62" t="s">
         <v>146</v>
@@ -6284,15 +6284,15 @@
         <v>137</v>
       </c>
       <c r="Q62" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="V62" t="s">
         <v>486</v>
-      </c>
-      <c r="V62" t="s">
-        <v>487</v>
       </c>
     </row>
     <row r="63" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B63" t="s">
         <v>139</v>
@@ -6301,7 +6301,7 @@
         <v>142</v>
       </c>
       <c r="D63" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E63" t="s">
         <v>212</v>
@@ -6310,36 +6310,36 @@
         <v>24917</v>
       </c>
       <c r="J63" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="K63" t="s">
         <v>208</v>
       </c>
       <c r="L63" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="M63" t="s">
         <v>246</v>
       </c>
       <c r="O63" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="P63" t="s">
         <v>137</v>
       </c>
       <c r="Q63" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="R63" t="s">
         <v>492</v>
       </c>
-      <c r="R63" t="s">
-        <v>493</v>
-      </c>
       <c r="V63" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B64" t="s">
         <v>139</v>
@@ -6348,7 +6348,7 @@
         <v>142</v>
       </c>
       <c r="D64" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="E64" t="s">
         <v>140</v>
@@ -6360,33 +6360,33 @@
         <v>83</v>
       </c>
       <c r="I64" s="5" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="J64" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="K64" t="s">
         <v>231</v>
       </c>
       <c r="L64" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="M64" t="s">
         <v>201</v>
       </c>
       <c r="P64" t="s">
+        <v>499</v>
+      </c>
+      <c r="Q64" s="3" t="s">
         <v>500</v>
       </c>
-      <c r="Q64" s="3" t="s">
-        <v>501</v>
-      </c>
       <c r="V64" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="65" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B65" t="s">
         <v>139</v>
@@ -6395,7 +6395,7 @@
         <v>142</v>
       </c>
       <c r="D65" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="E65" t="s">
         <v>140</v>
@@ -6410,30 +6410,30 @@
         <v>26956</v>
       </c>
       <c r="J65" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="K65" t="s">
         <v>231</v>
       </c>
       <c r="L65" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="M65" t="s">
         <v>201</v>
       </c>
       <c r="P65" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="Q65" s="3" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="V65" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="66" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B66" t="s">
         <v>139</v>
@@ -6442,7 +6442,7 @@
         <v>142</v>
       </c>
       <c r="D66" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="E66" t="s">
         <v>212</v>
@@ -6460,7 +6460,7 @@
         <v>208</v>
       </c>
       <c r="L66" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="M66" t="s">
         <v>201</v>
@@ -6469,18 +6469,18 @@
         <v>137</v>
       </c>
       <c r="Q66" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="R66" t="s">
         <v>511</v>
       </c>
-      <c r="R66" t="s">
+      <c r="V66" t="s">
         <v>512</v>
-      </c>
-      <c r="V66" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="67" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B67" t="s">
         <v>139</v>
@@ -6489,7 +6489,7 @@
         <v>142</v>
       </c>
       <c r="D67" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="E67" t="s">
         <v>212</v>
@@ -6507,7 +6507,7 @@
         <v>208</v>
       </c>
       <c r="L67" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="M67" t="s">
         <v>201</v>
@@ -6516,18 +6516,18 @@
         <v>137</v>
       </c>
       <c r="Q67" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="R67" t="s">
         <v>516</v>
       </c>
-      <c r="R67" t="s">
+      <c r="V67" t="s">
         <v>517</v>
-      </c>
-      <c r="V67" t="s">
-        <v>518</v>
       </c>
     </row>
     <row r="68" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B68" t="s">
         <v>139</v>
@@ -6536,7 +6536,7 @@
         <v>142</v>
       </c>
       <c r="D68" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E68" t="s">
         <v>140</v>
@@ -6563,18 +6563,18 @@
         <v>137</v>
       </c>
       <c r="Q68" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="R68" t="s">
         <v>521</v>
       </c>
-      <c r="R68" t="s">
+      <c r="V68" t="s">
         <v>522</v>
-      </c>
-      <c r="V68" t="s">
-        <v>523</v>
       </c>
     </row>
     <row r="69" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B69" t="s">
         <v>139</v>
@@ -6583,7 +6583,7 @@
         <v>142</v>
       </c>
       <c r="D69" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="E69" t="s">
         <v>140</v>
@@ -6595,10 +6595,10 @@
         <v>91</v>
       </c>
       <c r="I69" s="7" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="J69" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="K69" t="s">
         <v>260</v>
@@ -6613,15 +6613,15 @@
         <v>263</v>
       </c>
       <c r="Q69" s="3" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="V69" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="70" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B70" t="s">
         <v>139</v>
@@ -6630,7 +6630,7 @@
         <v>142</v>
       </c>
       <c r="D70" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="E70" t="s">
         <v>140</v>
@@ -6645,7 +6645,7 @@
         <v>25704</v>
       </c>
       <c r="J70" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="K70" t="s">
         <v>260</v>
@@ -6660,15 +6660,15 @@
         <v>263</v>
       </c>
       <c r="Q70" s="3" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="V70" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="71" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B71" t="s">
         <v>139</v>
@@ -6677,7 +6677,7 @@
         <v>142</v>
       </c>
       <c r="D71" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="E71" t="s">
         <v>140</v>
@@ -6692,7 +6692,7 @@
         <v>25718</v>
       </c>
       <c r="J71" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="K71" t="s">
         <v>260</v>
@@ -6707,15 +6707,15 @@
         <v>263</v>
       </c>
       <c r="Q71" s="3" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="V71" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="72" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B72" t="s">
         <v>139</v>
@@ -6724,7 +6724,7 @@
         <v>142</v>
       </c>
       <c r="D72" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="E72" t="s">
         <v>140</v>
@@ -6739,7 +6739,7 @@
         <v>25719</v>
       </c>
       <c r="J72" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="K72" t="s">
         <v>260</v>
@@ -6754,15 +6754,15 @@
         <v>263</v>
       </c>
       <c r="Q72" s="3" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="V72" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="73" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B73" t="s">
         <v>139</v>
@@ -6771,7 +6771,7 @@
         <v>142</v>
       </c>
       <c r="D73" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="E73" t="s">
         <v>140</v>
@@ -6786,7 +6786,7 @@
         <v>25740</v>
       </c>
       <c r="J73" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="K73" t="s">
         <v>260</v>
@@ -6801,15 +6801,15 @@
         <v>263</v>
       </c>
       <c r="Q73" s="3" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="V73" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="74" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B74" t="s">
         <v>139</v>
@@ -6818,7 +6818,7 @@
         <v>142</v>
       </c>
       <c r="D74" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="E74" t="s">
         <v>140</v>
@@ -6833,7 +6833,7 @@
         <v>25765</v>
       </c>
       <c r="J74" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="K74" t="s">
         <v>260</v>
@@ -6848,15 +6848,15 @@
         <v>263</v>
       </c>
       <c r="Q74" s="3" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="V74" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="75" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B75" t="s">
         <v>139</v>
@@ -6865,7 +6865,7 @@
         <v>142</v>
       </c>
       <c r="D75" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="E75" t="s">
         <v>140</v>
@@ -6880,7 +6880,7 @@
         <v>25824</v>
       </c>
       <c r="J75" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="K75" t="s">
         <v>260</v>
@@ -6895,15 +6895,15 @@
         <v>263</v>
       </c>
       <c r="Q75" s="3" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="V75" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="76" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B76" t="s">
         <v>139</v>
@@ -6912,7 +6912,7 @@
         <v>142</v>
       </c>
       <c r="D76" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="E76" t="s">
         <v>140</v>
@@ -6927,7 +6927,7 @@
         <v>25866</v>
       </c>
       <c r="J76" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="K76" t="s">
         <v>260</v>
@@ -6942,15 +6942,15 @@
         <v>263</v>
       </c>
       <c r="Q76" s="3" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="V76" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="77" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B77" t="s">
         <v>139</v>
@@ -6959,7 +6959,7 @@
         <v>142</v>
       </c>
       <c r="D77" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="E77" t="s">
         <v>140</v>
@@ -6974,7 +6974,7 @@
         <v>25887</v>
       </c>
       <c r="J77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="K77" t="s">
         <v>260</v>
@@ -6989,15 +6989,15 @@
         <v>263</v>
       </c>
       <c r="Q77" s="3" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="V77" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="78" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B78" t="s">
         <v>139</v>
@@ -7006,7 +7006,7 @@
         <v>142</v>
       </c>
       <c r="D78" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E78" t="s">
         <v>140</v>
@@ -7021,7 +7021,7 @@
         <v>25915</v>
       </c>
       <c r="J78" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="K78" t="s">
         <v>260</v>
@@ -7036,15 +7036,15 @@
         <v>263</v>
       </c>
       <c r="Q78" s="3" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="V78" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="79" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B79" t="s">
         <v>139</v>
@@ -7053,7 +7053,7 @@
         <v>142</v>
       </c>
       <c r="D79" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="E79" t="s">
         <v>140</v>
@@ -7068,7 +7068,7 @@
         <v>25950</v>
       </c>
       <c r="J79" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="K79" t="s">
         <v>260</v>
@@ -7083,15 +7083,15 @@
         <v>263</v>
       </c>
       <c r="Q79" s="3" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="V79" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="80" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B80" t="s">
         <v>139</v>
@@ -7100,7 +7100,7 @@
         <v>142</v>
       </c>
       <c r="D80" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="E80" t="s">
         <v>140</v>
@@ -7115,7 +7115,7 @@
         <v>25971</v>
       </c>
       <c r="J80" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="K80" t="s">
         <v>260</v>
@@ -7130,15 +7130,15 @@
         <v>263</v>
       </c>
       <c r="Q80" s="3" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="V80" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="81" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B81" t="s">
         <v>139</v>
@@ -7147,7 +7147,7 @@
         <v>142</v>
       </c>
       <c r="D81" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="E81" t="s">
         <v>140</v>
@@ -7162,7 +7162,7 @@
         <v>25999</v>
       </c>
       <c r="J81" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="K81" t="s">
         <v>260</v>
@@ -7177,15 +7177,15 @@
         <v>263</v>
       </c>
       <c r="Q81" s="3" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="V81" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="82" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B82" t="s">
         <v>139</v>
@@ -7194,7 +7194,7 @@
         <v>142</v>
       </c>
       <c r="D82" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E82" t="s">
         <v>140</v>
@@ -7209,7 +7209,7 @@
         <v>26027</v>
       </c>
       <c r="J82" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="K82" t="s">
         <v>260</v>
@@ -7224,15 +7224,15 @@
         <v>263</v>
       </c>
       <c r="Q82" s="3" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="V82" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="83" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B83" t="s">
         <v>139</v>
@@ -7241,7 +7241,7 @@
         <v>142</v>
       </c>
       <c r="D83" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E83" t="s">
         <v>140</v>
@@ -7256,7 +7256,7 @@
         <v>26054</v>
       </c>
       <c r="J83" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="K83" t="s">
         <v>260</v>
@@ -7271,15 +7271,15 @@
         <v>263</v>
       </c>
       <c r="Q83" s="3" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="V83" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="84" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B84" t="s">
         <v>139</v>
@@ -7288,7 +7288,7 @@
         <v>142</v>
       </c>
       <c r="D84" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E84" t="s">
         <v>140</v>
@@ -7303,7 +7303,7 @@
         <v>26076</v>
       </c>
       <c r="J84" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="K84" t="s">
         <v>260</v>
@@ -7318,15 +7318,15 @@
         <v>263</v>
       </c>
       <c r="Q84" s="3" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="V84" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="85" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B85" t="s">
         <v>139</v>
@@ -7335,7 +7335,7 @@
         <v>142</v>
       </c>
       <c r="D85" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="E85" t="s">
         <v>140</v>
@@ -7350,7 +7350,7 @@
         <v>26104</v>
       </c>
       <c r="J85" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="K85" t="s">
         <v>260</v>
@@ -7365,15 +7365,15 @@
         <v>263</v>
       </c>
       <c r="Q85" s="3" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="V85" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="86" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B86" t="s">
         <v>139</v>
@@ -7382,7 +7382,7 @@
         <v>142</v>
       </c>
       <c r="D86" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="E86" t="s">
         <v>140</v>
@@ -7397,7 +7397,7 @@
         <v>26139</v>
       </c>
       <c r="J86" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="K86" t="s">
         <v>260</v>
@@ -7412,15 +7412,15 @@
         <v>263</v>
       </c>
       <c r="Q86" s="3" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="V86" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="87" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B87" t="s">
         <v>139</v>
@@ -7429,7 +7429,7 @@
         <v>142</v>
       </c>
       <c r="D87" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="E87" t="s">
         <v>140</v>
@@ -7444,7 +7444,7 @@
         <v>26265</v>
       </c>
       <c r="J87" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="K87" t="s">
         <v>260</v>
@@ -7459,15 +7459,15 @@
         <v>263</v>
       </c>
       <c r="Q87" s="3" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="V87" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="88" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B88" t="s">
         <v>139</v>
@@ -7476,7 +7476,7 @@
         <v>142</v>
       </c>
       <c r="D88" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="E88" t="s">
         <v>140</v>
@@ -7491,7 +7491,7 @@
         <v>26307</v>
       </c>
       <c r="J88" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="K88" t="s">
         <v>260</v>
@@ -7506,15 +7506,15 @@
         <v>263</v>
       </c>
       <c r="Q88" s="3" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="V88" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="89" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B89" t="s">
         <v>139</v>
@@ -7523,7 +7523,7 @@
         <v>142</v>
       </c>
       <c r="D89" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="E89" t="s">
         <v>140</v>
@@ -7538,7 +7538,7 @@
         <v>26370</v>
       </c>
       <c r="J89" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="K89" t="s">
         <v>260</v>
@@ -7553,15 +7553,15 @@
         <v>263</v>
       </c>
       <c r="Q89" s="3" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="V89" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="90" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B90" t="s">
         <v>139</v>
@@ -7570,7 +7570,7 @@
         <v>142</v>
       </c>
       <c r="D90" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="E90" t="s">
         <v>140</v>
@@ -7585,7 +7585,7 @@
         <v>26420</v>
       </c>
       <c r="J90" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="K90" t="s">
         <v>260</v>
@@ -7600,15 +7600,15 @@
         <v>263</v>
       </c>
       <c r="Q90" s="3" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="V90" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="91" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B91" t="s">
         <v>139</v>
@@ -7617,7 +7617,7 @@
         <v>142</v>
       </c>
       <c r="D91" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="E91" t="s">
         <v>140</v>
@@ -7632,7 +7632,7 @@
         <v>26608</v>
       </c>
       <c r="J91" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="K91" t="s">
         <v>260</v>
@@ -7647,15 +7647,15 @@
         <v>263</v>
       </c>
       <c r="Q91" s="3" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="V91" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="92" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B92" t="s">
         <v>139</v>
@@ -7664,7 +7664,7 @@
         <v>142</v>
       </c>
       <c r="D92" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="E92" t="s">
         <v>140</v>
@@ -7679,7 +7679,7 @@
         <v>26785</v>
       </c>
       <c r="J92" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="K92" t="s">
         <v>260</v>
@@ -7694,15 +7694,15 @@
         <v>263</v>
       </c>
       <c r="Q92" s="3" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="V92" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="93" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B93" t="s">
         <v>139</v>
@@ -7711,7 +7711,7 @@
         <v>142</v>
       </c>
       <c r="D93" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="E93" t="s">
         <v>140</v>
@@ -7720,7 +7720,7 @@
         <v>66</v>
       </c>
       <c r="H93" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="I93">
         <v>1969</v>
@@ -7732,7 +7732,7 @@
         <v>134</v>
       </c>
       <c r="L93" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="M93" t="s">
         <v>158</v>
@@ -7744,15 +7744,15 @@
         <v>137</v>
       </c>
       <c r="Q93" s="3" t="s">
+        <v>647</v>
+      </c>
+      <c r="V93" t="s">
         <v>648</v>
-      </c>
-      <c r="V93" t="s">
-        <v>649</v>
       </c>
     </row>
     <row r="94" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B94" t="s">
         <v>139</v>
@@ -7761,7 +7761,7 @@
         <v>142</v>
       </c>
       <c r="D94" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="E94" t="s">
         <v>140</v>
@@ -7773,16 +7773,16 @@
         <v>93</v>
       </c>
       <c r="I94" s="5" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="J94" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="K94" t="s">
         <v>146</v>
       </c>
       <c r="L94" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="M94" t="s">
         <v>201</v>
@@ -7791,15 +7791,15 @@
         <v>137</v>
       </c>
       <c r="Q94" s="3" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="V94" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="95" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B95" t="s">
         <v>139</v>
@@ -7808,7 +7808,7 @@
         <v>142</v>
       </c>
       <c r="D95" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="E95" t="s">
         <v>140</v>
@@ -7841,15 +7841,15 @@
         <v>159</v>
       </c>
       <c r="Q95" s="3" t="s">
+        <v>658</v>
+      </c>
+      <c r="V95" t="s">
         <v>659</v>
-      </c>
-      <c r="V95" t="s">
-        <v>660</v>
       </c>
     </row>
     <row r="96" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B96" t="s">
         <v>139</v>
@@ -7858,7 +7858,7 @@
         <v>142</v>
       </c>
       <c r="D96" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="E96" t="s">
         <v>140</v>
@@ -7894,15 +7894,15 @@
         <v>159</v>
       </c>
       <c r="Q96" s="3" t="s">
+        <v>662</v>
+      </c>
+      <c r="V96" t="s">
         <v>663</v>
-      </c>
-      <c r="V96" t="s">
-        <v>664</v>
       </c>
     </row>
     <row r="97" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B97" t="s">
         <v>139</v>
@@ -7911,7 +7911,7 @@
         <v>142</v>
       </c>
       <c r="D97" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="E97" t="s">
         <v>212</v>
@@ -7920,7 +7920,7 @@
         <v>1973</v>
       </c>
       <c r="J97" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="K97" t="s">
         <v>208</v>
@@ -7935,13 +7935,13 @@
         <v>137</v>
       </c>
       <c r="Q97" s="3" t="s">
+        <v>666</v>
+      </c>
+      <c r="R97" t="s">
         <v>667</v>
       </c>
-      <c r="R97" t="s">
-        <v>668</v>
-      </c>
       <c r="V97" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
   </sheetData>
@@ -8063,275 +8063,275 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
+        <v>670</v>
+      </c>
+      <c r="B1" s="10" t="s">
         <v>671</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="C1" s="10" t="s">
         <v>672</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="D1" s="10" t="s">
         <v>673</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>674</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
+        <v>674</v>
+      </c>
+      <c r="B2" s="11" t="s">
         <v>675</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="C2" s="11" t="s">
         <v>676</v>
-      </c>
-      <c r="C2" s="11" t="s">
-        <v>677</v>
       </c>
       <c r="D2" s="11"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B3" s="11" t="s">
         <v>110</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="D3" s="11"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="11" t="s">
+        <v>679</v>
+      </c>
+      <c r="B4" s="11" t="s">
         <v>680</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>681</v>
       </c>
       <c r="C4" s="11"/>
       <c r="D4" s="11" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
+        <v>681</v>
+      </c>
+      <c r="B5" s="11" t="s">
         <v>682</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="C5" s="11" t="s">
         <v>683</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>684</v>
       </c>
       <c r="D5" s="11"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>128</v>
       </c>
       <c r="C6" s="11"/>
       <c r="D6" s="11" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
+        <v>685</v>
+      </c>
+      <c r="B7" s="11" t="s">
         <v>686</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="C7" s="11" t="s">
         <v>687</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>688</v>
       </c>
       <c r="D7" s="11"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
+        <v>688</v>
+      </c>
+      <c r="B8" s="11" t="s">
         <v>689</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>690</v>
       </c>
       <c r="C8" s="11"/>
       <c r="D8" s="11"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
+        <v>690</v>
+      </c>
+      <c r="B9" s="11" t="s">
         <v>691</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>692</v>
       </c>
       <c r="C9" s="11"/>
       <c r="D9" s="11" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
+        <v>693</v>
+      </c>
+      <c r="B10" s="11" t="s">
         <v>694</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>695</v>
       </c>
       <c r="C10" s="11"/>
       <c r="D10" s="11" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
+        <v>696</v>
+      </c>
+      <c r="B11" s="11" t="s">
         <v>697</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>698</v>
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
+        <v>699</v>
+      </c>
+      <c r="B12" s="11" t="s">
         <v>700</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>701</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
+        <v>701</v>
+      </c>
+      <c r="B13" s="11" t="s">
         <v>702</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="C13" s="11" t="s">
         <v>703</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>704</v>
       </c>
       <c r="D13" s="11"/>
     </row>
     <row r="14" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
+        <v>704</v>
+      </c>
+      <c r="B14" s="11" t="s">
         <v>705</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="C14" s="11" t="s">
         <v>706</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>707</v>
       </c>
       <c r="D14" s="11"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
+        <v>707</v>
+      </c>
+      <c r="B15" s="11" t="s">
         <v>708</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="C15" s="11" t="s">
         <v>709</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>710</v>
       </c>
       <c r="D15" s="11"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="11" t="s">
+        <v>710</v>
+      </c>
+      <c r="B16" s="11" t="s">
         <v>711</v>
       </c>
-      <c r="B16" s="11" t="s">
-        <v>712</v>
-      </c>
       <c r="C16" s="11" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="D16" s="11"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B17" s="11" t="s">
         <v>129</v>
       </c>
       <c r="C17" s="11"/>
       <c r="D17" s="11" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
+        <v>713</v>
+      </c>
+      <c r="B18" s="11" t="s">
         <v>714</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="C18" s="11" t="s">
         <v>715</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>716</v>
       </c>
       <c r="D18" s="11"/>
     </row>
     <row r="19" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
+        <v>716</v>
+      </c>
+      <c r="B19" s="11" t="s">
         <v>717</v>
-      </c>
-      <c r="B19" s="11" t="s">
-        <v>718</v>
       </c>
       <c r="C19" s="11"/>
       <c r="D19" s="11" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
+        <v>719</v>
+      </c>
+      <c r="B20" s="11" t="s">
         <v>720</v>
       </c>
-      <c r="B20" s="11" t="s">
+      <c r="C20" s="11" t="s">
         <v>721</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>722</v>
       </c>
       <c r="D20" s="11"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
+        <v>722</v>
+      </c>
+      <c r="B21" s="11" t="s">
         <v>723</v>
       </c>
-      <c r="B21" s="11" t="s">
+      <c r="C21" s="11" t="s">
         <v>724</v>
-      </c>
-      <c r="C21" s="11" t="s">
-        <v>725</v>
       </c>
       <c r="D21" s="11"/>
     </row>
     <row r="22" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A22" s="11" t="s">
+        <v>725</v>
+      </c>
+      <c r="B22" s="11" t="s">
         <v>726</v>
       </c>
-      <c r="B22" s="11" t="s">
+      <c r="C22" s="11" t="s">
         <v>727</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>728</v>
       </c>
       <c r="D22" s="11"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
+        <v>728</v>
+      </c>
+      <c r="B23" s="11" t="s">
         <v>729</v>
       </c>
-      <c r="B23" s="11" t="s">
+      <c r="C23" s="11" t="s">
         <v>730</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>731</v>
       </c>
       <c r="D23" s="11"/>
     </row>
@@ -8380,22 +8380,22 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="G1" s="9" t="s">
         <v>5</v>
       </c>
       <c r="H1" t="s">
+        <v>732</v>
+      </c>
+      <c r="I1" t="s">
         <v>733</v>
-      </c>
-      <c r="I1" t="s">
-        <v>734</v>
       </c>
       <c r="J1" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="L1" s="9" t="s">
         <v>11</v>
@@ -8421,10 +8421,10 @@
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>735</v>
+      </c>
+      <c r="B2" t="s">
         <v>736</v>
-      </c>
-      <c r="B2" t="s">
-        <v>737</v>
       </c>
       <c r="C2" t="s">
         <v>20</v>
@@ -8436,10 +8436,10 @@
         <v>133</v>
       </c>
       <c r="F2" t="s">
+        <v>737</v>
+      </c>
+      <c r="G2" t="s">
         <v>738</v>
-      </c>
-      <c r="G2" t="s">
-        <v>739</v>
       </c>
       <c r="H2">
         <v>1893</v>
@@ -8448,7 +8448,7 @@
         <v>1976</v>
       </c>
       <c r="J2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O2" t="s">
         <v>25</v>
@@ -8460,15 +8460,15 @@
         <v>46297</v>
       </c>
       <c r="R2" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="B3" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C3" t="s">
         <v>20</v>
@@ -8477,10 +8477,10 @@
         <v>21</v>
       </c>
       <c r="E3" t="s">
+        <v>742</v>
+      </c>
+      <c r="F3" t="s">
         <v>743</v>
-      </c>
-      <c r="F3" t="s">
-        <v>744</v>
       </c>
       <c r="H3">
         <v>1921</v>
@@ -8489,7 +8489,7 @@
         <v>1993</v>
       </c>
       <c r="J3" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="O3" t="s">
         <v>25</v>
@@ -8501,15 +8501,15 @@
         <v>46297</v>
       </c>
       <c r="R3" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="B4" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C4" t="s">
         <v>20</v>
@@ -8518,10 +8518,10 @@
         <v>21</v>
       </c>
       <c r="E4" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="F4" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="H4">
         <v>1938</v>
@@ -8530,7 +8530,7 @@
         <v>2021</v>
       </c>
       <c r="J4" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="O4" t="s">
         <v>25</v>
@@ -8542,15 +8542,15 @@
         <v>46297</v>
       </c>
       <c r="R4" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B5" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C5" t="s">
         <v>20</v>
@@ -8562,7 +8562,7 @@
         <v>194</v>
       </c>
       <c r="F5" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H5">
         <v>1931</v>
@@ -8580,15 +8580,15 @@
         <v>46297</v>
       </c>
       <c r="R5" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B6" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C6" t="s">
         <v>20</v>
@@ -8597,10 +8597,10 @@
         <v>21</v>
       </c>
       <c r="E6" t="s">
+        <v>751</v>
+      </c>
+      <c r="F6" t="s">
         <v>752</v>
-      </c>
-      <c r="F6" t="s">
-        <v>753</v>
       </c>
       <c r="H6">
         <v>1960</v>
@@ -8618,15 +8618,15 @@
         <v>46297</v>
       </c>
       <c r="R6" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B7" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C7" t="s">
         <v>20</v>
@@ -8638,7 +8638,7 @@
         <v>328</v>
       </c>
       <c r="F7" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="H7" t="s">
         <v>81</v>
@@ -8656,15 +8656,15 @@
         <v>46297</v>
       </c>
       <c r="R7" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B8" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C8" t="s">
         <v>20</v>
@@ -8673,10 +8673,10 @@
         <v>21</v>
       </c>
       <c r="E8" t="s">
+        <v>756</v>
+      </c>
+      <c r="F8" t="s">
         <v>757</v>
-      </c>
-      <c r="F8" t="s">
-        <v>758</v>
       </c>
       <c r="H8" t="s">
         <v>81</v>
@@ -8694,15 +8694,15 @@
         <v>46297</v>
       </c>
       <c r="R8" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B9" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C9" t="s">
         <v>20</v>
@@ -8711,13 +8711,13 @@
         <v>21</v>
       </c>
       <c r="E9" t="s">
+        <v>759</v>
+      </c>
+      <c r="F9" t="s">
         <v>760</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>761</v>
-      </c>
-      <c r="G9" t="s">
-        <v>762</v>
       </c>
       <c r="H9">
         <v>1907</v>
@@ -8735,15 +8735,15 @@
         <v>46297</v>
       </c>
       <c r="R9" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B10" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C10" t="s">
         <v>20</v>
@@ -8752,10 +8752,10 @@
         <v>21</v>
       </c>
       <c r="E10" t="s">
+        <v>763</v>
+      </c>
+      <c r="F10" t="s">
         <v>764</v>
-      </c>
-      <c r="F10" t="s">
-        <v>765</v>
       </c>
       <c r="H10">
         <v>1898</v>
@@ -8773,15 +8773,15 @@
         <v>46297</v>
       </c>
       <c r="R10" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="B11" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C11" t="s">
         <v>20</v>
@@ -8790,13 +8790,13 @@
         <v>21</v>
       </c>
       <c r="E11" t="s">
+        <v>766</v>
+      </c>
+      <c r="F11" t="s">
         <v>767</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>768</v>
-      </c>
-      <c r="G11" t="s">
-        <v>769</v>
       </c>
       <c r="H11">
         <v>1898</v>
@@ -8814,15 +8814,15 @@
         <v>46297</v>
       </c>
       <c r="R11" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B12" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C12" t="s">
         <v>20</v>
@@ -8831,13 +8831,13 @@
         <v>21</v>
       </c>
       <c r="E12" t="s">
+        <v>770</v>
+      </c>
+      <c r="F12" t="s">
         <v>771</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>772</v>
-      </c>
-      <c r="G12" t="s">
-        <v>773</v>
       </c>
       <c r="H12">
         <v>1904</v>
@@ -8855,15 +8855,15 @@
         <v>46297</v>
       </c>
       <c r="R12" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B13" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C13" t="s">
         <v>20</v>
@@ -8872,13 +8872,13 @@
         <v>21</v>
       </c>
       <c r="E13" t="s">
+        <v>774</v>
+      </c>
+      <c r="F13" t="s">
         <v>775</v>
       </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
         <v>776</v>
-      </c>
-      <c r="G13" t="s">
-        <v>777</v>
       </c>
       <c r="H13">
         <v>1914</v>
@@ -8896,15 +8896,15 @@
         <v>46297</v>
       </c>
       <c r="R13" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B14" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C14" t="s">
         <v>20</v>
@@ -8913,10 +8913,10 @@
         <v>21</v>
       </c>
       <c r="E14" t="s">
+        <v>778</v>
+      </c>
+      <c r="F14" t="s">
         <v>779</v>
-      </c>
-      <c r="F14" t="s">
-        <v>780</v>
       </c>
       <c r="H14">
         <v>1920</v>
@@ -8934,15 +8934,15 @@
         <v>46297</v>
       </c>
       <c r="R14" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="B15" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C15" t="s">
         <v>20</v>
@@ -8951,10 +8951,10 @@
         <v>21</v>
       </c>
       <c r="E15" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="F15" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="H15">
         <v>1920</v>
@@ -8972,15 +8972,15 @@
         <v>46297</v>
       </c>
       <c r="R15" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="B16" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C16" t="s">
         <v>20</v>
@@ -8989,13 +8989,13 @@
         <v>21</v>
       </c>
       <c r="E16" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="F16" t="s">
+        <v>783</v>
+      </c>
+      <c r="G16" t="s">
         <v>784</v>
-      </c>
-      <c r="G16" t="s">
-        <v>785</v>
       </c>
       <c r="H16">
         <v>1898</v>
@@ -9013,15 +9013,15 @@
         <v>46297</v>
       </c>
       <c r="R16" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="B17" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C17" t="s">
         <v>20</v>
@@ -9030,10 +9030,10 @@
         <v>21</v>
       </c>
       <c r="E17" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F17" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="H17">
         <v>1924</v>
@@ -9051,15 +9051,15 @@
         <v>46297</v>
       </c>
       <c r="R17" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B18" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C18" t="s">
         <v>20</v>
@@ -9068,10 +9068,10 @@
         <v>21</v>
       </c>
       <c r="E18" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F18" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="H18">
         <v>1933</v>
@@ -9089,7 +9089,7 @@
         <v>46297</v>
       </c>
       <c r="R18" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
   </sheetData>
@@ -9574,7 +9574,7 @@
         <v>57</v>
       </c>
       <c r="G12" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="H12">
         <v>1966</v>
@@ -10306,45 +10306,45 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
+        <v>789</v>
+      </c>
+      <c r="B1" s="9" t="s">
         <v>790</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="C1" s="9" t="s">
         <v>791</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="D1" s="9" t="s">
         <v>792</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="E1" s="9" t="s">
         <v>793</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="F1" s="9" t="s">
         <v>794</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="G1" s="9" t="s">
         <v>795</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="H1" s="9" t="s">
+        <v>680</v>
+      </c>
+      <c r="I1" s="9" t="s">
         <v>796</v>
       </c>
-      <c r="H1" s="9" t="s">
-        <v>681</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>797</v>
-      </c>
       <c r="J1" s="9" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="B2" t="s">
+        <v>741</v>
+      </c>
+      <c r="C2" t="s">
         <v>742</v>
-      </c>
-      <c r="C2" t="s">
-        <v>743</v>
       </c>
       <c r="D2" t="s">
         <v>60</v>
@@ -10353,24 +10353,24 @@
         <v>61</v>
       </c>
       <c r="F2" t="s">
+        <v>798</v>
+      </c>
+      <c r="G2" t="s">
         <v>799</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>800</v>
-      </c>
-      <c r="H2" t="s">
-        <v>801</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="B3" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="C3" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="D3" t="s">
         <v>60</v>
@@ -10379,24 +10379,24 @@
         <v>61</v>
       </c>
       <c r="F3" t="s">
+        <v>802</v>
+      </c>
+      <c r="G3" t="s">
         <v>803</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>804</v>
-      </c>
-      <c r="H3" t="s">
-        <v>805</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B4" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="C4" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="D4" t="s">
         <v>100</v>
@@ -10405,24 +10405,24 @@
         <v>101</v>
       </c>
       <c r="F4" t="s">
+        <v>798</v>
+      </c>
+      <c r="G4" t="s">
         <v>799</v>
       </c>
-      <c r="G4" t="s">
-        <v>800</v>
-      </c>
       <c r="H4" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B5" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="C5" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="D5" t="s">
         <v>87</v>
@@ -10431,21 +10431,21 @@
         <v>88</v>
       </c>
       <c r="F5" t="s">
+        <v>798</v>
+      </c>
+      <c r="G5" t="s">
         <v>799</v>
       </c>
-      <c r="G5" t="s">
-        <v>800</v>
-      </c>
       <c r="H5" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="B6" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="C6" t="s">
         <v>133</v>
@@ -10457,21 +10457,21 @@
         <v>70</v>
       </c>
       <c r="F6" t="s">
+        <v>810</v>
+      </c>
+      <c r="G6" t="s">
+        <v>799</v>
+      </c>
+      <c r="H6" t="s">
         <v>811</v>
-      </c>
-      <c r="G6" t="s">
-        <v>800</v>
-      </c>
-      <c r="H6" t="s">
-        <v>812</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="B7" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="C7" t="s">
         <v>133</v>
@@ -10483,24 +10483,24 @@
         <v>59</v>
       </c>
       <c r="F7" t="s">
+        <v>810</v>
+      </c>
+      <c r="G7" t="s">
+        <v>799</v>
+      </c>
+      <c r="H7" t="s">
         <v>811</v>
-      </c>
-      <c r="G7" t="s">
-        <v>800</v>
-      </c>
-      <c r="H7" t="s">
-        <v>812</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="B8" t="s">
+        <v>755</v>
+      </c>
+      <c r="C8" t="s">
         <v>756</v>
-      </c>
-      <c r="C8" t="s">
-        <v>757</v>
       </c>
       <c r="D8" t="s">
         <v>60</v>
@@ -10509,24 +10509,24 @@
         <v>61</v>
       </c>
       <c r="F8" t="s">
+        <v>802</v>
+      </c>
+      <c r="G8" t="s">
         <v>803</v>
       </c>
-      <c r="G8" t="s">
-        <v>804</v>
-      </c>
       <c r="H8" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="B9" t="s">
+        <v>755</v>
+      </c>
+      <c r="C9" t="s">
         <v>756</v>
-      </c>
-      <c r="C9" t="s">
-        <v>757</v>
       </c>
       <c r="D9" t="s">
         <v>73</v>
@@ -10535,18 +10535,18 @@
         <v>74</v>
       </c>
       <c r="F9" t="s">
+        <v>802</v>
+      </c>
+      <c r="G9" t="s">
         <v>803</v>
       </c>
-      <c r="G9" t="s">
-        <v>804</v>
-      </c>
       <c r="H9" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="B10" t="s">
         <v>51</v>
@@ -10561,15 +10561,15 @@
         <v>61</v>
       </c>
       <c r="F10" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="G10" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B11" t="s">
         <v>54</v>
@@ -10584,15 +10584,15 @@
         <v>66</v>
       </c>
       <c r="F11" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="G11" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="B12" t="s">
         <v>58</v>
@@ -10607,15 +10607,15 @@
         <v>70</v>
       </c>
       <c r="F12" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="G12" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="B13" t="s">
         <v>73</v>
@@ -10630,10 +10630,10 @@
         <v>61</v>
       </c>
       <c r="F13" t="s">
+        <v>823</v>
+      </c>
+      <c r="G13" t="s">
         <v>824</v>
-      </c>
-      <c r="G13" t="s">
-        <v>825</v>
       </c>
     </row>
   </sheetData>

--- a/data/dati.xlsx
+++ b/data/dati.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan_\Desktop\AMI\GitHub\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{041153CE-BB4E-499A-8E40-EBA3A27C5714}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCCB5099-04C0-43FF-8CAA-FD03A5D0D9CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Catalogo" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2753" uniqueCount="1069">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2684" uniqueCount="1050">
   <si>
     <t>ID_autorita</t>
   </si>
@@ -2799,9 +2799,6 @@
     <t>Coscienza Operaia</t>
   </si>
   <si>
-    <t>AMI-O-031</t>
-  </si>
-  <si>
     <t>Federazione Marxista-Leninista d'Italia</t>
   </si>
   <si>
@@ -2868,9 +2865,6 @@
     <t>Categoria_ISAAR</t>
   </si>
   <si>
-    <t>Fonte</t>
-  </si>
-  <si>
     <t>AMI-R-001</t>
   </si>
   <si>
@@ -2883,9 +2877,6 @@
     <t>1966-1991</t>
   </si>
   <si>
-    <t>AMI-0013; AMI-0016</t>
-  </si>
-  <si>
     <t>AMI-R-002</t>
   </si>
   <si>
@@ -2898,9 +2889,6 @@
     <t>1966-1970</t>
   </si>
   <si>
-    <t>AMI-0014; AMI-0033</t>
-  </si>
-  <si>
     <t>AMI-R-003</t>
   </si>
   <si>
@@ -2913,9 +2901,6 @@
     <t>1977-1984</t>
   </si>
   <si>
-    <t>AMI-0057; AMI-0054</t>
-  </si>
-  <si>
     <t>AMI-R-005</t>
   </si>
   <si>
@@ -2967,9 +2952,6 @@
     <t>AMI-R-013</t>
   </si>
   <si>
-    <t>AMI-0032; AMI-0036</t>
-  </si>
-  <si>
     <t>AMI-R-014</t>
   </si>
   <si>
@@ -2979,18 +2961,9 @@
     <t>temporale</t>
   </si>
   <si>
-    <t>1976</t>
-  </si>
-  <si>
     <t>AMI-R-015</t>
   </si>
   <si>
-    <t>prima del 1969</t>
-  </si>
-  <si>
-    <t>Tipo di entità da verificare (gruppo o testata)</t>
-  </si>
-  <si>
     <t>AMI-R-016</t>
   </si>
   <si>
@@ -3000,9 +2973,6 @@
     <t>AMI-R-018</t>
   </si>
   <si>
-    <t>attestato 1967</t>
-  </si>
-  <si>
     <t>AMI-R-019</t>
   </si>
   <si>
@@ -3012,60 +2982,24 @@
     <t>AMI-R-020</t>
   </si>
   <si>
-    <t>rappresentante di</t>
-  </si>
-  <si>
-    <t>1964</t>
-  </si>
-  <si>
-    <t>Nome di battaglia "Livio": da registrare come variante</t>
-  </si>
-  <si>
     <t>AMI-R-021</t>
   </si>
   <si>
-    <t>Variante del nome: "Gino"</t>
-  </si>
-  <si>
     <t>AMI-R-022</t>
   </si>
   <si>
-    <t>casa editrice di</t>
-  </si>
-  <si>
-    <t>attestato 1969</t>
-  </si>
-  <si>
-    <t>AMI-0035; AMI-0092</t>
-  </si>
-  <si>
-    <t>AMI-R-023</t>
-  </si>
-  <si>
-    <t>AMI-0053; AMI-0063</t>
-  </si>
-  <si>
     <t>AMI-R-024</t>
   </si>
   <si>
-    <t>La fonte dice "UCI di Aldo Brandirali"</t>
-  </si>
-  <si>
     <t>AMI-R-025</t>
   </si>
   <si>
-    <t>attestato 1974</t>
-  </si>
-  <si>
     <t>AMI-R-026</t>
   </si>
   <si>
     <t>dirigente di</t>
   </si>
   <si>
-    <t>La fonte dice "animato da"</t>
-  </si>
-  <si>
     <t>AMI-R-027</t>
   </si>
   <si>
@@ -3111,12 +3045,6 @@
     <t>AMI-R-037</t>
   </si>
   <si>
-    <t>AMI-0057; AMI-0064</t>
-  </si>
-  <si>
-    <t>Variante del nome: "Beppe"</t>
-  </si>
-  <si>
     <t>AMI-R-038</t>
   </si>
   <si>
@@ -3126,78 +3054,42 @@
     <t>organo di stampa di</t>
   </si>
   <si>
-    <t>dal 1977</t>
-  </si>
-  <si>
     <t>AMI-R-040</t>
   </si>
   <si>
-    <t>fino al 1977</t>
-  </si>
-  <si>
     <t>AMI-R-041</t>
   </si>
   <si>
-    <t>Anno 1973 ricavato da AMI-0057 ("nata nel 1973")</t>
-  </si>
-  <si>
     <t>AMI-R-042</t>
   </si>
   <si>
-    <t>Testata omonima dell'organizzazione</t>
-  </si>
-  <si>
     <t>AMI-R-043</t>
   </si>
   <si>
-    <t>attestato 1970</t>
-  </si>
-  <si>
     <t>AMI-R-044</t>
   </si>
   <si>
     <t>curatore di</t>
   </si>
   <si>
-    <t>come sopra</t>
-  </si>
-  <si>
     <t>AMI-R-045</t>
   </si>
   <si>
     <t>derivato da</t>
   </si>
   <si>
-    <t>La descrizione cita come fonte BFS collezioni digitali (fonte secondaria)</t>
-  </si>
-  <si>
     <t>AMI-R-046</t>
   </si>
   <si>
-    <t>Con i Circoli Lenin toscani; fonte BFS come sopra</t>
-  </si>
-  <si>
     <t>AMI-R-047</t>
   </si>
   <si>
-    <t>attestato 1965</t>
-  </si>
-  <si>
     <t>AMI-R-048</t>
   </si>
   <si>
-    <t>attestato 1968</t>
-  </si>
-  <si>
     <t>AMI-R-049</t>
   </si>
   <si>
-    <t>1966</t>
-  </si>
-  <si>
-    <t>Infografica AMI «Il marxismo-leninismo italiano»</t>
-  </si>
-  <si>
     <t>AMI-R-050</t>
   </si>
   <si>
@@ -3291,9 +3183,6 @@
     <t>Il Partito</t>
   </si>
   <si>
-    <t>-1973</t>
-  </si>
-  <si>
     <t>AMI-R-067</t>
   </si>
   <si>
@@ -3307,13 +3196,67 @@
   </si>
   <si>
     <t>giovanile di</t>
+  </si>
+  <si>
+    <t>UGCd'I(m-l)</t>
+  </si>
+  <si>
+    <t>Dino Frangioni; Giacomo Monemezzani</t>
+  </si>
+  <si>
+    <t>1921-</t>
+  </si>
+  <si>
+    <t>1966-1967</t>
+  </si>
+  <si>
+    <t>1968-1969</t>
+  </si>
+  <si>
+    <t>1969-1976</t>
+  </si>
+  <si>
+    <t>1976-1981</t>
+  </si>
+  <si>
+    <t>1962-1963</t>
+  </si>
+  <si>
+    <t>AMI-R-069</t>
+  </si>
+  <si>
+    <t>1962-2010</t>
+  </si>
+  <si>
+    <t>1964-1966</t>
+  </si>
+  <si>
+    <t>1968-1972</t>
+  </si>
+  <si>
+    <t>1969-1977</t>
+  </si>
+  <si>
+    <t>1968-1977</t>
+  </si>
+  <si>
+    <t>1969-1973</t>
+  </si>
+  <si>
+    <t>1970-1973</t>
+  </si>
+  <si>
+    <t>1968-1976</t>
+  </si>
+  <si>
+    <t>1973-1977</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3341,6 +3284,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Georgia"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -3373,7 +3322,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -3387,6 +3336,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Collegamento ipertestuale" xfId="1" builtinId="8"/>
@@ -3549,9 +3499,9 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Tabella5" displayName="Tabella5" ref="A1:J84" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A1:J84" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
-  <tableColumns count="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Tabella5" displayName="Tabella5" ref="A1:H84" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A1:H84" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
+  <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="ID_relazione"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="ID_entita_A"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="Entita_A"/>
@@ -3560,8 +3510,6 @@
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="Relazione"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" name="Categoria_ISAAR"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0400-000008000000}" name="Date"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0400-000009000000}" name="Fonte"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0400-00000A000000}" name="Note"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4854,6 +4802,9 @@
       <c r="M19" t="s">
         <v>233</v>
       </c>
+      <c r="N19" s="11" t="s">
+        <v>1033</v>
+      </c>
       <c r="P19" t="s">
         <v>172</v>
       </c>
@@ -5376,6 +5327,9 @@
       </c>
       <c r="M30" t="s">
         <v>304</v>
+      </c>
+      <c r="N30" t="s">
+        <v>86</v>
       </c>
       <c r="O30" t="s">
         <v>354</v>
@@ -8870,8 +8824,9 @@
     <hyperlink ref="Q97" r:id="rId96" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId97"/>
   <tableParts count="1">
-    <tablePart r:id="rId97"/>
+    <tablePart r:id="rId98"/>
   </tableParts>
 </worksheet>
 </file>
@@ -10788,6 +10743,9 @@
       <c r="E12" t="s">
         <v>845</v>
       </c>
+      <c r="F12" t="s">
+        <v>1032</v>
+      </c>
       <c r="G12" t="s">
         <v>846</v>
       </c>
@@ -11573,7 +11531,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:J69"/>
+  <dimension ref="A1:H69"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.21875" customWidth="1"/>
@@ -11589,41 +11547,35 @@
     <col min="12" max="12" width="55" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
+        <v>914</v>
+      </c>
+      <c r="B1" s="9" t="s">
         <v>915</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="C1" s="9" t="s">
         <v>916</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="D1" s="9" t="s">
         <v>917</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="E1" s="9" t="s">
         <v>918</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="F1" s="9" t="s">
         <v>919</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="G1" s="9" t="s">
         <v>920</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>921</v>
       </c>
       <c r="H1" s="9" t="s">
         <v>754</v>
       </c>
-      <c r="I1" s="9" t="s">
-        <v>922</v>
-      </c>
-      <c r="J1" s="9" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="B2" t="s">
         <v>31</v>
@@ -11638,21 +11590,18 @@
         <v>229</v>
       </c>
       <c r="F2" t="s">
+        <v>922</v>
+      </c>
+      <c r="G2" t="s">
+        <v>923</v>
+      </c>
+      <c r="H2" t="s">
         <v>924</v>
       </c>
-      <c r="G2" t="s">
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>925</v>
-      </c>
-      <c r="H2" t="s">
-        <v>926</v>
-      </c>
-      <c r="I2" t="s">
-        <v>927</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>928</v>
       </c>
       <c r="B3" t="s">
         <v>36</v>
@@ -11667,21 +11616,18 @@
         <v>229</v>
       </c>
       <c r="F3" t="s">
+        <v>926</v>
+      </c>
+      <c r="G3" t="s">
+        <v>927</v>
+      </c>
+      <c r="H3" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>929</v>
-      </c>
-      <c r="G3" t="s">
-        <v>930</v>
-      </c>
-      <c r="H3" t="s">
-        <v>931</v>
-      </c>
-      <c r="I3" t="s">
-        <v>932</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>933</v>
       </c>
       <c r="B4" t="s">
         <v>36</v>
@@ -11696,21 +11642,18 @@
         <v>887</v>
       </c>
       <c r="F4" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="G4" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="H4" t="s">
-        <v>934</v>
-      </c>
-      <c r="I4" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>935</v>
+        <v>931</v>
       </c>
       <c r="B5" t="s">
         <v>36</v>
@@ -11725,21 +11668,18 @@
         <v>505</v>
       </c>
       <c r="F5" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="G5" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="H5" t="s">
-        <v>936</v>
-      </c>
-      <c r="I5" t="s">
-        <v>937</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>938</v>
+        <v>933</v>
       </c>
       <c r="B6" t="s">
         <v>18</v>
@@ -11754,21 +11694,18 @@
         <v>166</v>
       </c>
       <c r="F6" t="s">
-        <v>939</v>
+        <v>934</v>
       </c>
       <c r="G6" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="H6" t="s">
-        <v>940</v>
-      </c>
-      <c r="I6" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>941</v>
+        <v>936</v>
       </c>
       <c r="B7" t="s">
         <v>18</v>
@@ -11783,21 +11720,18 @@
         <v>412</v>
       </c>
       <c r="F7" t="s">
-        <v>939</v>
+        <v>934</v>
       </c>
       <c r="G7" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="H7" t="s">
-        <v>940</v>
-      </c>
-      <c r="I7" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>942</v>
+        <v>937</v>
       </c>
       <c r="B8" t="s">
         <v>53</v>
@@ -11812,21 +11746,18 @@
         <v>229</v>
       </c>
       <c r="F8" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="G8" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="H8" t="s">
-        <v>943</v>
-      </c>
-      <c r="I8" t="s">
-        <v>932</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>944</v>
+        <v>939</v>
       </c>
       <c r="B9" t="s">
         <v>53</v>
@@ -11841,18 +11772,18 @@
         <v>867</v>
       </c>
       <c r="F9" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="G9" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="H9" t="s">
-        <v>945</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>946</v>
+        <v>941</v>
       </c>
       <c r="B10" t="s">
         <v>841</v>
@@ -11867,15 +11798,18 @@
         <v>229</v>
       </c>
       <c r="F10" t="s">
-        <v>947</v>
+        <v>942</v>
       </c>
       <c r="G10" t="s">
-        <v>925</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+        <v>923</v>
+      </c>
+      <c r="H10" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>948</v>
+        <v>943</v>
       </c>
       <c r="B11" t="s">
         <v>843</v>
@@ -11890,15 +11824,15 @@
         <v>267</v>
       </c>
       <c r="F11" t="s">
-        <v>949</v>
+        <v>944</v>
       </c>
       <c r="G11" t="s">
-        <v>925</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>950</v>
+        <v>945</v>
       </c>
       <c r="B12" t="s">
         <v>847</v>
@@ -11913,15 +11847,18 @@
         <v>166</v>
       </c>
       <c r="F12" t="s">
-        <v>947</v>
+        <v>942</v>
       </c>
       <c r="G12" t="s">
-        <v>925</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+        <v>923</v>
+      </c>
+      <c r="H12" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>951</v>
+        <v>946</v>
       </c>
       <c r="B13" t="s">
         <v>866</v>
@@ -11936,15 +11873,18 @@
         <v>229</v>
       </c>
       <c r="F13" t="s">
-        <v>952</v>
+        <v>947</v>
       </c>
       <c r="G13" t="s">
-        <v>953</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+        <v>948</v>
+      </c>
+      <c r="H13">
+        <v>1968</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>954</v>
+        <v>949</v>
       </c>
       <c r="B14" t="s">
         <v>49</v>
@@ -11959,21 +11899,18 @@
         <v>369</v>
       </c>
       <c r="F14" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="G14" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="H14" t="s">
-        <v>168</v>
-      </c>
-      <c r="I14" t="s">
-        <v>955</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>956</v>
+        <v>950</v>
       </c>
       <c r="B15" t="s">
         <v>869</v>
@@ -11982,24 +11919,21 @@
         <v>369</v>
       </c>
       <c r="E15" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="F15" t="s">
-        <v>957</v>
+        <v>951</v>
       </c>
       <c r="G15" t="s">
-        <v>958</v>
+        <v>952</v>
       </c>
       <c r="H15" t="s">
-        <v>959</v>
-      </c>
-      <c r="I15" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>960</v>
+        <v>953</v>
       </c>
       <c r="B16" t="s">
         <v>49</v>
@@ -12008,27 +11942,21 @@
         <v>50</v>
       </c>
       <c r="E16" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="F16" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="G16" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="H16" t="s">
-        <v>961</v>
-      </c>
-      <c r="I16" t="s">
-        <v>367</v>
-      </c>
-      <c r="J16" t="s">
-        <v>962</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>963</v>
+        <v>954</v>
       </c>
       <c r="B17" t="s">
         <v>49</v>
@@ -12037,24 +11965,21 @@
         <v>50</v>
       </c>
       <c r="E17" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="F17" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="G17" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="H17" t="s">
-        <v>961</v>
-      </c>
-      <c r="I17" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>964</v>
+        <v>955</v>
       </c>
       <c r="B18" t="s">
         <v>49</v>
@@ -12063,27 +11988,21 @@
         <v>50</v>
       </c>
       <c r="E18" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="F18" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="G18" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="H18" t="s">
-        <v>961</v>
-      </c>
-      <c r="I18" t="s">
-        <v>367</v>
-      </c>
-      <c r="J18" t="s">
-        <v>962</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>965</v>
+        <v>956</v>
       </c>
       <c r="B19" t="s">
         <v>90</v>
@@ -12098,21 +12017,18 @@
         <v>439</v>
       </c>
       <c r="F19" t="s">
-        <v>939</v>
+        <v>934</v>
       </c>
       <c r="G19" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="H19" t="s">
-        <v>966</v>
-      </c>
-      <c r="I19" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>967</v>
+        <v>957</v>
       </c>
       <c r="B20" t="s">
         <v>90</v>
@@ -12121,24 +12037,21 @@
         <v>91</v>
       </c>
       <c r="E20" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="F20" t="s">
-        <v>968</v>
+        <v>958</v>
       </c>
       <c r="G20" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="H20" t="s">
-        <v>966</v>
-      </c>
-      <c r="I20" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>969</v>
+        <v>959</v>
       </c>
       <c r="B21" t="s">
         <v>115</v>
@@ -12147,88 +12060,73 @@
         <v>116</v>
       </c>
       <c r="D21" t="s">
+        <v>850</v>
+      </c>
+      <c r="E21" t="s">
+        <v>229</v>
+      </c>
+      <c r="F21" t="s">
+        <v>926</v>
+      </c>
+      <c r="G21" t="s">
+        <v>927</v>
+      </c>
+      <c r="H21">
+        <v>1966</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>960</v>
+      </c>
+      <c r="B22" t="s">
+        <v>115</v>
+      </c>
+      <c r="C22" t="s">
+        <v>116</v>
+      </c>
+      <c r="D22" t="s">
         <v>821</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E22" t="s">
         <v>276</v>
       </c>
-      <c r="F21" t="s">
-        <v>970</v>
-      </c>
-      <c r="G21" t="s">
-        <v>930</v>
-      </c>
-      <c r="H21" t="s">
-        <v>971</v>
-      </c>
-      <c r="I21" t="s">
-        <v>274</v>
-      </c>
-      <c r="J21" t="s">
-        <v>972</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>973</v>
-      </c>
-      <c r="B22" t="s">
+      <c r="F22" t="s">
+        <v>926</v>
+      </c>
+      <c r="G22" t="s">
+        <v>927</v>
+      </c>
+      <c r="H22" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>961</v>
+      </c>
+      <c r="B23" t="s">
         <v>119</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C23" t="s">
         <v>120</v>
       </c>
-      <c r="E22" t="s">
-        <v>903</v>
-      </c>
-      <c r="F22" t="s">
-        <v>970</v>
-      </c>
-      <c r="G22" t="s">
-        <v>930</v>
-      </c>
-      <c r="H22" t="s">
-        <v>971</v>
-      </c>
-      <c r="I22" t="s">
-        <v>274</v>
-      </c>
-      <c r="J22" t="s">
-        <v>974</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>975</v>
-      </c>
-      <c r="B23" t="s">
-        <v>899</v>
-      </c>
-      <c r="C23" t="s">
-        <v>715</v>
-      </c>
-      <c r="D23" t="s">
-        <v>856</v>
-      </c>
       <c r="E23" t="s">
-        <v>267</v>
+        <v>902</v>
       </c>
       <c r="F23" t="s">
-        <v>976</v>
+        <v>926</v>
       </c>
       <c r="G23" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="H23" t="s">
-        <v>977</v>
-      </c>
-      <c r="I23" t="s">
-        <v>978</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>979</v>
+        <v>962</v>
       </c>
       <c r="B24" t="s">
         <v>856</v>
@@ -12243,21 +12141,18 @@
         <v>500</v>
       </c>
       <c r="F24" t="s">
-        <v>957</v>
+        <v>951</v>
       </c>
       <c r="G24" t="s">
-        <v>958</v>
-      </c>
-      <c r="H24" t="s">
-        <v>498</v>
-      </c>
-      <c r="I24" t="s">
-        <v>980</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+        <v>952</v>
+      </c>
+      <c r="H24">
+        <v>1972</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>981</v>
+        <v>963</v>
       </c>
       <c r="B25" t="s">
         <v>109</v>
@@ -12272,21 +12167,18 @@
         <v>267</v>
       </c>
       <c r="F25" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="G25" t="s">
-        <v>925</v>
-      </c>
-      <c r="I25" t="s">
-        <v>560</v>
-      </c>
-      <c r="J25" t="s">
-        <v>982</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+        <v>923</v>
+      </c>
+      <c r="H25" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>983</v>
+        <v>964</v>
       </c>
       <c r="B26" t="s">
         <v>895</v>
@@ -12301,21 +12193,15 @@
         <v>500</v>
       </c>
       <c r="F26" t="s">
-        <v>949</v>
+        <v>944</v>
       </c>
       <c r="G26" t="s">
-        <v>925</v>
-      </c>
-      <c r="H26" t="s">
-        <v>984</v>
-      </c>
-      <c r="I26" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>985</v>
+        <v>966</v>
       </c>
       <c r="B27" t="s">
         <v>123</v>
@@ -12330,21 +12216,18 @@
         <v>491</v>
       </c>
       <c r="F27" t="s">
-        <v>986</v>
+        <v>965</v>
       </c>
       <c r="G27" t="s">
-        <v>925</v>
-      </c>
-      <c r="I27" t="s">
-        <v>489</v>
-      </c>
-      <c r="J27" t="s">
-        <v>987</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+        <v>923</v>
+      </c>
+      <c r="H27" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>988</v>
+        <v>967</v>
       </c>
       <c r="B28" t="s">
         <v>136</v>
@@ -12359,18 +12242,18 @@
         <v>491</v>
       </c>
       <c r="F28" t="s">
-        <v>986</v>
+        <v>965</v>
       </c>
       <c r="G28" t="s">
-        <v>925</v>
-      </c>
-      <c r="I28" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+        <v>923</v>
+      </c>
+      <c r="H28" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>989</v>
+        <v>969</v>
       </c>
       <c r="B29" t="s">
         <v>871</v>
@@ -12379,24 +12262,21 @@
         <v>491</v>
       </c>
       <c r="E29" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="F29" t="s">
-        <v>990</v>
+        <v>968</v>
       </c>
       <c r="G29" t="s">
-        <v>958</v>
+        <v>952</v>
       </c>
       <c r="H29" t="s">
         <v>184</v>
       </c>
-      <c r="I29" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>991</v>
+        <v>970</v>
       </c>
       <c r="B30" t="s">
         <v>892</v>
@@ -12411,21 +12291,18 @@
         <v>491</v>
       </c>
       <c r="F30" t="s">
+        <v>947</v>
+      </c>
+      <c r="G30" t="s">
         <v>952</v>
-      </c>
-      <c r="G30" t="s">
-        <v>958</v>
       </c>
       <c r="H30" t="s">
         <v>168</v>
       </c>
-      <c r="I30" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>992</v>
+        <v>971</v>
       </c>
       <c r="B31" t="s">
         <v>136</v>
@@ -12440,18 +12317,18 @@
         <v>893</v>
       </c>
       <c r="F31" t="s">
-        <v>986</v>
+        <v>965</v>
       </c>
       <c r="G31" t="s">
-        <v>925</v>
-      </c>
-      <c r="I31" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+        <v>923</v>
+      </c>
+      <c r="H31" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>993</v>
+        <v>974</v>
       </c>
       <c r="B32" t="s">
         <v>886</v>
@@ -12466,21 +12343,18 @@
         <v>505</v>
       </c>
       <c r="F32" t="s">
-        <v>994</v>
+        <v>972</v>
       </c>
       <c r="G32" t="s">
-        <v>958</v>
+        <v>952</v>
       </c>
       <c r="H32" t="s">
-        <v>995</v>
-      </c>
-      <c r="I32" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>996</v>
+        <v>975</v>
       </c>
       <c r="B33" t="s">
         <v>880</v>
@@ -12495,21 +12369,18 @@
         <v>505</v>
       </c>
       <c r="F33" t="s">
-        <v>994</v>
+        <v>972</v>
       </c>
       <c r="G33" t="s">
-        <v>958</v>
+        <v>952</v>
       </c>
       <c r="H33" t="s">
-        <v>995</v>
-      </c>
-      <c r="I33" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>997</v>
+        <v>977</v>
       </c>
       <c r="B34" t="s">
         <v>889</v>
@@ -12524,21 +12395,18 @@
         <v>505</v>
       </c>
       <c r="F34" t="s">
-        <v>998</v>
+        <v>976</v>
       </c>
       <c r="G34" t="s">
-        <v>958</v>
+        <v>952</v>
       </c>
       <c r="H34" t="s">
-        <v>995</v>
-      </c>
-      <c r="I34" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>999</v>
+        <v>978</v>
       </c>
       <c r="B35" t="s">
         <v>892</v>
@@ -12553,21 +12421,18 @@
         <v>505</v>
       </c>
       <c r="F35" t="s">
-        <v>998</v>
+        <v>976</v>
       </c>
       <c r="G35" t="s">
-        <v>958</v>
+        <v>952</v>
       </c>
       <c r="H35" t="s">
-        <v>995</v>
-      </c>
-      <c r="I35" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>1000</v>
+        <v>979</v>
       </c>
       <c r="B36" t="s">
         <v>897</v>
@@ -12582,27 +12447,24 @@
         <v>505</v>
       </c>
       <c r="F36" t="s">
-        <v>998</v>
+        <v>976</v>
       </c>
       <c r="G36" t="s">
-        <v>958</v>
+        <v>952</v>
       </c>
       <c r="H36" t="s">
-        <v>995</v>
-      </c>
-      <c r="I36" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>1001</v>
+        <v>980</v>
       </c>
       <c r="B37" t="s">
+        <v>903</v>
+      </c>
+      <c r="C37" t="s">
         <v>904</v>
-      </c>
-      <c r="C37" t="s">
-        <v>905</v>
       </c>
       <c r="D37" t="s">
         <v>875</v>
@@ -12611,21 +12473,18 @@
         <v>505</v>
       </c>
       <c r="F37" t="s">
-        <v>998</v>
+        <v>976</v>
       </c>
       <c r="G37" t="s">
-        <v>958</v>
+        <v>952</v>
       </c>
       <c r="H37" t="s">
-        <v>995</v>
-      </c>
-      <c r="I37" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>1002</v>
+        <v>981</v>
       </c>
       <c r="B38" t="s">
         <v>126</v>
@@ -12640,21 +12499,18 @@
         <v>570</v>
       </c>
       <c r="F38" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="G38" t="s">
-        <v>925</v>
-      </c>
-      <c r="I38" t="s">
-        <v>1003</v>
-      </c>
-      <c r="J38" t="s">
-        <v>1004</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+        <v>923</v>
+      </c>
+      <c r="H38" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>1005</v>
+        <v>982</v>
       </c>
       <c r="B39" t="s">
         <v>130</v>
@@ -12669,21 +12525,21 @@
         <v>890</v>
       </c>
       <c r="F39" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="G39" t="s">
-        <v>925</v>
-      </c>
-      <c r="I39" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+        <v>923</v>
+      </c>
+      <c r="H39" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>1006</v>
+        <v>984</v>
       </c>
       <c r="B40" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="C40" t="s">
         <v>506</v>
@@ -12695,24 +12551,21 @@
         <v>505</v>
       </c>
       <c r="F40" t="s">
-        <v>1007</v>
+        <v>983</v>
       </c>
       <c r="G40" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="H40" t="s">
-        <v>1008</v>
-      </c>
-      <c r="I40" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>1009</v>
+        <v>985</v>
       </c>
       <c r="B41" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="C41" t="s">
         <v>506</v>
@@ -12724,21 +12577,18 @@
         <v>887</v>
       </c>
       <c r="F41" t="s">
-        <v>1007</v>
+        <v>983</v>
       </c>
       <c r="G41" t="s">
+        <v>927</v>
+      </c>
+      <c r="H41" t="s">
         <v>930</v>
       </c>
-      <c r="H41" t="s">
-        <v>1010</v>
-      </c>
-      <c r="I41" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>1011</v>
+        <v>986</v>
       </c>
       <c r="B42" t="s">
         <v>880</v>
@@ -12753,30 +12603,24 @@
         <v>229</v>
       </c>
       <c r="F42" t="s">
+        <v>947</v>
+      </c>
+      <c r="G42" t="s">
         <v>952</v>
-      </c>
-      <c r="G42" t="s">
-        <v>958</v>
       </c>
       <c r="H42" t="s">
         <v>739</v>
       </c>
-      <c r="I42" t="s">
-        <v>568</v>
-      </c>
-      <c r="J42" t="s">
-        <v>1012</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>1013</v>
+        <v>987</v>
       </c>
       <c r="B43" t="s">
+        <v>900</v>
+      </c>
+      <c r="C43" t="s">
         <v>901</v>
-      </c>
-      <c r="C43" t="s">
-        <v>902</v>
       </c>
       <c r="D43" t="s">
         <v>880</v>
@@ -12785,21 +12629,18 @@
         <v>570</v>
       </c>
       <c r="F43" t="s">
-        <v>1007</v>
+        <v>983</v>
       </c>
       <c r="G43" t="s">
-        <v>930</v>
-      </c>
-      <c r="I43" t="s">
-        <v>568</v>
-      </c>
-      <c r="J43" t="s">
-        <v>1014</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+        <v>927</v>
+      </c>
+      <c r="H43" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>1015</v>
+        <v>988</v>
       </c>
       <c r="B44" t="s">
         <v>133</v>
@@ -12814,21 +12655,18 @@
         <v>581</v>
       </c>
       <c r="F44" t="s">
-        <v>986</v>
+        <v>965</v>
       </c>
       <c r="G44" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="H44" t="s">
-        <v>1016</v>
-      </c>
-      <c r="I44" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>1017</v>
+        <v>990</v>
       </c>
       <c r="B45" t="s">
         <v>878</v>
@@ -12837,27 +12675,21 @@
         <v>593</v>
       </c>
       <c r="E45" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="F45" t="s">
-        <v>1018</v>
+        <v>989</v>
       </c>
       <c r="G45" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="H45" t="s">
-        <v>1016</v>
-      </c>
-      <c r="I45" t="s">
-        <v>603</v>
-      </c>
-      <c r="J45" t="s">
-        <v>1019</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>1020</v>
+        <v>992</v>
       </c>
       <c r="B46" t="s">
         <v>879</v>
@@ -12866,27 +12698,21 @@
         <v>721</v>
       </c>
       <c r="E46" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="F46" t="s">
-        <v>1021</v>
+        <v>991</v>
       </c>
       <c r="G46" t="s">
-        <v>958</v>
+        <v>952</v>
       </c>
       <c r="H46" t="s">
         <v>168</v>
       </c>
-      <c r="I46" t="s">
-        <v>719</v>
-      </c>
-      <c r="J46" t="s">
-        <v>1022</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>1023</v>
+        <v>993</v>
       </c>
       <c r="B47" t="s">
         <v>879</v>
@@ -12895,27 +12721,21 @@
         <v>721</v>
       </c>
       <c r="E47" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="F47" t="s">
-        <v>957</v>
+        <v>951</v>
       </c>
       <c r="G47" t="s">
-        <v>958</v>
+        <v>952</v>
       </c>
       <c r="H47" t="s">
         <v>498</v>
       </c>
-      <c r="I47" t="s">
-        <v>719</v>
-      </c>
-      <c r="J47" t="s">
-        <v>1024</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>1025</v>
+        <v>994</v>
       </c>
       <c r="B48" t="s">
         <v>104</v>
@@ -12924,24 +12744,18 @@
         <v>105</v>
       </c>
       <c r="E48" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="F48" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="G48" t="s">
-        <v>930</v>
-      </c>
-      <c r="H48" t="s">
-        <v>1026</v>
-      </c>
-      <c r="I48" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>1027</v>
+        <v>995</v>
       </c>
       <c r="B49" t="s">
         <v>112</v>
@@ -12956,21 +12770,15 @@
         <v>229</v>
       </c>
       <c r="F49" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="G49" t="s">
-        <v>930</v>
-      </c>
-      <c r="H49" t="s">
-        <v>1028</v>
-      </c>
-      <c r="I49" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>1029</v>
+        <v>996</v>
       </c>
       <c r="B50" t="s">
         <v>832</v>
@@ -12985,47 +12793,41 @@
         <v>229</v>
       </c>
       <c r="F50" t="s">
-        <v>1066</v>
+        <v>1029</v>
       </c>
       <c r="G50" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="H50" t="s">
-        <v>1030</v>
-      </c>
-      <c r="I50" t="s">
-        <v>1031</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>1032</v>
+        <v>997</v>
       </c>
       <c r="C51" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="E51" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="F51" t="s">
+        <v>947</v>
+      </c>
+      <c r="G51" t="s">
         <v>952</v>
-      </c>
-      <c r="G51" t="s">
-        <v>958</v>
       </c>
       <c r="H51" t="s">
         <v>177</v>
       </c>
-      <c r="I51" t="s">
-        <v>1031</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>1033</v>
+        <v>998</v>
       </c>
       <c r="C52" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="D52" t="s">
         <v>869</v>
@@ -13034,24 +12836,21 @@
         <v>369</v>
       </c>
       <c r="F52" t="s">
-        <v>957</v>
+        <v>951</v>
       </c>
       <c r="G52" t="s">
-        <v>958</v>
+        <v>952</v>
       </c>
       <c r="H52" t="s">
         <v>168</v>
       </c>
-      <c r="I52" t="s">
-        <v>1031</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>1034</v>
+        <v>1000</v>
       </c>
       <c r="C53" t="s">
-        <v>1035</v>
+        <v>999</v>
       </c>
       <c r="D53" t="s">
         <v>856</v>
@@ -13060,24 +12859,21 @@
         <v>267</v>
       </c>
       <c r="F53" t="s">
-        <v>998</v>
+        <v>976</v>
       </c>
       <c r="G53" t="s">
-        <v>958</v>
+        <v>952</v>
       </c>
       <c r="H53" t="s">
         <v>184</v>
       </c>
-      <c r="I53" t="s">
-        <v>1031</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>1036</v>
+        <v>1002</v>
       </c>
       <c r="C54" t="s">
-        <v>1037</v>
+        <v>1001</v>
       </c>
       <c r="D54" t="s">
         <v>850</v>
@@ -13086,21 +12882,18 @@
         <v>229</v>
       </c>
       <c r="F54" t="s">
+        <v>947</v>
+      </c>
+      <c r="G54" t="s">
         <v>952</v>
-      </c>
-      <c r="G54" t="s">
-        <v>958</v>
       </c>
       <c r="H54" t="s">
         <v>168</v>
       </c>
-      <c r="I54" t="s">
-        <v>1031</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>1038</v>
+        <v>1003</v>
       </c>
       <c r="B55" t="s">
         <v>889</v>
@@ -13115,24 +12908,21 @@
         <v>229</v>
       </c>
       <c r="F55" t="s">
+        <v>947</v>
+      </c>
+      <c r="G55" t="s">
         <v>952</v>
-      </c>
-      <c r="G55" t="s">
-        <v>958</v>
       </c>
       <c r="H55" t="s">
         <v>168</v>
       </c>
-      <c r="I55" t="s">
-        <v>1031</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>1039</v>
+        <v>1005</v>
       </c>
       <c r="C56" t="s">
-        <v>1040</v>
+        <v>1004</v>
       </c>
       <c r="D56" t="s">
         <v>850</v>
@@ -13141,21 +12931,18 @@
         <v>229</v>
       </c>
       <c r="F56" t="s">
+        <v>947</v>
+      </c>
+      <c r="G56" t="s">
         <v>952</v>
-      </c>
-      <c r="G56" t="s">
-        <v>958</v>
       </c>
       <c r="H56" t="s">
         <v>168</v>
       </c>
-      <c r="I56" t="s">
-        <v>1031</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>1041</v>
+        <v>1006</v>
       </c>
       <c r="B57" t="s">
         <v>886</v>
@@ -13170,47 +12957,41 @@
         <v>229</v>
       </c>
       <c r="F57" t="s">
+        <v>947</v>
+      </c>
+      <c r="G57" t="s">
         <v>952</v>
-      </c>
-      <c r="G57" t="s">
-        <v>958</v>
       </c>
       <c r="H57" t="s">
         <v>215</v>
       </c>
-      <c r="I57" t="s">
-        <v>1031</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>1042</v>
+        <v>1008</v>
       </c>
       <c r="C58" t="s">
-        <v>1040</v>
+        <v>1004</v>
       </c>
       <c r="E58" t="s">
-        <v>1043</v>
+        <v>1007</v>
       </c>
       <c r="F58" t="s">
-        <v>957</v>
+        <v>951</v>
       </c>
       <c r="G58" t="s">
-        <v>958</v>
+        <v>952</v>
       </c>
       <c r="H58" t="s">
-        <v>995</v>
-      </c>
-      <c r="I58" t="s">
-        <v>1031</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>1044</v>
+        <v>1011</v>
       </c>
       <c r="C59" t="s">
-        <v>1045</v>
+        <v>1009</v>
       </c>
       <c r="D59" t="s">
         <v>850</v>
@@ -13219,24 +13000,21 @@
         <v>229</v>
       </c>
       <c r="F59" t="s">
+        <v>947</v>
+      </c>
+      <c r="G59" t="s">
         <v>952</v>
       </c>
-      <c r="G59" t="s">
-        <v>958</v>
-      </c>
       <c r="H59" t="s">
-        <v>1046</v>
-      </c>
-      <c r="I59" t="s">
-        <v>1031</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>1047</v>
+        <v>1014</v>
       </c>
       <c r="C60" t="s">
-        <v>1048</v>
+        <v>1012</v>
       </c>
       <c r="D60" t="s">
         <v>850</v>
@@ -13245,21 +13023,18 @@
         <v>229</v>
       </c>
       <c r="F60" t="s">
+        <v>947</v>
+      </c>
+      <c r="G60" t="s">
         <v>952</v>
       </c>
-      <c r="G60" t="s">
-        <v>958</v>
-      </c>
       <c r="H60" t="s">
-        <v>1049</v>
-      </c>
-      <c r="I60" t="s">
-        <v>1031</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>1050</v>
+        <v>1017</v>
       </c>
       <c r="B61" t="s">
         <v>850</v>
@@ -13268,24 +13043,21 @@
         <v>229</v>
       </c>
       <c r="E61" t="s">
-        <v>1051</v>
+        <v>1015</v>
       </c>
       <c r="F61" t="s">
-        <v>998</v>
+        <v>976</v>
       </c>
       <c r="G61" t="s">
-        <v>958</v>
+        <v>952</v>
       </c>
       <c r="H61" t="s">
-        <v>1052</v>
-      </c>
-      <c r="I61" t="s">
-        <v>1031</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>1053</v>
+        <v>1018</v>
       </c>
       <c r="B62" t="s">
         <v>85</v>
@@ -13300,21 +13072,18 @@
         <v>867</v>
       </c>
       <c r="F62" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="G62" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="H62" t="s">
-        <v>184</v>
-      </c>
-      <c r="I62" t="s">
-        <v>1031</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>1054</v>
+        <v>1019</v>
       </c>
       <c r="B63" t="s">
         <v>874</v>
@@ -13329,24 +13098,21 @@
         <v>867</v>
       </c>
       <c r="F63" t="s">
-        <v>998</v>
+        <v>976</v>
       </c>
       <c r="G63" t="s">
-        <v>958</v>
+        <v>952</v>
       </c>
       <c r="H63" t="s">
         <v>184</v>
       </c>
-      <c r="I63" t="s">
-        <v>1031</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>1055</v>
+        <v>1021</v>
       </c>
       <c r="C64" t="s">
-        <v>1056</v>
+        <v>1020</v>
       </c>
       <c r="D64" t="s">
         <v>874</v>
@@ -13355,21 +13121,18 @@
         <v>298</v>
       </c>
       <c r="F64" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="G64" t="s">
-        <v>930</v>
-      </c>
-      <c r="I64" t="s">
-        <v>1031</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>1057</v>
+        <v>1023</v>
       </c>
       <c r="C65" t="s">
-        <v>1058</v>
+        <v>1022</v>
       </c>
       <c r="D65" t="s">
         <v>874</v>
@@ -13378,21 +13141,18 @@
         <v>298</v>
       </c>
       <c r="F65" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="G65" t="s">
-        <v>930</v>
-      </c>
-      <c r="I65" t="s">
-        <v>1031</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>1059</v>
+        <v>1025</v>
       </c>
       <c r="C66" t="s">
-        <v>1060</v>
+        <v>1024</v>
       </c>
       <c r="D66" t="s">
         <v>874</v>
@@ -13401,21 +13161,18 @@
         <v>298</v>
       </c>
       <c r="F66" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="G66" t="s">
-        <v>930</v>
-      </c>
-      <c r="I66" t="s">
-        <v>1031</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>1061</v>
+        <v>1027</v>
       </c>
       <c r="C67" t="s">
-        <v>1062</v>
+        <v>1026</v>
       </c>
       <c r="D67" t="s">
         <v>866</v>
@@ -13424,21 +13181,18 @@
         <v>867</v>
       </c>
       <c r="F67" t="s">
-        <v>1007</v>
+        <v>983</v>
       </c>
       <c r="G67" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="H67" t="s">
-        <v>1063</v>
-      </c>
-      <c r="I67" t="s">
-        <v>1031</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>1064</v>
+        <v>1030</v>
       </c>
       <c r="B68" t="s">
         <v>866</v>
@@ -13447,24 +13201,21 @@
         <v>867</v>
       </c>
       <c r="E68" t="s">
-        <v>1065</v>
+        <v>1028</v>
       </c>
       <c r="F68" t="s">
-        <v>998</v>
+        <v>976</v>
       </c>
       <c r="G68" t="s">
-        <v>958</v>
+        <v>952</v>
       </c>
       <c r="H68" t="s">
-        <v>995</v>
-      </c>
-      <c r="I68" t="s">
-        <v>1031</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>1067</v>
+        <v>1040</v>
       </c>
       <c r="B69" t="s">
         <v>844</v>
@@ -13479,13 +13230,13 @@
         <v>229</v>
       </c>
       <c r="F69" t="s">
-        <v>1068</v>
+        <v>1031</v>
       </c>
       <c r="G69" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="H69" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
     </row>
   </sheetData>

--- a/data/dati.xlsx
+++ b/data/dati.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan_\Desktop\AMI\GitHub\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50390168-6F12-4919-B523-A308F8F83507}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E00CFD43-FB2B-448F-AE27-357FA06C7482}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2706" uniqueCount="1067">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2723" uniqueCount="1071">
   <si>
     <t>ID_relazione</t>
   </si>
@@ -3302,12 +3302,24 @@
   <si>
     <t>1967-1969</t>
   </si>
+  <si>
+    <t>AMI-R-070</t>
+  </si>
+  <si>
+    <t>1972-1977</t>
+  </si>
+  <si>
+    <t>AMI-R-071</t>
+  </si>
+  <si>
+    <t>dino-dini.png</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3335,6 +3347,12 @@
       <color theme="1"/>
       <name val="Georgia"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -9588,6 +9606,9 @@
       <c r="I8" t="s">
         <v>942</v>
       </c>
+      <c r="J8" t="s">
+        <v>1070</v>
+      </c>
       <c r="O8" t="s">
         <v>925</v>
       </c>
@@ -11681,7 +11702,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:H69"/>
+  <dimension ref="A1:H71"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.21875" customWidth="1"/>
@@ -13377,7 +13398,60 @@
         <v>15</v>
       </c>
     </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B70" t="s">
+        <v>107</v>
+      </c>
+      <c r="C70" t="s">
+        <v>108</v>
+      </c>
+      <c r="D70" t="s">
+        <v>104</v>
+      </c>
+      <c r="E70" t="s">
+        <v>105</v>
+      </c>
+      <c r="F70" t="s">
+        <v>13</v>
+      </c>
+      <c r="G70" t="s">
+        <v>14</v>
+      </c>
+      <c r="H70" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B71" t="s">
+        <v>217</v>
+      </c>
+      <c r="C71" t="s">
+        <v>218</v>
+      </c>
+      <c r="D71" t="s">
+        <v>11</v>
+      </c>
+      <c r="E71" t="s">
+        <v>12</v>
+      </c>
+      <c r="F71" t="s">
+        <v>19</v>
+      </c>
+      <c r="G71" t="s">
+        <v>20</v>
+      </c>
+      <c r="H71" t="s">
+        <v>43</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/data/dati.xlsx
+++ b/data/dati.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan_\Desktop\AMI\GitHub\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan_\Desktop\AMI\GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E00CFD43-FB2B-448F-AE27-357FA06C7482}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DC73B3D-7387-4037-8C05-23CC62F14CF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -614,6 +614,9 @@
     <t>AMI-R-052</t>
   </si>
   <si>
+    <t>1967-1969</t>
+  </si>
+  <si>
     <t>AMI-R-053</t>
   </si>
   <si>
@@ -735,6 +738,15 @@
   </si>
   <si>
     <t>giovanile di</t>
+  </si>
+  <si>
+    <t>AMI-R-070</t>
+  </si>
+  <si>
+    <t>1972-1977</t>
+  </si>
+  <si>
+    <t>AMI-R-071</t>
   </si>
   <si>
     <t>ID</t>
@@ -2934,6 +2946,9 @@
     <t>Dini</t>
   </si>
   <si>
+    <t>dino-dini.png</t>
+  </si>
+  <si>
     <t>AMI-P-008</t>
   </si>
   <si>
@@ -3298,28 +3313,13 @@
   </si>
   <si>
     <t>PC(m-l-m)I</t>
-  </si>
-  <si>
-    <t>1967-1969</t>
-  </si>
-  <si>
-    <t>AMI-R-070</t>
-  </si>
-  <si>
-    <t>1972-1977</t>
-  </si>
-  <si>
-    <t>AMI-R-071</t>
-  </si>
-  <si>
-    <t>dino-dini.png</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3347,12 +3347,6 @@
       <color theme="1"/>
       <name val="Georgia"/>
       <family val="1"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -3885,87 +3879,87 @@
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D1" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="F1" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="G1" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="H1" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="I1" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="J1" s="9" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="K1" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="L1" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="M1" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="N1" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="O1" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="P1" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="Q1" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="R1" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="S1" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="T1" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="U1" s="9" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="V1" s="9" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B2" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C2" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D2" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="E2" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F2" t="s">
         <v>34</v>
@@ -3974,7 +3968,7 @@
         <v>32</v>
       </c>
       <c r="H2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="I2" s="1">
         <v>1969</v>
@@ -3983,39 +3977,39 @@
         <v>130</v>
       </c>
       <c r="K2" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="L2" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="M2" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="P2" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="V2" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B3" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C3" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D3" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="E3" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F3" t="s">
         <v>34</v>
@@ -4024,7 +4018,7 @@
         <v>32</v>
       </c>
       <c r="H3" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="I3" s="1">
         <v>1967</v>
@@ -4033,39 +4027,39 @@
         <v>194</v>
       </c>
       <c r="K3" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="L3" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="M3" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="P3" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="V3" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B4" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C4" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D4" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="E4" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F4" t="s">
         <v>34</v>
@@ -4074,7 +4068,7 @@
         <v>32</v>
       </c>
       <c r="H4" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="I4" s="1">
         <v>1968</v>
@@ -4083,39 +4077,39 @@
         <v>126</v>
       </c>
       <c r="K4" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="L4" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="M4" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="P4" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="V4" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B5" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C5" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D5" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="E5" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F5" t="s">
         <v>34</v>
@@ -4124,7 +4118,7 @@
         <v>32</v>
       </c>
       <c r="H5" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="I5" s="1">
         <v>1968</v>
@@ -4133,42 +4127,42 @@
         <v>126</v>
       </c>
       <c r="K5" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="L5" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="M5" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="N5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="P5" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="V5" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="B6" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C6" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D6" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="E6" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F6" t="s">
         <v>34</v>
@@ -4177,7 +4171,7 @@
         <v>32</v>
       </c>
       <c r="H6" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="I6" s="1">
         <v>1968</v>
@@ -4186,42 +4180,42 @@
         <v>126</v>
       </c>
       <c r="K6" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="L6" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="M6" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="O6" t="s">
         <v>39</v>
       </c>
       <c r="P6" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="V6" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B7" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C7" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D7" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="E7" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F7" t="s">
         <v>34</v>
@@ -4230,7 +4224,7 @@
         <v>32</v>
       </c>
       <c r="H7" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="I7" s="1">
         <v>1968</v>
@@ -4239,39 +4233,39 @@
         <v>126</v>
       </c>
       <c r="K7" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="L7" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="M7" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="P7" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="V7" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="B8" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C8" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D8" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="E8" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F8" t="s">
         <v>34</v>
@@ -4280,7 +4274,7 @@
         <v>32</v>
       </c>
       <c r="H8" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="I8" s="1">
         <v>1968</v>
@@ -4289,39 +4283,39 @@
         <v>126</v>
       </c>
       <c r="K8" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="L8" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="M8" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="P8" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="V8" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="B9" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C9" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D9" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="E9" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F9" t="s">
         <v>34</v>
@@ -4330,7 +4324,7 @@
         <v>32</v>
       </c>
       <c r="H9" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="I9" s="1">
         <v>1969</v>
@@ -4339,39 +4333,39 @@
         <v>130</v>
       </c>
       <c r="K9" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="L9" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="M9" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="P9" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="V9" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="B10" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C10" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D10" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="E10" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F10" t="s">
         <v>34</v>
@@ -4380,7 +4374,7 @@
         <v>32</v>
       </c>
       <c r="H10" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="I10" s="1">
         <v>1969</v>
@@ -4389,39 +4383,39 @@
         <v>130</v>
       </c>
       <c r="K10" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="L10" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="M10" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="P10" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="V10" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="B11" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C11" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D11" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="E11" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F11" t="s">
         <v>34</v>
@@ -4430,57 +4424,57 @@
         <v>32</v>
       </c>
       <c r="H11" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="I11" s="1">
         <v>1970</v>
       </c>
       <c r="J11" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K11" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="L11" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="M11" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="P11" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="V11" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="B12" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C12" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D12" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="E12" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F12" t="s">
         <v>34</v>
       </c>
       <c r="G12" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="H12" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="I12" s="1">
         <v>1968</v>
@@ -4489,51 +4483,51 @@
         <v>126</v>
       </c>
       <c r="K12" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="L12" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="M12" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="O12" t="s">
         <v>34</v>
       </c>
       <c r="P12" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="V12" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="B13" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C13" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D13" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="E13" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F13" t="s">
         <v>34</v>
       </c>
       <c r="G13" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="H13" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="I13" s="1">
         <v>1968</v>
@@ -4542,42 +4536,42 @@
         <v>126</v>
       </c>
       <c r="K13" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="L13" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="M13" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="O13" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="P13" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="V13" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B14" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C14" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D14" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="E14" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F14" t="s">
         <v>12</v>
@@ -4586,7 +4580,7 @@
         <v>50</v>
       </c>
       <c r="H14" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="I14" s="1">
         <v>1967</v>
@@ -4595,107 +4589,107 @@
         <v>194</v>
       </c>
       <c r="K14" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="L14" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="M14" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="N14" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="O14" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="P14" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="U14" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="V14" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="B15" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C15" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D15" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="E15" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="F15" t="s">
         <v>12</v>
       </c>
       <c r="G15" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="I15" s="2">
         <v>25064</v>
       </c>
       <c r="J15" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="K15" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="L15" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="M15" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="N15" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="O15" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="P15" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="R15" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="U15" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="V15" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="B16" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C16" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D16" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="E16" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="F16" t="s">
         <v>12</v>
@@ -4707,113 +4701,113 @@
         <v>25081</v>
       </c>
       <c r="J16" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="K16" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="L16" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="M16" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="N16" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="O16" t="s">
         <v>34</v>
       </c>
       <c r="P16" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q16" s="3" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="R16" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="U16" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="V16" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="B17" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C17" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D17" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="E17" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="F17" t="s">
         <v>12</v>
       </c>
       <c r="G17" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="I17" s="2">
         <v>25479</v>
       </c>
       <c r="J17" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="K17" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="L17" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="M17" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="N17" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="O17" t="s">
         <v>34</v>
       </c>
       <c r="P17" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q17" s="3" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="R17" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="U17" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="V17" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="B18" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C18" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D18" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="E18" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F18" t="s">
         <v>56</v>
@@ -4825,42 +4819,42 @@
         <v>25485</v>
       </c>
       <c r="J18" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="K18" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="L18" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="M18" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="P18" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q18" s="3" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="V18" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="B19" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C19" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D19" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="E19" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="F19" t="s">
         <v>97</v>
@@ -4872,60 +4866,60 @@
         <v>23514</v>
       </c>
       <c r="J19" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="K19" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="L19" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="M19" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="N19" s="11" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="O19" t="s">
         <v>102</v>
       </c>
       <c r="P19" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q19" s="3" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="R19" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="U19" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="V19" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="B20" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C20" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D20" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="E20" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="G20" t="s">
         <v>32</v>
       </c>
       <c r="H20" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="I20" s="1">
         <v>1969</v>
@@ -4934,524 +4928,524 @@
         <v>130</v>
       </c>
       <c r="K20" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="M20" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="P20" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q20" s="3" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="V20" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="B21" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C21" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D21" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="E21" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="G21" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="H21" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="I21" s="1">
         <v>1993</v>
       </c>
       <c r="J21" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="K21" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="L21" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="M21" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="P21" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q21" s="3" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="V21" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="B22" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C22" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D22" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="E22" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F22" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H22" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="J22" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="K22" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="L22" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="M22" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="P22" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="Q22" s="3" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="V22" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>403</v>
+      </c>
+      <c r="B23" t="s">
+        <v>264</v>
+      </c>
+      <c r="C23" t="s">
+        <v>265</v>
+      </c>
+      <c r="D23" t="s">
+        <v>404</v>
+      </c>
+      <c r="E23" t="s">
+        <v>267</v>
+      </c>
+      <c r="F23" t="s">
+        <v>222</v>
+      </c>
+      <c r="H23" t="s">
+        <v>394</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>405</v>
+      </c>
+      <c r="J23" t="s">
+        <v>406</v>
+      </c>
+      <c r="K23" t="s">
+        <v>397</v>
+      </c>
+      <c r="L23" t="s">
+        <v>398</v>
+      </c>
+      <c r="M23" t="s">
         <v>399</v>
       </c>
-      <c r="B23" t="s">
-        <v>260</v>
-      </c>
-      <c r="C23" t="s">
-        <v>261</v>
-      </c>
-      <c r="D23" t="s">
+      <c r="P23" t="s">
         <v>400</v>
       </c>
-      <c r="E23" t="s">
-        <v>263</v>
-      </c>
-      <c r="F23" t="s">
-        <v>221</v>
-      </c>
-      <c r="H23" t="s">
-        <v>390</v>
-      </c>
-      <c r="I23" s="6" t="s">
-        <v>401</v>
-      </c>
-      <c r="J23" t="s">
-        <v>402</v>
-      </c>
-      <c r="K23" t="s">
-        <v>393</v>
-      </c>
-      <c r="L23" t="s">
-        <v>394</v>
-      </c>
-      <c r="M23" t="s">
-        <v>395</v>
-      </c>
-      <c r="P23" t="s">
-        <v>396</v>
-      </c>
       <c r="Q23" s="3" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="V23" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="B24" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C24" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D24" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="E24" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F24" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H24" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="J24" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="K24" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="L24" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="M24" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="P24" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="Q24" s="3" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="V24" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="B25" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C25" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D25" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="E25" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F25" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H25" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="J25" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="K25" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="L25" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="M25" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="P25" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="Q25" s="3" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="V25" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="B26" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C26" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D26" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="E26" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F26" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H26" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="J26" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="K26" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="L26" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="M26" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="P26" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="Q26" s="3" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="V26" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="27" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="B27" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C27" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D27" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="E27" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F27" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H27" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="J27" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="K27" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="L27" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="M27" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="P27" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="Q27" s="3" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="V27" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="28" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="B28" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C28" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D28" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="E28" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F28" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H28" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="J28" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="K28" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="L28" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="M28" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="P28" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="Q28" s="3" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="V28" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="29" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="B29" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C29" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D29" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="E29" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F29" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H29" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="J29" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="K29" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="L29" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="M29" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="O29" t="s">
         <v>12</v>
       </c>
       <c r="P29" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="Q29" s="3" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="V29" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
     <row r="30" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="B30" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C30" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D30" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="E30" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F30" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H30" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="J30" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="K30" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="L30" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="M30" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="N30" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O30" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="P30" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="Q30" s="3" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="V30" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="31" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="B31" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C31" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D31" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="E31" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F31" t="s">
         <v>34</v>
       </c>
       <c r="G31" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="H31" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="I31" s="1">
         <v>1968</v>
@@ -5460,42 +5454,42 @@
         <v>126</v>
       </c>
       <c r="K31" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="L31" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="M31" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="P31" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q31" s="3" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="U31" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="V31" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
     </row>
     <row r="32" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="B32" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C32" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D32" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="E32" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F32" t="s">
         <v>34</v>
@@ -5504,7 +5498,7 @@
         <v>32</v>
       </c>
       <c r="H32" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="I32" s="1">
         <v>1968</v>
@@ -5513,39 +5507,39 @@
         <v>126</v>
       </c>
       <c r="K32" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="L32" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="M32" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="P32" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="Q32" s="3" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="V32" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="B33" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C33" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D33" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="E33" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F33" t="s">
         <v>67</v>
@@ -5554,45 +5548,45 @@
         <v>1970</v>
       </c>
       <c r="J33" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K33" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="M33" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="N33" t="s">
         <v>65</v>
       </c>
       <c r="P33" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q33" s="3" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="R33" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="V33" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="B34" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C34" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="D34" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="E34" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F34" t="s">
         <v>12</v>
@@ -5601,54 +5595,54 @@
         <v>25063</v>
       </c>
       <c r="J34" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="K34" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="L34" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="M34" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="N34" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="O34" t="s">
         <v>34</v>
       </c>
       <c r="P34" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q34" s="3" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="S34" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="T34" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="V34" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
     </row>
     <row r="35" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="B35" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C35" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="D35" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="E35" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F35" t="s">
         <v>34</v>
@@ -5660,101 +5654,101 @@
         <v>25081</v>
       </c>
       <c r="J35" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="K35" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="L35" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="M35" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="N35" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="O35" t="s">
         <v>12</v>
       </c>
       <c r="P35" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q35" s="3" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="S35" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="T35" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="V35" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="B36" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C36" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D36" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="E36" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F36" t="s">
         <v>56</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="J36" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="K36" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="L36" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="M36" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="N36" t="s">
         <v>32</v>
       </c>
       <c r="P36" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q36" s="3" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="V36" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="B37" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C37" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D37" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="E37" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F37" t="s">
         <v>67</v>
@@ -5763,54 +5757,54 @@
         <v>65</v>
       </c>
       <c r="H37" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="I37" s="1">
         <v>1975</v>
       </c>
       <c r="J37" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="K37" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="L37" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="M37" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="N37" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="O37" t="s">
         <v>67</v>
       </c>
       <c r="P37" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q37" s="3" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="V37" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
     </row>
     <row r="38" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="B38" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C38" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D38" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="E38" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F38" t="s">
         <v>34</v>
@@ -5819,7 +5813,7 @@
         <v>32</v>
       </c>
       <c r="H38" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="I38" s="1">
         <v>1968</v>
@@ -5828,42 +5822,42 @@
         <v>126</v>
       </c>
       <c r="K38" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="L38" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="M38" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="P38" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q38" s="3" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="U38" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="V38" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
     </row>
     <row r="39" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="B39" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C39" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D39" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="E39" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F39" t="s">
         <v>34</v>
@@ -5872,54 +5866,54 @@
         <v>39</v>
       </c>
       <c r="H39" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="I39" s="1">
         <v>1970</v>
       </c>
       <c r="J39" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K39" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="L39" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="M39" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="N39" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="P39" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q39" s="3" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="U39" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="V39" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="B40" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C40" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D40" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="E40" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F40" t="s">
         <v>34</v>
@@ -5928,7 +5922,7 @@
         <v>32</v>
       </c>
       <c r="H40" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="I40" s="1">
         <v>1968</v>
@@ -5937,101 +5931,101 @@
         <v>126</v>
       </c>
       <c r="K40" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="L40" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="M40" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="P40" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q40" s="3" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="U40" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="V40" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="B41" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C41" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D41" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="E41" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F41" t="s">
         <v>34</v>
       </c>
       <c r="G41" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="H41" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="I41" s="1">
         <v>1970</v>
       </c>
       <c r="J41" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K41" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="L41" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="M41" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="P41" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q41" s="3" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="U41" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="V41" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
     </row>
     <row r="42" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="B42" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C42" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D42" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="E42" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="G42" t="s">
         <v>32</v>
       </c>
       <c r="H42" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="I42" s="1">
         <v>1968</v>
@@ -6040,48 +6034,48 @@
         <v>126</v>
       </c>
       <c r="K42" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="L42" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="M42" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="P42" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q42" s="3" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="U42" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="V42" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
     </row>
     <row r="43" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="B43" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C43" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D43" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="E43" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="G43" t="s">
         <v>32</v>
       </c>
       <c r="H43" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="I43" s="1">
         <v>1967</v>
@@ -6090,13 +6084,13 @@
         <v>194</v>
       </c>
       <c r="K43" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="L43" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="M43" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="N43" t="s">
         <v>84</v>
@@ -6105,33 +6099,33 @@
         <v>86</v>
       </c>
       <c r="P43" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q43" s="3" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="U43" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="V43" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="B44" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C44" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D44" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="E44" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F44" t="s">
         <v>34</v>
@@ -6140,7 +6134,7 @@
         <v>32</v>
       </c>
       <c r="H44" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="I44" s="1">
         <v>1968</v>
@@ -6149,42 +6143,42 @@
         <v>126</v>
       </c>
       <c r="K44" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="L44" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="M44" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="P44" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q44" s="3" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="U44" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="V44" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
     </row>
     <row r="45" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="B45" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C45" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D45" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="E45" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F45" t="s">
         <v>34</v>
@@ -6193,7 +6187,7 @@
         <v>32</v>
       </c>
       <c r="H45" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="I45" s="1">
         <v>1967</v>
@@ -6202,45 +6196,45 @@
         <v>194</v>
       </c>
       <c r="K45" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="L45" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="M45" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="O45" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="P45" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q45" s="3" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="U45" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="V45" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
     </row>
     <row r="46" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="B46" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C46" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D46" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="E46" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F46" t="s">
         <v>34</v>
@@ -6249,7 +6243,7 @@
         <v>32</v>
       </c>
       <c r="H46" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="I46" s="1">
         <v>1968</v>
@@ -6258,42 +6252,42 @@
         <v>126</v>
       </c>
       <c r="K46" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="L46" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="M46" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="P46" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q46" s="3" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="U46" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="V46" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
     </row>
     <row r="47" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="B47" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C47" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D47" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="E47" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F47" t="s">
         <v>34</v>
@@ -6302,7 +6296,7 @@
         <v>32</v>
       </c>
       <c r="H47" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="I47" s="1">
         <v>1969</v>
@@ -6311,42 +6305,42 @@
         <v>130</v>
       </c>
       <c r="K47" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="L47" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="M47" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="P47" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q47" s="3" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="U47" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="V47" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
     </row>
     <row r="48" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="B48" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C48" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D48" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="E48" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F48" t="s">
         <v>34</v>
@@ -6355,51 +6349,51 @@
         <v>32</v>
       </c>
       <c r="H48" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="I48" s="1">
         <v>1971</v>
       </c>
       <c r="J48" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="K48" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="L48" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="M48" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="P48" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q48" s="3" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="U48" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="V48" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="B49" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C49" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D49" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="E49" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F49" t="s">
         <v>34</v>
@@ -6408,7 +6402,7 @@
         <v>32</v>
       </c>
       <c r="H49" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="I49" s="1">
         <v>1968</v>
@@ -6417,42 +6411,42 @@
         <v>126</v>
       </c>
       <c r="K49" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="L49" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="M49" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="P49" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q49" s="3" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="U49" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="V49" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
     </row>
     <row r="50" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="B50" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C50" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D50" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="E50" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F50" t="s">
         <v>34</v>
@@ -6461,7 +6455,7 @@
         <v>32</v>
       </c>
       <c r="H50" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="I50" s="1">
         <v>1968</v>
@@ -6470,42 +6464,42 @@
         <v>126</v>
       </c>
       <c r="K50" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="L50" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="M50" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="P50" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q50" s="3" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="U50" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="V50" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
     </row>
     <row r="51" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="B51" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C51" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D51" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="E51" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F51" t="s">
         <v>34</v>
@@ -6514,7 +6508,7 @@
         <v>32</v>
       </c>
       <c r="H51" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="I51" s="1">
         <v>1968</v>
@@ -6523,42 +6517,42 @@
         <v>126</v>
       </c>
       <c r="K51" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="L51" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="M51" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="P51" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q51" s="3" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="U51" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="V51" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="B52" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C52" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D52" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="E52" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F52" t="s">
         <v>34</v>
@@ -6567,7 +6561,7 @@
         <v>32</v>
       </c>
       <c r="H52" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="I52" s="1">
         <v>1968</v>
@@ -6576,42 +6570,42 @@
         <v>126</v>
       </c>
       <c r="K52" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="L52" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="M52" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="P52" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q52" s="3" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="U52" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="V52" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
     </row>
     <row r="53" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="B53" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C53" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D53" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="E53" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F53" t="s">
         <v>118</v>
@@ -6620,7 +6614,7 @@
         <v>118</v>
       </c>
       <c r="H53" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="I53" s="1">
         <v>1969</v>
@@ -6629,45 +6623,45 @@
         <v>130</v>
       </c>
       <c r="K53" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="L53" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="M53" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="N53" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="P53" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q53" s="3" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="U53" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="V53" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="B54" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C54" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D54" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="E54" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F54" t="s">
         <v>56</v>
@@ -6679,42 +6673,42 @@
         <v>182</v>
       </c>
       <c r="K54" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="L54" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="M54" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="O54" t="s">
         <v>105</v>
       </c>
       <c r="P54" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q54" s="3" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="V54" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
     </row>
     <row r="55" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="B55" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C55" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D55" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="E55" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F55" t="s">
         <v>28</v>
@@ -6726,54 +6720,54 @@
         <v>156</v>
       </c>
       <c r="I55" s="6" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="J55" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="K55" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="L55" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="M55" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="N55" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="P55" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q55" s="3" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="R55" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="U55" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="V55" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
     </row>
     <row r="56" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="B56" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C56" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D56" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="E56" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F56" t="s">
         <v>12</v>
@@ -6791,45 +6785,45 @@
         <v>194</v>
       </c>
       <c r="K56" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="M56" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="N56" t="s">
         <v>32</v>
       </c>
       <c r="P56" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q56" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="R56" t="s">
+        <v>608</v>
+      </c>
+      <c r="U56" t="s">
         <v>603</v>
       </c>
-      <c r="R56" t="s">
-        <v>604</v>
-      </c>
-      <c r="U56" t="s">
-        <v>599</v>
-      </c>
       <c r="V56" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
     </row>
     <row r="57" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="B57" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C57" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D57" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="E57" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F57" t="s">
         <v>97</v>
@@ -6847,42 +6841,42 @@
         <v>194</v>
       </c>
       <c r="K57" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="L57" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="M57" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="P57" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q57" s="3" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="U57" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="V57" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
     </row>
     <row r="58" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="B58" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C58" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D58" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="E58" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="F58" t="s">
         <v>28</v>
@@ -6897,60 +6891,60 @@
         <v>28253</v>
       </c>
       <c r="J58" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="K58" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="L58" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="M58" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="N58" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="O58" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="P58" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q58" s="3" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="R58" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="U58" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="V58" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
     </row>
     <row r="59" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="B59" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C59" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D59" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="E59" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F59" t="s">
         <v>97</v>
       </c>
       <c r="G59" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="H59" t="s">
         <v>97</v>
@@ -6959,51 +6953,51 @@
         <v>1970</v>
       </c>
       <c r="J59" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K59" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="L59" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="M59" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="P59" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q59" s="3" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="U59" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="V59" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
     </row>
     <row r="60" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="B60" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C60" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D60" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="E60" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F60" t="s">
         <v>97</v>
       </c>
       <c r="G60" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="H60" t="s">
         <v>97</v>
@@ -7012,51 +7006,51 @@
         <v>1970</v>
       </c>
       <c r="J60" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K60" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="L60" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="M60" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="P60" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q60" s="3" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="U60" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="V60" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
     </row>
     <row r="61" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="B61" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C61" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D61" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="E61" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F61" t="s">
         <v>97</v>
       </c>
       <c r="G61" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="H61" t="s">
         <v>97</v>
@@ -7065,51 +7059,51 @@
         <v>1965</v>
       </c>
       <c r="J61" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="K61" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="L61" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="M61" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="N61" t="s">
         <v>185</v>
       </c>
       <c r="O61" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="P61" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q61" s="3" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="U61" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="V61" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
     </row>
     <row r="62" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="B62" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C62" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D62" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="E62" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F62" t="s">
         <v>34</v>
@@ -7118,104 +7112,104 @@
         <v>32</v>
       </c>
       <c r="H62" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="I62" s="1">
         <v>1971</v>
       </c>
       <c r="J62" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="K62" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="L62" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="M62" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="P62" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q62" s="3" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="U62" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="V62" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
     </row>
     <row r="63" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="B63" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C63" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D63" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="E63" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="I63" s="4">
         <v>24917</v>
       </c>
       <c r="J63" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="K63" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="L63" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="M63" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="N63" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="O63" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="P63" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q63" s="3" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="R63" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="U63" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="V63" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="B64" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C64" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D64" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="E64" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F64" t="s">
         <v>105</v>
@@ -7224,48 +7218,48 @@
         <v>105</v>
       </c>
       <c r="I64" s="5" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="J64" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="K64" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="L64" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="M64" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="N64" t="s">
         <v>108</v>
       </c>
       <c r="P64" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="Q64" s="3" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="V64" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
     </row>
     <row r="65" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="B65" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C65" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D65" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="E65" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F65" t="s">
         <v>138</v>
@@ -7277,45 +7271,45 @@
         <v>26956</v>
       </c>
       <c r="J65" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="K65" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="L65" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="M65" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="O65" t="s">
         <v>162</v>
       </c>
       <c r="P65" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="Q65" s="3" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="V65" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
     </row>
     <row r="66" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="B66" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C66" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D66" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="E66" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="F66" t="s">
         <v>12</v>
@@ -7327,48 +7321,48 @@
         <v>126</v>
       </c>
       <c r="K66" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="L66" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="M66" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="N66" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="P66" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q66" s="3" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="R66" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="U66" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="V66" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
     </row>
     <row r="67" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="B67" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C67" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D67" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="E67" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="F67" t="s">
         <v>167</v>
@@ -7377,98 +7371,98 @@
         <v>1970</v>
       </c>
       <c r="J67" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K67" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="L67" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="M67" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="N67" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="P67" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q67" s="3" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="R67" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="U67" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="V67" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
     </row>
     <row r="68" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="B68" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C68" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D68" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="E68" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F68" t="s">
         <v>12</v>
       </c>
       <c r="I68" s="5" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="J68" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="K68" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="L68" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="M68" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="P68" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q68" s="3" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="R68" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="V68" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
     </row>
     <row r="69" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="B69" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C69" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D69" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="E69" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F69" t="s">
         <v>171</v>
@@ -7477,45 +7471,45 @@
         <v>171</v>
       </c>
       <c r="I69" s="7" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="J69" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="K69" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="L69" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="M69" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="P69" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="Q69" s="3" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="V69" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
     </row>
     <row r="70" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="B70" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C70" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D70" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="E70" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F70" t="s">
         <v>171</v>
@@ -7527,42 +7521,42 @@
         <v>25704</v>
       </c>
       <c r="J70" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="K70" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="L70" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="M70" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="P70" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="Q70" s="3" t="s">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="V70" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
     </row>
     <row r="71" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="B71" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C71" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D71" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="E71" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F71" t="s">
         <v>171</v>
@@ -7574,42 +7568,42 @@
         <v>25718</v>
       </c>
       <c r="J71" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="K71" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="L71" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="M71" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="P71" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="Q71" s="3" t="s">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="V71" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
     </row>
     <row r="72" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="B72" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C72" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D72" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="E72" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F72" t="s">
         <v>171</v>
@@ -7621,42 +7615,42 @@
         <v>25719</v>
       </c>
       <c r="J72" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="K72" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="L72" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="M72" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="P72" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="Q72" s="3" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="V72" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
     </row>
     <row r="73" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="B73" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C73" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D73" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="E73" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F73" t="s">
         <v>171</v>
@@ -7668,42 +7662,42 @@
         <v>25740</v>
       </c>
       <c r="J73" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="K73" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="L73" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="M73" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="P73" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="Q73" s="3" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="V73" t="s">
-        <v>708</v>
+        <v>712</v>
       </c>
     </row>
     <row r="74" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="B74" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C74" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D74" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="E74" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F74" t="s">
         <v>171</v>
@@ -7715,42 +7709,42 @@
         <v>25765</v>
       </c>
       <c r="J74" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="K74" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="L74" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="M74" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="P74" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="Q74" s="3" t="s">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="V74" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
     </row>
     <row r="75" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="B75" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C75" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D75" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="E75" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F75" t="s">
         <v>171</v>
@@ -7762,42 +7756,42 @@
         <v>25824</v>
       </c>
       <c r="J75" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="K75" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="L75" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="M75" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="P75" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="Q75" s="3" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="V75" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
     </row>
     <row r="76" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="B76" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C76" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D76" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="E76" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F76" t="s">
         <v>171</v>
@@ -7809,42 +7803,42 @@
         <v>25866</v>
       </c>
       <c r="J76" t="s">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="K76" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="L76" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="M76" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="P76" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="Q76" s="3" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="V76" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
     </row>
     <row r="77" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="B77" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C77" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D77" t="s">
-        <v>725</v>
+        <v>729</v>
       </c>
       <c r="E77" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F77" t="s">
         <v>171</v>
@@ -7856,42 +7850,42 @@
         <v>25887</v>
       </c>
       <c r="J77" t="s">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="K77" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="L77" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="M77" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="P77" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="Q77" s="3" t="s">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="V77" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
     </row>
     <row r="78" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="B78" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C78" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D78" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="E78" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F78" t="s">
         <v>171</v>
@@ -7903,42 +7897,42 @@
         <v>25915</v>
       </c>
       <c r="J78" t="s">
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="K78" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="L78" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="M78" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="P78" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="Q78" s="3" t="s">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="V78" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
     </row>
     <row r="79" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="B79" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C79" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D79" t="s">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="E79" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F79" t="s">
         <v>171</v>
@@ -7950,42 +7944,42 @@
         <v>25950</v>
       </c>
       <c r="J79" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="K79" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="L79" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="M79" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="P79" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="Q79" s="3" t="s">
-        <v>737</v>
+        <v>741</v>
       </c>
       <c r="V79" t="s">
-        <v>738</v>
+        <v>742</v>
       </c>
     </row>
     <row r="80" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="B80" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C80" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D80" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="E80" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F80" t="s">
         <v>171</v>
@@ -7997,42 +7991,42 @@
         <v>25971</v>
       </c>
       <c r="J80" t="s">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="K80" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="L80" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="M80" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="P80" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="Q80" s="3" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="V80" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
     </row>
     <row r="81" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="B81" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C81" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D81" t="s">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="E81" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F81" t="s">
         <v>171</v>
@@ -8044,42 +8038,42 @@
         <v>25999</v>
       </c>
       <c r="J81" t="s">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="K81" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="L81" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="M81" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="P81" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="Q81" s="3" t="s">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="V81" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="82" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="B82" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C82" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D82" t="s">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="E82" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F82" t="s">
         <v>171</v>
@@ -8091,42 +8085,42 @@
         <v>26027</v>
       </c>
       <c r="J82" t="s">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="K82" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="L82" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="M82" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="P82" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="Q82" s="3" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="V82" t="s">
-        <v>753</v>
+        <v>757</v>
       </c>
     </row>
     <row r="83" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="B83" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C83" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D83" t="s">
-        <v>755</v>
+        <v>759</v>
       </c>
       <c r="E83" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F83" t="s">
         <v>171</v>
@@ -8138,42 +8132,42 @@
         <v>26054</v>
       </c>
       <c r="J83" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="K83" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="L83" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="M83" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="P83" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="Q83" s="3" t="s">
-        <v>757</v>
+        <v>761</v>
       </c>
       <c r="V83" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
     </row>
     <row r="84" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
       <c r="B84" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C84" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D84" t="s">
-        <v>760</v>
+        <v>764</v>
       </c>
       <c r="E84" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F84" t="s">
         <v>171</v>
@@ -8185,42 +8179,42 @@
         <v>26076</v>
       </c>
       <c r="J84" t="s">
-        <v>761</v>
+        <v>765</v>
       </c>
       <c r="K84" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="L84" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="M84" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="P84" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="Q84" s="3" t="s">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="V84" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
     </row>
     <row r="85" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
       <c r="B85" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C85" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D85" t="s">
-        <v>765</v>
+        <v>769</v>
       </c>
       <c r="E85" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F85" t="s">
         <v>171</v>
@@ -8232,42 +8226,42 @@
         <v>26104</v>
       </c>
       <c r="J85" t="s">
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="K85" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="L85" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="M85" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="P85" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="Q85" s="3" t="s">
-        <v>767</v>
+        <v>771</v>
       </c>
       <c r="V85" t="s">
-        <v>768</v>
+        <v>772</v>
       </c>
     </row>
     <row r="86" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>769</v>
+        <v>773</v>
       </c>
       <c r="B86" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C86" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D86" t="s">
-        <v>770</v>
+        <v>774</v>
       </c>
       <c r="E86" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F86" t="s">
         <v>171</v>
@@ -8279,42 +8273,42 @@
         <v>26139</v>
       </c>
       <c r="J86" t="s">
-        <v>771</v>
+        <v>775</v>
       </c>
       <c r="K86" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="L86" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="M86" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="P86" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="Q86" s="3" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="V86" t="s">
-        <v>773</v>
+        <v>777</v>
       </c>
     </row>
     <row r="87" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>774</v>
+        <v>778</v>
       </c>
       <c r="B87" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C87" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D87" t="s">
-        <v>775</v>
+        <v>779</v>
       </c>
       <c r="E87" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F87" t="s">
         <v>171</v>
@@ -8326,42 +8320,42 @@
         <v>26265</v>
       </c>
       <c r="J87" t="s">
-        <v>776</v>
+        <v>780</v>
       </c>
       <c r="K87" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="L87" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="M87" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="P87" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="Q87" s="3" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="V87" t="s">
-        <v>778</v>
+        <v>782</v>
       </c>
     </row>
     <row r="88" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>779</v>
+        <v>783</v>
       </c>
       <c r="B88" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C88" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D88" t="s">
-        <v>780</v>
+        <v>784</v>
       </c>
       <c r="E88" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F88" t="s">
         <v>171</v>
@@ -8373,42 +8367,42 @@
         <v>26307</v>
       </c>
       <c r="J88" t="s">
-        <v>781</v>
+        <v>785</v>
       </c>
       <c r="K88" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="L88" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="M88" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="P88" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="Q88" s="3" t="s">
-        <v>782</v>
+        <v>786</v>
       </c>
       <c r="V88" t="s">
-        <v>783</v>
+        <v>787</v>
       </c>
     </row>
     <row r="89" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="B89" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C89" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D89" t="s">
-        <v>785</v>
+        <v>789</v>
       </c>
       <c r="E89" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F89" t="s">
         <v>171</v>
@@ -8420,42 +8414,42 @@
         <v>26370</v>
       </c>
       <c r="J89" t="s">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="K89" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="L89" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="M89" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="P89" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="Q89" s="3" t="s">
-        <v>787</v>
+        <v>791</v>
       </c>
       <c r="V89" t="s">
-        <v>788</v>
+        <v>792</v>
       </c>
     </row>
     <row r="90" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>789</v>
+        <v>793</v>
       </c>
       <c r="B90" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C90" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D90" t="s">
-        <v>790</v>
+        <v>794</v>
       </c>
       <c r="E90" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F90" t="s">
         <v>171</v>
@@ -8467,42 +8461,42 @@
         <v>26420</v>
       </c>
       <c r="J90" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="K90" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="L90" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="M90" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="P90" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="Q90" s="3" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="V90" t="s">
-        <v>793</v>
+        <v>797</v>
       </c>
     </row>
     <row r="91" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>794</v>
+        <v>798</v>
       </c>
       <c r="B91" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C91" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D91" t="s">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="E91" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F91" t="s">
         <v>171</v>
@@ -8514,42 +8508,42 @@
         <v>26608</v>
       </c>
       <c r="J91" t="s">
-        <v>796</v>
+        <v>800</v>
       </c>
       <c r="K91" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="L91" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="M91" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="P91" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="Q91" s="3" t="s">
-        <v>797</v>
+        <v>801</v>
       </c>
       <c r="V91" t="s">
-        <v>798</v>
+        <v>802</v>
       </c>
     </row>
     <row r="92" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="B92" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C92" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D92" t="s">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="E92" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F92" t="s">
         <v>171</v>
@@ -8561,48 +8555,48 @@
         <v>26785</v>
       </c>
       <c r="J92" t="s">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="K92" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="L92" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="M92" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="P92" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="Q92" s="3" t="s">
-        <v>802</v>
+        <v>806</v>
       </c>
       <c r="V92" t="s">
-        <v>803</v>
+        <v>807</v>
       </c>
     </row>
     <row r="93" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="B93" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C93" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D93" t="s">
-        <v>805</v>
+        <v>809</v>
       </c>
       <c r="E93" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F93" t="s">
         <v>56</v>
       </c>
       <c r="H93" t="s">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="I93">
         <v>1969</v>
@@ -8611,48 +8605,48 @@
         <v>130</v>
       </c>
       <c r="K93" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="L93" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="M93" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="N93" t="s">
-        <v>807</v>
+        <v>811</v>
       </c>
       <c r="O93" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="P93" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q93" s="3" t="s">
-        <v>809</v>
+        <v>813</v>
       </c>
       <c r="U93" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="V93" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
     </row>
     <row r="94" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>812</v>
+        <v>816</v>
       </c>
       <c r="B94" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C94" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D94" t="s">
-        <v>813</v>
+        <v>817</v>
       </c>
       <c r="E94" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F94" t="s">
         <v>177</v>
@@ -8661,51 +8655,51 @@
         <v>177</v>
       </c>
       <c r="I94" s="5" t="s">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="J94" t="s">
-        <v>815</v>
+        <v>819</v>
       </c>
       <c r="K94" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="L94" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="M94" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="O94" t="s">
-        <v>817</v>
+        <v>821</v>
       </c>
       <c r="P94" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q94" s="3" t="s">
-        <v>818</v>
+        <v>822</v>
       </c>
       <c r="U94" t="s">
-        <v>819</v>
+        <v>823</v>
       </c>
       <c r="V94" t="s">
-        <v>820</v>
+        <v>824</v>
       </c>
     </row>
     <row r="95" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>821</v>
+        <v>825</v>
       </c>
       <c r="B95" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C95" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D95" t="s">
-        <v>822</v>
+        <v>826</v>
       </c>
       <c r="E95" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F95" t="s">
         <v>34</v>
@@ -8714,7 +8708,7 @@
         <v>32</v>
       </c>
       <c r="H95" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="I95">
         <v>1968</v>
@@ -8723,42 +8717,42 @@
         <v>126</v>
       </c>
       <c r="K95" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="L95" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="M95" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="P95" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="Q95" s="3" t="s">
-        <v>823</v>
+        <v>827</v>
       </c>
       <c r="U95" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="V95" t="s">
-        <v>824</v>
+        <v>828</v>
       </c>
     </row>
     <row r="96" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>825</v>
+        <v>829</v>
       </c>
       <c r="B96" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C96" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D96" t="s">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="E96" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F96" t="s">
         <v>34</v>
@@ -8767,7 +8761,7 @@
         <v>32</v>
       </c>
       <c r="H96" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="I96">
         <v>1969</v>
@@ -8776,45 +8770,45 @@
         <v>130</v>
       </c>
       <c r="K96" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="L96" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="M96" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="O96" t="s">
         <v>86</v>
       </c>
       <c r="P96" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="Q96" s="3" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="U96" t="s">
-        <v>828</v>
+        <v>832</v>
       </c>
       <c r="V96" t="s">
-        <v>829</v>
+        <v>833</v>
       </c>
     </row>
     <row r="97" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="B97" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C97" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D97" t="s">
-        <v>831</v>
+        <v>835</v>
       </c>
       <c r="E97" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="I97">
         <v>1973</v>
@@ -8823,31 +8817,42 @@
         <v>160</v>
       </c>
       <c r="K97" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="M97" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="N97" t="s">
         <v>32</v>
       </c>
       <c r="P97" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q97" s="3" t="s">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="R97" t="s">
-        <v>833</v>
+        <v>837</v>
       </c>
       <c r="U97" t="s">
-        <v>834</v>
+        <v>838</v>
       </c>
       <c r="V97" t="s">
-        <v>835</v>
+        <v>839</v>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valore non previsto" error="Scegli un valore dal menu (Altro, Archivio, Articolo, Audio, Corrispondenza, Documento, Foto, Fotografia, Giornale, Libro, Manifesto, Opuscolo, Periodico, Rivista, Testo, Testo_bilingue, Volantino)." promptTitle="Tipo" prompt="Scegli dal menu a tendina." sqref="K2:K5000" xr:uid="{00000000-0002-0000-0000-000000000000}">
+      <formula1>"Altro,Archivio,Articolo,Audio,Corrispondenza,Documento,Foto,Fotografia,Giornale,Libro,Manifesto,Opuscolo,Periodico,Rivista,Testo,Testo_bilingue,Volantino"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valore non previsto" error="Scegli un valore dal menu (unità)." promptTitle="Livello" prompt="Scegli dal menu a tendina." sqref="B2:B5000" xr:uid="{00000000-0002-0000-0000-000001000000}">
+      <formula1>"unità"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valore non previsto" error="Scegli un valore dal menu (Sì, No)." promptTitle="Titolo_attribuito" prompt="Scegli dal menu a tendina." sqref="E2:E5000" xr:uid="{00000000-0002-0000-0000-000002000000}">
+      <formula1>"Sì,No"</formula1>
+    </dataValidation>
+  </dataValidations>
   <hyperlinks>
     <hyperlink ref="Q2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="Q3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
@@ -8967,275 +8972,275 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>837</v>
+        <v>841</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>839</v>
+        <v>843</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
-        <v>840</v>
+        <v>844</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>841</v>
+        <v>845</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="D2" s="10"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="D3" s="10"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
-        <v>845</v>
+        <v>849</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="10"/>
       <c r="D4" s="10" t="s">
-        <v>846</v>
+        <v>850</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
-        <v>847</v>
+        <v>851</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>848</v>
+        <v>852</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>849</v>
+        <v>853</v>
       </c>
       <c r="D5" s="10"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
-        <v>850</v>
+        <v>854</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="C6" s="10"/>
       <c r="D6" s="10" t="s">
-        <v>851</v>
+        <v>855</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
-        <v>852</v>
+        <v>856</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>853</v>
+        <v>857</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>854</v>
+        <v>858</v>
       </c>
       <c r="D7" s="10"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="10" t="s">
-        <v>855</v>
+        <v>859</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="C8" s="10"/>
       <c r="D8" s="10"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
-        <v>857</v>
+        <v>861</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>858</v>
+        <v>862</v>
       </c>
       <c r="C9" s="10"/>
       <c r="D9" s="10" t="s">
-        <v>859</v>
+        <v>863</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="10" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>861</v>
+        <v>865</v>
       </c>
       <c r="C10" s="10"/>
       <c r="D10" s="10" t="s">
-        <v>862</v>
+        <v>866</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
-        <v>863</v>
+        <v>867</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="C11" s="10"/>
       <c r="D11" s="10" t="s">
-        <v>865</v>
+        <v>869</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="10" t="s">
-        <v>866</v>
+        <v>870</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>867</v>
+        <v>871</v>
       </c>
       <c r="C12" s="10"/>
       <c r="D12" s="10"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="10" t="s">
-        <v>868</v>
+        <v>872</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>869</v>
+        <v>873</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>870</v>
+        <v>874</v>
       </c>
       <c r="D13" s="10"/>
     </row>
     <row r="14" spans="1:4" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="10" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>872</v>
+        <v>876</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>873</v>
+        <v>877</v>
       </c>
       <c r="D14" s="10"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="10" t="s">
-        <v>874</v>
+        <v>878</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>876</v>
+        <v>880</v>
       </c>
       <c r="D15" s="10"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="10" t="s">
-        <v>877</v>
+        <v>881</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>878</v>
+        <v>882</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>876</v>
+        <v>880</v>
       </c>
       <c r="D16" s="10"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="10" t="s">
-        <v>880</v>
+        <v>884</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="10" t="s">
-        <v>881</v>
+        <v>885</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>882</v>
+        <v>886</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="D18" s="10"/>
     </row>
     <row r="19" spans="1:4" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>885</v>
+        <v>889</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="10" t="s">
-        <v>886</v>
+        <v>890</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="10" t="s">
-        <v>887</v>
+        <v>891</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>888</v>
+        <v>892</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>889</v>
+        <v>893</v>
       </c>
       <c r="D20" s="10"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
-        <v>890</v>
+        <v>894</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>891</v>
+        <v>895</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
       <c r="D21" s="10"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="10" t="s">
-        <v>893</v>
+        <v>897</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>894</v>
+        <v>898</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>895</v>
+        <v>899</v>
       </c>
       <c r="D22" s="10"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
-        <v>896</v>
+        <v>900</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>897</v>
+        <v>901</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>898</v>
+        <v>902</v>
       </c>
       <c r="D23" s="10"/>
     </row>
@@ -9269,58 +9274,58 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
-        <v>899</v>
+        <v>903</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>900</v>
+        <v>904</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>901</v>
+        <v>905</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>902</v>
+        <v>906</v>
       </c>
       <c r="E1" t="s">
-        <v>903</v>
+        <v>907</v>
       </c>
       <c r="F1" t="s">
-        <v>904</v>
+        <v>908</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>905</v>
+        <v>909</v>
       </c>
       <c r="H1" t="s">
-        <v>906</v>
+        <v>910</v>
       </c>
       <c r="I1" t="s">
-        <v>907</v>
+        <v>911</v>
       </c>
       <c r="J1" t="s">
-        <v>908</v>
+        <v>912</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>909</v>
+        <v>913</v>
       </c>
       <c r="L1" s="9" t="s">
-        <v>910</v>
+        <v>914</v>
       </c>
       <c r="M1" s="9" t="s">
-        <v>911</v>
+        <v>915</v>
       </c>
       <c r="N1" s="9" t="s">
-        <v>912</v>
+        <v>916</v>
       </c>
       <c r="O1" s="9" t="s">
-        <v>913</v>
+        <v>917</v>
       </c>
       <c r="P1" s="9" t="s">
-        <v>914</v>
+        <v>918</v>
       </c>
       <c r="Q1" s="9" t="s">
-        <v>915</v>
+        <v>919</v>
       </c>
       <c r="R1" s="9" t="s">
-        <v>916</v>
+        <v>920</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
@@ -9328,22 +9333,22 @@
         <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>917</v>
+        <v>921</v>
       </c>
       <c r="C2" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="D2" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="E2" t="s">
         <v>32</v>
       </c>
       <c r="F2" t="s">
-        <v>920</v>
+        <v>924</v>
       </c>
       <c r="G2" t="s">
-        <v>921</v>
+        <v>925</v>
       </c>
       <c r="H2">
         <v>1893</v>
@@ -9352,25 +9357,25 @@
         <v>1976</v>
       </c>
       <c r="J2" t="s">
-        <v>922</v>
+        <v>926</v>
       </c>
       <c r="M2" t="s">
-        <v>923</v>
+        <v>927</v>
       </c>
       <c r="N2" t="s">
-        <v>924</v>
+        <v>928</v>
       </c>
       <c r="O2" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="P2" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="Q2" s="4">
         <v>46297</v>
       </c>
       <c r="R2" t="s">
-        <v>927</v>
+        <v>931</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
@@ -9378,19 +9383,19 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>917</v>
+        <v>921</v>
       </c>
       <c r="C3" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="D3" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>928</v>
+        <v>932</v>
       </c>
       <c r="H3">
         <v>1921</v>
@@ -9399,22 +9404,22 @@
         <v>1993</v>
       </c>
       <c r="J3" t="s">
+        <v>933</v>
+      </c>
+      <c r="M3" t="s">
+        <v>934</v>
+      </c>
+      <c r="O3" t="s">
         <v>929</v>
       </c>
-      <c r="M3" t="s">
+      <c r="P3" t="s">
         <v>930</v>
-      </c>
-      <c r="O3" t="s">
-        <v>925</v>
-      </c>
-      <c r="P3" t="s">
-        <v>926</v>
       </c>
       <c r="Q3" s="4">
         <v>46297</v>
       </c>
       <c r="R3" t="s">
-        <v>927</v>
+        <v>931</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
@@ -9422,19 +9427,19 @@
         <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>917</v>
+        <v>921</v>
       </c>
       <c r="C4" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="D4" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="E4" t="s">
         <v>18</v>
       </c>
       <c r="F4" t="s">
-        <v>931</v>
+        <v>935</v>
       </c>
       <c r="H4">
         <v>1938</v>
@@ -9443,42 +9448,42 @@
         <v>2021</v>
       </c>
       <c r="J4" t="s">
-        <v>932</v>
+        <v>936</v>
       </c>
       <c r="O4" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="P4" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="Q4" s="4">
         <v>46297</v>
       </c>
       <c r="R4" t="s">
-        <v>927</v>
+        <v>931</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>933</v>
+        <v>937</v>
       </c>
       <c r="B5" t="s">
-        <v>917</v>
+        <v>921</v>
       </c>
       <c r="C5" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="D5" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="E5" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="F5" t="s">
-        <v>934</v>
+        <v>938</v>
       </c>
       <c r="G5" t="s">
-        <v>935</v>
+        <v>939</v>
       </c>
       <c r="H5">
         <v>1931</v>
@@ -9487,42 +9492,42 @@
         <v>2005</v>
       </c>
       <c r="M5" t="s">
-        <v>936</v>
+        <v>940</v>
       </c>
       <c r="N5" t="s">
-        <v>937</v>
+        <v>941</v>
       </c>
       <c r="O5" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="P5" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="Q5" s="4">
         <v>46297</v>
       </c>
       <c r="R5" t="s">
-        <v>927</v>
+        <v>931</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>938</v>
+        <v>942</v>
       </c>
       <c r="B6" t="s">
-        <v>917</v>
+        <v>921</v>
       </c>
       <c r="C6" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="D6" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="E6" t="s">
-        <v>939</v>
+        <v>943</v>
       </c>
       <c r="F6" t="s">
-        <v>940</v>
+        <v>944</v>
       </c>
       <c r="H6">
         <v>1960</v>
@@ -9531,16 +9536,16 @@
         <v>2023</v>
       </c>
       <c r="O6" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="P6" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="Q6" s="4">
         <v>46297</v>
       </c>
       <c r="R6" t="s">
-        <v>927</v>
+        <v>931</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
@@ -9548,37 +9553,37 @@
         <v>64</v>
       </c>
       <c r="B7" t="s">
-        <v>917</v>
+        <v>921</v>
       </c>
       <c r="C7" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="D7" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="E7" t="s">
         <v>65</v>
       </c>
       <c r="F7" t="s">
-        <v>941</v>
+        <v>945</v>
       </c>
       <c r="H7" t="s">
-        <v>942</v>
+        <v>946</v>
       </c>
       <c r="I7" t="s">
-        <v>942</v>
+        <v>946</v>
       </c>
       <c r="O7" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="P7" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="Q7" s="4">
         <v>46297</v>
       </c>
       <c r="R7" t="s">
-        <v>927</v>
+        <v>931</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
@@ -9586,63 +9591,63 @@
         <v>41</v>
       </c>
       <c r="B8" t="s">
-        <v>917</v>
+        <v>921</v>
       </c>
       <c r="C8" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="D8" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="E8" t="s">
         <v>42</v>
       </c>
       <c r="F8" t="s">
-        <v>943</v>
+        <v>947</v>
       </c>
       <c r="H8" t="s">
-        <v>942</v>
+        <v>946</v>
       </c>
       <c r="I8" t="s">
-        <v>942</v>
+        <v>946</v>
       </c>
       <c r="J8" t="s">
-        <v>1070</v>
+        <v>948</v>
       </c>
       <c r="O8" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="P8" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="Q8" s="4">
         <v>46297</v>
       </c>
       <c r="R8" t="s">
-        <v>927</v>
+        <v>931</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>944</v>
+        <v>949</v>
       </c>
       <c r="B9" t="s">
-        <v>917</v>
+        <v>921</v>
       </c>
       <c r="C9" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="D9" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="E9" t="s">
-        <v>807</v>
+        <v>811</v>
       </c>
       <c r="F9" t="s">
-        <v>945</v>
+        <v>950</v>
       </c>
       <c r="G9" t="s">
-        <v>946</v>
+        <v>951</v>
       </c>
       <c r="H9">
         <v>1907</v>
@@ -9651,42 +9656,42 @@
         <v>1971</v>
       </c>
       <c r="M9" t="s">
-        <v>947</v>
+        <v>952</v>
       </c>
       <c r="N9" t="s">
-        <v>948</v>
+        <v>953</v>
       </c>
       <c r="O9" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="P9" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="Q9" s="4">
         <v>46297</v>
       </c>
       <c r="R9" t="s">
-        <v>927</v>
+        <v>931</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>949</v>
+        <v>954</v>
       </c>
       <c r="B10" t="s">
-        <v>917</v>
+        <v>921</v>
       </c>
       <c r="C10" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="D10" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="E10" t="s">
-        <v>950</v>
+        <v>955</v>
       </c>
       <c r="F10" t="s">
-        <v>951</v>
+        <v>956</v>
       </c>
       <c r="H10">
         <v>1898</v>
@@ -9695,45 +9700,45 @@
         <v>1975</v>
       </c>
       <c r="M10" t="s">
-        <v>952</v>
+        <v>957</v>
       </c>
       <c r="N10" t="s">
-        <v>953</v>
+        <v>958</v>
       </c>
       <c r="O10" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="P10" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="Q10" s="4">
         <v>46297</v>
       </c>
       <c r="R10" t="s">
-        <v>927</v>
+        <v>931</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>954</v>
+        <v>959</v>
       </c>
       <c r="B11" t="s">
-        <v>917</v>
+        <v>921</v>
       </c>
       <c r="C11" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="D11" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="E11" t="s">
-        <v>955</v>
+        <v>960</v>
       </c>
       <c r="F11" t="s">
-        <v>956</v>
+        <v>961</v>
       </c>
       <c r="G11" t="s">
-        <v>957</v>
+        <v>962</v>
       </c>
       <c r="H11">
         <v>1898</v>
@@ -9742,45 +9747,45 @@
         <v>1976</v>
       </c>
       <c r="M11" t="s">
-        <v>958</v>
+        <v>963</v>
       </c>
       <c r="N11" t="s">
-        <v>959</v>
+        <v>964</v>
       </c>
       <c r="O11" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="P11" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="Q11" s="4">
         <v>46297</v>
       </c>
       <c r="R11" t="s">
-        <v>927</v>
+        <v>931</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>960</v>
+        <v>965</v>
       </c>
       <c r="B12" t="s">
-        <v>917</v>
+        <v>921</v>
       </c>
       <c r="C12" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="D12" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="E12" t="s">
-        <v>961</v>
+        <v>966</v>
       </c>
       <c r="F12" t="s">
-        <v>962</v>
+        <v>967</v>
       </c>
       <c r="G12" t="s">
-        <v>963</v>
+        <v>968</v>
       </c>
       <c r="H12">
         <v>1904</v>
@@ -9789,45 +9794,45 @@
         <v>1989</v>
       </c>
       <c r="M12" t="s">
-        <v>964</v>
+        <v>969</v>
       </c>
       <c r="N12" t="s">
-        <v>965</v>
+        <v>970</v>
       </c>
       <c r="O12" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="P12" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="Q12" s="4">
         <v>46297</v>
       </c>
       <c r="R12" t="s">
-        <v>927</v>
+        <v>931</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>966</v>
+        <v>971</v>
       </c>
       <c r="B13" t="s">
-        <v>917</v>
+        <v>921</v>
       </c>
       <c r="C13" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="D13" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="E13" t="s">
-        <v>967</v>
+        <v>972</v>
       </c>
       <c r="F13" t="s">
-        <v>968</v>
+        <v>973</v>
       </c>
       <c r="G13" t="s">
-        <v>969</v>
+        <v>974</v>
       </c>
       <c r="H13">
         <v>1914</v>
@@ -9836,42 +9841,42 @@
         <v>1991</v>
       </c>
       <c r="M13" t="s">
-        <v>970</v>
+        <v>975</v>
       </c>
       <c r="N13" t="s">
-        <v>971</v>
+        <v>976</v>
       </c>
       <c r="O13" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="P13" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="Q13" s="4">
         <v>46297</v>
       </c>
       <c r="R13" t="s">
-        <v>927</v>
+        <v>931</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B14" t="s">
-        <v>917</v>
+        <v>921</v>
       </c>
       <c r="C14" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="D14" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="E14" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F14" t="s">
-        <v>972</v>
+        <v>977</v>
       </c>
       <c r="H14">
         <v>1920</v>
@@ -9880,22 +9885,22 @@
         <v>2004</v>
       </c>
       <c r="M14" t="s">
-        <v>973</v>
+        <v>978</v>
       </c>
       <c r="N14" t="s">
-        <v>974</v>
+        <v>979</v>
       </c>
       <c r="O14" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="P14" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="Q14" s="4">
         <v>46297</v>
       </c>
       <c r="R14" t="s">
-        <v>927</v>
+        <v>931</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
@@ -9903,19 +9908,19 @@
         <v>83</v>
       </c>
       <c r="B15" t="s">
-        <v>917</v>
+        <v>921</v>
       </c>
       <c r="C15" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="D15" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="E15" t="s">
         <v>84</v>
       </c>
       <c r="F15" t="s">
-        <v>975</v>
+        <v>980</v>
       </c>
       <c r="H15">
         <v>1920</v>
@@ -9924,39 +9929,39 @@
         <v>1997</v>
       </c>
       <c r="O15" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="P15" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="Q15" s="4">
         <v>46297</v>
       </c>
       <c r="R15" t="s">
-        <v>927</v>
+        <v>931</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>976</v>
+        <v>981</v>
       </c>
       <c r="B16" t="s">
-        <v>917</v>
+        <v>921</v>
       </c>
       <c r="C16" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="D16" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="E16" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="F16" t="s">
-        <v>977</v>
+        <v>982</v>
       </c>
       <c r="G16" t="s">
-        <v>978</v>
+        <v>983</v>
       </c>
       <c r="H16">
         <v>1898</v>
@@ -9965,42 +9970,42 @@
         <v>1969</v>
       </c>
       <c r="M16" t="s">
-        <v>979</v>
+        <v>984</v>
       </c>
       <c r="N16" t="s">
-        <v>980</v>
+        <v>985</v>
       </c>
       <c r="O16" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="P16" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="Q16" s="4">
         <v>46297</v>
       </c>
       <c r="R16" t="s">
-        <v>927</v>
+        <v>931</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>981</v>
+        <v>986</v>
       </c>
       <c r="B17" t="s">
-        <v>917</v>
+        <v>921</v>
       </c>
       <c r="C17" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="D17" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="E17" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="F17" t="s">
-        <v>982</v>
+        <v>987</v>
       </c>
       <c r="H17">
         <v>1924</v>
@@ -10009,22 +10014,22 @@
         <v>2010</v>
       </c>
       <c r="M17" t="s">
-        <v>983</v>
+        <v>988</v>
       </c>
       <c r="N17" t="s">
-        <v>984</v>
+        <v>989</v>
       </c>
       <c r="O17" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="P17" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="Q17" s="4">
         <v>46297</v>
       </c>
       <c r="R17" t="s">
-        <v>927</v>
+        <v>931</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
@@ -10032,19 +10037,19 @@
         <v>184</v>
       </c>
       <c r="B18" t="s">
-        <v>917</v>
+        <v>921</v>
       </c>
       <c r="C18" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="D18" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="E18" t="s">
         <v>185</v>
       </c>
       <c r="F18" t="s">
-        <v>985</v>
+        <v>990</v>
       </c>
       <c r="H18">
         <v>1933</v>
@@ -10053,22 +10058,22 @@
         <v>1996</v>
       </c>
       <c r="M18" t="s">
-        <v>986</v>
+        <v>991</v>
       </c>
       <c r="N18" t="s">
-        <v>987</v>
+        <v>992</v>
       </c>
       <c r="O18" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="P18" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="Q18" s="4">
         <v>46297</v>
       </c>
       <c r="R18" t="s">
-        <v>927</v>
+        <v>931</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
@@ -10076,40 +10081,40 @@
         <v>107</v>
       </c>
       <c r="B19" t="s">
-        <v>917</v>
+        <v>921</v>
       </c>
       <c r="C19" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="D19" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="E19" t="s">
         <v>108</v>
       </c>
       <c r="F19" t="s">
-        <v>988</v>
+        <v>993</v>
       </c>
       <c r="H19">
         <v>1941</v>
       </c>
       <c r="M19" t="s">
-        <v>989</v>
+        <v>994</v>
       </c>
       <c r="N19" t="s">
-        <v>990</v>
+        <v>995</v>
       </c>
       <c r="O19" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="P19" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="Q19" s="4">
         <v>46299</v>
       </c>
       <c r="R19" t="s">
-        <v>927</v>
+        <v>931</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
@@ -10117,31 +10122,31 @@
         <v>188</v>
       </c>
       <c r="B20" t="s">
-        <v>917</v>
+        <v>921</v>
       </c>
       <c r="C20" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="D20" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="E20" t="s">
         <v>189</v>
       </c>
       <c r="F20" t="s">
-        <v>991</v>
+        <v>996</v>
       </c>
       <c r="O20" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="P20" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="Q20" s="4">
         <v>46299</v>
       </c>
       <c r="R20" t="s">
-        <v>927</v>
+        <v>931</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
@@ -10149,22 +10154,22 @@
         <v>93</v>
       </c>
       <c r="B21" t="s">
-        <v>917</v>
+        <v>921</v>
       </c>
       <c r="C21" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="D21" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="E21" t="s">
         <v>94</v>
       </c>
       <c r="F21" t="s">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="G21" t="s">
-        <v>993</v>
+        <v>998</v>
       </c>
       <c r="H21">
         <v>1898</v>
@@ -10173,19 +10178,19 @@
         <v>1973</v>
       </c>
       <c r="M21" t="s">
-        <v>994</v>
+        <v>999</v>
       </c>
       <c r="O21" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="P21" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="Q21" s="4">
         <v>46299</v>
       </c>
       <c r="R21" t="s">
-        <v>927</v>
+        <v>931</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
@@ -10193,22 +10198,22 @@
         <v>100</v>
       </c>
       <c r="B22" t="s">
-        <v>917</v>
+        <v>921</v>
       </c>
       <c r="C22" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="D22" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="E22" t="s">
         <v>101</v>
       </c>
       <c r="F22" t="s">
-        <v>995</v>
+        <v>1000</v>
       </c>
       <c r="G22" t="s">
-        <v>996</v>
+        <v>1001</v>
       </c>
       <c r="H22">
         <v>1927</v>
@@ -10217,16 +10222,16 @@
         <v>2009</v>
       </c>
       <c r="O22" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="P22" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="Q22" s="4">
         <v>46299</v>
       </c>
       <c r="R22" t="s">
-        <v>927</v>
+        <v>931</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
@@ -10234,19 +10239,19 @@
         <v>115</v>
       </c>
       <c r="B23" t="s">
-        <v>917</v>
+        <v>921</v>
       </c>
       <c r="C23" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="D23" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="E23" t="s">
         <v>116</v>
       </c>
       <c r="F23" t="s">
-        <v>997</v>
+        <v>1002</v>
       </c>
       <c r="H23">
         <v>1936</v>
@@ -10255,22 +10260,22 @@
         <v>1994</v>
       </c>
       <c r="M23" t="s">
-        <v>998</v>
+        <v>1003</v>
       </c>
       <c r="N23" t="s">
-        <v>999</v>
+        <v>1004</v>
       </c>
       <c r="O23" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="P23" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="Q23" s="4">
         <v>46299</v>
       </c>
       <c r="R23" t="s">
-        <v>1000</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
@@ -10278,34 +10283,34 @@
         <v>149</v>
       </c>
       <c r="B24" t="s">
-        <v>917</v>
+        <v>921</v>
       </c>
       <c r="C24" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="D24" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="E24" t="s">
         <v>150</v>
       </c>
       <c r="F24" t="s">
-        <v>1001</v>
+        <v>1006</v>
       </c>
       <c r="G24" t="s">
-        <v>1002</v>
+        <v>1007</v>
       </c>
       <c r="O24" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="P24" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="Q24" s="4">
         <v>46299</v>
       </c>
       <c r="R24" t="s">
-        <v>927</v>
+        <v>931</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.3">
@@ -10313,31 +10318,31 @@
         <v>153</v>
       </c>
       <c r="B25" t="s">
-        <v>917</v>
+        <v>921</v>
       </c>
       <c r="C25" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="D25" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="E25" t="s">
         <v>154</v>
       </c>
       <c r="F25" t="s">
-        <v>1003</v>
+        <v>1008</v>
       </c>
       <c r="O25" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="P25" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="Q25" s="4">
         <v>46299</v>
       </c>
       <c r="R25" t="s">
-        <v>927</v>
+        <v>931</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.3">
@@ -10345,40 +10350,40 @@
         <v>164</v>
       </c>
       <c r="B26" t="s">
-        <v>917</v>
+        <v>921</v>
       </c>
       <c r="C26" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="D26" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="E26" t="s">
         <v>165</v>
       </c>
       <c r="F26" t="s">
-        <v>1004</v>
+        <v>1009</v>
       </c>
       <c r="H26">
         <v>1945</v>
       </c>
       <c r="M26" t="s">
-        <v>1005</v>
+        <v>1010</v>
       </c>
       <c r="N26" t="s">
-        <v>1006</v>
+        <v>1011</v>
       </c>
       <c r="O26" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="P26" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="Q26" s="4">
         <v>46299</v>
       </c>
       <c r="R26" t="s">
-        <v>927</v>
+        <v>931</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.3">
@@ -10386,31 +10391,31 @@
         <v>121</v>
       </c>
       <c r="B27" t="s">
-        <v>917</v>
+        <v>921</v>
       </c>
       <c r="C27" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="D27" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="E27" t="s">
         <v>122</v>
       </c>
       <c r="F27" t="s">
-        <v>1007</v>
+        <v>1012</v>
       </c>
       <c r="O27" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="P27" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="Q27" s="4">
         <v>46299</v>
       </c>
       <c r="R27" t="s">
-        <v>927</v>
+        <v>931</v>
       </c>
     </row>
   </sheetData>
@@ -10446,58 +10451,58 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
-        <v>899</v>
+        <v>903</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>900</v>
+        <v>904</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>901</v>
+        <v>905</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>902</v>
+        <v>906</v>
       </c>
       <c r="E1" t="s">
-        <v>903</v>
+        <v>907</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>905</v>
+        <v>909</v>
       </c>
       <c r="G1" t="s">
-        <v>1008</v>
+        <v>1013</v>
       </c>
       <c r="H1" t="s">
-        <v>1009</v>
+        <v>1014</v>
       </c>
       <c r="I1" t="s">
-        <v>1010</v>
+        <v>1015</v>
       </c>
       <c r="J1" t="s">
-        <v>908</v>
+        <v>912</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>1011</v>
+        <v>1016</v>
       </c>
       <c r="L1" s="9" t="s">
-        <v>910</v>
+        <v>914</v>
       </c>
       <c r="M1" s="9" t="s">
-        <v>911</v>
+        <v>915</v>
       </c>
       <c r="N1" s="9" t="s">
-        <v>912</v>
+        <v>916</v>
       </c>
       <c r="O1" s="9" t="s">
-        <v>913</v>
+        <v>917</v>
       </c>
       <c r="P1" s="9" t="s">
-        <v>914</v>
+        <v>918</v>
       </c>
       <c r="Q1" s="9" t="s">
-        <v>915</v>
+        <v>919</v>
       </c>
       <c r="R1" s="9" t="s">
-        <v>916</v>
+        <v>920</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
@@ -10505,78 +10510,78 @@
         <v>85</v>
       </c>
       <c r="B2" t="s">
-        <v>1012</v>
+        <v>1017</v>
       </c>
       <c r="C2" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="D2" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="E2" t="s">
         <v>86</v>
       </c>
       <c r="G2" t="s">
-        <v>1013</v>
+        <v>1018</v>
       </c>
       <c r="H2">
         <v>1962</v>
       </c>
       <c r="I2" t="s">
-        <v>1014</v>
+        <v>1019</v>
       </c>
       <c r="O2" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="P2" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="Q2" s="4">
         <v>46297</v>
       </c>
       <c r="R2" t="s">
-        <v>1015</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>1016</v>
+        <v>1021</v>
       </c>
       <c r="B3" t="s">
-        <v>1012</v>
+        <v>1017</v>
       </c>
       <c r="C3" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="D3" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="E3" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="G3" t="s">
-        <v>1017</v>
+        <v>1022</v>
       </c>
       <c r="H3">
         <v>1952</v>
       </c>
       <c r="M3" t="s">
-        <v>1018</v>
+        <v>1023</v>
       </c>
       <c r="N3" t="s">
-        <v>1019</v>
+        <v>1024</v>
       </c>
       <c r="O3" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="P3" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="Q3" s="4">
         <v>46297</v>
       </c>
       <c r="R3" t="s">
-        <v>1015</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
@@ -10584,19 +10589,19 @@
         <v>96</v>
       </c>
       <c r="B4" t="s">
-        <v>1012</v>
+        <v>1017</v>
       </c>
       <c r="C4" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="D4" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="E4" t="s">
         <v>97</v>
       </c>
       <c r="G4" t="s">
-        <v>1017</v>
+        <v>1022</v>
       </c>
       <c r="H4">
         <v>1963</v>
@@ -10605,80 +10610,80 @@
         <v>1979</v>
       </c>
       <c r="O4" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="P4" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="Q4" s="4">
         <v>46297</v>
       </c>
       <c r="R4" t="s">
-        <v>1015</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>1020</v>
+        <v>1025</v>
       </c>
       <c r="B5" t="s">
-        <v>1012</v>
+        <v>1017</v>
       </c>
       <c r="C5" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="D5" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="E5" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="F5" t="s">
-        <v>1021</v>
+        <v>1026</v>
       </c>
       <c r="G5" t="s">
-        <v>1022</v>
+        <v>1027</v>
       </c>
       <c r="H5">
         <v>1948</v>
       </c>
       <c r="M5" t="s">
-        <v>1023</v>
+        <v>1028</v>
       </c>
       <c r="O5" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="P5" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="Q5" s="4">
         <v>46297</v>
       </c>
       <c r="R5" t="s">
-        <v>1015</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>1024</v>
+        <v>1029</v>
       </c>
       <c r="B6" t="s">
-        <v>1012</v>
+        <v>1017</v>
       </c>
       <c r="C6" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="D6" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="E6" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="F6" t="s">
-        <v>1025</v>
+        <v>1030</v>
       </c>
       <c r="G6" t="s">
-        <v>1026</v>
+        <v>1031</v>
       </c>
       <c r="H6">
         <v>1958</v>
@@ -10687,22 +10692,22 @@
         <v>1988</v>
       </c>
       <c r="M6" t="s">
-        <v>1027</v>
+        <v>1032</v>
       </c>
       <c r="N6" t="s">
-        <v>1028</v>
+        <v>1033</v>
       </c>
       <c r="O6" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="P6" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="Q6" s="4">
         <v>46297</v>
       </c>
       <c r="R6" t="s">
-        <v>1015</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
@@ -10710,19 +10715,19 @@
         <v>191</v>
       </c>
       <c r="B7" t="s">
-        <v>1012</v>
+        <v>1017</v>
       </c>
       <c r="C7" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="D7" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="E7" t="s">
         <v>192</v>
       </c>
       <c r="G7" t="s">
-        <v>1022</v>
+        <v>1027</v>
       </c>
       <c r="H7">
         <v>1964</v>
@@ -10731,95 +10736,95 @@
         <v>1991</v>
       </c>
       <c r="O7" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="P7" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="Q7" s="4">
         <v>46297</v>
       </c>
       <c r="R7" t="s">
-        <v>1015</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>1029</v>
+        <v>1034</v>
       </c>
       <c r="B8" t="s">
-        <v>1012</v>
+        <v>1017</v>
       </c>
       <c r="C8" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="D8" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="E8" t="s">
-        <v>1030</v>
+        <v>1035</v>
       </c>
       <c r="F8" t="s">
-        <v>1031</v>
+        <v>1036</v>
       </c>
       <c r="G8" t="s">
-        <v>1022</v>
+        <v>1027</v>
       </c>
       <c r="H8">
         <v>1956</v>
       </c>
       <c r="M8" t="s">
-        <v>1032</v>
+        <v>1037</v>
       </c>
       <c r="O8" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="P8" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="Q8" s="4">
         <v>46297</v>
       </c>
       <c r="R8" t="s">
-        <v>1015</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>1033</v>
+        <v>1038</v>
       </c>
       <c r="B9" t="s">
-        <v>1012</v>
+        <v>1017</v>
       </c>
       <c r="C9" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="D9" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="E9" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="G9" t="s">
-        <v>1034</v>
+        <v>1039</v>
       </c>
       <c r="H9" t="s">
         <v>91</v>
       </c>
       <c r="I9" t="s">
-        <v>1035</v>
+        <v>1040</v>
       </c>
       <c r="O9" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="P9" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="Q9" s="4">
         <v>46297</v>
       </c>
       <c r="R9" t="s">
-        <v>1015</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
@@ -10827,19 +10832,19 @@
         <v>49</v>
       </c>
       <c r="B10" t="s">
-        <v>1012</v>
+        <v>1017</v>
       </c>
       <c r="C10" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="D10" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="E10" t="s">
         <v>50</v>
       </c>
       <c r="G10" t="s">
-        <v>1036</v>
+        <v>1041</v>
       </c>
       <c r="H10">
         <v>1966</v>
@@ -10848,16 +10853,16 @@
         <v>1991</v>
       </c>
       <c r="O10" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="P10" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="Q10" s="4">
         <v>46297</v>
       </c>
       <c r="R10" t="s">
-        <v>1015</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
@@ -10865,19 +10870,19 @@
         <v>53</v>
       </c>
       <c r="B11" t="s">
-        <v>1012</v>
+        <v>1017</v>
       </c>
       <c r="C11" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="D11" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="E11" t="s">
         <v>54</v>
       </c>
       <c r="G11" t="s">
-        <v>1036</v>
+        <v>1041</v>
       </c>
       <c r="H11">
         <v>1968</v>
@@ -10886,39 +10891,39 @@
         <v>1972</v>
       </c>
       <c r="O11" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="P11" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="Q11" s="4">
         <v>46297</v>
       </c>
       <c r="R11" t="s">
-        <v>1015</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B12" t="s">
-        <v>1012</v>
+        <v>1017</v>
       </c>
       <c r="C12" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="D12" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="E12" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F12" t="s">
-        <v>1037</v>
+        <v>1042</v>
       </c>
       <c r="G12" t="s">
-        <v>1038</v>
+        <v>1043</v>
       </c>
       <c r="H12">
         <v>1966</v>
@@ -10927,16 +10932,16 @@
         <v>1991</v>
       </c>
       <c r="O12" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="P12" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="Q12" s="4">
         <v>46297</v>
       </c>
       <c r="R12" t="s">
-        <v>1015</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
@@ -10944,40 +10949,40 @@
         <v>38</v>
       </c>
       <c r="B13" t="s">
-        <v>1012</v>
+        <v>1017</v>
       </c>
       <c r="C13" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="D13" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="E13" t="s">
         <v>39</v>
       </c>
       <c r="G13" t="s">
-        <v>1036</v>
+        <v>1041</v>
       </c>
       <c r="H13">
         <v>1921</v>
       </c>
       <c r="M13" t="s">
-        <v>1039</v>
+        <v>1044</v>
       </c>
       <c r="N13" t="s">
-        <v>1040</v>
+        <v>1045</v>
       </c>
       <c r="O13" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="P13" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="Q13" s="4">
         <v>46297</v>
       </c>
       <c r="R13" t="s">
-        <v>1015</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
@@ -10985,22 +10990,22 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>1012</v>
+        <v>1017</v>
       </c>
       <c r="C14" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="D14" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="E14" t="s">
         <v>12</v>
       </c>
       <c r="F14" t="s">
-        <v>1041</v>
+        <v>1046</v>
       </c>
       <c r="G14" t="s">
-        <v>1042</v>
+        <v>1047</v>
       </c>
       <c r="H14">
         <v>1966</v>
@@ -11009,25 +11014,25 @@
         <v>1991</v>
       </c>
       <c r="J14" t="s">
-        <v>1043</v>
+        <v>1048</v>
       </c>
       <c r="M14" t="s">
-        <v>1044</v>
+        <v>1049</v>
       </c>
       <c r="N14" t="s">
-        <v>1045</v>
+        <v>1050</v>
       </c>
       <c r="O14" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="P14" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="Q14" s="4">
         <v>46297</v>
       </c>
       <c r="R14" t="s">
-        <v>1015</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
@@ -11035,22 +11040,22 @@
         <v>55</v>
       </c>
       <c r="B15" t="s">
-        <v>1012</v>
+        <v>1017</v>
       </c>
       <c r="C15" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="D15" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="E15" t="s">
         <v>56</v>
       </c>
       <c r="F15" t="s">
-        <v>1046</v>
+        <v>1051</v>
       </c>
       <c r="G15" t="s">
-        <v>1042</v>
+        <v>1047</v>
       </c>
       <c r="H15">
         <v>1968</v>
@@ -11059,25 +11064,25 @@
         <v>1972</v>
       </c>
       <c r="J15" t="s">
-        <v>1047</v>
+        <v>1052</v>
       </c>
       <c r="M15" t="s">
-        <v>1048</v>
+        <v>1053</v>
       </c>
       <c r="N15" t="s">
-        <v>1049</v>
+        <v>1054</v>
       </c>
       <c r="O15" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="P15" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="Q15" s="4">
         <v>46297</v>
       </c>
       <c r="R15" t="s">
-        <v>1015</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
@@ -11085,46 +11090,46 @@
         <v>33</v>
       </c>
       <c r="B16" t="s">
-        <v>1012</v>
+        <v>1017</v>
       </c>
       <c r="C16" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="D16" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="E16" t="s">
         <v>34</v>
       </c>
       <c r="F16" t="s">
-        <v>1050</v>
+        <v>1055</v>
       </c>
       <c r="G16" t="s">
-        <v>1042</v>
+        <v>1047</v>
       </c>
       <c r="H16">
         <v>1921</v>
       </c>
       <c r="J16" t="s">
-        <v>1051</v>
+        <v>1056</v>
       </c>
       <c r="M16" t="s">
-        <v>1052</v>
+        <v>1057</v>
       </c>
       <c r="N16" t="s">
-        <v>1053</v>
+        <v>1058</v>
       </c>
       <c r="O16" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="P16" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="Q16" s="4">
         <v>46297</v>
       </c>
       <c r="R16" t="s">
-        <v>1015</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
@@ -11132,22 +11137,22 @@
         <v>45</v>
       </c>
       <c r="B17" t="s">
-        <v>1012</v>
+        <v>1017</v>
       </c>
       <c r="C17" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="D17" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="E17" t="s">
         <v>46</v>
       </c>
       <c r="F17" t="s">
-        <v>1054</v>
+        <v>1059</v>
       </c>
       <c r="G17" t="s">
-        <v>1042</v>
+        <v>1047</v>
       </c>
       <c r="H17">
         <v>1968</v>
@@ -11156,16 +11161,16 @@
         <v>1977</v>
       </c>
       <c r="O17" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="P17" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="Q17" s="4">
         <v>46297</v>
       </c>
       <c r="R17" t="s">
-        <v>1015</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
@@ -11173,22 +11178,22 @@
         <v>66</v>
       </c>
       <c r="B18" t="s">
-        <v>1012</v>
+        <v>1017</v>
       </c>
       <c r="C18" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="D18" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="E18" t="s">
         <v>67</v>
       </c>
       <c r="F18" t="s">
-        <v>1055</v>
+        <v>1060</v>
       </c>
       <c r="G18" t="s">
-        <v>1042</v>
+        <v>1047</v>
       </c>
       <c r="H18">
         <v>1969</v>
@@ -11197,16 +11202,16 @@
         <v>1976</v>
       </c>
       <c r="O18" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="P18" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="Q18" s="4">
         <v>46297</v>
       </c>
       <c r="R18" t="s">
-        <v>1015</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
@@ -11214,37 +11219,37 @@
         <v>117</v>
       </c>
       <c r="B19" t="s">
-        <v>1012</v>
+        <v>1017</v>
       </c>
       <c r="C19" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="D19" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="E19" t="s">
         <v>118</v>
       </c>
       <c r="G19" t="s">
-        <v>1042</v>
+        <v>1047</v>
       </c>
       <c r="H19">
         <v>1968</v>
       </c>
       <c r="I19" t="s">
-        <v>1035</v>
+        <v>1040</v>
       </c>
       <c r="O19" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="P19" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="Q19" s="4">
         <v>46297</v>
       </c>
       <c r="R19" t="s">
-        <v>1015</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
@@ -11252,22 +11257,22 @@
         <v>104</v>
       </c>
       <c r="B20" t="s">
-        <v>1012</v>
+        <v>1017</v>
       </c>
       <c r="C20" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="D20" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="E20" t="s">
         <v>105</v>
       </c>
       <c r="F20" t="s">
-        <v>1056</v>
+        <v>1061</v>
       </c>
       <c r="G20" t="s">
-        <v>1042</v>
+        <v>1047</v>
       </c>
       <c r="H20">
         <v>1972</v>
@@ -11276,42 +11281,42 @@
         <v>1978</v>
       </c>
       <c r="M20" t="s">
-        <v>1048</v>
+        <v>1053</v>
       </c>
       <c r="N20" t="s">
-        <v>1049</v>
+        <v>1054</v>
       </c>
       <c r="O20" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="P20" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="Q20" s="4">
         <v>46297</v>
       </c>
       <c r="R20" t="s">
-        <v>1015</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B21" t="s">
-        <v>1012</v>
+        <v>1017</v>
       </c>
       <c r="C21" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="D21" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="E21" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="G21" t="s">
-        <v>1026</v>
+        <v>1031</v>
       </c>
       <c r="H21">
         <v>1967</v>
@@ -11320,16 +11325,16 @@
         <v>1969</v>
       </c>
       <c r="O21" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="P21" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="Q21" s="4">
         <v>46297</v>
       </c>
       <c r="R21" t="s">
-        <v>1015</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
@@ -11337,22 +11342,22 @@
         <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>1012</v>
+        <v>1017</v>
       </c>
       <c r="C22" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="D22" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="E22" t="s">
         <v>28</v>
       </c>
       <c r="F22" t="s">
-        <v>1057</v>
+        <v>1062</v>
       </c>
       <c r="G22" t="s">
-        <v>1042</v>
+        <v>1047</v>
       </c>
       <c r="H22">
         <v>1977</v>
@@ -11361,19 +11366,19 @@
         <v>1984</v>
       </c>
       <c r="M22" t="s">
-        <v>1058</v>
+        <v>1063</v>
       </c>
       <c r="O22" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="P22" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="Q22" s="4">
         <v>46297</v>
       </c>
       <c r="R22" t="s">
-        <v>1015</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
@@ -11381,19 +11386,19 @@
         <v>170</v>
       </c>
       <c r="B23" t="s">
-        <v>1012</v>
+        <v>1017</v>
       </c>
       <c r="C23" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="D23" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="E23" t="s">
         <v>171</v>
       </c>
       <c r="G23" t="s">
-        <v>1034</v>
+        <v>1039</v>
       </c>
       <c r="H23">
         <v>1970</v>
@@ -11402,16 +11407,16 @@
         <v>1973</v>
       </c>
       <c r="O23" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="P23" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="Q23" s="4">
         <v>46297</v>
       </c>
       <c r="R23" t="s">
-        <v>1015</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
@@ -11419,19 +11424,19 @@
         <v>176</v>
       </c>
       <c r="B24" t="s">
-        <v>1012</v>
+        <v>1017</v>
       </c>
       <c r="C24" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="D24" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="E24" t="s">
         <v>177</v>
       </c>
       <c r="G24" t="s">
-        <v>1034</v>
+        <v>1039</v>
       </c>
       <c r="H24">
         <v>1969</v>
@@ -11440,16 +11445,16 @@
         <v>1972</v>
       </c>
       <c r="O24" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="P24" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="Q24" s="4">
         <v>46297</v>
       </c>
       <c r="R24" t="s">
-        <v>1015</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.3">
@@ -11457,22 +11462,22 @@
         <v>137</v>
       </c>
       <c r="B25" t="s">
-        <v>1012</v>
+        <v>1017</v>
       </c>
       <c r="C25" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="D25" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="E25" t="s">
         <v>138</v>
       </c>
       <c r="F25" t="s">
-        <v>1059</v>
+        <v>1064</v>
       </c>
       <c r="G25" t="s">
-        <v>1042</v>
+        <v>1047</v>
       </c>
       <c r="H25">
         <v>1973</v>
@@ -11481,16 +11486,16 @@
         <v>1977</v>
       </c>
       <c r="O25" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="P25" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="Q25" s="4">
         <v>46297</v>
       </c>
       <c r="R25" t="s">
-        <v>1015</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.3">
@@ -11498,19 +11503,19 @@
         <v>166</v>
       </c>
       <c r="B26" t="s">
-        <v>1012</v>
+        <v>1017</v>
       </c>
       <c r="C26" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="D26" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="E26" t="s">
         <v>167</v>
       </c>
       <c r="G26" t="s">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="H26">
         <v>1968</v>
@@ -11519,22 +11524,22 @@
         <v>1976</v>
       </c>
       <c r="M26" t="s">
-        <v>1061</v>
+        <v>1066</v>
       </c>
       <c r="N26" t="s">
-        <v>1062</v>
+        <v>1067</v>
       </c>
       <c r="O26" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="P26" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="Q26" s="4">
         <v>46297</v>
       </c>
       <c r="R26" t="s">
-        <v>1015</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.3">
@@ -11542,22 +11547,22 @@
         <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>1012</v>
+        <v>1017</v>
       </c>
       <c r="C27" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="D27" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="E27" t="s">
         <v>24</v>
       </c>
       <c r="F27" t="s">
-        <v>1063</v>
+        <v>1068</v>
       </c>
       <c r="G27" t="s">
-        <v>1042</v>
+        <v>1047</v>
       </c>
       <c r="H27">
         <v>1970</v>
@@ -11566,16 +11571,16 @@
         <v>1977</v>
       </c>
       <c r="O27" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="P27" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="Q27" s="4">
         <v>46297</v>
       </c>
       <c r="R27" t="s">
-        <v>1015</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.3">
@@ -11583,22 +11588,22 @@
         <v>140</v>
       </c>
       <c r="B28" t="s">
-        <v>1012</v>
+        <v>1017</v>
       </c>
       <c r="C28" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="D28" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="E28" t="s">
         <v>141</v>
       </c>
       <c r="F28" t="s">
-        <v>1064</v>
+        <v>1069</v>
       </c>
       <c r="G28" t="s">
-        <v>1042</v>
+        <v>1047</v>
       </c>
       <c r="H28">
         <v>1969</v>
@@ -11607,16 +11612,16 @@
         <v>1977</v>
       </c>
       <c r="O28" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="P28" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="Q28" s="4">
         <v>46297</v>
       </c>
       <c r="R28" t="s">
-        <v>1015</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.3">
@@ -11624,22 +11629,22 @@
         <v>128</v>
       </c>
       <c r="B29" t="s">
-        <v>1012</v>
+        <v>1017</v>
       </c>
       <c r="C29" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="D29" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="E29" t="s">
         <v>129</v>
       </c>
       <c r="F29" t="s">
-        <v>1065</v>
+        <v>1070</v>
       </c>
       <c r="G29" t="s">
-        <v>1042</v>
+        <v>1047</v>
       </c>
       <c r="H29">
         <v>1969</v>
@@ -11648,16 +11653,16 @@
         <v>1977</v>
       </c>
       <c r="O29" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="P29" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="Q29" s="4">
         <v>46297</v>
       </c>
       <c r="R29" t="s">
-        <v>1015</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.3">
@@ -11665,31 +11670,31 @@
         <v>111</v>
       </c>
       <c r="B30" t="s">
-        <v>1012</v>
+        <v>1017</v>
       </c>
       <c r="C30" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="D30" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="E30" t="s">
         <v>112</v>
       </c>
       <c r="G30" t="s">
-        <v>1036</v>
+        <v>1041</v>
       </c>
       <c r="O30" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="P30" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="Q30" s="4">
         <v>46299</v>
       </c>
       <c r="R30" t="s">
-        <v>1015</v>
+        <v>1020</v>
       </c>
     </row>
   </sheetData>
@@ -12073,7 +12078,7 @@
         <v>13</v>
       </c>
       <c r="G14" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H14" t="s">
         <v>68</v>
@@ -13001,15 +13006,15 @@
         <v>62</v>
       </c>
       <c r="H52" t="s">
-        <v>1066</v>
+        <v>196</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C53" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D53" t="s">
         <v>55</v>
@@ -13029,10 +13034,10 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C54" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D54" t="s">
         <v>11</v>
@@ -13052,7 +13057,7 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B55" t="s">
         <v>140</v>
@@ -13078,10 +13083,10 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C56" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D56" t="s">
         <v>11</v>
@@ -13101,7 +13106,7 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B57" t="s">
         <v>23</v>
@@ -13122,18 +13127,18 @@
         <v>62</v>
       </c>
       <c r="H57" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C58" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E58" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F58" t="s">
         <v>71</v>
@@ -13147,10 +13152,10 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C59" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D59" t="s">
         <v>11</v>
@@ -13165,15 +13170,15 @@
         <v>62</v>
       </c>
       <c r="H59" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C60" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D60" t="s">
         <v>11</v>
@@ -13188,12 +13193,12 @@
         <v>62</v>
       </c>
       <c r="H60" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B61" t="s">
         <v>11</v>
@@ -13202,7 +13207,7 @@
         <v>12</v>
       </c>
       <c r="E61" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F61" t="s">
         <v>142</v>
@@ -13211,18 +13216,18 @@
         <v>62</v>
       </c>
       <c r="H61" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B62" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C62" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D62" t="s">
         <v>45</v>
@@ -13242,13 +13247,13 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B63" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C63" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D63" t="s">
         <v>45</v>
@@ -13268,16 +13273,16 @@
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
+        <v>223</v>
+      </c>
+      <c r="C64" t="s">
+        <v>224</v>
+      </c>
+      <c r="D64" t="s">
+        <v>221</v>
+      </c>
+      <c r="E64" t="s">
         <v>222</v>
-      </c>
-      <c r="C64" t="s">
-        <v>223</v>
-      </c>
-      <c r="D64" t="s">
-        <v>220</v>
-      </c>
-      <c r="E64" t="s">
-        <v>221</v>
       </c>
       <c r="F64" t="s">
         <v>19</v>
@@ -13288,16 +13293,16 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C65" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D65" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E65" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F65" t="s">
         <v>19</v>
@@ -13308,16 +13313,16 @@
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C66" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D66" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E66" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F66" t="s">
         <v>19</v>
@@ -13328,10 +13333,10 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C67" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D67" t="s">
         <v>45</v>
@@ -13346,12 +13351,12 @@
         <v>20</v>
       </c>
       <c r="H67" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B68" t="s">
         <v>45</v>
@@ -13360,7 +13365,7 @@
         <v>46</v>
       </c>
       <c r="E68" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F68" t="s">
         <v>142</v>
@@ -13374,13 +13379,13 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B69" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C69" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D69" t="s">
         <v>11</v>
@@ -13389,7 +13394,7 @@
         <v>12</v>
       </c>
       <c r="F69" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G69" t="s">
         <v>14</v>
@@ -13400,7 +13405,7 @@
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>1067</v>
+        <v>238</v>
       </c>
       <c r="B70" t="s">
         <v>107</v>
@@ -13421,18 +13426,18 @@
         <v>14</v>
       </c>
       <c r="H70" t="s">
-        <v>1068</v>
+        <v>239</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>1069</v>
+        <v>240</v>
       </c>
       <c r="B71" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C71" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D71" t="s">
         <v>11</v>
@@ -13451,7 +13456,11 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valore non previsto" error="Scegli un valore dal menu (associativa, familiare, gerarchica, temporale)." promptTitle="Categoria_ISAAR" prompt="Scegli dal menu a tendina." sqref="G2:G5000" xr:uid="{00000000-0002-0000-0400-000000000000}">
+      <formula1>"associativa,familiare,gerarchica,temporale"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/data/dati.xlsx
+++ b/data/dati.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan_\Desktop\AMI\GitHub\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan_\Desktop\AMI\GitHub\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DC73B3D-7387-4037-8C05-23CC62F14CF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC8135C5-AAF0-4479-9100-CED900110887}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Catalogo" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2723" uniqueCount="1071">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2724" uniqueCount="1072">
   <si>
     <t>ID_relazione</t>
   </si>
@@ -3313,6 +3313,9 @@
   </si>
   <si>
     <t>PC(m-l-m)I</t>
+  </si>
+  <si>
+    <t>Circolo Lenin di Budrio; Circolo Lenin di Faenza; Circoli Lenin di Budrio, Bologna e Castenaso</t>
   </si>
 </sst>
 </file>
@@ -11397,6 +11400,9 @@
       <c r="E23" t="s">
         <v>171</v>
       </c>
+      <c r="F23" t="s">
+        <v>1071</v>
+      </c>
       <c r="G23" t="s">
         <v>1039</v>
       </c>

--- a/data/dati.xlsx
+++ b/data/dati.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan_\Desktop\AMI\GitHub\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC8135C5-AAF0-4479-9100-CED900110887}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71EFCEA6-CEB7-4FA5-B71C-62A0BACB7EB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2724" uniqueCount="1072">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2725" uniqueCount="1073">
   <si>
     <t>ID_relazione</t>
   </si>
@@ -3316,6 +3316,9 @@
   </si>
   <si>
     <t>Circolo Lenin di Budrio; Circolo Lenin di Faenza; Circoli Lenin di Budrio, Bologna e Castenaso</t>
+  </si>
+  <si>
+    <t>Per la vittoria del marxismo-leninismo; Organo del Movimento Marxista-Leninista Italiano; Organo centrale del Partito Comunista d’Italia (m-l)</t>
   </si>
 </sst>
 </file>
@@ -3404,6 +3407,21 @@
   </cellStyles>
   <dxfs count="7">
     <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
       <alignment horizontal="general" vertical="top" wrapText="1"/>
     </dxf>
     <dxf>
@@ -3430,21 +3448,6 @@
         <sz val="11"/>
         <color theme="0"/>
         <name val="Calibri"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
       </font>
     </dxf>
   </dxfs>
@@ -3492,13 +3495,13 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabella6" displayName="Tabella6" ref="A1:D23" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabella6" displayName="Tabella6" ref="A1:D23" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
   <autoFilter ref="A1:D23" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Codice_ISAD" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Elemento" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Valore" dataDxfId="1"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Note" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Codice_ISAD" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Elemento" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Valore" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Note" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3559,7 +3562,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Tabella5" displayName="Tabella5" ref="A1:H84" totalsRowShown="0" headerRowDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Tabella5" displayName="Tabella5" ref="A1:H84" totalsRowShown="0" headerRowDxfId="0">
   <autoFilter ref="A1:H84" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="ID_relazione"/>
@@ -10729,6 +10732,9 @@
       <c r="E7" t="s">
         <v>192</v>
       </c>
+      <c r="F7" t="s">
+        <v>1072</v>
+      </c>
       <c r="G7" t="s">
         <v>1027</v>
       </c>

--- a/data/dati.xlsx
+++ b/data/dati.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan_\Desktop\AMI\GitHub\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71EFCEA6-CEB7-4FA5-B71C-62A0BACB7EB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AD50801-7EC8-4628-8EED-0350CC3ADCF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Catalogo" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2725" uniqueCount="1073">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2724" uniqueCount="1073">
   <si>
     <t>ID_relazione</t>
   </si>
@@ -846,9 +846,6 @@
   </si>
   <si>
     <t>https://archive.org/details/1967-citazioni-dalle-opere-del-presidente-mao-tse-tung-lingue-estere/mode/2up</t>
-  </si>
-  <si>
-    <t>Traduzione ufficiale in lingua italiana del famoso Libretto rosso (毛主席语录, Máo Zhǔxí Yǔlù), contenente le iconiche citazioni del Presidente cinese Mao Zedong, stampata a Pechino dalla Casa editrice in lingue estere. L'edizione qui presente è la ristampa in formato tascabile del 1969 (11×7 cm).</t>
   </si>
   <si>
     <t>AMI-0002</t>
@@ -3319,6 +3316,9 @@
   </si>
   <si>
     <t>Per la vittoria del marxismo-leninismo; Organo del Movimento Marxista-Leninista Italiano; Organo centrale del Partito Comunista d’Italia (m-l)</t>
+  </si>
+  <si>
+    <t>Seconda edizione in italiano (1968) del famosissimo "Libretto rosso" (Quotations from Chairman Mao Tse-tung o ​毛主席语录), antologia contenente le iconiche citazioni del presidente cinese Mao Zedong, stampata a Pechino dalla Casa editrice in lingue estere. Libro tradotto da un team di italiani residenti a Pechino, tra cui Manlio Dinucci e Primerose Gigliesi, e pubblicato dalla Casa editrice in lingue estere, Pechino, pp. 328, 1968. Copertina in vinile rosso, 14 cm.</t>
   </si>
 </sst>
 </file>
@@ -3977,10 +3977,10 @@
         <v>268</v>
       </c>
       <c r="I2" s="1">
-        <v>1969</v>
-      </c>
-      <c r="J2" t="s">
-        <v>130</v>
+        <v>1968</v>
+      </c>
+      <c r="J2">
+        <v>1968</v>
       </c>
       <c r="K2" t="s">
         <v>269</v>
@@ -3998,12 +3998,12 @@
         <v>273</v>
       </c>
       <c r="V2" t="s">
-        <v>274</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B3" t="s">
         <v>264</v>
@@ -4012,7 +4012,7 @@
         <v>265</v>
       </c>
       <c r="D3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E3" t="s">
         <v>267</v>
@@ -4033,27 +4033,27 @@
         <v>194</v>
       </c>
       <c r="K3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="L3" t="s">
         <v>270</v>
       </c>
       <c r="M3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="P3" t="s">
         <v>272</v>
       </c>
       <c r="Q3" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="V3" t="s">
         <v>279</v>
-      </c>
-      <c r="V3" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B4" t="s">
         <v>264</v>
@@ -4062,7 +4062,7 @@
         <v>265</v>
       </c>
       <c r="D4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E4" t="s">
         <v>267</v>
@@ -4083,27 +4083,27 @@
         <v>126</v>
       </c>
       <c r="K4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="L4" t="s">
         <v>270</v>
       </c>
       <c r="M4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="P4" t="s">
         <v>272</v>
       </c>
       <c r="Q4" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="V4" t="s">
         <v>283</v>
-      </c>
-      <c r="V4" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B5" t="s">
         <v>264</v>
@@ -4112,7 +4112,7 @@
         <v>265</v>
       </c>
       <c r="D5" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E5" t="s">
         <v>267</v>
@@ -4133,30 +4133,30 @@
         <v>126</v>
       </c>
       <c r="K5" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="L5" t="s">
         <v>270</v>
       </c>
       <c r="M5" t="s">
+        <v>286</v>
+      </c>
+      <c r="N5" t="s">
         <v>287</v>
       </c>
-      <c r="N5" t="s">
+      <c r="P5" t="s">
         <v>288</v>
       </c>
-      <c r="P5" t="s">
+      <c r="Q5" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="Q5" s="3" t="s">
+      <c r="V5" t="s">
         <v>290</v>
-      </c>
-      <c r="V5" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B6" t="s">
         <v>264</v>
@@ -4165,7 +4165,7 @@
         <v>265</v>
       </c>
       <c r="D6" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E6" t="s">
         <v>267</v>
@@ -4186,30 +4186,30 @@
         <v>126</v>
       </c>
       <c r="K6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="L6" t="s">
         <v>270</v>
       </c>
       <c r="M6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="O6" t="s">
         <v>39</v>
       </c>
       <c r="P6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="Q6" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="V6" t="s">
         <v>294</v>
-      </c>
-      <c r="V6" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B7" t="s">
         <v>264</v>
@@ -4218,7 +4218,7 @@
         <v>265</v>
       </c>
       <c r="D7" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E7" t="s">
         <v>267</v>
@@ -4239,27 +4239,27 @@
         <v>126</v>
       </c>
       <c r="K7" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="L7" t="s">
         <v>270</v>
       </c>
       <c r="M7" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="P7" t="s">
         <v>272</v>
       </c>
       <c r="Q7" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="V7" t="s">
         <v>298</v>
-      </c>
-      <c r="V7" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B8" t="s">
         <v>264</v>
@@ -4268,7 +4268,7 @@
         <v>265</v>
       </c>
       <c r="D8" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E8" t="s">
         <v>267</v>
@@ -4289,27 +4289,27 @@
         <v>126</v>
       </c>
       <c r="K8" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="L8" t="s">
         <v>270</v>
       </c>
       <c r="M8" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="P8" t="s">
         <v>272</v>
       </c>
       <c r="Q8" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="V8" t="s">
         <v>302</v>
-      </c>
-      <c r="V8" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B9" t="s">
         <v>264</v>
@@ -4318,7 +4318,7 @@
         <v>265</v>
       </c>
       <c r="D9" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E9" t="s">
         <v>267</v>
@@ -4339,27 +4339,27 @@
         <v>130</v>
       </c>
       <c r="K9" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="L9" t="s">
         <v>270</v>
       </c>
       <c r="M9" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="P9" t="s">
         <v>272</v>
       </c>
       <c r="Q9" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="V9" t="s">
         <v>306</v>
-      </c>
-      <c r="V9" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B10" t="s">
         <v>264</v>
@@ -4368,7 +4368,7 @@
         <v>265</v>
       </c>
       <c r="D10" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E10" t="s">
         <v>267</v>
@@ -4389,27 +4389,27 @@
         <v>130</v>
       </c>
       <c r="K10" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="L10" t="s">
         <v>270</v>
       </c>
       <c r="M10" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="P10" t="s">
         <v>272</v>
       </c>
       <c r="Q10" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="V10" t="s">
         <v>310</v>
-      </c>
-      <c r="V10" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B11" t="s">
         <v>264</v>
@@ -4418,7 +4418,7 @@
         <v>265</v>
       </c>
       <c r="D11" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E11" t="s">
         <v>267</v>
@@ -4439,27 +4439,27 @@
         <v>205</v>
       </c>
       <c r="K11" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="L11" t="s">
         <v>270</v>
       </c>
       <c r="M11" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="P11" t="s">
         <v>272</v>
       </c>
       <c r="Q11" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="V11" t="s">
         <v>314</v>
-      </c>
-      <c r="V11" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B12" t="s">
         <v>264</v>
@@ -4468,7 +4468,7 @@
         <v>265</v>
       </c>
       <c r="D12" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E12" t="s">
         <v>267</v>
@@ -4477,7 +4477,7 @@
         <v>34</v>
       </c>
       <c r="G12" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H12" t="s">
         <v>268</v>
@@ -4489,13 +4489,13 @@
         <v>126</v>
       </c>
       <c r="K12" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="L12" t="s">
         <v>270</v>
       </c>
       <c r="M12" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="O12" t="s">
         <v>34</v>
@@ -4504,15 +4504,15 @@
         <v>272</v>
       </c>
       <c r="Q12" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="V12" t="s">
         <v>319</v>
-      </c>
-      <c r="V12" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B13" t="s">
         <v>264</v>
@@ -4521,7 +4521,7 @@
         <v>265</v>
       </c>
       <c r="D13" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E13" t="s">
         <v>267</v>
@@ -4530,7 +4530,7 @@
         <v>34</v>
       </c>
       <c r="G13" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H13" t="s">
         <v>268</v>
@@ -4542,30 +4542,30 @@
         <v>126</v>
       </c>
       <c r="K13" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="L13" t="s">
         <v>270</v>
       </c>
       <c r="M13" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="O13" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="P13" t="s">
         <v>272</v>
       </c>
       <c r="Q13" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="V13" t="s">
         <v>325</v>
-      </c>
-      <c r="V13" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B14" t="s">
         <v>264</v>
@@ -4574,7 +4574,7 @@
         <v>265</v>
       </c>
       <c r="D14" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E14" t="s">
         <v>267</v>
@@ -4586,7 +4586,7 @@
         <v>50</v>
       </c>
       <c r="H14" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="I14" s="1">
         <v>1967</v>
@@ -4595,36 +4595,36 @@
         <v>194</v>
       </c>
       <c r="K14" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="L14" t="s">
+        <v>329</v>
+      </c>
+      <c r="M14" t="s">
         <v>330</v>
       </c>
-      <c r="M14" t="s">
+      <c r="N14" t="s">
         <v>331</v>
       </c>
-      <c r="N14" t="s">
+      <c r="O14" t="s">
         <v>332</v>
-      </c>
-      <c r="O14" t="s">
-        <v>333</v>
       </c>
       <c r="P14" t="s">
         <v>272</v>
       </c>
       <c r="Q14" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="U14" t="s">
         <v>334</v>
       </c>
-      <c r="U14" t="s">
+      <c r="V14" t="s">
         <v>335</v>
-      </c>
-      <c r="V14" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B15" t="s">
         <v>264</v>
@@ -4633,57 +4633,57 @@
         <v>265</v>
       </c>
       <c r="D15" t="s">
+        <v>337</v>
+      </c>
+      <c r="E15" t="s">
         <v>338</v>
-      </c>
-      <c r="E15" t="s">
-        <v>339</v>
       </c>
       <c r="F15" t="s">
         <v>12</v>
       </c>
       <c r="G15" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="I15" s="2">
         <v>25064</v>
       </c>
       <c r="J15" t="s">
+        <v>340</v>
+      </c>
+      <c r="K15" t="s">
         <v>341</v>
-      </c>
-      <c r="K15" t="s">
-        <v>342</v>
       </c>
       <c r="L15" t="s">
         <v>270</v>
       </c>
       <c r="M15" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="N15" t="s">
+        <v>342</v>
+      </c>
+      <c r="O15" t="s">
         <v>343</v>
-      </c>
-      <c r="O15" t="s">
-        <v>344</v>
       </c>
       <c r="P15" t="s">
         <v>272</v>
       </c>
       <c r="Q15" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="R15" t="s">
         <v>345</v>
       </c>
-      <c r="R15" t="s">
+      <c r="U15" t="s">
         <v>346</v>
       </c>
-      <c r="U15" t="s">
+      <c r="V15" t="s">
         <v>347</v>
-      </c>
-      <c r="V15" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B16" t="s">
         <v>264</v>
@@ -4692,10 +4692,10 @@
         <v>265</v>
       </c>
       <c r="D16" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E16" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F16" t="s">
         <v>12</v>
@@ -4707,19 +4707,19 @@
         <v>25081</v>
       </c>
       <c r="J16" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="K16" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="L16" t="s">
         <v>270</v>
       </c>
       <c r="M16" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="N16" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="O16" t="s">
         <v>34</v>
@@ -4728,21 +4728,21 @@
         <v>272</v>
       </c>
       <c r="Q16" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="R16" t="s">
         <v>353</v>
       </c>
-      <c r="R16" t="s">
+      <c r="U16" t="s">
+        <v>346</v>
+      </c>
+      <c r="V16" t="s">
         <v>354</v>
-      </c>
-      <c r="U16" t="s">
-        <v>347</v>
-      </c>
-      <c r="V16" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B17" t="s">
         <v>264</v>
@@ -4751,34 +4751,34 @@
         <v>265</v>
       </c>
       <c r="D17" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E17" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F17" t="s">
         <v>12</v>
       </c>
       <c r="G17" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="I17" s="2">
         <v>25479</v>
       </c>
       <c r="J17" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="K17" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="L17" t="s">
         <v>270</v>
       </c>
       <c r="M17" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="N17" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="O17" t="s">
         <v>34</v>
@@ -4787,21 +4787,21 @@
         <v>272</v>
       </c>
       <c r="Q17" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="R17" t="s">
         <v>360</v>
       </c>
-      <c r="R17" t="s">
+      <c r="U17" t="s">
+        <v>346</v>
+      </c>
+      <c r="V17" t="s">
         <v>361</v>
-      </c>
-      <c r="U17" t="s">
-        <v>347</v>
-      </c>
-      <c r="V17" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B18" t="s">
         <v>264</v>
@@ -4810,7 +4810,7 @@
         <v>265</v>
       </c>
       <c r="D18" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E18" t="s">
         <v>267</v>
@@ -4825,30 +4825,30 @@
         <v>25485</v>
       </c>
       <c r="J18" t="s">
+        <v>364</v>
+      </c>
+      <c r="K18" t="s">
         <v>365</v>
       </c>
-      <c r="K18" t="s">
+      <c r="L18" t="s">
         <v>366</v>
       </c>
-      <c r="L18" t="s">
-        <v>367</v>
-      </c>
       <c r="M18" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="P18" t="s">
         <v>272</v>
       </c>
       <c r="Q18" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="V18" t="s">
         <v>368</v>
-      </c>
-      <c r="V18" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B19" t="s">
         <v>264</v>
@@ -4857,10 +4857,10 @@
         <v>265</v>
       </c>
       <c r="D19" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E19" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F19" t="s">
         <v>97</v>
@@ -4872,19 +4872,19 @@
         <v>23514</v>
       </c>
       <c r="J19" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="K19" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="L19" t="s">
         <v>270</v>
       </c>
       <c r="M19" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="N19" s="11" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="O19" t="s">
         <v>102</v>
@@ -4893,21 +4893,21 @@
         <v>272</v>
       </c>
       <c r="Q19" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="R19" t="s">
         <v>374</v>
       </c>
-      <c r="R19" t="s">
+      <c r="U19" t="s">
+        <v>346</v>
+      </c>
+      <c r="V19" t="s">
         <v>375</v>
-      </c>
-      <c r="U19" t="s">
-        <v>347</v>
-      </c>
-      <c r="V19" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B20" t="s">
         <v>264</v>
@@ -4916,7 +4916,7 @@
         <v>265</v>
       </c>
       <c r="D20" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E20" t="s">
         <v>267</v>
@@ -4925,7 +4925,7 @@
         <v>32</v>
       </c>
       <c r="H20" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="I20" s="1">
         <v>1969</v>
@@ -4934,24 +4934,24 @@
         <v>130</v>
       </c>
       <c r="K20" t="s">
+        <v>379</v>
+      </c>
+      <c r="M20" t="s">
         <v>380</v>
-      </c>
-      <c r="M20" t="s">
-        <v>381</v>
       </c>
       <c r="P20" t="s">
         <v>272</v>
       </c>
       <c r="Q20" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="V20" t="s">
         <v>382</v>
-      </c>
-      <c r="V20" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B21" t="s">
         <v>264</v>
@@ -4960,45 +4960,45 @@
         <v>265</v>
       </c>
       <c r="D21" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E21" t="s">
         <v>267</v>
       </c>
       <c r="G21" t="s">
+        <v>385</v>
+      </c>
+      <c r="H21" t="s">
         <v>386</v>
-      </c>
-      <c r="H21" t="s">
-        <v>387</v>
       </c>
       <c r="I21" s="1">
         <v>1993</v>
       </c>
       <c r="J21" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="K21" t="s">
         <v>269</v>
       </c>
       <c r="L21" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="M21" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="P21" t="s">
         <v>272</v>
       </c>
       <c r="Q21" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="V21" t="s">
         <v>390</v>
-      </c>
-      <c r="V21" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B22" t="s">
         <v>264</v>
@@ -5007,7 +5007,7 @@
         <v>265</v>
       </c>
       <c r="D22" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="E22" t="s">
         <v>267</v>
@@ -5016,36 +5016,36 @@
         <v>222</v>
       </c>
       <c r="H22" t="s">
+        <v>393</v>
+      </c>
+      <c r="I22" s="6" t="s">
         <v>394</v>
       </c>
-      <c r="I22" s="6" t="s">
+      <c r="J22" t="s">
         <v>395</v>
       </c>
-      <c r="J22" t="s">
+      <c r="K22" t="s">
         <v>396</v>
       </c>
-      <c r="K22" t="s">
+      <c r="L22" t="s">
         <v>397</v>
       </c>
-      <c r="L22" t="s">
+      <c r="M22" t="s">
         <v>398</v>
       </c>
-      <c r="M22" t="s">
+      <c r="P22" t="s">
         <v>399</v>
       </c>
-      <c r="P22" t="s">
+      <c r="Q22" s="3" t="s">
         <v>400</v>
       </c>
-      <c r="Q22" s="3" t="s">
+      <c r="V22" t="s">
         <v>401</v>
-      </c>
-      <c r="V22" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B23" t="s">
         <v>264</v>
@@ -5054,7 +5054,7 @@
         <v>265</v>
       </c>
       <c r="D23" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E23" t="s">
         <v>267</v>
@@ -5063,36 +5063,36 @@
         <v>222</v>
       </c>
       <c r="H23" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="I23" s="6" t="s">
+        <v>404</v>
+      </c>
+      <c r="J23" t="s">
         <v>405</v>
       </c>
-      <c r="J23" t="s">
+      <c r="K23" t="s">
+        <v>396</v>
+      </c>
+      <c r="L23" t="s">
+        <v>397</v>
+      </c>
+      <c r="M23" t="s">
+        <v>398</v>
+      </c>
+      <c r="P23" t="s">
+        <v>399</v>
+      </c>
+      <c r="Q23" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="K23" t="s">
-        <v>397</v>
-      </c>
-      <c r="L23" t="s">
-        <v>398</v>
-      </c>
-      <c r="M23" t="s">
-        <v>399</v>
-      </c>
-      <c r="P23" t="s">
-        <v>400</v>
-      </c>
-      <c r="Q23" s="3" t="s">
+      <c r="V23" t="s">
         <v>407</v>
-      </c>
-      <c r="V23" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B24" t="s">
         <v>264</v>
@@ -5101,7 +5101,7 @@
         <v>265</v>
       </c>
       <c r="D24" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E24" t="s">
         <v>267</v>
@@ -5110,36 +5110,36 @@
         <v>222</v>
       </c>
       <c r="H24" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="I24" s="6" t="s">
+        <v>410</v>
+      </c>
+      <c r="J24" t="s">
         <v>411</v>
       </c>
-      <c r="J24" t="s">
+      <c r="K24" t="s">
+        <v>396</v>
+      </c>
+      <c r="L24" t="s">
+        <v>397</v>
+      </c>
+      <c r="M24" t="s">
+        <v>398</v>
+      </c>
+      <c r="P24" t="s">
+        <v>399</v>
+      </c>
+      <c r="Q24" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="K24" t="s">
-        <v>397</v>
-      </c>
-      <c r="L24" t="s">
-        <v>398</v>
-      </c>
-      <c r="M24" t="s">
-        <v>399</v>
-      </c>
-      <c r="P24" t="s">
-        <v>400</v>
-      </c>
-      <c r="Q24" s="3" t="s">
+      <c r="V24" t="s">
         <v>413</v>
-      </c>
-      <c r="V24" t="s">
-        <v>414</v>
       </c>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B25" t="s">
         <v>264</v>
@@ -5148,7 +5148,7 @@
         <v>265</v>
       </c>
       <c r="D25" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E25" t="s">
         <v>267</v>
@@ -5157,36 +5157,36 @@
         <v>222</v>
       </c>
       <c r="H25" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="I25" s="6" t="s">
+        <v>416</v>
+      </c>
+      <c r="J25" t="s">
         <v>417</v>
       </c>
-      <c r="J25" t="s">
+      <c r="K25" t="s">
+        <v>396</v>
+      </c>
+      <c r="L25" t="s">
+        <v>397</v>
+      </c>
+      <c r="M25" t="s">
+        <v>398</v>
+      </c>
+      <c r="P25" t="s">
+        <v>399</v>
+      </c>
+      <c r="Q25" s="3" t="s">
         <v>418</v>
       </c>
-      <c r="K25" t="s">
-        <v>397</v>
-      </c>
-      <c r="L25" t="s">
-        <v>398</v>
-      </c>
-      <c r="M25" t="s">
-        <v>399</v>
-      </c>
-      <c r="P25" t="s">
-        <v>400</v>
-      </c>
-      <c r="Q25" s="3" t="s">
+      <c r="V25" t="s">
         <v>419</v>
-      </c>
-      <c r="V25" t="s">
-        <v>420</v>
       </c>
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B26" t="s">
         <v>264</v>
@@ -5195,7 +5195,7 @@
         <v>265</v>
       </c>
       <c r="D26" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E26" t="s">
         <v>267</v>
@@ -5204,36 +5204,36 @@
         <v>222</v>
       </c>
       <c r="H26" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="I26" s="6" t="s">
+        <v>422</v>
+      </c>
+      <c r="J26" t="s">
         <v>423</v>
       </c>
-      <c r="J26" t="s">
+      <c r="K26" t="s">
+        <v>396</v>
+      </c>
+      <c r="L26" t="s">
+        <v>397</v>
+      </c>
+      <c r="M26" t="s">
+        <v>398</v>
+      </c>
+      <c r="P26" t="s">
+        <v>399</v>
+      </c>
+      <c r="Q26" s="3" t="s">
         <v>424</v>
       </c>
-      <c r="K26" t="s">
-        <v>397</v>
-      </c>
-      <c r="L26" t="s">
-        <v>398</v>
-      </c>
-      <c r="M26" t="s">
-        <v>399</v>
-      </c>
-      <c r="P26" t="s">
-        <v>400</v>
-      </c>
-      <c r="Q26" s="3" t="s">
+      <c r="V26" t="s">
         <v>425</v>
-      </c>
-      <c r="V26" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="27" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B27" t="s">
         <v>264</v>
@@ -5242,7 +5242,7 @@
         <v>265</v>
       </c>
       <c r="D27" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E27" t="s">
         <v>267</v>
@@ -5251,36 +5251,36 @@
         <v>222</v>
       </c>
       <c r="H27" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="I27" s="6" t="s">
+        <v>428</v>
+      </c>
+      <c r="J27" t="s">
         <v>429</v>
       </c>
-      <c r="J27" t="s">
+      <c r="K27" t="s">
+        <v>396</v>
+      </c>
+      <c r="L27" t="s">
+        <v>397</v>
+      </c>
+      <c r="M27" t="s">
+        <v>398</v>
+      </c>
+      <c r="P27" t="s">
+        <v>399</v>
+      </c>
+      <c r="Q27" s="3" t="s">
         <v>430</v>
       </c>
-      <c r="K27" t="s">
-        <v>397</v>
-      </c>
-      <c r="L27" t="s">
-        <v>398</v>
-      </c>
-      <c r="M27" t="s">
-        <v>399</v>
-      </c>
-      <c r="P27" t="s">
-        <v>400</v>
-      </c>
-      <c r="Q27" s="3" t="s">
+      <c r="V27" t="s">
         <v>431</v>
-      </c>
-      <c r="V27" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="28" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B28" t="s">
         <v>264</v>
@@ -5289,7 +5289,7 @@
         <v>265</v>
       </c>
       <c r="D28" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E28" t="s">
         <v>267</v>
@@ -5298,36 +5298,36 @@
         <v>222</v>
       </c>
       <c r="H28" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="I28" s="6" t="s">
+        <v>434</v>
+      </c>
+      <c r="J28" t="s">
         <v>435</v>
       </c>
-      <c r="J28" t="s">
+      <c r="K28" t="s">
+        <v>396</v>
+      </c>
+      <c r="L28" t="s">
+        <v>397</v>
+      </c>
+      <c r="M28" t="s">
+        <v>398</v>
+      </c>
+      <c r="P28" t="s">
+        <v>399</v>
+      </c>
+      <c r="Q28" s="3" t="s">
         <v>436</v>
       </c>
-      <c r="K28" t="s">
-        <v>397</v>
-      </c>
-      <c r="L28" t="s">
-        <v>398</v>
-      </c>
-      <c r="M28" t="s">
-        <v>399</v>
-      </c>
-      <c r="P28" t="s">
-        <v>400</v>
-      </c>
-      <c r="Q28" s="3" t="s">
+      <c r="V28" t="s">
         <v>437</v>
-      </c>
-      <c r="V28" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="29" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B29" t="s">
         <v>264</v>
@@ -5336,7 +5336,7 @@
         <v>265</v>
       </c>
       <c r="D29" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E29" t="s">
         <v>267</v>
@@ -5345,39 +5345,39 @@
         <v>222</v>
       </c>
       <c r="H29" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="I29" s="6" t="s">
+        <v>440</v>
+      </c>
+      <c r="J29" t="s">
         <v>441</v>
       </c>
-      <c r="J29" t="s">
-        <v>442</v>
-      </c>
       <c r="K29" t="s">
+        <v>396</v>
+      </c>
+      <c r="L29" t="s">
         <v>397</v>
       </c>
-      <c r="L29" t="s">
+      <c r="M29" t="s">
         <v>398</v>
-      </c>
-      <c r="M29" t="s">
-        <v>399</v>
       </c>
       <c r="O29" t="s">
         <v>12</v>
       </c>
       <c r="P29" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="Q29" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="V29" t="s">
         <v>443</v>
-      </c>
-      <c r="V29" t="s">
-        <v>444</v>
       </c>
     </row>
     <row r="30" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B30" t="s">
         <v>264</v>
@@ -5386,7 +5386,7 @@
         <v>265</v>
       </c>
       <c r="D30" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="E30" t="s">
         <v>267</v>
@@ -5395,42 +5395,42 @@
         <v>222</v>
       </c>
       <c r="H30" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="I30" s="6" t="s">
+        <v>446</v>
+      </c>
+      <c r="J30" t="s">
         <v>447</v>
       </c>
-      <c r="J30" t="s">
-        <v>448</v>
-      </c>
       <c r="K30" t="s">
+        <v>396</v>
+      </c>
+      <c r="L30" t="s">
         <v>397</v>
       </c>
-      <c r="L30" t="s">
+      <c r="M30" t="s">
         <v>398</v>
-      </c>
-      <c r="M30" t="s">
-        <v>399</v>
       </c>
       <c r="N30" t="s">
         <v>219</v>
       </c>
       <c r="O30" t="s">
+        <v>448</v>
+      </c>
+      <c r="P30" t="s">
+        <v>399</v>
+      </c>
+      <c r="Q30" s="3" t="s">
         <v>449</v>
       </c>
-      <c r="P30" t="s">
-        <v>400</v>
-      </c>
-      <c r="Q30" s="3" t="s">
+      <c r="V30" t="s">
         <v>450</v>
-      </c>
-      <c r="V30" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="31" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B31" t="s">
         <v>264</v>
@@ -5439,7 +5439,7 @@
         <v>265</v>
       </c>
       <c r="D31" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E31" t="s">
         <v>267</v>
@@ -5448,7 +5448,7 @@
         <v>34</v>
       </c>
       <c r="G31" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H31" t="s">
         <v>268</v>
@@ -5460,30 +5460,30 @@
         <v>126</v>
       </c>
       <c r="K31" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="L31" t="s">
         <v>270</v>
       </c>
       <c r="M31" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="P31" t="s">
         <v>272</v>
       </c>
       <c r="Q31" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="U31" t="s">
         <v>455</v>
       </c>
-      <c r="U31" t="s">
+      <c r="V31" t="s">
         <v>456</v>
-      </c>
-      <c r="V31" t="s">
-        <v>457</v>
       </c>
     </row>
     <row r="32" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B32" t="s">
         <v>264</v>
@@ -5492,7 +5492,7 @@
         <v>265</v>
       </c>
       <c r="D32" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="E32" t="s">
         <v>267</v>
@@ -5513,27 +5513,27 @@
         <v>126</v>
       </c>
       <c r="K32" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="L32" t="s">
         <v>270</v>
       </c>
       <c r="M32" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="P32" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="Q32" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="V32" t="s">
         <v>460</v>
-      </c>
-      <c r="V32" t="s">
-        <v>461</v>
       </c>
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B33" t="s">
         <v>264</v>
@@ -5542,7 +5542,7 @@
         <v>265</v>
       </c>
       <c r="D33" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="E33" t="s">
         <v>267</v>
@@ -5557,10 +5557,10 @@
         <v>205</v>
       </c>
       <c r="K33" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="M33" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="N33" t="s">
         <v>65</v>
@@ -5569,27 +5569,27 @@
         <v>272</v>
       </c>
       <c r="Q33" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="R33" t="s">
         <v>465</v>
       </c>
-      <c r="R33" t="s">
+      <c r="V33" t="s">
         <v>466</v>
-      </c>
-      <c r="V33" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B34" t="s">
         <v>264</v>
       </c>
       <c r="C34" t="s">
+        <v>468</v>
+      </c>
+      <c r="D34" t="s">
         <v>469</v>
-      </c>
-      <c r="D34" t="s">
-        <v>470</v>
       </c>
       <c r="E34" t="s">
         <v>267</v>
@@ -5601,19 +5601,19 @@
         <v>25063</v>
       </c>
       <c r="J34" t="s">
+        <v>470</v>
+      </c>
+      <c r="K34" t="s">
         <v>471</v>
-      </c>
-      <c r="K34" t="s">
-        <v>472</v>
       </c>
       <c r="L34" t="s">
         <v>270</v>
       </c>
       <c r="M34" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="N34" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="O34" t="s">
         <v>34</v>
@@ -5622,30 +5622,30 @@
         <v>272</v>
       </c>
       <c r="Q34" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="S34" t="s">
         <v>474</v>
       </c>
-      <c r="S34" t="s">
+      <c r="T34" t="s">
         <v>475</v>
       </c>
-      <c r="T34" t="s">
+      <c r="V34" t="s">
         <v>476</v>
-      </c>
-      <c r="V34" t="s">
-        <v>477</v>
       </c>
     </row>
     <row r="35" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B35" t="s">
         <v>264</v>
       </c>
       <c r="C35" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="D35" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E35" t="s">
         <v>267</v>
@@ -5660,19 +5660,19 @@
         <v>25081</v>
       </c>
       <c r="J35" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="K35" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="L35" t="s">
         <v>270</v>
       </c>
       <c r="M35" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="N35" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="O35" t="s">
         <v>12</v>
@@ -5681,21 +5681,21 @@
         <v>272</v>
       </c>
       <c r="Q35" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="S35" t="s">
         <v>481</v>
       </c>
-      <c r="S35" t="s">
+      <c r="T35" t="s">
         <v>482</v>
       </c>
-      <c r="T35" t="s">
+      <c r="V35" t="s">
         <v>483</v>
-      </c>
-      <c r="V35" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B36" t="s">
         <v>264</v>
@@ -5704,7 +5704,7 @@
         <v>265</v>
       </c>
       <c r="D36" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="E36" t="s">
         <v>267</v>
@@ -5713,19 +5713,19 @@
         <v>56</v>
       </c>
       <c r="I36" s="6" t="s">
+        <v>486</v>
+      </c>
+      <c r="J36" t="s">
         <v>487</v>
       </c>
-      <c r="J36" t="s">
+      <c r="K36" t="s">
+        <v>396</v>
+      </c>
+      <c r="L36" t="s">
         <v>488</v>
       </c>
-      <c r="K36" t="s">
-        <v>397</v>
-      </c>
-      <c r="L36" t="s">
-        <v>489</v>
-      </c>
       <c r="M36" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="N36" t="s">
         <v>32</v>
@@ -5734,15 +5734,15 @@
         <v>272</v>
       </c>
       <c r="Q36" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="V36" t="s">
         <v>490</v>
-      </c>
-      <c r="V36" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B37" t="s">
         <v>264</v>
@@ -5751,7 +5751,7 @@
         <v>265</v>
       </c>
       <c r="D37" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="E37" t="s">
         <v>267</v>
@@ -5763,25 +5763,25 @@
         <v>65</v>
       </c>
       <c r="H37" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="I37" s="1">
         <v>1975</v>
       </c>
       <c r="J37" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="K37" t="s">
         <v>269</v>
       </c>
       <c r="L37" t="s">
+        <v>495</v>
+      </c>
+      <c r="M37" t="s">
+        <v>380</v>
+      </c>
+      <c r="N37" t="s">
         <v>496</v>
-      </c>
-      <c r="M37" t="s">
-        <v>381</v>
-      </c>
-      <c r="N37" t="s">
-        <v>497</v>
       </c>
       <c r="O37" t="s">
         <v>67</v>
@@ -5790,15 +5790,15 @@
         <v>272</v>
       </c>
       <c r="Q37" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="V37" t="s">
         <v>498</v>
-      </c>
-      <c r="V37" t="s">
-        <v>499</v>
       </c>
     </row>
     <row r="38" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B38" t="s">
         <v>264</v>
@@ -5807,7 +5807,7 @@
         <v>265</v>
       </c>
       <c r="D38" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="E38" t="s">
         <v>267</v>
@@ -5828,30 +5828,30 @@
         <v>126</v>
       </c>
       <c r="K38" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="L38" t="s">
         <v>270</v>
       </c>
       <c r="M38" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="P38" t="s">
         <v>272</v>
       </c>
       <c r="Q38" s="3" t="s">
+        <v>501</v>
+      </c>
+      <c r="U38" t="s">
         <v>502</v>
       </c>
-      <c r="U38" t="s">
+      <c r="V38" t="s">
         <v>503</v>
-      </c>
-      <c r="V38" t="s">
-        <v>504</v>
       </c>
     </row>
     <row r="39" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B39" t="s">
         <v>264</v>
@@ -5860,7 +5860,7 @@
         <v>265</v>
       </c>
       <c r="D39" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="E39" t="s">
         <v>267</v>
@@ -5881,33 +5881,33 @@
         <v>205</v>
       </c>
       <c r="K39" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="L39" t="s">
         <v>270</v>
       </c>
       <c r="M39" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="N39" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="P39" t="s">
         <v>272</v>
       </c>
       <c r="Q39" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="U39" t="s">
         <v>508</v>
       </c>
-      <c r="U39" t="s">
+      <c r="V39" t="s">
         <v>509</v>
-      </c>
-      <c r="V39" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B40" t="s">
         <v>264</v>
@@ -5916,7 +5916,7 @@
         <v>265</v>
       </c>
       <c r="D40" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E40" t="s">
         <v>267</v>
@@ -5943,24 +5943,24 @@
         <v>270</v>
       </c>
       <c r="M40" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="P40" t="s">
         <v>272</v>
       </c>
       <c r="Q40" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="U40" t="s">
         <v>514</v>
       </c>
-      <c r="U40" t="s">
+      <c r="V40" t="s">
         <v>515</v>
-      </c>
-      <c r="V40" t="s">
-        <v>516</v>
       </c>
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B41" t="s">
         <v>264</v>
@@ -5969,7 +5969,7 @@
         <v>265</v>
       </c>
       <c r="D41" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E41" t="s">
         <v>267</v>
@@ -5978,7 +5978,7 @@
         <v>34</v>
       </c>
       <c r="G41" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H41" t="s">
         <v>268</v>
@@ -5990,30 +5990,30 @@
         <v>205</v>
       </c>
       <c r="K41" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="L41" t="s">
         <v>270</v>
       </c>
       <c r="M41" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="P41" t="s">
         <v>272</v>
       </c>
       <c r="Q41" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="U41" t="s">
         <v>520</v>
       </c>
-      <c r="U41" t="s">
+      <c r="V41" t="s">
         <v>521</v>
-      </c>
-      <c r="V41" t="s">
-        <v>522</v>
       </c>
     </row>
     <row r="42" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B42" t="s">
         <v>264</v>
@@ -6022,7 +6022,7 @@
         <v>265</v>
       </c>
       <c r="D42" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="E42" t="s">
         <v>267</v>
@@ -6031,7 +6031,7 @@
         <v>32</v>
       </c>
       <c r="H42" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="I42" s="1">
         <v>1968</v>
@@ -6043,27 +6043,27 @@
         <v>269</v>
       </c>
       <c r="L42" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="M42" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="P42" t="s">
         <v>272</v>
       </c>
       <c r="Q42" s="3" t="s">
+        <v>526</v>
+      </c>
+      <c r="U42" t="s">
         <v>527</v>
       </c>
-      <c r="U42" t="s">
+      <c r="V42" t="s">
         <v>528</v>
-      </c>
-      <c r="V42" t="s">
-        <v>529</v>
       </c>
     </row>
     <row r="43" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B43" t="s">
         <v>264</v>
@@ -6072,7 +6072,7 @@
         <v>265</v>
       </c>
       <c r="D43" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="E43" t="s">
         <v>267</v>
@@ -6081,7 +6081,7 @@
         <v>32</v>
       </c>
       <c r="H43" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="I43" s="1">
         <v>1967</v>
@@ -6093,10 +6093,10 @@
         <v>269</v>
       </c>
       <c r="L43" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="M43" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="N43" t="s">
         <v>84</v>
@@ -6108,18 +6108,18 @@
         <v>272</v>
       </c>
       <c r="Q43" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="U43" t="s">
         <v>533</v>
       </c>
-      <c r="U43" t="s">
+      <c r="V43" t="s">
         <v>534</v>
-      </c>
-      <c r="V43" t="s">
-        <v>535</v>
       </c>
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B44" t="s">
         <v>264</v>
@@ -6128,7 +6128,7 @@
         <v>265</v>
       </c>
       <c r="D44" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="E44" t="s">
         <v>267</v>
@@ -6149,30 +6149,30 @@
         <v>126</v>
       </c>
       <c r="K44" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="L44" t="s">
         <v>270</v>
       </c>
       <c r="M44" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="P44" t="s">
         <v>272</v>
       </c>
       <c r="Q44" s="3" t="s">
+        <v>537</v>
+      </c>
+      <c r="U44" t="s">
         <v>538</v>
       </c>
-      <c r="U44" t="s">
+      <c r="V44" t="s">
         <v>539</v>
-      </c>
-      <c r="V44" t="s">
-        <v>540</v>
       </c>
     </row>
     <row r="45" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B45" t="s">
         <v>264</v>
@@ -6181,7 +6181,7 @@
         <v>265</v>
       </c>
       <c r="D45" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="E45" t="s">
         <v>267</v>
@@ -6202,33 +6202,33 @@
         <v>194</v>
       </c>
       <c r="K45" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="L45" t="s">
         <v>270</v>
       </c>
       <c r="M45" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="O45" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="P45" t="s">
         <v>272</v>
       </c>
       <c r="Q45" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="U45" t="s">
         <v>544</v>
       </c>
-      <c r="U45" t="s">
+      <c r="V45" t="s">
         <v>545</v>
-      </c>
-      <c r="V45" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="46" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B46" t="s">
         <v>264</v>
@@ -6237,7 +6237,7 @@
         <v>265</v>
       </c>
       <c r="D46" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="E46" t="s">
         <v>267</v>
@@ -6258,30 +6258,30 @@
         <v>126</v>
       </c>
       <c r="K46" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="L46" t="s">
         <v>270</v>
       </c>
       <c r="M46" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="P46" t="s">
         <v>272</v>
       </c>
       <c r="Q46" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="U46" t="s">
         <v>549</v>
       </c>
-      <c r="U46" t="s">
+      <c r="V46" t="s">
         <v>550</v>
-      </c>
-      <c r="V46" t="s">
-        <v>551</v>
       </c>
     </row>
     <row r="47" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B47" t="s">
         <v>264</v>
@@ -6290,7 +6290,7 @@
         <v>265</v>
       </c>
       <c r="D47" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="E47" t="s">
         <v>267</v>
@@ -6311,30 +6311,30 @@
         <v>130</v>
       </c>
       <c r="K47" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="L47" t="s">
         <v>270</v>
       </c>
       <c r="M47" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="P47" t="s">
         <v>272</v>
       </c>
       <c r="Q47" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="U47" t="s">
         <v>554</v>
       </c>
-      <c r="U47" t="s">
+      <c r="V47" t="s">
         <v>555</v>
-      </c>
-      <c r="V47" t="s">
-        <v>556</v>
       </c>
     </row>
     <row r="48" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B48" t="s">
         <v>264</v>
@@ -6343,7 +6343,7 @@
         <v>265</v>
       </c>
       <c r="D48" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="E48" t="s">
         <v>267</v>
@@ -6361,33 +6361,33 @@
         <v>1971</v>
       </c>
       <c r="J48" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="K48" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="L48" t="s">
         <v>270</v>
       </c>
       <c r="M48" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="P48" t="s">
         <v>272</v>
       </c>
       <c r="Q48" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="U48" t="s">
         <v>560</v>
       </c>
-      <c r="U48" t="s">
+      <c r="V48" t="s">
         <v>561</v>
-      </c>
-      <c r="V48" t="s">
-        <v>562</v>
       </c>
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B49" t="s">
         <v>264</v>
@@ -6396,7 +6396,7 @@
         <v>265</v>
       </c>
       <c r="D49" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E49" t="s">
         <v>267</v>
@@ -6417,30 +6417,30 @@
         <v>126</v>
       </c>
       <c r="K49" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="L49" t="s">
         <v>270</v>
       </c>
       <c r="M49" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="P49" t="s">
         <v>272</v>
       </c>
       <c r="Q49" s="3" t="s">
+        <v>564</v>
+      </c>
+      <c r="U49" t="s">
         <v>565</v>
       </c>
-      <c r="U49" t="s">
+      <c r="V49" t="s">
         <v>566</v>
-      </c>
-      <c r="V49" t="s">
-        <v>567</v>
       </c>
     </row>
     <row r="50" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B50" t="s">
         <v>264</v>
@@ -6449,7 +6449,7 @@
         <v>265</v>
       </c>
       <c r="D50" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="E50" t="s">
         <v>267</v>
@@ -6470,30 +6470,30 @@
         <v>126</v>
       </c>
       <c r="K50" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="L50" t="s">
         <v>270</v>
       </c>
       <c r="M50" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="P50" t="s">
         <v>272</v>
       </c>
       <c r="Q50" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="U50" t="s">
         <v>570</v>
       </c>
-      <c r="U50" t="s">
+      <c r="V50" t="s">
         <v>571</v>
-      </c>
-      <c r="V50" t="s">
-        <v>572</v>
       </c>
     </row>
     <row r="51" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B51" t="s">
         <v>264</v>
@@ -6502,7 +6502,7 @@
         <v>265</v>
       </c>
       <c r="D51" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="E51" t="s">
         <v>267</v>
@@ -6523,30 +6523,30 @@
         <v>126</v>
       </c>
       <c r="K51" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="L51" t="s">
         <v>270</v>
       </c>
       <c r="M51" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="P51" t="s">
         <v>272</v>
       </c>
       <c r="Q51" s="3" t="s">
+        <v>574</v>
+      </c>
+      <c r="U51" t="s">
         <v>575</v>
       </c>
-      <c r="U51" t="s">
+      <c r="V51" t="s">
         <v>576</v>
-      </c>
-      <c r="V51" t="s">
-        <v>577</v>
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B52" t="s">
         <v>264</v>
@@ -6555,7 +6555,7 @@
         <v>265</v>
       </c>
       <c r="D52" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="E52" t="s">
         <v>267</v>
@@ -6576,30 +6576,30 @@
         <v>126</v>
       </c>
       <c r="K52" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="L52" t="s">
         <v>270</v>
       </c>
       <c r="M52" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="P52" t="s">
         <v>272</v>
       </c>
       <c r="Q52" s="3" t="s">
+        <v>579</v>
+      </c>
+      <c r="U52" t="s">
         <v>580</v>
       </c>
-      <c r="U52" t="s">
+      <c r="V52" t="s">
         <v>581</v>
-      </c>
-      <c r="V52" t="s">
-        <v>582</v>
       </c>
     </row>
     <row r="53" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B53" t="s">
         <v>264</v>
@@ -6608,7 +6608,7 @@
         <v>265</v>
       </c>
       <c r="D53" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="E53" t="s">
         <v>267</v>
@@ -6620,7 +6620,7 @@
         <v>118</v>
       </c>
       <c r="H53" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="I53" s="1">
         <v>1969</v>
@@ -6632,30 +6632,30 @@
         <v>269</v>
       </c>
       <c r="L53" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="M53" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="N53" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="P53" t="s">
         <v>272</v>
       </c>
       <c r="Q53" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="U53" t="s">
         <v>587</v>
       </c>
-      <c r="U53" t="s">
+      <c r="V53" t="s">
         <v>588</v>
-      </c>
-      <c r="V53" t="s">
-        <v>589</v>
       </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B54" t="s">
         <v>264</v>
@@ -6664,7 +6664,7 @@
         <v>265</v>
       </c>
       <c r="D54" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E54" t="s">
         <v>267</v>
@@ -6679,13 +6679,13 @@
         <v>182</v>
       </c>
       <c r="K54" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="L54" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="M54" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="O54" t="s">
         <v>105</v>
@@ -6694,15 +6694,15 @@
         <v>272</v>
       </c>
       <c r="Q54" s="3" t="s">
+        <v>592</v>
+      </c>
+      <c r="V54" t="s">
         <v>593</v>
-      </c>
-      <c r="V54" t="s">
-        <v>594</v>
       </c>
     </row>
     <row r="55" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B55" t="s">
         <v>264</v>
@@ -6711,7 +6711,7 @@
         <v>265</v>
       </c>
       <c r="D55" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E55" t="s">
         <v>267</v>
@@ -6726,42 +6726,42 @@
         <v>156</v>
       </c>
       <c r="I55" s="6" t="s">
+        <v>596</v>
+      </c>
+      <c r="J55" t="s">
         <v>597</v>
       </c>
-      <c r="J55" t="s">
+      <c r="K55" t="s">
         <v>598</v>
       </c>
-      <c r="K55" t="s">
+      <c r="L55" t="s">
+        <v>488</v>
+      </c>
+      <c r="M55" t="s">
+        <v>330</v>
+      </c>
+      <c r="N55" t="s">
         <v>599</v>
-      </c>
-      <c r="L55" t="s">
-        <v>489</v>
-      </c>
-      <c r="M55" t="s">
-        <v>331</v>
-      </c>
-      <c r="N55" t="s">
-        <v>600</v>
       </c>
       <c r="P55" t="s">
         <v>272</v>
       </c>
       <c r="Q55" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="R55" t="s">
         <v>601</v>
       </c>
-      <c r="R55" t="s">
+      <c r="U55" t="s">
         <v>602</v>
       </c>
-      <c r="U55" t="s">
+      <c r="V55" t="s">
         <v>603</v>
-      </c>
-      <c r="V55" t="s">
-        <v>604</v>
       </c>
     </row>
     <row r="56" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B56" t="s">
         <v>264</v>
@@ -6770,7 +6770,7 @@
         <v>265</v>
       </c>
       <c r="D56" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="E56" t="s">
         <v>267</v>
@@ -6791,10 +6791,10 @@
         <v>194</v>
       </c>
       <c r="K56" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="M56" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="N56" t="s">
         <v>32</v>
@@ -6803,21 +6803,21 @@
         <v>272</v>
       </c>
       <c r="Q56" s="3" t="s">
+        <v>606</v>
+      </c>
+      <c r="R56" t="s">
         <v>607</v>
       </c>
-      <c r="R56" t="s">
+      <c r="U56" t="s">
+        <v>602</v>
+      </c>
+      <c r="V56" t="s">
         <v>608</v>
-      </c>
-      <c r="U56" t="s">
-        <v>603</v>
-      </c>
-      <c r="V56" t="s">
-        <v>609</v>
       </c>
     </row>
     <row r="57" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B57" t="s">
         <v>264</v>
@@ -6826,7 +6826,7 @@
         <v>265</v>
       </c>
       <c r="D57" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="E57" t="s">
         <v>267</v>
@@ -6850,27 +6850,27 @@
         <v>269</v>
       </c>
       <c r="L57" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="M57" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="P57" t="s">
         <v>272</v>
       </c>
       <c r="Q57" s="3" t="s">
+        <v>611</v>
+      </c>
+      <c r="U57" t="s">
         <v>612</v>
       </c>
-      <c r="U57" t="s">
+      <c r="V57" t="s">
         <v>613</v>
-      </c>
-      <c r="V57" t="s">
-        <v>614</v>
       </c>
     </row>
     <row r="58" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B58" t="s">
         <v>264</v>
@@ -6879,10 +6879,10 @@
         <v>265</v>
       </c>
       <c r="D58" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="E58" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F58" t="s">
         <v>28</v>
@@ -6897,42 +6897,42 @@
         <v>28253</v>
       </c>
       <c r="J58" t="s">
+        <v>616</v>
+      </c>
+      <c r="K58" t="s">
+        <v>341</v>
+      </c>
+      <c r="L58" t="s">
+        <v>495</v>
+      </c>
+      <c r="M58" t="s">
+        <v>330</v>
+      </c>
+      <c r="N58" t="s">
         <v>617</v>
       </c>
-      <c r="K58" t="s">
-        <v>342</v>
-      </c>
-      <c r="L58" t="s">
-        <v>496</v>
-      </c>
-      <c r="M58" t="s">
-        <v>331</v>
-      </c>
-      <c r="N58" t="s">
+      <c r="O58" t="s">
         <v>618</v>
-      </c>
-      <c r="O58" t="s">
-        <v>619</v>
       </c>
       <c r="P58" t="s">
         <v>272</v>
       </c>
       <c r="Q58" s="3" t="s">
+        <v>619</v>
+      </c>
+      <c r="R58" t="s">
         <v>620</v>
       </c>
-      <c r="R58" t="s">
+      <c r="U58" t="s">
+        <v>346</v>
+      </c>
+      <c r="V58" t="s">
         <v>621</v>
-      </c>
-      <c r="U58" t="s">
-        <v>347</v>
-      </c>
-      <c r="V58" t="s">
-        <v>622</v>
       </c>
     </row>
     <row r="59" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B59" t="s">
         <v>264</v>
@@ -6941,7 +6941,7 @@
         <v>265</v>
       </c>
       <c r="D59" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="E59" t="s">
         <v>267</v>
@@ -6950,7 +6950,7 @@
         <v>97</v>
       </c>
       <c r="G59" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="H59" t="s">
         <v>97</v>
@@ -6965,27 +6965,27 @@
         <v>269</v>
       </c>
       <c r="L59" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="M59" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="P59" t="s">
         <v>272</v>
       </c>
       <c r="Q59" s="3" t="s">
+        <v>625</v>
+      </c>
+      <c r="U59" t="s">
         <v>626</v>
       </c>
-      <c r="U59" t="s">
+      <c r="V59" t="s">
         <v>627</v>
-      </c>
-      <c r="V59" t="s">
-        <v>628</v>
       </c>
     </row>
     <row r="60" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B60" t="s">
         <v>264</v>
@@ -6994,7 +6994,7 @@
         <v>265</v>
       </c>
       <c r="D60" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="E60" t="s">
         <v>267</v>
@@ -7003,7 +7003,7 @@
         <v>97</v>
       </c>
       <c r="G60" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="H60" t="s">
         <v>97</v>
@@ -7018,27 +7018,27 @@
         <v>269</v>
       </c>
       <c r="L60" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="M60" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="P60" t="s">
         <v>272</v>
       </c>
       <c r="Q60" s="3" t="s">
+        <v>630</v>
+      </c>
+      <c r="U60" t="s">
         <v>631</v>
       </c>
-      <c r="U60" t="s">
+      <c r="V60" t="s">
         <v>632</v>
-      </c>
-      <c r="V60" t="s">
-        <v>633</v>
       </c>
     </row>
     <row r="61" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B61" t="s">
         <v>264</v>
@@ -7047,7 +7047,7 @@
         <v>265</v>
       </c>
       <c r="D61" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="E61" t="s">
         <v>267</v>
@@ -7056,7 +7056,7 @@
         <v>97</v>
       </c>
       <c r="G61" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H61" t="s">
         <v>97</v>
@@ -7065,39 +7065,39 @@
         <v>1965</v>
       </c>
       <c r="J61" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="K61" t="s">
         <v>269</v>
       </c>
       <c r="L61" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="M61" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="N61" t="s">
         <v>185</v>
       </c>
       <c r="O61" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="P61" t="s">
         <v>272</v>
       </c>
       <c r="Q61" s="3" t="s">
+        <v>638</v>
+      </c>
+      <c r="U61" t="s">
         <v>639</v>
       </c>
-      <c r="U61" t="s">
+      <c r="V61" t="s">
         <v>640</v>
-      </c>
-      <c r="V61" t="s">
-        <v>641</v>
       </c>
     </row>
     <row r="62" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B62" t="s">
         <v>264</v>
@@ -7106,7 +7106,7 @@
         <v>265</v>
       </c>
       <c r="D62" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="E62" t="s">
         <v>267</v>
@@ -7124,33 +7124,33 @@
         <v>1971</v>
       </c>
       <c r="J62" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="K62" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="L62" t="s">
         <v>270</v>
       </c>
       <c r="M62" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="P62" t="s">
         <v>272</v>
       </c>
       <c r="Q62" s="3" t="s">
+        <v>643</v>
+      </c>
+      <c r="U62" t="s">
         <v>644</v>
       </c>
-      <c r="U62" t="s">
+      <c r="V62" t="s">
         <v>645</v>
-      </c>
-      <c r="V62" t="s">
-        <v>646</v>
       </c>
     </row>
     <row r="63" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B63" t="s">
         <v>264</v>
@@ -7159,51 +7159,51 @@
         <v>265</v>
       </c>
       <c r="D63" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="E63" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="I63" s="4">
         <v>24917</v>
       </c>
       <c r="J63" t="s">
+        <v>648</v>
+      </c>
+      <c r="K63" t="s">
+        <v>341</v>
+      </c>
+      <c r="L63" t="s">
         <v>649</v>
       </c>
-      <c r="K63" t="s">
-        <v>342</v>
-      </c>
-      <c r="L63" t="s">
+      <c r="M63" t="s">
+        <v>380</v>
+      </c>
+      <c r="N63" t="s">
         <v>650</v>
       </c>
-      <c r="M63" t="s">
-        <v>381</v>
-      </c>
-      <c r="N63" t="s">
+      <c r="O63" t="s">
         <v>651</v>
-      </c>
-      <c r="O63" t="s">
-        <v>652</v>
       </c>
       <c r="P63" t="s">
         <v>272</v>
       </c>
       <c r="Q63" s="3" t="s">
+        <v>652</v>
+      </c>
+      <c r="R63" t="s">
         <v>653</v>
       </c>
-      <c r="R63" t="s">
+      <c r="U63" t="s">
+        <v>346</v>
+      </c>
+      <c r="V63" t="s">
         <v>654</v>
-      </c>
-      <c r="U63" t="s">
-        <v>347</v>
-      </c>
-      <c r="V63" t="s">
-        <v>655</v>
       </c>
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B64" t="s">
         <v>264</v>
@@ -7212,7 +7212,7 @@
         <v>265</v>
       </c>
       <c r="D64" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="E64" t="s">
         <v>267</v>
@@ -7224,36 +7224,36 @@
         <v>105</v>
       </c>
       <c r="I64" s="5" t="s">
+        <v>657</v>
+      </c>
+      <c r="J64" t="s">
         <v>658</v>
       </c>
-      <c r="J64" t="s">
+      <c r="K64" t="s">
+        <v>365</v>
+      </c>
+      <c r="L64" t="s">
         <v>659</v>
       </c>
-      <c r="K64" t="s">
-        <v>366</v>
-      </c>
-      <c r="L64" t="s">
-        <v>660</v>
-      </c>
       <c r="M64" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="N64" t="s">
         <v>108</v>
       </c>
       <c r="P64" t="s">
+        <v>660</v>
+      </c>
+      <c r="Q64" s="3" t="s">
         <v>661</v>
       </c>
-      <c r="Q64" s="3" t="s">
+      <c r="V64" t="s">
         <v>662</v>
-      </c>
-      <c r="V64" t="s">
-        <v>663</v>
       </c>
     </row>
     <row r="65" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B65" t="s">
         <v>264</v>
@@ -7262,7 +7262,7 @@
         <v>265</v>
       </c>
       <c r="D65" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="E65" t="s">
         <v>267</v>
@@ -7277,33 +7277,33 @@
         <v>26956</v>
       </c>
       <c r="J65" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="K65" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="L65" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="M65" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="O65" t="s">
         <v>162</v>
       </c>
       <c r="P65" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="Q65" s="3" t="s">
+        <v>666</v>
+      </c>
+      <c r="V65" t="s">
         <v>667</v>
-      </c>
-      <c r="V65" t="s">
-        <v>668</v>
       </c>
     </row>
     <row r="66" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B66" t="s">
         <v>264</v>
@@ -7312,10 +7312,10 @@
         <v>265</v>
       </c>
       <c r="D66" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="E66" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F66" t="s">
         <v>12</v>
@@ -7327,36 +7327,36 @@
         <v>126</v>
       </c>
       <c r="K66" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="L66" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="M66" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="N66" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="P66" t="s">
         <v>272</v>
       </c>
       <c r="Q66" s="3" t="s">
+        <v>671</v>
+      </c>
+      <c r="R66" t="s">
         <v>672</v>
       </c>
-      <c r="R66" t="s">
+      <c r="U66" t="s">
+        <v>346</v>
+      </c>
+      <c r="V66" t="s">
         <v>673</v>
-      </c>
-      <c r="U66" t="s">
-        <v>347</v>
-      </c>
-      <c r="V66" t="s">
-        <v>674</v>
       </c>
     </row>
     <row r="67" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B67" t="s">
         <v>264</v>
@@ -7365,10 +7365,10 @@
         <v>265</v>
       </c>
       <c r="D67" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="E67" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F67" t="s">
         <v>167</v>
@@ -7380,36 +7380,36 @@
         <v>205</v>
       </c>
       <c r="K67" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="L67" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="M67" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="N67" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="P67" t="s">
         <v>272</v>
       </c>
       <c r="Q67" s="3" t="s">
+        <v>677</v>
+      </c>
+      <c r="R67" t="s">
         <v>678</v>
       </c>
-      <c r="R67" t="s">
+      <c r="U67" t="s">
         <v>679</v>
       </c>
-      <c r="U67" t="s">
+      <c r="V67" t="s">
         <v>680</v>
-      </c>
-      <c r="V67" t="s">
-        <v>681</v>
       </c>
     </row>
     <row r="68" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B68" t="s">
         <v>264</v>
@@ -7418,7 +7418,7 @@
         <v>265</v>
       </c>
       <c r="D68" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="E68" t="s">
         <v>267</v>
@@ -7427,36 +7427,36 @@
         <v>12</v>
       </c>
       <c r="I68" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="J68" t="s">
         <v>447</v>
       </c>
-      <c r="J68" t="s">
-        <v>448</v>
-      </c>
       <c r="K68" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="L68" t="s">
+        <v>329</v>
+      </c>
+      <c r="M68" t="s">
         <v>330</v>
-      </c>
-      <c r="M68" t="s">
-        <v>331</v>
       </c>
       <c r="P68" t="s">
         <v>272</v>
       </c>
       <c r="Q68" s="3" t="s">
+        <v>683</v>
+      </c>
+      <c r="R68" t="s">
         <v>684</v>
       </c>
-      <c r="R68" t="s">
+      <c r="V68" t="s">
         <v>685</v>
-      </c>
-      <c r="V68" t="s">
-        <v>686</v>
       </c>
     </row>
     <row r="69" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B69" t="s">
         <v>264</v>
@@ -7465,7 +7465,7 @@
         <v>265</v>
       </c>
       <c r="D69" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="E69" t="s">
         <v>267</v>
@@ -7477,33 +7477,33 @@
         <v>171</v>
       </c>
       <c r="I69" s="7" t="s">
+        <v>688</v>
+      </c>
+      <c r="J69" t="s">
         <v>689</v>
       </c>
-      <c r="J69" t="s">
+      <c r="K69" t="s">
+        <v>396</v>
+      </c>
+      <c r="L69" t="s">
+        <v>388</v>
+      </c>
+      <c r="M69" t="s">
+        <v>398</v>
+      </c>
+      <c r="P69" t="s">
+        <v>399</v>
+      </c>
+      <c r="Q69" s="3" t="s">
         <v>690</v>
       </c>
-      <c r="K69" t="s">
-        <v>397</v>
-      </c>
-      <c r="L69" t="s">
-        <v>389</v>
-      </c>
-      <c r="M69" t="s">
-        <v>399</v>
-      </c>
-      <c r="P69" t="s">
-        <v>400</v>
-      </c>
-      <c r="Q69" s="3" t="s">
+      <c r="V69" t="s">
         <v>691</v>
-      </c>
-      <c r="V69" t="s">
-        <v>692</v>
       </c>
     </row>
     <row r="70" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B70" t="s">
         <v>264</v>
@@ -7512,7 +7512,7 @@
         <v>265</v>
       </c>
       <c r="D70" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="E70" t="s">
         <v>267</v>
@@ -7527,30 +7527,30 @@
         <v>25704</v>
       </c>
       <c r="J70" t="s">
+        <v>694</v>
+      </c>
+      <c r="K70" t="s">
+        <v>396</v>
+      </c>
+      <c r="L70" t="s">
+        <v>388</v>
+      </c>
+      <c r="M70" t="s">
+        <v>398</v>
+      </c>
+      <c r="P70" t="s">
+        <v>399</v>
+      </c>
+      <c r="Q70" s="3" t="s">
         <v>695</v>
       </c>
-      <c r="K70" t="s">
-        <v>397</v>
-      </c>
-      <c r="L70" t="s">
-        <v>389</v>
-      </c>
-      <c r="M70" t="s">
-        <v>399</v>
-      </c>
-      <c r="P70" t="s">
-        <v>400</v>
-      </c>
-      <c r="Q70" s="3" t="s">
+      <c r="V70" t="s">
         <v>696</v>
-      </c>
-      <c r="V70" t="s">
-        <v>697</v>
       </c>
     </row>
     <row r="71" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B71" t="s">
         <v>264</v>
@@ -7559,7 +7559,7 @@
         <v>265</v>
       </c>
       <c r="D71" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="E71" t="s">
         <v>267</v>
@@ -7574,30 +7574,30 @@
         <v>25718</v>
       </c>
       <c r="J71" t="s">
+        <v>699</v>
+      </c>
+      <c r="K71" t="s">
+        <v>396</v>
+      </c>
+      <c r="L71" t="s">
+        <v>388</v>
+      </c>
+      <c r="M71" t="s">
+        <v>398</v>
+      </c>
+      <c r="P71" t="s">
+        <v>399</v>
+      </c>
+      <c r="Q71" s="3" t="s">
         <v>700</v>
       </c>
-      <c r="K71" t="s">
-        <v>397</v>
-      </c>
-      <c r="L71" t="s">
-        <v>389</v>
-      </c>
-      <c r="M71" t="s">
-        <v>399</v>
-      </c>
-      <c r="P71" t="s">
-        <v>400</v>
-      </c>
-      <c r="Q71" s="3" t="s">
+      <c r="V71" t="s">
         <v>701</v>
-      </c>
-      <c r="V71" t="s">
-        <v>702</v>
       </c>
     </row>
     <row r="72" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B72" t="s">
         <v>264</v>
@@ -7606,7 +7606,7 @@
         <v>265</v>
       </c>
       <c r="D72" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="E72" t="s">
         <v>267</v>
@@ -7621,30 +7621,30 @@
         <v>25719</v>
       </c>
       <c r="J72" t="s">
+        <v>704</v>
+      </c>
+      <c r="K72" t="s">
+        <v>396</v>
+      </c>
+      <c r="L72" t="s">
+        <v>388</v>
+      </c>
+      <c r="M72" t="s">
+        <v>398</v>
+      </c>
+      <c r="P72" t="s">
+        <v>399</v>
+      </c>
+      <c r="Q72" s="3" t="s">
         <v>705</v>
       </c>
-      <c r="K72" t="s">
-        <v>397</v>
-      </c>
-      <c r="L72" t="s">
-        <v>389</v>
-      </c>
-      <c r="M72" t="s">
-        <v>399</v>
-      </c>
-      <c r="P72" t="s">
-        <v>400</v>
-      </c>
-      <c r="Q72" s="3" t="s">
+      <c r="V72" t="s">
         <v>706</v>
-      </c>
-      <c r="V72" t="s">
-        <v>707</v>
       </c>
     </row>
     <row r="73" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B73" t="s">
         <v>264</v>
@@ -7653,7 +7653,7 @@
         <v>265</v>
       </c>
       <c r="D73" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="E73" t="s">
         <v>267</v>
@@ -7668,30 +7668,30 @@
         <v>25740</v>
       </c>
       <c r="J73" t="s">
+        <v>709</v>
+      </c>
+      <c r="K73" t="s">
+        <v>396</v>
+      </c>
+      <c r="L73" t="s">
+        <v>388</v>
+      </c>
+      <c r="M73" t="s">
+        <v>398</v>
+      </c>
+      <c r="P73" t="s">
+        <v>399</v>
+      </c>
+      <c r="Q73" s="3" t="s">
         <v>710</v>
       </c>
-      <c r="K73" t="s">
-        <v>397</v>
-      </c>
-      <c r="L73" t="s">
-        <v>389</v>
-      </c>
-      <c r="M73" t="s">
-        <v>399</v>
-      </c>
-      <c r="P73" t="s">
-        <v>400</v>
-      </c>
-      <c r="Q73" s="3" t="s">
+      <c r="V73" t="s">
         <v>711</v>
-      </c>
-      <c r="V73" t="s">
-        <v>712</v>
       </c>
     </row>
     <row r="74" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B74" t="s">
         <v>264</v>
@@ -7700,7 +7700,7 @@
         <v>265</v>
       </c>
       <c r="D74" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="E74" t="s">
         <v>267</v>
@@ -7715,30 +7715,30 @@
         <v>25765</v>
       </c>
       <c r="J74" t="s">
+        <v>714</v>
+      </c>
+      <c r="K74" t="s">
+        <v>396</v>
+      </c>
+      <c r="L74" t="s">
+        <v>388</v>
+      </c>
+      <c r="M74" t="s">
+        <v>398</v>
+      </c>
+      <c r="P74" t="s">
+        <v>399</v>
+      </c>
+      <c r="Q74" s="3" t="s">
         <v>715</v>
       </c>
-      <c r="K74" t="s">
-        <v>397</v>
-      </c>
-      <c r="L74" t="s">
-        <v>389</v>
-      </c>
-      <c r="M74" t="s">
-        <v>399</v>
-      </c>
-      <c r="P74" t="s">
-        <v>400</v>
-      </c>
-      <c r="Q74" s="3" t="s">
+      <c r="V74" t="s">
         <v>716</v>
-      </c>
-      <c r="V74" t="s">
-        <v>717</v>
       </c>
     </row>
     <row r="75" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B75" t="s">
         <v>264</v>
@@ -7747,7 +7747,7 @@
         <v>265</v>
       </c>
       <c r="D75" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="E75" t="s">
         <v>267</v>
@@ -7762,30 +7762,30 @@
         <v>25824</v>
       </c>
       <c r="J75" t="s">
+        <v>719</v>
+      </c>
+      <c r="K75" t="s">
+        <v>396</v>
+      </c>
+      <c r="L75" t="s">
+        <v>388</v>
+      </c>
+      <c r="M75" t="s">
+        <v>398</v>
+      </c>
+      <c r="P75" t="s">
+        <v>399</v>
+      </c>
+      <c r="Q75" s="3" t="s">
         <v>720</v>
       </c>
-      <c r="K75" t="s">
-        <v>397</v>
-      </c>
-      <c r="L75" t="s">
-        <v>389</v>
-      </c>
-      <c r="M75" t="s">
-        <v>399</v>
-      </c>
-      <c r="P75" t="s">
-        <v>400</v>
-      </c>
-      <c r="Q75" s="3" t="s">
+      <c r="V75" t="s">
         <v>721</v>
-      </c>
-      <c r="V75" t="s">
-        <v>722</v>
       </c>
     </row>
     <row r="76" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B76" t="s">
         <v>264</v>
@@ -7794,7 +7794,7 @@
         <v>265</v>
       </c>
       <c r="D76" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="E76" t="s">
         <v>267</v>
@@ -7809,30 +7809,30 @@
         <v>25866</v>
       </c>
       <c r="J76" t="s">
+        <v>724</v>
+      </c>
+      <c r="K76" t="s">
+        <v>396</v>
+      </c>
+      <c r="L76" t="s">
+        <v>388</v>
+      </c>
+      <c r="M76" t="s">
+        <v>398</v>
+      </c>
+      <c r="P76" t="s">
+        <v>399</v>
+      </c>
+      <c r="Q76" s="3" t="s">
         <v>725</v>
       </c>
-      <c r="K76" t="s">
-        <v>397</v>
-      </c>
-      <c r="L76" t="s">
-        <v>389</v>
-      </c>
-      <c r="M76" t="s">
-        <v>399</v>
-      </c>
-      <c r="P76" t="s">
-        <v>400</v>
-      </c>
-      <c r="Q76" s="3" t="s">
+      <c r="V76" t="s">
         <v>726</v>
-      </c>
-      <c r="V76" t="s">
-        <v>727</v>
       </c>
     </row>
     <row r="77" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B77" t="s">
         <v>264</v>
@@ -7841,7 +7841,7 @@
         <v>265</v>
       </c>
       <c r="D77" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E77" t="s">
         <v>267</v>
@@ -7856,30 +7856,30 @@
         <v>25887</v>
       </c>
       <c r="J77" t="s">
+        <v>729</v>
+      </c>
+      <c r="K77" t="s">
+        <v>396</v>
+      </c>
+      <c r="L77" t="s">
+        <v>388</v>
+      </c>
+      <c r="M77" t="s">
+        <v>398</v>
+      </c>
+      <c r="P77" t="s">
+        <v>399</v>
+      </c>
+      <c r="Q77" s="3" t="s">
         <v>730</v>
       </c>
-      <c r="K77" t="s">
-        <v>397</v>
-      </c>
-      <c r="L77" t="s">
-        <v>389</v>
-      </c>
-      <c r="M77" t="s">
-        <v>399</v>
-      </c>
-      <c r="P77" t="s">
-        <v>400</v>
-      </c>
-      <c r="Q77" s="3" t="s">
+      <c r="V77" t="s">
         <v>731</v>
-      </c>
-      <c r="V77" t="s">
-        <v>732</v>
       </c>
     </row>
     <row r="78" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B78" t="s">
         <v>264</v>
@@ -7888,7 +7888,7 @@
         <v>265</v>
       </c>
       <c r="D78" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="E78" t="s">
         <v>267</v>
@@ -7903,30 +7903,30 @@
         <v>25915</v>
       </c>
       <c r="J78" t="s">
+        <v>734</v>
+      </c>
+      <c r="K78" t="s">
+        <v>396</v>
+      </c>
+      <c r="L78" t="s">
+        <v>388</v>
+      </c>
+      <c r="M78" t="s">
+        <v>398</v>
+      </c>
+      <c r="P78" t="s">
+        <v>399</v>
+      </c>
+      <c r="Q78" s="3" t="s">
         <v>735</v>
       </c>
-      <c r="K78" t="s">
-        <v>397</v>
-      </c>
-      <c r="L78" t="s">
-        <v>389</v>
-      </c>
-      <c r="M78" t="s">
-        <v>399</v>
-      </c>
-      <c r="P78" t="s">
-        <v>400</v>
-      </c>
-      <c r="Q78" s="3" t="s">
+      <c r="V78" t="s">
         <v>736</v>
-      </c>
-      <c r="V78" t="s">
-        <v>737</v>
       </c>
     </row>
     <row r="79" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B79" t="s">
         <v>264</v>
@@ -7935,7 +7935,7 @@
         <v>265</v>
       </c>
       <c r="D79" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="E79" t="s">
         <v>267</v>
@@ -7950,30 +7950,30 @@
         <v>25950</v>
       </c>
       <c r="J79" t="s">
+        <v>739</v>
+      </c>
+      <c r="K79" t="s">
+        <v>396</v>
+      </c>
+      <c r="L79" t="s">
+        <v>388</v>
+      </c>
+      <c r="M79" t="s">
+        <v>398</v>
+      </c>
+      <c r="P79" t="s">
+        <v>399</v>
+      </c>
+      <c r="Q79" s="3" t="s">
         <v>740</v>
       </c>
-      <c r="K79" t="s">
-        <v>397</v>
-      </c>
-      <c r="L79" t="s">
-        <v>389</v>
-      </c>
-      <c r="M79" t="s">
-        <v>399</v>
-      </c>
-      <c r="P79" t="s">
-        <v>400</v>
-      </c>
-      <c r="Q79" s="3" t="s">
+      <c r="V79" t="s">
         <v>741</v>
-      </c>
-      <c r="V79" t="s">
-        <v>742</v>
       </c>
     </row>
     <row r="80" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="B80" t="s">
         <v>264</v>
@@ -7982,7 +7982,7 @@
         <v>265</v>
       </c>
       <c r="D80" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="E80" t="s">
         <v>267</v>
@@ -7997,30 +7997,30 @@
         <v>25971</v>
       </c>
       <c r="J80" t="s">
+        <v>744</v>
+      </c>
+      <c r="K80" t="s">
+        <v>396</v>
+      </c>
+      <c r="L80" t="s">
+        <v>388</v>
+      </c>
+      <c r="M80" t="s">
+        <v>398</v>
+      </c>
+      <c r="P80" t="s">
+        <v>399</v>
+      </c>
+      <c r="Q80" s="3" t="s">
         <v>745</v>
       </c>
-      <c r="K80" t="s">
-        <v>397</v>
-      </c>
-      <c r="L80" t="s">
-        <v>389</v>
-      </c>
-      <c r="M80" t="s">
-        <v>399</v>
-      </c>
-      <c r="P80" t="s">
-        <v>400</v>
-      </c>
-      <c r="Q80" s="3" t="s">
+      <c r="V80" t="s">
         <v>746</v>
-      </c>
-      <c r="V80" t="s">
-        <v>747</v>
       </c>
     </row>
     <row r="81" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B81" t="s">
         <v>264</v>
@@ -8029,7 +8029,7 @@
         <v>265</v>
       </c>
       <c r="D81" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="E81" t="s">
         <v>267</v>
@@ -8044,30 +8044,30 @@
         <v>25999</v>
       </c>
       <c r="J81" t="s">
+        <v>749</v>
+      </c>
+      <c r="K81" t="s">
+        <v>396</v>
+      </c>
+      <c r="L81" t="s">
+        <v>388</v>
+      </c>
+      <c r="M81" t="s">
+        <v>398</v>
+      </c>
+      <c r="P81" t="s">
+        <v>399</v>
+      </c>
+      <c r="Q81" s="3" t="s">
         <v>750</v>
       </c>
-      <c r="K81" t="s">
-        <v>397</v>
-      </c>
-      <c r="L81" t="s">
-        <v>389</v>
-      </c>
-      <c r="M81" t="s">
-        <v>399</v>
-      </c>
-      <c r="P81" t="s">
-        <v>400</v>
-      </c>
-      <c r="Q81" s="3" t="s">
+      <c r="V81" t="s">
         <v>751</v>
-      </c>
-      <c r="V81" t="s">
-        <v>752</v>
       </c>
     </row>
     <row r="82" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B82" t="s">
         <v>264</v>
@@ -8076,7 +8076,7 @@
         <v>265</v>
       </c>
       <c r="D82" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="E82" t="s">
         <v>267</v>
@@ -8091,30 +8091,30 @@
         <v>26027</v>
       </c>
       <c r="J82" t="s">
+        <v>754</v>
+      </c>
+      <c r="K82" t="s">
+        <v>396</v>
+      </c>
+      <c r="L82" t="s">
+        <v>388</v>
+      </c>
+      <c r="M82" t="s">
+        <v>398</v>
+      </c>
+      <c r="P82" t="s">
+        <v>399</v>
+      </c>
+      <c r="Q82" s="3" t="s">
         <v>755</v>
       </c>
-      <c r="K82" t="s">
-        <v>397</v>
-      </c>
-      <c r="L82" t="s">
-        <v>389</v>
-      </c>
-      <c r="M82" t="s">
-        <v>399</v>
-      </c>
-      <c r="P82" t="s">
-        <v>400</v>
-      </c>
-      <c r="Q82" s="3" t="s">
+      <c r="V82" t="s">
         <v>756</v>
-      </c>
-      <c r="V82" t="s">
-        <v>757</v>
       </c>
     </row>
     <row r="83" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B83" t="s">
         <v>264</v>
@@ -8123,7 +8123,7 @@
         <v>265</v>
       </c>
       <c r="D83" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E83" t="s">
         <v>267</v>
@@ -8138,30 +8138,30 @@
         <v>26054</v>
       </c>
       <c r="J83" t="s">
+        <v>759</v>
+      </c>
+      <c r="K83" t="s">
+        <v>396</v>
+      </c>
+      <c r="L83" t="s">
+        <v>388</v>
+      </c>
+      <c r="M83" t="s">
+        <v>398</v>
+      </c>
+      <c r="P83" t="s">
+        <v>399</v>
+      </c>
+      <c r="Q83" s="3" t="s">
         <v>760</v>
       </c>
-      <c r="K83" t="s">
-        <v>397</v>
-      </c>
-      <c r="L83" t="s">
-        <v>389</v>
-      </c>
-      <c r="M83" t="s">
-        <v>399</v>
-      </c>
-      <c r="P83" t="s">
-        <v>400</v>
-      </c>
-      <c r="Q83" s="3" t="s">
+      <c r="V83" t="s">
         <v>761</v>
-      </c>
-      <c r="V83" t="s">
-        <v>762</v>
       </c>
     </row>
     <row r="84" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B84" t="s">
         <v>264</v>
@@ -8170,7 +8170,7 @@
         <v>265</v>
       </c>
       <c r="D84" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="E84" t="s">
         <v>267</v>
@@ -8185,30 +8185,30 @@
         <v>26076</v>
       </c>
       <c r="J84" t="s">
+        <v>764</v>
+      </c>
+      <c r="K84" t="s">
+        <v>396</v>
+      </c>
+      <c r="L84" t="s">
+        <v>388</v>
+      </c>
+      <c r="M84" t="s">
+        <v>398</v>
+      </c>
+      <c r="P84" t="s">
+        <v>399</v>
+      </c>
+      <c r="Q84" s="3" t="s">
         <v>765</v>
       </c>
-      <c r="K84" t="s">
-        <v>397</v>
-      </c>
-      <c r="L84" t="s">
-        <v>389</v>
-      </c>
-      <c r="M84" t="s">
-        <v>399</v>
-      </c>
-      <c r="P84" t="s">
-        <v>400</v>
-      </c>
-      <c r="Q84" s="3" t="s">
+      <c r="V84" t="s">
         <v>766</v>
-      </c>
-      <c r="V84" t="s">
-        <v>767</v>
       </c>
     </row>
     <row r="85" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="B85" t="s">
         <v>264</v>
@@ -8217,7 +8217,7 @@
         <v>265</v>
       </c>
       <c r="D85" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="E85" t="s">
         <v>267</v>
@@ -8232,30 +8232,30 @@
         <v>26104</v>
       </c>
       <c r="J85" t="s">
+        <v>769</v>
+      </c>
+      <c r="K85" t="s">
+        <v>396</v>
+      </c>
+      <c r="L85" t="s">
+        <v>388</v>
+      </c>
+      <c r="M85" t="s">
+        <v>398</v>
+      </c>
+      <c r="P85" t="s">
+        <v>399</v>
+      </c>
+      <c r="Q85" s="3" t="s">
         <v>770</v>
       </c>
-      <c r="K85" t="s">
-        <v>397</v>
-      </c>
-      <c r="L85" t="s">
-        <v>389</v>
-      </c>
-      <c r="M85" t="s">
-        <v>399</v>
-      </c>
-      <c r="P85" t="s">
-        <v>400</v>
-      </c>
-      <c r="Q85" s="3" t="s">
+      <c r="V85" t="s">
         <v>771</v>
-      </c>
-      <c r="V85" t="s">
-        <v>772</v>
       </c>
     </row>
     <row r="86" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="B86" t="s">
         <v>264</v>
@@ -8264,7 +8264,7 @@
         <v>265</v>
       </c>
       <c r="D86" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="E86" t="s">
         <v>267</v>
@@ -8279,30 +8279,30 @@
         <v>26139</v>
       </c>
       <c r="J86" t="s">
+        <v>774</v>
+      </c>
+      <c r="K86" t="s">
+        <v>396</v>
+      </c>
+      <c r="L86" t="s">
+        <v>388</v>
+      </c>
+      <c r="M86" t="s">
+        <v>398</v>
+      </c>
+      <c r="P86" t="s">
+        <v>399</v>
+      </c>
+      <c r="Q86" s="3" t="s">
         <v>775</v>
       </c>
-      <c r="K86" t="s">
-        <v>397</v>
-      </c>
-      <c r="L86" t="s">
-        <v>389</v>
-      </c>
-      <c r="M86" t="s">
-        <v>399</v>
-      </c>
-      <c r="P86" t="s">
-        <v>400</v>
-      </c>
-      <c r="Q86" s="3" t="s">
+      <c r="V86" t="s">
         <v>776</v>
-      </c>
-      <c r="V86" t="s">
-        <v>777</v>
       </c>
     </row>
     <row r="87" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B87" t="s">
         <v>264</v>
@@ -8311,7 +8311,7 @@
         <v>265</v>
       </c>
       <c r="D87" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="E87" t="s">
         <v>267</v>
@@ -8326,30 +8326,30 @@
         <v>26265</v>
       </c>
       <c r="J87" t="s">
+        <v>779</v>
+      </c>
+      <c r="K87" t="s">
+        <v>396</v>
+      </c>
+      <c r="L87" t="s">
+        <v>388</v>
+      </c>
+      <c r="M87" t="s">
+        <v>398</v>
+      </c>
+      <c r="P87" t="s">
+        <v>399</v>
+      </c>
+      <c r="Q87" s="3" t="s">
         <v>780</v>
       </c>
-      <c r="K87" t="s">
-        <v>397</v>
-      </c>
-      <c r="L87" t="s">
-        <v>389</v>
-      </c>
-      <c r="M87" t="s">
-        <v>399</v>
-      </c>
-      <c r="P87" t="s">
-        <v>400</v>
-      </c>
-      <c r="Q87" s="3" t="s">
+      <c r="V87" t="s">
         <v>781</v>
-      </c>
-      <c r="V87" t="s">
-        <v>782</v>
       </c>
     </row>
     <row r="88" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="B88" t="s">
         <v>264</v>
@@ -8358,7 +8358,7 @@
         <v>265</v>
       </c>
       <c r="D88" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="E88" t="s">
         <v>267</v>
@@ -8373,30 +8373,30 @@
         <v>26307</v>
       </c>
       <c r="J88" t="s">
+        <v>784</v>
+      </c>
+      <c r="K88" t="s">
+        <v>396</v>
+      </c>
+      <c r="L88" t="s">
+        <v>388</v>
+      </c>
+      <c r="M88" t="s">
+        <v>398</v>
+      </c>
+      <c r="P88" t="s">
+        <v>399</v>
+      </c>
+      <c r="Q88" s="3" t="s">
         <v>785</v>
       </c>
-      <c r="K88" t="s">
-        <v>397</v>
-      </c>
-      <c r="L88" t="s">
-        <v>389</v>
-      </c>
-      <c r="M88" t="s">
-        <v>399</v>
-      </c>
-      <c r="P88" t="s">
-        <v>400</v>
-      </c>
-      <c r="Q88" s="3" t="s">
+      <c r="V88" t="s">
         <v>786</v>
-      </c>
-      <c r="V88" t="s">
-        <v>787</v>
       </c>
     </row>
     <row r="89" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B89" t="s">
         <v>264</v>
@@ -8405,7 +8405,7 @@
         <v>265</v>
       </c>
       <c r="D89" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="E89" t="s">
         <v>267</v>
@@ -8420,30 +8420,30 @@
         <v>26370</v>
       </c>
       <c r="J89" t="s">
+        <v>789</v>
+      </c>
+      <c r="K89" t="s">
+        <v>396</v>
+      </c>
+      <c r="L89" t="s">
+        <v>388</v>
+      </c>
+      <c r="M89" t="s">
+        <v>398</v>
+      </c>
+      <c r="P89" t="s">
+        <v>399</v>
+      </c>
+      <c r="Q89" s="3" t="s">
         <v>790</v>
       </c>
-      <c r="K89" t="s">
-        <v>397</v>
-      </c>
-      <c r="L89" t="s">
-        <v>389</v>
-      </c>
-      <c r="M89" t="s">
-        <v>399</v>
-      </c>
-      <c r="P89" t="s">
-        <v>400</v>
-      </c>
-      <c r="Q89" s="3" t="s">
+      <c r="V89" t="s">
         <v>791</v>
-      </c>
-      <c r="V89" t="s">
-        <v>792</v>
       </c>
     </row>
     <row r="90" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B90" t="s">
         <v>264</v>
@@ -8452,7 +8452,7 @@
         <v>265</v>
       </c>
       <c r="D90" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="E90" t="s">
         <v>267</v>
@@ -8467,30 +8467,30 @@
         <v>26420</v>
       </c>
       <c r="J90" t="s">
+        <v>794</v>
+      </c>
+      <c r="K90" t="s">
+        <v>396</v>
+      </c>
+      <c r="L90" t="s">
+        <v>388</v>
+      </c>
+      <c r="M90" t="s">
+        <v>398</v>
+      </c>
+      <c r="P90" t="s">
+        <v>399</v>
+      </c>
+      <c r="Q90" s="3" t="s">
         <v>795</v>
       </c>
-      <c r="K90" t="s">
-        <v>397</v>
-      </c>
-      <c r="L90" t="s">
-        <v>389</v>
-      </c>
-      <c r="M90" t="s">
-        <v>399</v>
-      </c>
-      <c r="P90" t="s">
-        <v>400</v>
-      </c>
-      <c r="Q90" s="3" t="s">
+      <c r="V90" t="s">
         <v>796</v>
-      </c>
-      <c r="V90" t="s">
-        <v>797</v>
       </c>
     </row>
     <row r="91" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="B91" t="s">
         <v>264</v>
@@ -8499,7 +8499,7 @@
         <v>265</v>
       </c>
       <c r="D91" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="E91" t="s">
         <v>267</v>
@@ -8514,30 +8514,30 @@
         <v>26608</v>
       </c>
       <c r="J91" t="s">
+        <v>799</v>
+      </c>
+      <c r="K91" t="s">
+        <v>396</v>
+      </c>
+      <c r="L91" t="s">
+        <v>388</v>
+      </c>
+      <c r="M91" t="s">
+        <v>398</v>
+      </c>
+      <c r="P91" t="s">
+        <v>399</v>
+      </c>
+      <c r="Q91" s="3" t="s">
         <v>800</v>
       </c>
-      <c r="K91" t="s">
-        <v>397</v>
-      </c>
-      <c r="L91" t="s">
-        <v>389</v>
-      </c>
-      <c r="M91" t="s">
-        <v>399</v>
-      </c>
-      <c r="P91" t="s">
-        <v>400</v>
-      </c>
-      <c r="Q91" s="3" t="s">
+      <c r="V91" t="s">
         <v>801</v>
-      </c>
-      <c r="V91" t="s">
-        <v>802</v>
       </c>
     </row>
     <row r="92" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="B92" t="s">
         <v>264</v>
@@ -8546,7 +8546,7 @@
         <v>265</v>
       </c>
       <c r="D92" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="E92" t="s">
         <v>267</v>
@@ -8561,30 +8561,30 @@
         <v>26785</v>
       </c>
       <c r="J92" t="s">
+        <v>804</v>
+      </c>
+      <c r="K92" t="s">
+        <v>396</v>
+      </c>
+      <c r="L92" t="s">
+        <v>388</v>
+      </c>
+      <c r="M92" t="s">
+        <v>398</v>
+      </c>
+      <c r="P92" t="s">
+        <v>399</v>
+      </c>
+      <c r="Q92" s="3" t="s">
         <v>805</v>
       </c>
-      <c r="K92" t="s">
-        <v>397</v>
-      </c>
-      <c r="L92" t="s">
-        <v>389</v>
-      </c>
-      <c r="M92" t="s">
-        <v>399</v>
-      </c>
-      <c r="P92" t="s">
-        <v>400</v>
-      </c>
-      <c r="Q92" s="3" t="s">
+      <c r="V92" t="s">
         <v>806</v>
-      </c>
-      <c r="V92" t="s">
-        <v>807</v>
       </c>
     </row>
     <row r="93" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B93" t="s">
         <v>264</v>
@@ -8593,7 +8593,7 @@
         <v>265</v>
       </c>
       <c r="D93" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="E93" t="s">
         <v>267</v>
@@ -8602,7 +8602,7 @@
         <v>56</v>
       </c>
       <c r="H93" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="I93">
         <v>1969</v>
@@ -8614,33 +8614,33 @@
         <v>269</v>
       </c>
       <c r="L93" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="M93" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="N93" t="s">
+        <v>810</v>
+      </c>
+      <c r="O93" t="s">
         <v>811</v>
-      </c>
-      <c r="O93" t="s">
-        <v>812</v>
       </c>
       <c r="P93" t="s">
         <v>272</v>
       </c>
       <c r="Q93" s="3" t="s">
+        <v>812</v>
+      </c>
+      <c r="U93" t="s">
         <v>813</v>
       </c>
-      <c r="U93" t="s">
+      <c r="V93" t="s">
         <v>814</v>
-      </c>
-      <c r="V93" t="s">
-        <v>815</v>
       </c>
     </row>
     <row r="94" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="B94" t="s">
         <v>264</v>
@@ -8649,7 +8649,7 @@
         <v>265</v>
       </c>
       <c r="D94" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="E94" t="s">
         <v>267</v>
@@ -8661,39 +8661,39 @@
         <v>177</v>
       </c>
       <c r="I94" s="5" t="s">
+        <v>817</v>
+      </c>
+      <c r="J94" t="s">
         <v>818</v>
       </c>
-      <c r="J94" t="s">
+      <c r="K94" t="s">
+        <v>276</v>
+      </c>
+      <c r="L94" t="s">
         <v>819</v>
       </c>
-      <c r="K94" t="s">
-        <v>277</v>
-      </c>
-      <c r="L94" t="s">
+      <c r="M94" t="s">
+        <v>330</v>
+      </c>
+      <c r="O94" t="s">
         <v>820</v>
-      </c>
-      <c r="M94" t="s">
-        <v>331</v>
-      </c>
-      <c r="O94" t="s">
-        <v>821</v>
       </c>
       <c r="P94" t="s">
         <v>272</v>
       </c>
       <c r="Q94" s="3" t="s">
+        <v>821</v>
+      </c>
+      <c r="U94" t="s">
         <v>822</v>
       </c>
-      <c r="U94" t="s">
+      <c r="V94" t="s">
         <v>823</v>
-      </c>
-      <c r="V94" t="s">
-        <v>824</v>
       </c>
     </row>
     <row r="95" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="B95" t="s">
         <v>264</v>
@@ -8702,7 +8702,7 @@
         <v>265</v>
       </c>
       <c r="D95" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="E95" t="s">
         <v>267</v>
@@ -8723,30 +8723,30 @@
         <v>126</v>
       </c>
       <c r="K95" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="L95" t="s">
         <v>270</v>
       </c>
       <c r="M95" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="P95" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="Q95" s="3" t="s">
+        <v>826</v>
+      </c>
+      <c r="U95" t="s">
+        <v>560</v>
+      </c>
+      <c r="V95" t="s">
         <v>827</v>
-      </c>
-      <c r="U95" t="s">
-        <v>561</v>
-      </c>
-      <c r="V95" t="s">
-        <v>828</v>
       </c>
     </row>
     <row r="96" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="B96" t="s">
         <v>264</v>
@@ -8755,7 +8755,7 @@
         <v>265</v>
       </c>
       <c r="D96" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="E96" t="s">
         <v>267</v>
@@ -8776,33 +8776,33 @@
         <v>130</v>
       </c>
       <c r="K96" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="L96" t="s">
         <v>270</v>
       </c>
       <c r="M96" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="O96" t="s">
         <v>86</v>
       </c>
       <c r="P96" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="Q96" s="3" t="s">
+        <v>830</v>
+      </c>
+      <c r="U96" t="s">
         <v>831</v>
       </c>
-      <c r="U96" t="s">
+      <c r="V96" t="s">
         <v>832</v>
-      </c>
-      <c r="V96" t="s">
-        <v>833</v>
       </c>
     </row>
     <row r="97" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B97" t="s">
         <v>264</v>
@@ -8811,10 +8811,10 @@
         <v>265</v>
       </c>
       <c r="D97" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="E97" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="I97">
         <v>1973</v>
@@ -8823,10 +8823,10 @@
         <v>160</v>
       </c>
       <c r="K97" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="M97" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="N97" t="s">
         <v>32</v>
@@ -8835,16 +8835,16 @@
         <v>272</v>
       </c>
       <c r="Q97" s="3" t="s">
+        <v>835</v>
+      </c>
+      <c r="R97" t="s">
         <v>836</v>
       </c>
-      <c r="R97" t="s">
+      <c r="U97" t="s">
         <v>837</v>
       </c>
-      <c r="U97" t="s">
+      <c r="V97" t="s">
         <v>838</v>
-      </c>
-      <c r="V97" t="s">
-        <v>839</v>
       </c>
     </row>
   </sheetData>
@@ -8958,9 +8958,9 @@
     <hyperlink ref="Q97" r:id="rId96" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId97"/>
   <tableParts count="1">
-    <tablePart r:id="rId97"/>
+    <tablePart r:id="rId98"/>
   </tableParts>
 </worksheet>
 </file>
@@ -8978,275 +8978,275 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
+        <v>839</v>
+      </c>
+      <c r="B1" s="9" t="s">
         <v>840</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="C1" s="9" t="s">
         <v>841</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="D1" s="9" t="s">
         <v>842</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>843</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
+        <v>843</v>
+      </c>
+      <c r="B2" s="10" t="s">
         <v>844</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="C2" s="10" t="s">
         <v>845</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>846</v>
       </c>
       <c r="D2" s="10"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>244</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="D3" s="10"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="10"/>
       <c r="D4" s="10" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
+        <v>850</v>
+      </c>
+      <c r="B5" s="10" t="s">
         <v>851</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="C5" s="10" t="s">
         <v>852</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>853</v>
       </c>
       <c r="D5" s="10"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>261</v>
       </c>
       <c r="C6" s="10"/>
       <c r="D6" s="10" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
+        <v>855</v>
+      </c>
+      <c r="B7" s="10" t="s">
         <v>856</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="C7" s="10" t="s">
         <v>857</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>858</v>
       </c>
       <c r="D7" s="10"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="10" t="s">
+        <v>858</v>
+      </c>
+      <c r="B8" s="10" t="s">
         <v>859</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>860</v>
       </c>
       <c r="C8" s="10"/>
       <c r="D8" s="10"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
+        <v>860</v>
+      </c>
+      <c r="B9" s="10" t="s">
         <v>861</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>862</v>
       </c>
       <c r="C9" s="10"/>
       <c r="D9" s="10" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="10" t="s">
+        <v>863</v>
+      </c>
+      <c r="B10" s="10" t="s">
         <v>864</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>865</v>
       </c>
       <c r="C10" s="10"/>
       <c r="D10" s="10" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
+        <v>866</v>
+      </c>
+      <c r="B11" s="10" t="s">
         <v>867</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>868</v>
       </c>
       <c r="C11" s="10"/>
       <c r="D11" s="10" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="10" t="s">
+        <v>869</v>
+      </c>
+      <c r="B12" s="10" t="s">
         <v>870</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>871</v>
       </c>
       <c r="C12" s="10"/>
       <c r="D12" s="10"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="10" t="s">
+        <v>871</v>
+      </c>
+      <c r="B13" s="10" t="s">
         <v>872</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="C13" s="10" t="s">
         <v>873</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>874</v>
       </c>
       <c r="D13" s="10"/>
     </row>
     <row r="14" spans="1:4" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="10" t="s">
+        <v>874</v>
+      </c>
+      <c r="B14" s="10" t="s">
         <v>875</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="C14" s="10" t="s">
         <v>876</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>877</v>
       </c>
       <c r="D14" s="10"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="10" t="s">
+        <v>877</v>
+      </c>
+      <c r="B15" s="10" t="s">
         <v>878</v>
       </c>
-      <c r="B15" s="10" t="s">
+      <c r="C15" s="10" t="s">
         <v>879</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>880</v>
       </c>
       <c r="D15" s="10"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="10" t="s">
+        <v>880</v>
+      </c>
+      <c r="B16" s="10" t="s">
         <v>881</v>
       </c>
-      <c r="B16" s="10" t="s">
-        <v>882</v>
-      </c>
       <c r="C16" s="10" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="D16" s="10"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="B17" s="10" t="s">
         <v>243</v>
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="10" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="10" t="s">
+        <v>884</v>
+      </c>
+      <c r="B18" s="10" t="s">
         <v>885</v>
       </c>
-      <c r="B18" s="10" t="s">
+      <c r="C18" s="10" t="s">
         <v>886</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>887</v>
       </c>
       <c r="D18" s="10"/>
     </row>
     <row r="19" spans="1:4" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
+        <v>887</v>
+      </c>
+      <c r="B19" s="10" t="s">
         <v>888</v>
-      </c>
-      <c r="B19" s="10" t="s">
-        <v>889</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="10" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="10" t="s">
+        <v>890</v>
+      </c>
+      <c r="B20" s="10" t="s">
         <v>891</v>
       </c>
-      <c r="B20" s="10" t="s">
+      <c r="C20" s="10" t="s">
         <v>892</v>
-      </c>
-      <c r="C20" s="10" t="s">
-        <v>893</v>
       </c>
       <c r="D20" s="10"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
+        <v>893</v>
+      </c>
+      <c r="B21" s="10" t="s">
         <v>894</v>
       </c>
-      <c r="B21" s="10" t="s">
+      <c r="C21" s="10" t="s">
         <v>895</v>
-      </c>
-      <c r="C21" s="10" t="s">
-        <v>896</v>
       </c>
       <c r="D21" s="10"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="10" t="s">
+        <v>896</v>
+      </c>
+      <c r="B22" s="10" t="s">
         <v>897</v>
       </c>
-      <c r="B22" s="10" t="s">
+      <c r="C22" s="10" t="s">
         <v>898</v>
-      </c>
-      <c r="C22" s="10" t="s">
-        <v>899</v>
       </c>
       <c r="D22" s="10"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
+        <v>899</v>
+      </c>
+      <c r="B23" s="10" t="s">
         <v>900</v>
       </c>
-      <c r="B23" s="10" t="s">
+      <c r="C23" s="10" t="s">
         <v>901</v>
-      </c>
-      <c r="C23" s="10" t="s">
-        <v>902</v>
       </c>
       <c r="D23" s="10"/>
     </row>
@@ -9280,58 +9280,58 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
+        <v>902</v>
+      </c>
+      <c r="B1" s="9" t="s">
         <v>903</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="C1" s="9" t="s">
         <v>904</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="D1" s="9" t="s">
         <v>905</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="E1" t="s">
         <v>906</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>907</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" s="9" t="s">
         <v>908</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="H1" t="s">
         <v>909</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>910</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>911</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" s="9" t="s">
         <v>912</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="L1" s="9" t="s">
         <v>913</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="M1" s="9" t="s">
         <v>914</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="N1" s="9" t="s">
         <v>915</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="O1" s="9" t="s">
         <v>916</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="P1" s="9" t="s">
         <v>917</v>
       </c>
-      <c r="P1" s="9" t="s">
+      <c r="Q1" s="9" t="s">
         <v>918</v>
       </c>
-      <c r="Q1" s="9" t="s">
+      <c r="R1" s="9" t="s">
         <v>919</v>
-      </c>
-      <c r="R1" s="9" t="s">
-        <v>920</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
@@ -9339,22 +9339,22 @@
         <v>31</v>
       </c>
       <c r="B2" t="s">
+        <v>920</v>
+      </c>
+      <c r="C2" t="s">
         <v>921</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>922</v>
-      </c>
-      <c r="D2" t="s">
-        <v>923</v>
       </c>
       <c r="E2" t="s">
         <v>32</v>
       </c>
       <c r="F2" t="s">
+        <v>923</v>
+      </c>
+      <c r="G2" t="s">
         <v>924</v>
-      </c>
-      <c r="G2" t="s">
-        <v>925</v>
       </c>
       <c r="H2">
         <v>1893</v>
@@ -9363,25 +9363,25 @@
         <v>1976</v>
       </c>
       <c r="J2" t="s">
+        <v>925</v>
+      </c>
+      <c r="M2" t="s">
         <v>926</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>927</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>928</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>929</v>
-      </c>
-      <c r="P2" t="s">
-        <v>930</v>
       </c>
       <c r="Q2" s="4">
         <v>46297</v>
       </c>
       <c r="R2" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
@@ -9389,19 +9389,19 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
+        <v>920</v>
+      </c>
+      <c r="C3" t="s">
         <v>921</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>922</v>
-      </c>
-      <c r="D3" t="s">
-        <v>923</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="H3">
         <v>1921</v>
@@ -9410,22 +9410,22 @@
         <v>1993</v>
       </c>
       <c r="J3" t="s">
+        <v>932</v>
+      </c>
+      <c r="M3" t="s">
         <v>933</v>
       </c>
-      <c r="M3" t="s">
-        <v>934</v>
-      </c>
       <c r="O3" t="s">
+        <v>928</v>
+      </c>
+      <c r="P3" t="s">
         <v>929</v>
-      </c>
-      <c r="P3" t="s">
-        <v>930</v>
       </c>
       <c r="Q3" s="4">
         <v>46297</v>
       </c>
       <c r="R3" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
@@ -9433,19 +9433,19 @@
         <v>17</v>
       </c>
       <c r="B4" t="s">
+        <v>920</v>
+      </c>
+      <c r="C4" t="s">
         <v>921</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>922</v>
-      </c>
-      <c r="D4" t="s">
-        <v>923</v>
       </c>
       <c r="E4" t="s">
         <v>18</v>
       </c>
       <c r="F4" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="H4">
         <v>1938</v>
@@ -9454,42 +9454,42 @@
         <v>2021</v>
       </c>
       <c r="J4" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="O4" t="s">
+        <v>928</v>
+      </c>
+      <c r="P4" t="s">
         <v>929</v>
-      </c>
-      <c r="P4" t="s">
-        <v>930</v>
       </c>
       <c r="Q4" s="4">
         <v>46297</v>
       </c>
       <c r="R4" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>936</v>
+      </c>
+      <c r="B5" t="s">
+        <v>920</v>
+      </c>
+      <c r="C5" t="s">
+        <v>921</v>
+      </c>
+      <c r="D5" t="s">
+        <v>922</v>
+      </c>
+      <c r="E5" t="s">
+        <v>322</v>
+      </c>
+      <c r="F5" t="s">
         <v>937</v>
       </c>
-      <c r="B5" t="s">
-        <v>921</v>
-      </c>
-      <c r="C5" t="s">
-        <v>922</v>
-      </c>
-      <c r="D5" t="s">
-        <v>923</v>
-      </c>
-      <c r="E5" t="s">
-        <v>323</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>938</v>
-      </c>
-      <c r="G5" t="s">
-        <v>939</v>
       </c>
       <c r="H5">
         <v>1931</v>
@@ -9498,42 +9498,42 @@
         <v>2005</v>
       </c>
       <c r="M5" t="s">
+        <v>939</v>
+      </c>
+      <c r="N5" t="s">
         <v>940</v>
       </c>
-      <c r="N5" t="s">
-        <v>941</v>
-      </c>
       <c r="O5" t="s">
+        <v>928</v>
+      </c>
+      <c r="P5" t="s">
         <v>929</v>
-      </c>
-      <c r="P5" t="s">
-        <v>930</v>
       </c>
       <c r="Q5" s="4">
         <v>46297</v>
       </c>
       <c r="R5" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>941</v>
+      </c>
+      <c r="B6" t="s">
+        <v>920</v>
+      </c>
+      <c r="C6" t="s">
+        <v>921</v>
+      </c>
+      <c r="D6" t="s">
+        <v>922</v>
+      </c>
+      <c r="E6" t="s">
         <v>942</v>
       </c>
-      <c r="B6" t="s">
-        <v>921</v>
-      </c>
-      <c r="C6" t="s">
-        <v>922</v>
-      </c>
-      <c r="D6" t="s">
-        <v>923</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>943</v>
-      </c>
-      <c r="F6" t="s">
-        <v>944</v>
       </c>
       <c r="H6">
         <v>1960</v>
@@ -9542,16 +9542,16 @@
         <v>2023</v>
       </c>
       <c r="O6" t="s">
+        <v>928</v>
+      </c>
+      <c r="P6" t="s">
         <v>929</v>
-      </c>
-      <c r="P6" t="s">
-        <v>930</v>
       </c>
       <c r="Q6" s="4">
         <v>46297</v>
       </c>
       <c r="R6" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
@@ -9559,37 +9559,37 @@
         <v>64</v>
       </c>
       <c r="B7" t="s">
+        <v>920</v>
+      </c>
+      <c r="C7" t="s">
         <v>921</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>922</v>
-      </c>
-      <c r="D7" t="s">
-        <v>923</v>
       </c>
       <c r="E7" t="s">
         <v>65</v>
       </c>
       <c r="F7" t="s">
+        <v>944</v>
+      </c>
+      <c r="H7" t="s">
         <v>945</v>
       </c>
-      <c r="H7" t="s">
-        <v>946</v>
-      </c>
       <c r="I7" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="O7" t="s">
+        <v>928</v>
+      </c>
+      <c r="P7" t="s">
         <v>929</v>
-      </c>
-      <c r="P7" t="s">
-        <v>930</v>
       </c>
       <c r="Q7" s="4">
         <v>46297</v>
       </c>
       <c r="R7" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
@@ -9597,63 +9597,63 @@
         <v>41</v>
       </c>
       <c r="B8" t="s">
+        <v>920</v>
+      </c>
+      <c r="C8" t="s">
         <v>921</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>922</v>
-      </c>
-      <c r="D8" t="s">
-        <v>923</v>
       </c>
       <c r="E8" t="s">
         <v>42</v>
       </c>
       <c r="F8" t="s">
+        <v>946</v>
+      </c>
+      <c r="H8" t="s">
+        <v>945</v>
+      </c>
+      <c r="I8" t="s">
+        <v>945</v>
+      </c>
+      <c r="J8" t="s">
         <v>947</v>
       </c>
-      <c r="H8" t="s">
-        <v>946</v>
-      </c>
-      <c r="I8" t="s">
-        <v>946</v>
-      </c>
-      <c r="J8" t="s">
-        <v>948</v>
-      </c>
       <c r="O8" t="s">
+        <v>928</v>
+      </c>
+      <c r="P8" t="s">
         <v>929</v>
-      </c>
-      <c r="P8" t="s">
-        <v>930</v>
       </c>
       <c r="Q8" s="4">
         <v>46297</v>
       </c>
       <c r="R8" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>948</v>
+      </c>
+      <c r="B9" t="s">
+        <v>920</v>
+      </c>
+      <c r="C9" t="s">
+        <v>921</v>
+      </c>
+      <c r="D9" t="s">
+        <v>922</v>
+      </c>
+      <c r="E9" t="s">
+        <v>810</v>
+      </c>
+      <c r="F9" t="s">
         <v>949</v>
       </c>
-      <c r="B9" t="s">
-        <v>921</v>
-      </c>
-      <c r="C9" t="s">
-        <v>922</v>
-      </c>
-      <c r="D9" t="s">
-        <v>923</v>
-      </c>
-      <c r="E9" t="s">
-        <v>811</v>
-      </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>950</v>
-      </c>
-      <c r="G9" t="s">
-        <v>951</v>
       </c>
       <c r="H9">
         <v>1907</v>
@@ -9662,42 +9662,42 @@
         <v>1971</v>
       </c>
       <c r="M9" t="s">
+        <v>951</v>
+      </c>
+      <c r="N9" t="s">
         <v>952</v>
       </c>
-      <c r="N9" t="s">
-        <v>953</v>
-      </c>
       <c r="O9" t="s">
+        <v>928</v>
+      </c>
+      <c r="P9" t="s">
         <v>929</v>
-      </c>
-      <c r="P9" t="s">
-        <v>930</v>
       </c>
       <c r="Q9" s="4">
         <v>46297</v>
       </c>
       <c r="R9" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>953</v>
+      </c>
+      <c r="B10" t="s">
+        <v>920</v>
+      </c>
+      <c r="C10" t="s">
+        <v>921</v>
+      </c>
+      <c r="D10" t="s">
+        <v>922</v>
+      </c>
+      <c r="E10" t="s">
         <v>954</v>
       </c>
-      <c r="B10" t="s">
-        <v>921</v>
-      </c>
-      <c r="C10" t="s">
-        <v>922</v>
-      </c>
-      <c r="D10" t="s">
-        <v>923</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>955</v>
-      </c>
-      <c r="F10" t="s">
-        <v>956</v>
       </c>
       <c r="H10">
         <v>1898</v>
@@ -9706,45 +9706,45 @@
         <v>1975</v>
       </c>
       <c r="M10" t="s">
+        <v>956</v>
+      </c>
+      <c r="N10" t="s">
         <v>957</v>
       </c>
-      <c r="N10" t="s">
-        <v>958</v>
-      </c>
       <c r="O10" t="s">
+        <v>928</v>
+      </c>
+      <c r="P10" t="s">
         <v>929</v>
-      </c>
-      <c r="P10" t="s">
-        <v>930</v>
       </c>
       <c r="Q10" s="4">
         <v>46297</v>
       </c>
       <c r="R10" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>958</v>
+      </c>
+      <c r="B11" t="s">
+        <v>920</v>
+      </c>
+      <c r="C11" t="s">
+        <v>921</v>
+      </c>
+      <c r="D11" t="s">
+        <v>922</v>
+      </c>
+      <c r="E11" t="s">
         <v>959</v>
       </c>
-      <c r="B11" t="s">
-        <v>921</v>
-      </c>
-      <c r="C11" t="s">
-        <v>922</v>
-      </c>
-      <c r="D11" t="s">
-        <v>923</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>960</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>961</v>
-      </c>
-      <c r="G11" t="s">
-        <v>962</v>
       </c>
       <c r="H11">
         <v>1898</v>
@@ -9753,45 +9753,45 @@
         <v>1976</v>
       </c>
       <c r="M11" t="s">
+        <v>962</v>
+      </c>
+      <c r="N11" t="s">
         <v>963</v>
       </c>
-      <c r="N11" t="s">
-        <v>964</v>
-      </c>
       <c r="O11" t="s">
+        <v>928</v>
+      </c>
+      <c r="P11" t="s">
         <v>929</v>
-      </c>
-      <c r="P11" t="s">
-        <v>930</v>
       </c>
       <c r="Q11" s="4">
         <v>46297</v>
       </c>
       <c r="R11" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>964</v>
+      </c>
+      <c r="B12" t="s">
+        <v>920</v>
+      </c>
+      <c r="C12" t="s">
+        <v>921</v>
+      </c>
+      <c r="D12" t="s">
+        <v>922</v>
+      </c>
+      <c r="E12" t="s">
         <v>965</v>
       </c>
-      <c r="B12" t="s">
-        <v>921</v>
-      </c>
-      <c r="C12" t="s">
-        <v>922</v>
-      </c>
-      <c r="D12" t="s">
-        <v>923</v>
-      </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>966</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>967</v>
-      </c>
-      <c r="G12" t="s">
-        <v>968</v>
       </c>
       <c r="H12">
         <v>1904</v>
@@ -9800,45 +9800,45 @@
         <v>1989</v>
       </c>
       <c r="M12" t="s">
+        <v>968</v>
+      </c>
+      <c r="N12" t="s">
         <v>969</v>
       </c>
-      <c r="N12" t="s">
-        <v>970</v>
-      </c>
       <c r="O12" t="s">
+        <v>928</v>
+      </c>
+      <c r="P12" t="s">
         <v>929</v>
-      </c>
-      <c r="P12" t="s">
-        <v>930</v>
       </c>
       <c r="Q12" s="4">
         <v>46297</v>
       </c>
       <c r="R12" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>970</v>
+      </c>
+      <c r="B13" t="s">
+        <v>920</v>
+      </c>
+      <c r="C13" t="s">
+        <v>921</v>
+      </c>
+      <c r="D13" t="s">
+        <v>922</v>
+      </c>
+      <c r="E13" t="s">
         <v>971</v>
       </c>
-      <c r="B13" t="s">
-        <v>921</v>
-      </c>
-      <c r="C13" t="s">
-        <v>922</v>
-      </c>
-      <c r="D13" t="s">
-        <v>923</v>
-      </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>972</v>
       </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
         <v>973</v>
-      </c>
-      <c r="G13" t="s">
-        <v>974</v>
       </c>
       <c r="H13">
         <v>1914</v>
@@ -9847,22 +9847,22 @@
         <v>1991</v>
       </c>
       <c r="M13" t="s">
+        <v>974</v>
+      </c>
+      <c r="N13" t="s">
         <v>975</v>
       </c>
-      <c r="N13" t="s">
-        <v>976</v>
-      </c>
       <c r="O13" t="s">
+        <v>928</v>
+      </c>
+      <c r="P13" t="s">
         <v>929</v>
-      </c>
-      <c r="P13" t="s">
-        <v>930</v>
       </c>
       <c r="Q13" s="4">
         <v>46297</v>
       </c>
       <c r="R13" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
@@ -9870,19 +9870,19 @@
         <v>218</v>
       </c>
       <c r="B14" t="s">
+        <v>920</v>
+      </c>
+      <c r="C14" t="s">
         <v>921</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>922</v>
-      </c>
-      <c r="D14" t="s">
-        <v>923</v>
       </c>
       <c r="E14" t="s">
         <v>219</v>
       </c>
       <c r="F14" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="H14">
         <v>1920</v>
@@ -9891,22 +9891,22 @@
         <v>2004</v>
       </c>
       <c r="M14" t="s">
+        <v>977</v>
+      </c>
+      <c r="N14" t="s">
         <v>978</v>
       </c>
-      <c r="N14" t="s">
-        <v>979</v>
-      </c>
       <c r="O14" t="s">
+        <v>928</v>
+      </c>
+      <c r="P14" t="s">
         <v>929</v>
-      </c>
-      <c r="P14" t="s">
-        <v>930</v>
       </c>
       <c r="Q14" s="4">
         <v>46297</v>
       </c>
       <c r="R14" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
@@ -9914,19 +9914,19 @@
         <v>83</v>
       </c>
       <c r="B15" t="s">
+        <v>920</v>
+      </c>
+      <c r="C15" t="s">
         <v>921</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>922</v>
-      </c>
-      <c r="D15" t="s">
-        <v>923</v>
       </c>
       <c r="E15" t="s">
         <v>84</v>
       </c>
       <c r="F15" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="H15">
         <v>1920</v>
@@ -9935,39 +9935,39 @@
         <v>1997</v>
       </c>
       <c r="O15" t="s">
+        <v>928</v>
+      </c>
+      <c r="P15" t="s">
         <v>929</v>
-      </c>
-      <c r="P15" t="s">
-        <v>930</v>
       </c>
       <c r="Q15" s="4">
         <v>46297</v>
       </c>
       <c r="R15" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>980</v>
+      </c>
+      <c r="B16" t="s">
+        <v>920</v>
+      </c>
+      <c r="C16" t="s">
+        <v>921</v>
+      </c>
+      <c r="D16" t="s">
+        <v>922</v>
+      </c>
+      <c r="E16" t="s">
+        <v>635</v>
+      </c>
+      <c r="F16" t="s">
         <v>981</v>
       </c>
-      <c r="B16" t="s">
-        <v>921</v>
-      </c>
-      <c r="C16" t="s">
-        <v>922</v>
-      </c>
-      <c r="D16" t="s">
-        <v>923</v>
-      </c>
-      <c r="E16" t="s">
-        <v>636</v>
-      </c>
-      <c r="F16" t="s">
+      <c r="G16" t="s">
         <v>982</v>
-      </c>
-      <c r="G16" t="s">
-        <v>983</v>
       </c>
       <c r="H16">
         <v>1898</v>
@@ -9976,42 +9976,42 @@
         <v>1969</v>
       </c>
       <c r="M16" t="s">
+        <v>983</v>
+      </c>
+      <c r="N16" t="s">
         <v>984</v>
       </c>
-      <c r="N16" t="s">
-        <v>985</v>
-      </c>
       <c r="O16" t="s">
+        <v>928</v>
+      </c>
+      <c r="P16" t="s">
         <v>929</v>
-      </c>
-      <c r="P16" t="s">
-        <v>930</v>
       </c>
       <c r="Q16" s="4">
         <v>46297</v>
       </c>
       <c r="R16" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>985</v>
+      </c>
+      <c r="B17" t="s">
+        <v>920</v>
+      </c>
+      <c r="C17" t="s">
+        <v>921</v>
+      </c>
+      <c r="D17" t="s">
+        <v>922</v>
+      </c>
+      <c r="E17" t="s">
+        <v>624</v>
+      </c>
+      <c r="F17" t="s">
         <v>986</v>
-      </c>
-      <c r="B17" t="s">
-        <v>921</v>
-      </c>
-      <c r="C17" t="s">
-        <v>922</v>
-      </c>
-      <c r="D17" t="s">
-        <v>923</v>
-      </c>
-      <c r="E17" t="s">
-        <v>625</v>
-      </c>
-      <c r="F17" t="s">
-        <v>987</v>
       </c>
       <c r="H17">
         <v>1924</v>
@@ -10020,22 +10020,22 @@
         <v>2010</v>
       </c>
       <c r="M17" t="s">
+        <v>987</v>
+      </c>
+      <c r="N17" t="s">
         <v>988</v>
       </c>
-      <c r="N17" t="s">
-        <v>989</v>
-      </c>
       <c r="O17" t="s">
+        <v>928</v>
+      </c>
+      <c r="P17" t="s">
         <v>929</v>
-      </c>
-      <c r="P17" t="s">
-        <v>930</v>
       </c>
       <c r="Q17" s="4">
         <v>46297</v>
       </c>
       <c r="R17" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
@@ -10043,19 +10043,19 @@
         <v>184</v>
       </c>
       <c r="B18" t="s">
+        <v>920</v>
+      </c>
+      <c r="C18" t="s">
         <v>921</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>922</v>
-      </c>
-      <c r="D18" t="s">
-        <v>923</v>
       </c>
       <c r="E18" t="s">
         <v>185</v>
       </c>
       <c r="F18" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="H18">
         <v>1933</v>
@@ -10064,22 +10064,22 @@
         <v>1996</v>
       </c>
       <c r="M18" t="s">
+        <v>990</v>
+      </c>
+      <c r="N18" t="s">
         <v>991</v>
       </c>
-      <c r="N18" t="s">
-        <v>992</v>
-      </c>
       <c r="O18" t="s">
+        <v>928</v>
+      </c>
+      <c r="P18" t="s">
         <v>929</v>
-      </c>
-      <c r="P18" t="s">
-        <v>930</v>
       </c>
       <c r="Q18" s="4">
         <v>46297</v>
       </c>
       <c r="R18" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
@@ -10087,40 +10087,40 @@
         <v>107</v>
       </c>
       <c r="B19" t="s">
+        <v>920</v>
+      </c>
+      <c r="C19" t="s">
         <v>921</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>922</v>
-      </c>
-      <c r="D19" t="s">
-        <v>923</v>
       </c>
       <c r="E19" t="s">
         <v>108</v>
       </c>
       <c r="F19" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="H19">
         <v>1941</v>
       </c>
       <c r="M19" t="s">
+        <v>993</v>
+      </c>
+      <c r="N19" t="s">
         <v>994</v>
       </c>
-      <c r="N19" t="s">
-        <v>995</v>
-      </c>
       <c r="O19" t="s">
+        <v>928</v>
+      </c>
+      <c r="P19" t="s">
         <v>929</v>
-      </c>
-      <c r="P19" t="s">
-        <v>930</v>
       </c>
       <c r="Q19" s="4">
         <v>46299</v>
       </c>
       <c r="R19" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
@@ -10128,31 +10128,31 @@
         <v>188</v>
       </c>
       <c r="B20" t="s">
+        <v>920</v>
+      </c>
+      <c r="C20" t="s">
         <v>921</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>922</v>
-      </c>
-      <c r="D20" t="s">
-        <v>923</v>
       </c>
       <c r="E20" t="s">
         <v>189</v>
       </c>
       <c r="F20" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="O20" t="s">
+        <v>928</v>
+      </c>
+      <c r="P20" t="s">
         <v>929</v>
-      </c>
-      <c r="P20" t="s">
-        <v>930</v>
       </c>
       <c r="Q20" s="4">
         <v>46299</v>
       </c>
       <c r="R20" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
@@ -10160,22 +10160,22 @@
         <v>93</v>
       </c>
       <c r="B21" t="s">
+        <v>920</v>
+      </c>
+      <c r="C21" t="s">
         <v>921</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>922</v>
-      </c>
-      <c r="D21" t="s">
-        <v>923</v>
       </c>
       <c r="E21" t="s">
         <v>94</v>
       </c>
       <c r="F21" t="s">
+        <v>996</v>
+      </c>
+      <c r="G21" t="s">
         <v>997</v>
-      </c>
-      <c r="G21" t="s">
-        <v>998</v>
       </c>
       <c r="H21">
         <v>1898</v>
@@ -10184,19 +10184,19 @@
         <v>1973</v>
       </c>
       <c r="M21" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="O21" t="s">
+        <v>928</v>
+      </c>
+      <c r="P21" t="s">
         <v>929</v>
-      </c>
-      <c r="P21" t="s">
-        <v>930</v>
       </c>
       <c r="Q21" s="4">
         <v>46299</v>
       </c>
       <c r="R21" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
@@ -10204,22 +10204,22 @@
         <v>100</v>
       </c>
       <c r="B22" t="s">
+        <v>920</v>
+      </c>
+      <c r="C22" t="s">
         <v>921</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
         <v>922</v>
-      </c>
-      <c r="D22" t="s">
-        <v>923</v>
       </c>
       <c r="E22" t="s">
         <v>101</v>
       </c>
       <c r="F22" t="s">
+        <v>999</v>
+      </c>
+      <c r="G22" t="s">
         <v>1000</v>
-      </c>
-      <c r="G22" t="s">
-        <v>1001</v>
       </c>
       <c r="H22">
         <v>1927</v>
@@ -10228,16 +10228,16 @@
         <v>2009</v>
       </c>
       <c r="O22" t="s">
+        <v>928</v>
+      </c>
+      <c r="P22" t="s">
         <v>929</v>
-      </c>
-      <c r="P22" t="s">
-        <v>930</v>
       </c>
       <c r="Q22" s="4">
         <v>46299</v>
       </c>
       <c r="R22" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
@@ -10245,19 +10245,19 @@
         <v>115</v>
       </c>
       <c r="B23" t="s">
+        <v>920</v>
+      </c>
+      <c r="C23" t="s">
         <v>921</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D23" t="s">
         <v>922</v>
-      </c>
-      <c r="D23" t="s">
-        <v>923</v>
       </c>
       <c r="E23" t="s">
         <v>116</v>
       </c>
       <c r="F23" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="H23">
         <v>1936</v>
@@ -10266,22 +10266,22 @@
         <v>1994</v>
       </c>
       <c r="M23" t="s">
+        <v>1002</v>
+      </c>
+      <c r="N23" t="s">
         <v>1003</v>
       </c>
-      <c r="N23" t="s">
-        <v>1004</v>
-      </c>
       <c r="O23" t="s">
+        <v>928</v>
+      </c>
+      <c r="P23" t="s">
         <v>929</v>
-      </c>
-      <c r="P23" t="s">
-        <v>930</v>
       </c>
       <c r="Q23" s="4">
         <v>46299</v>
       </c>
       <c r="R23" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
@@ -10289,34 +10289,34 @@
         <v>149</v>
       </c>
       <c r="B24" t="s">
+        <v>920</v>
+      </c>
+      <c r="C24" t="s">
         <v>921</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D24" t="s">
         <v>922</v>
-      </c>
-      <c r="D24" t="s">
-        <v>923</v>
       </c>
       <c r="E24" t="s">
         <v>150</v>
       </c>
       <c r="F24" t="s">
+        <v>1005</v>
+      </c>
+      <c r="G24" t="s">
         <v>1006</v>
       </c>
-      <c r="G24" t="s">
-        <v>1007</v>
-      </c>
       <c r="O24" t="s">
+        <v>928</v>
+      </c>
+      <c r="P24" t="s">
         <v>929</v>
-      </c>
-      <c r="P24" t="s">
-        <v>930</v>
       </c>
       <c r="Q24" s="4">
         <v>46299</v>
       </c>
       <c r="R24" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.3">
@@ -10324,31 +10324,31 @@
         <v>153</v>
       </c>
       <c r="B25" t="s">
+        <v>920</v>
+      </c>
+      <c r="C25" t="s">
         <v>921</v>
       </c>
-      <c r="C25" t="s">
+      <c r="D25" t="s">
         <v>922</v>
-      </c>
-      <c r="D25" t="s">
-        <v>923</v>
       </c>
       <c r="E25" t="s">
         <v>154</v>
       </c>
       <c r="F25" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="O25" t="s">
+        <v>928</v>
+      </c>
+      <c r="P25" t="s">
         <v>929</v>
-      </c>
-      <c r="P25" t="s">
-        <v>930</v>
       </c>
       <c r="Q25" s="4">
         <v>46299</v>
       </c>
       <c r="R25" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.3">
@@ -10356,40 +10356,40 @@
         <v>164</v>
       </c>
       <c r="B26" t="s">
+        <v>920</v>
+      </c>
+      <c r="C26" t="s">
         <v>921</v>
       </c>
-      <c r="C26" t="s">
+      <c r="D26" t="s">
         <v>922</v>
-      </c>
-      <c r="D26" t="s">
-        <v>923</v>
       </c>
       <c r="E26" t="s">
         <v>165</v>
       </c>
       <c r="F26" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="H26">
         <v>1945</v>
       </c>
       <c r="M26" t="s">
+        <v>1009</v>
+      </c>
+      <c r="N26" t="s">
         <v>1010</v>
       </c>
-      <c r="N26" t="s">
-        <v>1011</v>
-      </c>
       <c r="O26" t="s">
+        <v>928</v>
+      </c>
+      <c r="P26" t="s">
         <v>929</v>
-      </c>
-      <c r="P26" t="s">
-        <v>930</v>
       </c>
       <c r="Q26" s="4">
         <v>46299</v>
       </c>
       <c r="R26" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.3">
@@ -10397,31 +10397,31 @@
         <v>121</v>
       </c>
       <c r="B27" t="s">
+        <v>920</v>
+      </c>
+      <c r="C27" t="s">
         <v>921</v>
       </c>
-      <c r="C27" t="s">
+      <c r="D27" t="s">
         <v>922</v>
-      </c>
-      <c r="D27" t="s">
-        <v>923</v>
       </c>
       <c r="E27" t="s">
         <v>122</v>
       </c>
       <c r="F27" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="O27" t="s">
+        <v>928</v>
+      </c>
+      <c r="P27" t="s">
         <v>929</v>
-      </c>
-      <c r="P27" t="s">
-        <v>930</v>
       </c>
       <c r="Q27" s="4">
         <v>46299</v>
       </c>
       <c r="R27" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
   </sheetData>
@@ -10457,58 +10457,58 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
+        <v>902</v>
+      </c>
+      <c r="B1" s="9" t="s">
         <v>903</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="C1" s="9" t="s">
         <v>904</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="D1" s="9" t="s">
         <v>905</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="E1" t="s">
         <v>906</v>
       </c>
-      <c r="E1" t="s">
-        <v>907</v>
-      </c>
       <c r="F1" s="9" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="G1" t="s">
+        <v>1012</v>
+      </c>
+      <c r="H1" t="s">
         <v>1013</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>1014</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
+        <v>911</v>
+      </c>
+      <c r="K1" s="9" t="s">
         <v>1015</v>
       </c>
-      <c r="J1" t="s">
-        <v>912</v>
-      </c>
-      <c r="K1" s="9" t="s">
-        <v>1016</v>
-      </c>
       <c r="L1" s="9" t="s">
+        <v>913</v>
+      </c>
+      <c r="M1" s="9" t="s">
         <v>914</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="N1" s="9" t="s">
         <v>915</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="O1" s="9" t="s">
         <v>916</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="P1" s="9" t="s">
         <v>917</v>
       </c>
-      <c r="P1" s="9" t="s">
+      <c r="Q1" s="9" t="s">
         <v>918</v>
       </c>
-      <c r="Q1" s="9" t="s">
+      <c r="R1" s="9" t="s">
         <v>919</v>
-      </c>
-      <c r="R1" s="9" t="s">
-        <v>920</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
@@ -10516,78 +10516,78 @@
         <v>85</v>
       </c>
       <c r="B2" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="C2" t="s">
+        <v>921</v>
+      </c>
+      <c r="D2" t="s">
         <v>922</v>
-      </c>
-      <c r="D2" t="s">
-        <v>923</v>
       </c>
       <c r="E2" t="s">
         <v>86</v>
       </c>
       <c r="G2" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="H2">
         <v>1962</v>
       </c>
       <c r="I2" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="O2" t="s">
+        <v>928</v>
+      </c>
+      <c r="P2" t="s">
         <v>929</v>
-      </c>
-      <c r="P2" t="s">
-        <v>930</v>
       </c>
       <c r="Q2" s="4">
         <v>46297</v>
       </c>
       <c r="R2" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B3" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="C3" t="s">
+        <v>921</v>
+      </c>
+      <c r="D3" t="s">
         <v>922</v>
-      </c>
-      <c r="D3" t="s">
-        <v>923</v>
       </c>
       <c r="E3" t="s">
         <v>268</v>
       </c>
       <c r="G3" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="H3">
         <v>1952</v>
       </c>
       <c r="M3" t="s">
+        <v>1022</v>
+      </c>
+      <c r="N3" t="s">
         <v>1023</v>
       </c>
-      <c r="N3" t="s">
-        <v>1024</v>
-      </c>
       <c r="O3" t="s">
+        <v>928</v>
+      </c>
+      <c r="P3" t="s">
         <v>929</v>
-      </c>
-      <c r="P3" t="s">
-        <v>930</v>
       </c>
       <c r="Q3" s="4">
         <v>46297</v>
       </c>
       <c r="R3" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
@@ -10595,19 +10595,19 @@
         <v>96</v>
       </c>
       <c r="B4" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="C4" t="s">
+        <v>921</v>
+      </c>
+      <c r="D4" t="s">
         <v>922</v>
-      </c>
-      <c r="D4" t="s">
-        <v>923</v>
       </c>
       <c r="E4" t="s">
         <v>97</v>
       </c>
       <c r="G4" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="H4">
         <v>1963</v>
@@ -10616,80 +10616,80 @@
         <v>1979</v>
       </c>
       <c r="O4" t="s">
+        <v>928</v>
+      </c>
+      <c r="P4" t="s">
         <v>929</v>
-      </c>
-      <c r="P4" t="s">
-        <v>930</v>
       </c>
       <c r="Q4" s="4">
         <v>46297</v>
       </c>
       <c r="R4" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C5" t="s">
+        <v>921</v>
+      </c>
+      <c r="D5" t="s">
+        <v>922</v>
+      </c>
+      <c r="E5" t="s">
+        <v>339</v>
+      </c>
+      <c r="F5" t="s">
         <v>1025</v>
       </c>
-      <c r="B5" t="s">
-        <v>1017</v>
-      </c>
-      <c r="C5" t="s">
-        <v>922</v>
-      </c>
-      <c r="D5" t="s">
-        <v>923</v>
-      </c>
-      <c r="E5" t="s">
-        <v>340</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>1026</v>
-      </c>
-      <c r="G5" t="s">
-        <v>1027</v>
       </c>
       <c r="H5">
         <v>1948</v>
       </c>
       <c r="M5" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="O5" t="s">
+        <v>928</v>
+      </c>
+      <c r="P5" t="s">
         <v>929</v>
-      </c>
-      <c r="P5" t="s">
-        <v>930</v>
       </c>
       <c r="Q5" s="4">
         <v>46297</v>
       </c>
       <c r="R5" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>1028</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C6" t="s">
+        <v>921</v>
+      </c>
+      <c r="D6" t="s">
+        <v>922</v>
+      </c>
+      <c r="E6" t="s">
+        <v>323</v>
+      </c>
+      <c r="F6" t="s">
         <v>1029</v>
       </c>
-      <c r="B6" t="s">
-        <v>1017</v>
-      </c>
-      <c r="C6" t="s">
-        <v>922</v>
-      </c>
-      <c r="D6" t="s">
-        <v>923</v>
-      </c>
-      <c r="E6" t="s">
-        <v>324</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>1030</v>
-      </c>
-      <c r="G6" t="s">
-        <v>1031</v>
       </c>
       <c r="H6">
         <v>1958</v>
@@ -10698,22 +10698,22 @@
         <v>1988</v>
       </c>
       <c r="M6" t="s">
+        <v>1031</v>
+      </c>
+      <c r="N6" t="s">
         <v>1032</v>
       </c>
-      <c r="N6" t="s">
-        <v>1033</v>
-      </c>
       <c r="O6" t="s">
+        <v>928</v>
+      </c>
+      <c r="P6" t="s">
         <v>929</v>
-      </c>
-      <c r="P6" t="s">
-        <v>930</v>
       </c>
       <c r="Q6" s="4">
         <v>46297</v>
       </c>
       <c r="R6" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
@@ -10721,22 +10721,22 @@
         <v>191</v>
       </c>
       <c r="B7" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="C7" t="s">
+        <v>921</v>
+      </c>
+      <c r="D7" t="s">
         <v>922</v>
-      </c>
-      <c r="D7" t="s">
-        <v>923</v>
       </c>
       <c r="E7" t="s">
         <v>192</v>
       </c>
       <c r="F7" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="G7" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="H7">
         <v>1964</v>
@@ -10745,95 +10745,95 @@
         <v>1991</v>
       </c>
       <c r="O7" t="s">
+        <v>928</v>
+      </c>
+      <c r="P7" t="s">
         <v>929</v>
-      </c>
-      <c r="P7" t="s">
-        <v>930</v>
       </c>
       <c r="Q7" s="4">
         <v>46297</v>
       </c>
       <c r="R7" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C8" t="s">
+        <v>921</v>
+      </c>
+      <c r="D8" t="s">
+        <v>922</v>
+      </c>
+      <c r="E8" t="s">
         <v>1034</v>
       </c>
-      <c r="B8" t="s">
-        <v>1017</v>
-      </c>
-      <c r="C8" t="s">
-        <v>922</v>
-      </c>
-      <c r="D8" t="s">
-        <v>923</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>1035</v>
       </c>
-      <c r="F8" t="s">
-        <v>1036</v>
-      </c>
       <c r="G8" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="H8">
         <v>1956</v>
       </c>
       <c r="M8" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="O8" t="s">
+        <v>928</v>
+      </c>
+      <c r="P8" t="s">
         <v>929</v>
-      </c>
-      <c r="P8" t="s">
-        <v>930</v>
       </c>
       <c r="Q8" s="4">
         <v>46297</v>
       </c>
       <c r="R8" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C9" t="s">
+        <v>921</v>
+      </c>
+      <c r="D9" t="s">
+        <v>922</v>
+      </c>
+      <c r="E9" t="s">
+        <v>393</v>
+      </c>
+      <c r="G9" t="s">
         <v>1038</v>
-      </c>
-      <c r="B9" t="s">
-        <v>1017</v>
-      </c>
-      <c r="C9" t="s">
-        <v>922</v>
-      </c>
-      <c r="D9" t="s">
-        <v>923</v>
-      </c>
-      <c r="E9" t="s">
-        <v>394</v>
-      </c>
-      <c r="G9" t="s">
-        <v>1039</v>
       </c>
       <c r="H9" t="s">
         <v>91</v>
       </c>
       <c r="I9" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="O9" t="s">
+        <v>928</v>
+      </c>
+      <c r="P9" t="s">
         <v>929</v>
-      </c>
-      <c r="P9" t="s">
-        <v>930</v>
       </c>
       <c r="Q9" s="4">
         <v>46297</v>
       </c>
       <c r="R9" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
@@ -10841,19 +10841,19 @@
         <v>49</v>
       </c>
       <c r="B10" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="C10" t="s">
+        <v>921</v>
+      </c>
+      <c r="D10" t="s">
         <v>922</v>
-      </c>
-      <c r="D10" t="s">
-        <v>923</v>
       </c>
       <c r="E10" t="s">
         <v>50</v>
       </c>
       <c r="G10" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="H10">
         <v>1966</v>
@@ -10862,16 +10862,16 @@
         <v>1991</v>
       </c>
       <c r="O10" t="s">
+        <v>928</v>
+      </c>
+      <c r="P10" t="s">
         <v>929</v>
-      </c>
-      <c r="P10" t="s">
-        <v>930</v>
       </c>
       <c r="Q10" s="4">
         <v>46297</v>
       </c>
       <c r="R10" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
@@ -10879,19 +10879,19 @@
         <v>53</v>
       </c>
       <c r="B11" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="C11" t="s">
+        <v>921</v>
+      </c>
+      <c r="D11" t="s">
         <v>922</v>
-      </c>
-      <c r="D11" t="s">
-        <v>923</v>
       </c>
       <c r="E11" t="s">
         <v>54</v>
       </c>
       <c r="G11" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="H11">
         <v>1968</v>
@@ -10900,16 +10900,16 @@
         <v>1972</v>
       </c>
       <c r="O11" t="s">
+        <v>928</v>
+      </c>
+      <c r="P11" t="s">
         <v>929</v>
-      </c>
-      <c r="P11" t="s">
-        <v>930</v>
       </c>
       <c r="Q11" s="4">
         <v>46297</v>
       </c>
       <c r="R11" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
@@ -10917,22 +10917,22 @@
         <v>235</v>
       </c>
       <c r="B12" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="C12" t="s">
+        <v>921</v>
+      </c>
+      <c r="D12" t="s">
         <v>922</v>
-      </c>
-      <c r="D12" t="s">
-        <v>923</v>
       </c>
       <c r="E12" t="s">
         <v>236</v>
       </c>
       <c r="F12" t="s">
+        <v>1041</v>
+      </c>
+      <c r="G12" t="s">
         <v>1042</v>
-      </c>
-      <c r="G12" t="s">
-        <v>1043</v>
       </c>
       <c r="H12">
         <v>1966</v>
@@ -10941,16 +10941,16 @@
         <v>1991</v>
       </c>
       <c r="O12" t="s">
+        <v>928</v>
+      </c>
+      <c r="P12" t="s">
         <v>929</v>
-      </c>
-      <c r="P12" t="s">
-        <v>930</v>
       </c>
       <c r="Q12" s="4">
         <v>46297</v>
       </c>
       <c r="R12" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
@@ -10958,40 +10958,40 @@
         <v>38</v>
       </c>
       <c r="B13" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="C13" t="s">
+        <v>921</v>
+      </c>
+      <c r="D13" t="s">
         <v>922</v>
-      </c>
-      <c r="D13" t="s">
-        <v>923</v>
       </c>
       <c r="E13" t="s">
         <v>39</v>
       </c>
       <c r="G13" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="H13">
         <v>1921</v>
       </c>
       <c r="M13" t="s">
+        <v>1043</v>
+      </c>
+      <c r="N13" t="s">
         <v>1044</v>
       </c>
-      <c r="N13" t="s">
-        <v>1045</v>
-      </c>
       <c r="O13" t="s">
+        <v>928</v>
+      </c>
+      <c r="P13" t="s">
         <v>929</v>
-      </c>
-      <c r="P13" t="s">
-        <v>930</v>
       </c>
       <c r="Q13" s="4">
         <v>46297</v>
       </c>
       <c r="R13" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
@@ -10999,22 +10999,22 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="C14" t="s">
+        <v>921</v>
+      </c>
+      <c r="D14" t="s">
         <v>922</v>
-      </c>
-      <c r="D14" t="s">
-        <v>923</v>
       </c>
       <c r="E14" t="s">
         <v>12</v>
       </c>
       <c r="F14" t="s">
+        <v>1045</v>
+      </c>
+      <c r="G14" t="s">
         <v>1046</v>
-      </c>
-      <c r="G14" t="s">
-        <v>1047</v>
       </c>
       <c r="H14">
         <v>1966</v>
@@ -11023,25 +11023,25 @@
         <v>1991</v>
       </c>
       <c r="J14" t="s">
+        <v>1047</v>
+      </c>
+      <c r="M14" t="s">
         <v>1048</v>
       </c>
-      <c r="M14" t="s">
+      <c r="N14" t="s">
         <v>1049</v>
       </c>
-      <c r="N14" t="s">
-        <v>1050</v>
-      </c>
       <c r="O14" t="s">
+        <v>928</v>
+      </c>
+      <c r="P14" t="s">
         <v>929</v>
-      </c>
-      <c r="P14" t="s">
-        <v>930</v>
       </c>
       <c r="Q14" s="4">
         <v>46297</v>
       </c>
       <c r="R14" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
@@ -11049,22 +11049,22 @@
         <v>55</v>
       </c>
       <c r="B15" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="C15" t="s">
+        <v>921</v>
+      </c>
+      <c r="D15" t="s">
         <v>922</v>
-      </c>
-      <c r="D15" t="s">
-        <v>923</v>
       </c>
       <c r="E15" t="s">
         <v>56</v>
       </c>
       <c r="F15" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="G15" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="H15">
         <v>1968</v>
@@ -11073,25 +11073,25 @@
         <v>1972</v>
       </c>
       <c r="J15" t="s">
+        <v>1051</v>
+      </c>
+      <c r="M15" t="s">
         <v>1052</v>
       </c>
-      <c r="M15" t="s">
+      <c r="N15" t="s">
         <v>1053</v>
       </c>
-      <c r="N15" t="s">
-        <v>1054</v>
-      </c>
       <c r="O15" t="s">
+        <v>928</v>
+      </c>
+      <c r="P15" t="s">
         <v>929</v>
-      </c>
-      <c r="P15" t="s">
-        <v>930</v>
       </c>
       <c r="Q15" s="4">
         <v>46297</v>
       </c>
       <c r="R15" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
@@ -11099,46 +11099,46 @@
         <v>33</v>
       </c>
       <c r="B16" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="C16" t="s">
+        <v>921</v>
+      </c>
+      <c r="D16" t="s">
         <v>922</v>
-      </c>
-      <c r="D16" t="s">
-        <v>923</v>
       </c>
       <c r="E16" t="s">
         <v>34</v>
       </c>
       <c r="F16" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="G16" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="H16">
         <v>1921</v>
       </c>
       <c r="J16" t="s">
+        <v>1055</v>
+      </c>
+      <c r="M16" t="s">
         <v>1056</v>
       </c>
-      <c r="M16" t="s">
+      <c r="N16" t="s">
         <v>1057</v>
       </c>
-      <c r="N16" t="s">
-        <v>1058</v>
-      </c>
       <c r="O16" t="s">
+        <v>928</v>
+      </c>
+      <c r="P16" t="s">
         <v>929</v>
-      </c>
-      <c r="P16" t="s">
-        <v>930</v>
       </c>
       <c r="Q16" s="4">
         <v>46297</v>
       </c>
       <c r="R16" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
@@ -11146,22 +11146,22 @@
         <v>45</v>
       </c>
       <c r="B17" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="C17" t="s">
+        <v>921</v>
+      </c>
+      <c r="D17" t="s">
         <v>922</v>
-      </c>
-      <c r="D17" t="s">
-        <v>923</v>
       </c>
       <c r="E17" t="s">
         <v>46</v>
       </c>
       <c r="F17" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="G17" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="H17">
         <v>1968</v>
@@ -11170,16 +11170,16 @@
         <v>1977</v>
       </c>
       <c r="O17" t="s">
+        <v>928</v>
+      </c>
+      <c r="P17" t="s">
         <v>929</v>
-      </c>
-      <c r="P17" t="s">
-        <v>930</v>
       </c>
       <c r="Q17" s="4">
         <v>46297</v>
       </c>
       <c r="R17" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
@@ -11187,22 +11187,22 @@
         <v>66</v>
       </c>
       <c r="B18" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="C18" t="s">
+        <v>921</v>
+      </c>
+      <c r="D18" t="s">
         <v>922</v>
-      </c>
-      <c r="D18" t="s">
-        <v>923</v>
       </c>
       <c r="E18" t="s">
         <v>67</v>
       </c>
       <c r="F18" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="G18" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="H18">
         <v>1969</v>
@@ -11211,16 +11211,16 @@
         <v>1976</v>
       </c>
       <c r="O18" t="s">
+        <v>928</v>
+      </c>
+      <c r="P18" t="s">
         <v>929</v>
-      </c>
-      <c r="P18" t="s">
-        <v>930</v>
       </c>
       <c r="Q18" s="4">
         <v>46297</v>
       </c>
       <c r="R18" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
@@ -11228,37 +11228,37 @@
         <v>117</v>
       </c>
       <c r="B19" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="C19" t="s">
+        <v>921</v>
+      </c>
+      <c r="D19" t="s">
         <v>922</v>
-      </c>
-      <c r="D19" t="s">
-        <v>923</v>
       </c>
       <c r="E19" t="s">
         <v>118</v>
       </c>
       <c r="G19" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="H19">
         <v>1968</v>
       </c>
       <c r="I19" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="O19" t="s">
+        <v>928</v>
+      </c>
+      <c r="P19" t="s">
         <v>929</v>
-      </c>
-      <c r="P19" t="s">
-        <v>930</v>
       </c>
       <c r="Q19" s="4">
         <v>46297</v>
       </c>
       <c r="R19" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
@@ -11266,22 +11266,22 @@
         <v>104</v>
       </c>
       <c r="B20" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="C20" t="s">
+        <v>921</v>
+      </c>
+      <c r="D20" t="s">
         <v>922</v>
-      </c>
-      <c r="D20" t="s">
-        <v>923</v>
       </c>
       <c r="E20" t="s">
         <v>105</v>
       </c>
       <c r="F20" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="G20" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="H20">
         <v>1972</v>
@@ -11290,22 +11290,22 @@
         <v>1978</v>
       </c>
       <c r="M20" t="s">
+        <v>1052</v>
+      </c>
+      <c r="N20" t="s">
         <v>1053</v>
       </c>
-      <c r="N20" t="s">
-        <v>1054</v>
-      </c>
       <c r="O20" t="s">
+        <v>928</v>
+      </c>
+      <c r="P20" t="s">
         <v>929</v>
-      </c>
-      <c r="P20" t="s">
-        <v>930</v>
       </c>
       <c r="Q20" s="4">
         <v>46297</v>
       </c>
       <c r="R20" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
@@ -11313,19 +11313,19 @@
         <v>221</v>
       </c>
       <c r="B21" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="C21" t="s">
+        <v>921</v>
+      </c>
+      <c r="D21" t="s">
         <v>922</v>
-      </c>
-      <c r="D21" t="s">
-        <v>923</v>
       </c>
       <c r="E21" t="s">
         <v>222</v>
       </c>
       <c r="G21" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="H21">
         <v>1967</v>
@@ -11334,16 +11334,16 @@
         <v>1969</v>
       </c>
       <c r="O21" t="s">
+        <v>928</v>
+      </c>
+      <c r="P21" t="s">
         <v>929</v>
-      </c>
-      <c r="P21" t="s">
-        <v>930</v>
       </c>
       <c r="Q21" s="4">
         <v>46297</v>
       </c>
       <c r="R21" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
@@ -11351,22 +11351,22 @@
         <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="C22" t="s">
+        <v>921</v>
+      </c>
+      <c r="D22" t="s">
         <v>922</v>
-      </c>
-      <c r="D22" t="s">
-        <v>923</v>
       </c>
       <c r="E22" t="s">
         <v>28</v>
       </c>
       <c r="F22" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="G22" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="H22">
         <v>1977</v>
@@ -11375,19 +11375,19 @@
         <v>1984</v>
       </c>
       <c r="M22" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="O22" t="s">
+        <v>928</v>
+      </c>
+      <c r="P22" t="s">
         <v>929</v>
-      </c>
-      <c r="P22" t="s">
-        <v>930</v>
       </c>
       <c r="Q22" s="4">
         <v>46297</v>
       </c>
       <c r="R22" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
@@ -11395,22 +11395,22 @@
         <v>170</v>
       </c>
       <c r="B23" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="C23" t="s">
+        <v>921</v>
+      </c>
+      <c r="D23" t="s">
         <v>922</v>
-      </c>
-      <c r="D23" t="s">
-        <v>923</v>
       </c>
       <c r="E23" t="s">
         <v>171</v>
       </c>
       <c r="F23" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="G23" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="H23">
         <v>1970</v>
@@ -11419,16 +11419,16 @@
         <v>1973</v>
       </c>
       <c r="O23" t="s">
+        <v>928</v>
+      </c>
+      <c r="P23" t="s">
         <v>929</v>
-      </c>
-      <c r="P23" t="s">
-        <v>930</v>
       </c>
       <c r="Q23" s="4">
         <v>46297</v>
       </c>
       <c r="R23" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
@@ -11436,19 +11436,19 @@
         <v>176</v>
       </c>
       <c r="B24" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="C24" t="s">
+        <v>921</v>
+      </c>
+      <c r="D24" t="s">
         <v>922</v>
-      </c>
-      <c r="D24" t="s">
-        <v>923</v>
       </c>
       <c r="E24" t="s">
         <v>177</v>
       </c>
       <c r="G24" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="H24">
         <v>1969</v>
@@ -11457,16 +11457,16 @@
         <v>1972</v>
       </c>
       <c r="O24" t="s">
+        <v>928</v>
+      </c>
+      <c r="P24" t="s">
         <v>929</v>
-      </c>
-      <c r="P24" t="s">
-        <v>930</v>
       </c>
       <c r="Q24" s="4">
         <v>46297</v>
       </c>
       <c r="R24" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.3">
@@ -11474,22 +11474,22 @@
         <v>137</v>
       </c>
       <c r="B25" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="C25" t="s">
+        <v>921</v>
+      </c>
+      <c r="D25" t="s">
         <v>922</v>
-      </c>
-      <c r="D25" t="s">
-        <v>923</v>
       </c>
       <c r="E25" t="s">
         <v>138</v>
       </c>
       <c r="F25" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="G25" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="H25">
         <v>1973</v>
@@ -11498,16 +11498,16 @@
         <v>1977</v>
       </c>
       <c r="O25" t="s">
+        <v>928</v>
+      </c>
+      <c r="P25" t="s">
         <v>929</v>
-      </c>
-      <c r="P25" t="s">
-        <v>930</v>
       </c>
       <c r="Q25" s="4">
         <v>46297</v>
       </c>
       <c r="R25" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.3">
@@ -11515,19 +11515,19 @@
         <v>166</v>
       </c>
       <c r="B26" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="C26" t="s">
+        <v>921</v>
+      </c>
+      <c r="D26" t="s">
         <v>922</v>
-      </c>
-      <c r="D26" t="s">
-        <v>923</v>
       </c>
       <c r="E26" t="s">
         <v>167</v>
       </c>
       <c r="G26" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="H26">
         <v>1968</v>
@@ -11536,22 +11536,22 @@
         <v>1976</v>
       </c>
       <c r="M26" t="s">
+        <v>1065</v>
+      </c>
+      <c r="N26" t="s">
         <v>1066</v>
       </c>
-      <c r="N26" t="s">
-        <v>1067</v>
-      </c>
       <c r="O26" t="s">
+        <v>928</v>
+      </c>
+      <c r="P26" t="s">
         <v>929</v>
-      </c>
-      <c r="P26" t="s">
-        <v>930</v>
       </c>
       <c r="Q26" s="4">
         <v>46297</v>
       </c>
       <c r="R26" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.3">
@@ -11559,22 +11559,22 @@
         <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="C27" t="s">
+        <v>921</v>
+      </c>
+      <c r="D27" t="s">
         <v>922</v>
-      </c>
-      <c r="D27" t="s">
-        <v>923</v>
       </c>
       <c r="E27" t="s">
         <v>24</v>
       </c>
       <c r="F27" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="G27" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="H27">
         <v>1970</v>
@@ -11583,16 +11583,16 @@
         <v>1977</v>
       </c>
       <c r="O27" t="s">
+        <v>928</v>
+      </c>
+      <c r="P27" t="s">
         <v>929</v>
-      </c>
-      <c r="P27" t="s">
-        <v>930</v>
       </c>
       <c r="Q27" s="4">
         <v>46297</v>
       </c>
       <c r="R27" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.3">
@@ -11600,22 +11600,22 @@
         <v>140</v>
       </c>
       <c r="B28" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="C28" t="s">
+        <v>921</v>
+      </c>
+      <c r="D28" t="s">
         <v>922</v>
-      </c>
-      <c r="D28" t="s">
-        <v>923</v>
       </c>
       <c r="E28" t="s">
         <v>141</v>
       </c>
       <c r="F28" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="G28" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="H28">
         <v>1969</v>
@@ -11624,16 +11624,16 @@
         <v>1977</v>
       </c>
       <c r="O28" t="s">
+        <v>928</v>
+      </c>
+      <c r="P28" t="s">
         <v>929</v>
-      </c>
-      <c r="P28" t="s">
-        <v>930</v>
       </c>
       <c r="Q28" s="4">
         <v>46297</v>
       </c>
       <c r="R28" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.3">
@@ -11641,22 +11641,22 @@
         <v>128</v>
       </c>
       <c r="B29" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="C29" t="s">
+        <v>921</v>
+      </c>
+      <c r="D29" t="s">
         <v>922</v>
-      </c>
-      <c r="D29" t="s">
-        <v>923</v>
       </c>
       <c r="E29" t="s">
         <v>129</v>
       </c>
       <c r="F29" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G29" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="H29">
         <v>1969</v>
@@ -11665,16 +11665,16 @@
         <v>1977</v>
       </c>
       <c r="O29" t="s">
+        <v>928</v>
+      </c>
+      <c r="P29" t="s">
         <v>929</v>
-      </c>
-      <c r="P29" t="s">
-        <v>930</v>
       </c>
       <c r="Q29" s="4">
         <v>46297</v>
       </c>
       <c r="R29" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.3">
@@ -11682,31 +11682,31 @@
         <v>111</v>
       </c>
       <c r="B30" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="C30" t="s">
+        <v>921</v>
+      </c>
+      <c r="D30" t="s">
         <v>922</v>
-      </c>
-      <c r="D30" t="s">
-        <v>923</v>
       </c>
       <c r="E30" t="s">
         <v>112</v>
       </c>
       <c r="G30" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="O30" t="s">
+        <v>928</v>
+      </c>
+      <c r="P30" t="s">
         <v>929</v>
-      </c>
-      <c r="P30" t="s">
-        <v>930</v>
       </c>
       <c r="Q30" s="4">
         <v>46299</v>
       </c>
       <c r="R30" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
     </row>
   </sheetData>

--- a/data/dati.xlsx
+++ b/data/dati.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan_\Desktop\AMI\GitHub\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30DA4354-B76C-4F26-A65D-13A58C67355E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38162B6B-3C75-4C7A-B06D-66E13B3A41B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Catalogo" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2724" uniqueCount="1073">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2932" uniqueCount="1140">
   <si>
     <t>ID_relazione</t>
   </si>
@@ -1982,18 +1982,10 @@
     <t>1965</t>
   </si>
   <si>
-    <t>Lega della gioventù comunista (marxista-leninista) d'Italia; Partito Comunista Cinese</t>
-  </si>
-  <si>
     <t>https://archive.org/details/come-diventare-un-buon-comunista/mode/2up</t>
   </si>
   <si>
     <t>pp. 143</t>
-  </si>
-  <si>
-    <t>Prima di essere identificato come capo della "linea nera anti-partito" durante la Rivoluzione culturale, il presidente della Repubblica Popolare Cinese Liu Shaoqi era considerato uno dei "vecchi gloriosi compagni" del Partito Comunista Cinese. Fino alla sua "scomunica", quindi, i filo-cinesi italiani leggono e pubblicano i suoi discorsi e le sue opere, tra cui il seguente volume, una guida all'autoeducazione ideologica dei comunisti cinesi, composto dalla compilazione di una serie di conferenze tenute da Liu nel 1939.
-Libro tradotto da Arnaldo Bressan (Lega della gioventù comunista (marxista-leninista) d'Italia) e pubblicato dalle Edizioni Oriente, Milano, pp. 143, 1965.
-Copertina ricostruita digitalmente sulla base del frontespizio e della comparazione con il catalogo delle Edizioni Oriente.</t>
   </si>
   <si>
     <t>AMI-0061</t>
@@ -3320,12 +3312,221 @@
 • I gruppi minori di "Coscienza Operaia" e "Ideologia Proletaria"
 Il partito pubblica il giornale "Linea Proletaria", ereditato dall'organizzazione di Pesce.</t>
   </si>
+  <si>
+    <t>AMI-0097</t>
+  </si>
+  <si>
+    <t>AMI-0098</t>
+  </si>
+  <si>
+    <t>AMI-0099</t>
+  </si>
+  <si>
+    <t>AMI-0100</t>
+  </si>
+  <si>
+    <t>AMI-0101</t>
+  </si>
+  <si>
+    <t>AMI-0102</t>
+  </si>
+  <si>
+    <t>AMI-0103</t>
+  </si>
+  <si>
+    <t>AMI-0104</t>
+  </si>
+  <si>
+    <t>AMI-0105</t>
+  </si>
+  <si>
+    <t>AMI-0106</t>
+  </si>
+  <si>
+    <t>AMI-0107</t>
+  </si>
+  <si>
+    <t>Centro Gramsci di Educazione</t>
+  </si>
+  <si>
+    <t>Nuova Unità, anno I, no. 1</t>
+  </si>
+  <si>
+    <t>Nuova Unità, anno I, no. 2</t>
+  </si>
+  <si>
+    <t>Nuova Unità, anno I, no. 3</t>
+  </si>
+  <si>
+    <t>Nuova Unità, anno I, no. 4</t>
+  </si>
+  <si>
+    <t>Nuova Unità, anno I, no. 7</t>
+  </si>
+  <si>
+    <t>Nuova Unità, anno I, no. 8</t>
+  </si>
+  <si>
+    <t>Nuova Unità, anno I, no. 9</t>
+  </si>
+  <si>
+    <t>Nuova Unità, anno I, no. 10</t>
+  </si>
+  <si>
+    <t>Nuova Unità, anno II, no. 1</t>
+  </si>
+  <si>
+    <t>Nuova Unità, anno II, no. 2</t>
+  </si>
+  <si>
+    <t>03/1964</t>
+  </si>
+  <si>
+    <t>04/1965</t>
+  </si>
+  <si>
+    <t>04/1964</t>
+  </si>
+  <si>
+    <t>05/1964</t>
+  </si>
+  <si>
+    <t>06/1964</t>
+  </si>
+  <si>
+    <t>08/1964</t>
+  </si>
+  <si>
+    <t>09/1964</t>
+  </si>
+  <si>
+    <t>10/1964</t>
+  </si>
+  <si>
+    <t>11/1964</t>
+  </si>
+  <si>
+    <t>12/1964</t>
+  </si>
+  <si>
+    <t>01/1965</t>
+  </si>
+  <si>
+    <t>1964-03</t>
+  </si>
+  <si>
+    <t>1964-04</t>
+  </si>
+  <si>
+    <t>1964-05</t>
+  </si>
+  <si>
+    <t>1964-06</t>
+  </si>
+  <si>
+    <t>1964-08</t>
+  </si>
+  <si>
+    <t>1964-09</t>
+  </si>
+  <si>
+    <t>1964-10</t>
+  </si>
+  <si>
+    <t>1964-11</t>
+  </si>
+  <si>
+    <t>1964-12</t>
+  </si>
+  <si>
+    <t>1965-01</t>
+  </si>
+  <si>
+    <t>1965-04</t>
+  </si>
+  <si>
+    <t>Movimento Marxista-Leninista Italiano</t>
+  </si>
+  <si>
+    <t>AMI-O-030</t>
+  </si>
+  <si>
+    <t>ISAAR(CPF), 2a ed., 2005</t>
+  </si>
+  <si>
+    <t>AMI-R-072</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/nuova-unita-1965-01/mode/2up</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/nuova-unita-1965-04/mode/2up</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/nuova-unita-1964-05/mode/2up</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/nuova-unita-1964-06/mode/2up</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/nuova-unita-1964-09/mode/2up</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/nuova-unita-1964-10/mode/2up</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/nuova-unita-1964-11/mode/2up</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/nuova-unita-1964-12/mode/2up</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/nuova-unita-1964-07-08/mode/2up</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/nuova-unita-1964-03/mode/2up</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/nuova-unita-1964-04/mode/2up</t>
+  </si>
+  <si>
+    <t>Nuova Unità, anno I, no. 5-6</t>
+  </si>
+  <si>
+    <t>Ugo Duse</t>
+  </si>
+  <si>
+    <t>Edizioni Oriente; Gruppo Proletario Luglio 60</t>
+  </si>
+  <si>
+    <t>Ugo Duse; Mario Geymonat; Giuseppe Regis; Franco Molfese</t>
+  </si>
+  <si>
+    <t>Ugo Duse; Mario Geymonat; Giuseppe Regis</t>
+  </si>
+  <si>
+    <t>Ugo Duse; Mario Geymonat</t>
+  </si>
+  <si>
+    <t>Lega della Gioventù Comunista (marxista-leninista) d'Italia</t>
+  </si>
+  <si>
+    <t>Lega della Gioventù Comunista (marxista-leninista) d'Italia; Partito Comunista Cinese</t>
+  </si>
+  <si>
+    <t>Prima di essere identificato come capo della "linea nera anti-partito" durante la Rivoluzione culturale, il presidente della Repubblica Popolare Cinese Liu Shaoqi era considerato uno dei "vecchi gloriosi compagni" del Partito Comunista Cinese. Fino alla sua "scomunica", quindi, i filo-cinesi italiani leggono e pubblicano i suoi discorsi e le sue opere, tra cui il seguente volume, una guida all'autoeducazione ideologica dei comunisti cinesi, composto dalla compilazione di una serie di conferenze tenute da Liu nel 1939.
+Libro tradotto da Arnaldo Bressan (Lega della Gioventù Comunista (marxista-leninista) d'Italia) e pubblicato dalle Edizioni Oriente, Milano, pp. 143, 1965.
+Copertina ricostruita digitalmente sulla base del frontespizio e della comparazione con il catalogo delle Edizioni Oriente.</t>
+  </si>
+  <si>
+    <t>Vincenzo Misefari</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3353,6 +3554,12 @@
       <color theme="1"/>
       <name val="Georgia"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -3866,7 +4073,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V97"/>
+  <dimension ref="A1:V151"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5546875" customWidth="1"/>
@@ -4001,7 +4208,7 @@
         <v>272</v>
       </c>
       <c r="V2" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
@@ -6915,7 +7122,7 @@
         <v>616</v>
       </c>
       <c r="O58" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="P58" t="s">
         <v>271</v>
@@ -6930,7 +7137,7 @@
         <v>345</v>
       </c>
       <c r="V58" s="12" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="59" spans="1:22" x14ac:dyDescent="0.3">
@@ -7039,7 +7246,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="61" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:22" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>630</v>
       </c>
@@ -7083,24 +7290,24 @@
         <v>184</v>
       </c>
       <c r="O61" t="s">
-        <v>634</v>
+        <v>1137</v>
       </c>
       <c r="P61" t="s">
         <v>271</v>
       </c>
       <c r="Q61" s="3" t="s">
+        <v>634</v>
+      </c>
+      <c r="U61" t="s">
         <v>635</v>
       </c>
-      <c r="U61" t="s">
-        <v>636</v>
-      </c>
-      <c r="V61" t="s">
-        <v>637</v>
+      <c r="V61" s="12" t="s">
+        <v>1138</v>
       </c>
     </row>
     <row r="62" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="B62" t="s">
         <v>263</v>
@@ -7109,7 +7316,7 @@
         <v>264</v>
       </c>
       <c r="D62" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="E62" t="s">
         <v>266</v>
@@ -7142,18 +7349,18 @@
         <v>271</v>
       </c>
       <c r="Q62" s="3" t="s">
+        <v>638</v>
+      </c>
+      <c r="U62" t="s">
+        <v>639</v>
+      </c>
+      <c r="V62" t="s">
         <v>640</v>
-      </c>
-      <c r="U62" t="s">
-        <v>641</v>
-      </c>
-      <c r="V62" t="s">
-        <v>642</v>
       </c>
     </row>
     <row r="63" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="B63" t="s">
         <v>263</v>
@@ -7162,7 +7369,7 @@
         <v>264</v>
       </c>
       <c r="D63" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="E63" t="s">
         <v>337</v>
@@ -7171,42 +7378,42 @@
         <v>24917</v>
       </c>
       <c r="J63" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="K63" t="s">
         <v>340</v>
       </c>
       <c r="L63" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="M63" t="s">
         <v>379</v>
       </c>
       <c r="N63" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="O63" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="P63" t="s">
         <v>271</v>
       </c>
       <c r="Q63" s="3" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="R63" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="U63" t="s">
         <v>345</v>
       </c>
       <c r="V63" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="B64" t="s">
         <v>263</v>
@@ -7215,7 +7422,7 @@
         <v>264</v>
       </c>
       <c r="D64" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E64" t="s">
         <v>266</v>
@@ -7227,16 +7434,16 @@
         <v>105</v>
       </c>
       <c r="I64" s="5" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="J64" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="K64" t="s">
         <v>364</v>
       </c>
       <c r="L64" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="M64" t="s">
         <v>329</v>
@@ -7245,18 +7452,18 @@
         <v>108</v>
       </c>
       <c r="P64" t="s">
+        <v>655</v>
+      </c>
+      <c r="Q64" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="V64" t="s">
         <v>657</v>
-      </c>
-      <c r="Q64" s="3" t="s">
-        <v>658</v>
-      </c>
-      <c r="V64" t="s">
-        <v>659</v>
       </c>
     </row>
     <row r="65" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="B65" t="s">
         <v>263</v>
@@ -7265,28 +7472,28 @@
         <v>264</v>
       </c>
       <c r="D65" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="E65" t="s">
         <v>266</v>
       </c>
       <c r="F65" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="G65" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="I65" s="4">
         <v>26956</v>
       </c>
       <c r="J65" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="K65" t="s">
         <v>364</v>
       </c>
       <c r="L65" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="M65" t="s">
         <v>329</v>
@@ -7295,18 +7502,18 @@
         <v>161</v>
       </c>
       <c r="P65" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="Q65" s="3" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="V65" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
     </row>
     <row r="66" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="B66" t="s">
         <v>263</v>
@@ -7315,7 +7522,7 @@
         <v>264</v>
       </c>
       <c r="D66" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="E66" t="s">
         <v>337</v>
@@ -7339,27 +7546,27 @@
         <v>329</v>
       </c>
       <c r="N66" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="P66" t="s">
         <v>271</v>
       </c>
       <c r="Q66" s="3" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="R66" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="U66" t="s">
         <v>345</v>
       </c>
       <c r="V66" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
     </row>
     <row r="67" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="B67" t="s">
         <v>263</v>
@@ -7368,7 +7575,7 @@
         <v>264</v>
       </c>
       <c r="D67" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="E67" t="s">
         <v>337</v>
@@ -7392,27 +7599,27 @@
         <v>329</v>
       </c>
       <c r="N67" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="P67" t="s">
         <v>271</v>
       </c>
       <c r="Q67" s="3" t="s">
+        <v>672</v>
+      </c>
+      <c r="R67" t="s">
+        <v>673</v>
+      </c>
+      <c r="U67" t="s">
         <v>674</v>
       </c>
-      <c r="R67" t="s">
+      <c r="V67" t="s">
         <v>675</v>
-      </c>
-      <c r="U67" t="s">
-        <v>676</v>
-      </c>
-      <c r="V67" t="s">
-        <v>677</v>
       </c>
     </row>
     <row r="68" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="B68" t="s">
         <v>263</v>
@@ -7421,7 +7628,7 @@
         <v>264</v>
       </c>
       <c r="D68" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="E68" t="s">
         <v>266</v>
@@ -7448,18 +7655,18 @@
         <v>271</v>
       </c>
       <c r="Q68" s="3" t="s">
+        <v>678</v>
+      </c>
+      <c r="R68" t="s">
+        <v>679</v>
+      </c>
+      <c r="V68" t="s">
         <v>680</v>
-      </c>
-      <c r="R68" t="s">
-        <v>681</v>
-      </c>
-      <c r="V68" t="s">
-        <v>682</v>
       </c>
     </row>
     <row r="69" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="B69" t="s">
         <v>263</v>
@@ -7468,7 +7675,7 @@
         <v>264</v>
       </c>
       <c r="D69" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="E69" t="s">
         <v>266</v>
@@ -7480,10 +7687,10 @@
         <v>170</v>
       </c>
       <c r="I69" s="7" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="J69" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="K69" t="s">
         <v>395</v>
@@ -7498,15 +7705,15 @@
         <v>398</v>
       </c>
       <c r="Q69" s="3" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="V69" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
     </row>
     <row r="70" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="B70" t="s">
         <v>263</v>
@@ -7515,7 +7722,7 @@
         <v>264</v>
       </c>
       <c r="D70" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="E70" t="s">
         <v>266</v>
@@ -7530,7 +7737,7 @@
         <v>25704</v>
       </c>
       <c r="J70" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="K70" t="s">
         <v>395</v>
@@ -7545,15 +7752,15 @@
         <v>398</v>
       </c>
       <c r="Q70" s="3" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="V70" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
     </row>
     <row r="71" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="B71" t="s">
         <v>263</v>
@@ -7562,7 +7769,7 @@
         <v>264</v>
       </c>
       <c r="D71" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="E71" t="s">
         <v>266</v>
@@ -7577,7 +7784,7 @@
         <v>25718</v>
       </c>
       <c r="J71" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="K71" t="s">
         <v>395</v>
@@ -7592,15 +7799,15 @@
         <v>398</v>
       </c>
       <c r="Q71" s="3" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="V71" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
     </row>
     <row r="72" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="B72" t="s">
         <v>263</v>
@@ -7609,7 +7816,7 @@
         <v>264</v>
       </c>
       <c r="D72" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="E72" t="s">
         <v>266</v>
@@ -7624,7 +7831,7 @@
         <v>25719</v>
       </c>
       <c r="J72" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="K72" t="s">
         <v>395</v>
@@ -7639,15 +7846,15 @@
         <v>398</v>
       </c>
       <c r="Q72" s="3" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="V72" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
     </row>
     <row r="73" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="B73" t="s">
         <v>263</v>
@@ -7656,7 +7863,7 @@
         <v>264</v>
       </c>
       <c r="D73" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="E73" t="s">
         <v>266</v>
@@ -7671,7 +7878,7 @@
         <v>25740</v>
       </c>
       <c r="J73" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="K73" t="s">
         <v>395</v>
@@ -7686,15 +7893,15 @@
         <v>398</v>
       </c>
       <c r="Q73" s="3" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="V73" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
     </row>
     <row r="74" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="B74" t="s">
         <v>263</v>
@@ -7703,7 +7910,7 @@
         <v>264</v>
       </c>
       <c r="D74" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="E74" t="s">
         <v>266</v>
@@ -7718,7 +7925,7 @@
         <v>25765</v>
       </c>
       <c r="J74" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="K74" t="s">
         <v>395</v>
@@ -7733,15 +7940,15 @@
         <v>398</v>
       </c>
       <c r="Q74" s="3" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="V74" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
     </row>
     <row r="75" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="B75" t="s">
         <v>263</v>
@@ -7750,7 +7957,7 @@
         <v>264</v>
       </c>
       <c r="D75" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="E75" t="s">
         <v>266</v>
@@ -7765,7 +7972,7 @@
         <v>25824</v>
       </c>
       <c r="J75" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="K75" t="s">
         <v>395</v>
@@ -7780,15 +7987,15 @@
         <v>398</v>
       </c>
       <c r="Q75" s="3" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="V75" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
     </row>
     <row r="76" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="B76" t="s">
         <v>263</v>
@@ -7797,7 +8004,7 @@
         <v>264</v>
       </c>
       <c r="D76" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="E76" t="s">
         <v>266</v>
@@ -7812,7 +8019,7 @@
         <v>25866</v>
       </c>
       <c r="J76" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="K76" t="s">
         <v>395</v>
@@ -7827,15 +8034,15 @@
         <v>398</v>
       </c>
       <c r="Q76" s="3" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="V76" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
     </row>
     <row r="77" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="B77" t="s">
         <v>263</v>
@@ -7844,7 +8051,7 @@
         <v>264</v>
       </c>
       <c r="D77" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="E77" t="s">
         <v>266</v>
@@ -7859,7 +8066,7 @@
         <v>25887</v>
       </c>
       <c r="J77" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="K77" t="s">
         <v>395</v>
@@ -7874,15 +8081,15 @@
         <v>398</v>
       </c>
       <c r="Q77" s="3" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="V77" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
     </row>
     <row r="78" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="B78" t="s">
         <v>263</v>
@@ -7891,7 +8098,7 @@
         <v>264</v>
       </c>
       <c r="D78" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="E78" t="s">
         <v>266</v>
@@ -7906,7 +8113,7 @@
         <v>25915</v>
       </c>
       <c r="J78" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="K78" t="s">
         <v>395</v>
@@ -7921,15 +8128,15 @@
         <v>398</v>
       </c>
       <c r="Q78" s="3" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="V78" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
     </row>
     <row r="79" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="B79" t="s">
         <v>263</v>
@@ -7938,7 +8145,7 @@
         <v>264</v>
       </c>
       <c r="D79" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="E79" t="s">
         <v>266</v>
@@ -7953,7 +8160,7 @@
         <v>25950</v>
       </c>
       <c r="J79" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="K79" t="s">
         <v>395</v>
@@ -7968,15 +8175,15 @@
         <v>398</v>
       </c>
       <c r="Q79" s="3" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="V79" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
     </row>
     <row r="80" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="B80" t="s">
         <v>263</v>
@@ -7985,7 +8192,7 @@
         <v>264</v>
       </c>
       <c r="D80" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="E80" t="s">
         <v>266</v>
@@ -8000,7 +8207,7 @@
         <v>25971</v>
       </c>
       <c r="J80" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="K80" t="s">
         <v>395</v>
@@ -8015,15 +8222,15 @@
         <v>398</v>
       </c>
       <c r="Q80" s="3" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="V80" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
     </row>
     <row r="81" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="B81" t="s">
         <v>263</v>
@@ -8032,7 +8239,7 @@
         <v>264</v>
       </c>
       <c r="D81" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="E81" t="s">
         <v>266</v>
@@ -8047,7 +8254,7 @@
         <v>25999</v>
       </c>
       <c r="J81" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="K81" t="s">
         <v>395</v>
@@ -8062,15 +8269,15 @@
         <v>398</v>
       </c>
       <c r="Q81" s="3" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="V81" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
     </row>
     <row r="82" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="B82" t="s">
         <v>263</v>
@@ -8079,7 +8286,7 @@
         <v>264</v>
       </c>
       <c r="D82" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="E82" t="s">
         <v>266</v>
@@ -8094,7 +8301,7 @@
         <v>26027</v>
       </c>
       <c r="J82" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="K82" t="s">
         <v>395</v>
@@ -8109,15 +8316,15 @@
         <v>398</v>
       </c>
       <c r="Q82" s="3" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="V82" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
     </row>
     <row r="83" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="B83" t="s">
         <v>263</v>
@@ -8126,7 +8333,7 @@
         <v>264</v>
       </c>
       <c r="D83" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="E83" t="s">
         <v>266</v>
@@ -8141,7 +8348,7 @@
         <v>26054</v>
       </c>
       <c r="J83" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="K83" t="s">
         <v>395</v>
@@ -8156,15 +8363,15 @@
         <v>398</v>
       </c>
       <c r="Q83" s="3" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="V83" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
     </row>
     <row r="84" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="B84" t="s">
         <v>263</v>
@@ -8173,7 +8380,7 @@
         <v>264</v>
       </c>
       <c r="D84" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="E84" t="s">
         <v>266</v>
@@ -8188,7 +8395,7 @@
         <v>26076</v>
       </c>
       <c r="J84" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="K84" t="s">
         <v>395</v>
@@ -8203,15 +8410,15 @@
         <v>398</v>
       </c>
       <c r="Q84" s="3" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="V84" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
     </row>
     <row r="85" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="B85" t="s">
         <v>263</v>
@@ -8220,7 +8427,7 @@
         <v>264</v>
       </c>
       <c r="D85" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="E85" t="s">
         <v>266</v>
@@ -8235,7 +8442,7 @@
         <v>26104</v>
       </c>
       <c r="J85" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="K85" t="s">
         <v>395</v>
@@ -8250,15 +8457,15 @@
         <v>398</v>
       </c>
       <c r="Q85" s="3" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="V85" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
     </row>
     <row r="86" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="B86" t="s">
         <v>263</v>
@@ -8267,7 +8474,7 @@
         <v>264</v>
       </c>
       <c r="D86" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="E86" t="s">
         <v>266</v>
@@ -8282,7 +8489,7 @@
         <v>26139</v>
       </c>
       <c r="J86" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="K86" t="s">
         <v>395</v>
@@ -8297,15 +8504,15 @@
         <v>398</v>
       </c>
       <c r="Q86" s="3" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="V86" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
     </row>
     <row r="87" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="B87" t="s">
         <v>263</v>
@@ -8314,7 +8521,7 @@
         <v>264</v>
       </c>
       <c r="D87" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="E87" t="s">
         <v>266</v>
@@ -8329,7 +8536,7 @@
         <v>26265</v>
       </c>
       <c r="J87" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="K87" t="s">
         <v>395</v>
@@ -8344,15 +8551,15 @@
         <v>398</v>
       </c>
       <c r="Q87" s="3" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="V87" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
     </row>
     <row r="88" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="B88" t="s">
         <v>263</v>
@@ -8361,7 +8568,7 @@
         <v>264</v>
       </c>
       <c r="D88" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="E88" t="s">
         <v>266</v>
@@ -8376,7 +8583,7 @@
         <v>26307</v>
       </c>
       <c r="J88" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="K88" t="s">
         <v>395</v>
@@ -8391,15 +8598,15 @@
         <v>398</v>
       </c>
       <c r="Q88" s="3" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="V88" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
     </row>
     <row r="89" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="B89" t="s">
         <v>263</v>
@@ -8408,7 +8615,7 @@
         <v>264</v>
       </c>
       <c r="D89" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="E89" t="s">
         <v>266</v>
@@ -8423,7 +8630,7 @@
         <v>26370</v>
       </c>
       <c r="J89" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="K89" t="s">
         <v>395</v>
@@ -8438,15 +8645,15 @@
         <v>398</v>
       </c>
       <c r="Q89" s="3" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="V89" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="90" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="B90" t="s">
         <v>263</v>
@@ -8455,7 +8662,7 @@
         <v>264</v>
       </c>
       <c r="D90" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="E90" t="s">
         <v>266</v>
@@ -8470,7 +8677,7 @@
         <v>26420</v>
       </c>
       <c r="J90" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="K90" t="s">
         <v>395</v>
@@ -8485,15 +8692,15 @@
         <v>398</v>
       </c>
       <c r="Q90" s="3" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="V90" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
     </row>
     <row r="91" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="B91" t="s">
         <v>263</v>
@@ -8502,7 +8709,7 @@
         <v>264</v>
       </c>
       <c r="D91" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="E91" t="s">
         <v>266</v>
@@ -8517,7 +8724,7 @@
         <v>26608</v>
       </c>
       <c r="J91" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="K91" t="s">
         <v>395</v>
@@ -8532,15 +8739,15 @@
         <v>398</v>
       </c>
       <c r="Q91" s="3" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="V91" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
     </row>
     <row r="92" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="B92" t="s">
         <v>263</v>
@@ -8549,7 +8756,7 @@
         <v>264</v>
       </c>
       <c r="D92" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="E92" t="s">
         <v>266</v>
@@ -8564,7 +8771,7 @@
         <v>26785</v>
       </c>
       <c r="J92" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="K92" t="s">
         <v>395</v>
@@ -8579,15 +8786,15 @@
         <v>398</v>
       </c>
       <c r="Q92" s="3" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="V92" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
     </row>
     <row r="93" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="B93" t="s">
         <v>263</v>
@@ -8596,7 +8803,7 @@
         <v>264</v>
       </c>
       <c r="D93" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="E93" t="s">
         <v>266</v>
@@ -8605,7 +8812,7 @@
         <v>56</v>
       </c>
       <c r="H93" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="I93">
         <v>1969</v>
@@ -8623,27 +8830,27 @@
         <v>285</v>
       </c>
       <c r="N93" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="O93" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="P93" t="s">
         <v>271</v>
       </c>
       <c r="Q93" s="3" t="s">
+        <v>807</v>
+      </c>
+      <c r="U93" t="s">
+        <v>808</v>
+      </c>
+      <c r="V93" t="s">
         <v>809</v>
-      </c>
-      <c r="U93" t="s">
-        <v>810</v>
-      </c>
-      <c r="V93" t="s">
-        <v>811</v>
       </c>
     </row>
     <row r="94" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B94" t="s">
         <v>263</v>
@@ -8652,7 +8859,7 @@
         <v>264</v>
       </c>
       <c r="D94" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="E94" t="s">
         <v>266</v>
@@ -8664,39 +8871,39 @@
         <v>176</v>
       </c>
       <c r="I94" s="5" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="J94" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="K94" t="s">
         <v>275</v>
       </c>
       <c r="L94" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="M94" t="s">
         <v>329</v>
       </c>
       <c r="O94" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="P94" t="s">
         <v>271</v>
       </c>
       <c r="Q94" s="3" t="s">
+        <v>816</v>
+      </c>
+      <c r="U94" t="s">
+        <v>817</v>
+      </c>
+      <c r="V94" t="s">
         <v>818</v>
-      </c>
-      <c r="U94" t="s">
-        <v>819</v>
-      </c>
-      <c r="V94" t="s">
-        <v>820</v>
       </c>
     </row>
     <row r="95" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="B95" t="s">
         <v>263</v>
@@ -8705,7 +8912,7 @@
         <v>264</v>
       </c>
       <c r="D95" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="E95" t="s">
         <v>266</v>
@@ -8738,18 +8945,18 @@
         <v>287</v>
       </c>
       <c r="Q95" s="3" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="U95" t="s">
         <v>559</v>
       </c>
       <c r="V95" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
     </row>
     <row r="96" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="B96" t="s">
         <v>263</v>
@@ -8758,7 +8965,7 @@
         <v>264</v>
       </c>
       <c r="D96" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="E96" t="s">
         <v>266</v>
@@ -8794,18 +9001,18 @@
         <v>287</v>
       </c>
       <c r="Q96" s="3" t="s">
+        <v>825</v>
+      </c>
+      <c r="U96" t="s">
+        <v>826</v>
+      </c>
+      <c r="V96" t="s">
         <v>827</v>
-      </c>
-      <c r="U96" t="s">
-        <v>828</v>
-      </c>
-      <c r="V96" t="s">
-        <v>829</v>
       </c>
     </row>
     <row r="97" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="B97" t="s">
         <v>263</v>
@@ -8814,7 +9021,7 @@
         <v>264</v>
       </c>
       <c r="D97" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="E97" t="s">
         <v>337</v>
@@ -8838,19 +9045,744 @@
         <v>271</v>
       </c>
       <c r="Q97" s="3" t="s">
+        <v>830</v>
+      </c>
+      <c r="R97" t="s">
+        <v>831</v>
+      </c>
+      <c r="U97" t="s">
         <v>832</v>
       </c>
-      <c r="R97" t="s">
+      <c r="V97" t="s">
         <v>833</v>
       </c>
-      <c r="U97" t="s">
-        <v>834</v>
-      </c>
-      <c r="V97" t="s">
-        <v>835</v>
-      </c>
+    </row>
+    <row r="98" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B98" t="s">
+        <v>263</v>
+      </c>
+      <c r="C98" t="s">
+        <v>264</v>
+      </c>
+      <c r="D98" t="s">
+        <v>1083</v>
+      </c>
+      <c r="E98" t="s">
+        <v>266</v>
+      </c>
+      <c r="F98" t="s">
+        <v>191</v>
+      </c>
+      <c r="G98" t="s">
+        <v>191</v>
+      </c>
+      <c r="H98" t="s">
+        <v>191</v>
+      </c>
+      <c r="I98" s="7" t="s">
+        <v>1093</v>
+      </c>
+      <c r="J98" t="s">
+        <v>1104</v>
+      </c>
+      <c r="K98" t="s">
+        <v>395</v>
+      </c>
+      <c r="L98" t="s">
+        <v>328</v>
+      </c>
+      <c r="M98" t="s">
+        <v>397</v>
+      </c>
+      <c r="N98" t="s">
+        <v>1131</v>
+      </c>
+      <c r="P98" t="s">
+        <v>1082</v>
+      </c>
+      <c r="Q98" s="3" t="s">
+        <v>1128</v>
+      </c>
+      <c r="U98" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="99" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>1072</v>
+      </c>
+      <c r="B99" t="s">
+        <v>263</v>
+      </c>
+      <c r="C99" t="s">
+        <v>264</v>
+      </c>
+      <c r="D99" t="s">
+        <v>1084</v>
+      </c>
+      <c r="E99" t="s">
+        <v>266</v>
+      </c>
+      <c r="F99" t="s">
+        <v>191</v>
+      </c>
+      <c r="G99" t="s">
+        <v>191</v>
+      </c>
+      <c r="H99" t="s">
+        <v>191</v>
+      </c>
+      <c r="I99" s="7" t="s">
+        <v>1095</v>
+      </c>
+      <c r="J99" t="s">
+        <v>1105</v>
+      </c>
+      <c r="K99" t="s">
+        <v>395</v>
+      </c>
+      <c r="L99" t="s">
+        <v>328</v>
+      </c>
+      <c r="M99" t="s">
+        <v>397</v>
+      </c>
+      <c r="N99" t="s">
+        <v>1134</v>
+      </c>
+      <c r="O99" t="s">
+        <v>1132</v>
+      </c>
+      <c r="P99" t="s">
+        <v>1082</v>
+      </c>
+      <c r="Q99" s="3" t="s">
+        <v>1129</v>
+      </c>
+      <c r="U99" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="100" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B100" t="s">
+        <v>263</v>
+      </c>
+      <c r="C100" t="s">
+        <v>264</v>
+      </c>
+      <c r="D100" t="s">
+        <v>1085</v>
+      </c>
+      <c r="E100" t="s">
+        <v>266</v>
+      </c>
+      <c r="F100" t="s">
+        <v>191</v>
+      </c>
+      <c r="G100" t="s">
+        <v>191</v>
+      </c>
+      <c r="H100" t="s">
+        <v>191</v>
+      </c>
+      <c r="I100" s="7" t="s">
+        <v>1096</v>
+      </c>
+      <c r="J100" t="s">
+        <v>1106</v>
+      </c>
+      <c r="K100" t="s">
+        <v>395</v>
+      </c>
+      <c r="L100" t="s">
+        <v>328</v>
+      </c>
+      <c r="M100" t="s">
+        <v>397</v>
+      </c>
+      <c r="N100" t="s">
+        <v>1133</v>
+      </c>
+      <c r="O100" t="s">
+        <v>1132</v>
+      </c>
+      <c r="P100" t="s">
+        <v>1082</v>
+      </c>
+      <c r="Q100" s="3" t="s">
+        <v>1121</v>
+      </c>
+      <c r="U100" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="101" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>1074</v>
+      </c>
+      <c r="B101" t="s">
+        <v>263</v>
+      </c>
+      <c r="C101" t="s">
+        <v>264</v>
+      </c>
+      <c r="D101" t="s">
+        <v>1086</v>
+      </c>
+      <c r="E101" t="s">
+        <v>266</v>
+      </c>
+      <c r="F101" t="s">
+        <v>191</v>
+      </c>
+      <c r="G101" t="s">
+        <v>191</v>
+      </c>
+      <c r="H101" t="s">
+        <v>191</v>
+      </c>
+      <c r="I101" s="7" t="s">
+        <v>1097</v>
+      </c>
+      <c r="J101" t="s">
+        <v>1107</v>
+      </c>
+      <c r="K101" t="s">
+        <v>395</v>
+      </c>
+      <c r="L101" t="s">
+        <v>328</v>
+      </c>
+      <c r="M101" t="s">
+        <v>397</v>
+      </c>
+      <c r="N101" t="s">
+        <v>1135</v>
+      </c>
+      <c r="O101" t="s">
+        <v>97</v>
+      </c>
+      <c r="P101" t="s">
+        <v>1082</v>
+      </c>
+      <c r="Q101" s="3" t="s">
+        <v>1122</v>
+      </c>
+      <c r="U101" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="102" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B102" t="s">
+        <v>263</v>
+      </c>
+      <c r="C102" t="s">
+        <v>264</v>
+      </c>
+      <c r="D102" t="s">
+        <v>1130</v>
+      </c>
+      <c r="E102" t="s">
+        <v>266</v>
+      </c>
+      <c r="F102" t="s">
+        <v>191</v>
+      </c>
+      <c r="G102" t="s">
+        <v>191</v>
+      </c>
+      <c r="H102" t="s">
+        <v>191</v>
+      </c>
+      <c r="I102" s="7" t="s">
+        <v>1098</v>
+      </c>
+      <c r="J102" t="s">
+        <v>1108</v>
+      </c>
+      <c r="K102" t="s">
+        <v>395</v>
+      </c>
+      <c r="L102" t="s">
+        <v>328</v>
+      </c>
+      <c r="M102" t="s">
+        <v>397</v>
+      </c>
+      <c r="N102" t="s">
+        <v>1135</v>
+      </c>
+      <c r="P102" t="s">
+        <v>1082</v>
+      </c>
+      <c r="Q102" s="3" t="s">
+        <v>1127</v>
+      </c>
+      <c r="U102" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="103" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B103" t="s">
+        <v>263</v>
+      </c>
+      <c r="C103" t="s">
+        <v>264</v>
+      </c>
+      <c r="D103" t="s">
+        <v>1087</v>
+      </c>
+      <c r="E103" t="s">
+        <v>266</v>
+      </c>
+      <c r="F103" t="s">
+        <v>191</v>
+      </c>
+      <c r="G103" t="s">
+        <v>191</v>
+      </c>
+      <c r="H103" t="s">
+        <v>191</v>
+      </c>
+      <c r="I103" s="7" t="s">
+        <v>1099</v>
+      </c>
+      <c r="J103" t="s">
+        <v>1109</v>
+      </c>
+      <c r="K103" t="s">
+        <v>395</v>
+      </c>
+      <c r="L103" t="s">
+        <v>328</v>
+      </c>
+      <c r="M103" t="s">
+        <v>397</v>
+      </c>
+      <c r="N103" t="s">
+        <v>1135</v>
+      </c>
+      <c r="P103" t="s">
+        <v>1082</v>
+      </c>
+      <c r="Q103" s="3" t="s">
+        <v>1123</v>
+      </c>
+      <c r="U103" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="104" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>1077</v>
+      </c>
+      <c r="B104" t="s">
+        <v>263</v>
+      </c>
+      <c r="C104" t="s">
+        <v>264</v>
+      </c>
+      <c r="D104" t="s">
+        <v>1088</v>
+      </c>
+      <c r="E104" t="s">
+        <v>266</v>
+      </c>
+      <c r="F104" t="s">
+        <v>191</v>
+      </c>
+      <c r="G104" t="s">
+        <v>191</v>
+      </c>
+      <c r="H104" t="s">
+        <v>191</v>
+      </c>
+      <c r="I104" s="7" t="s">
+        <v>1100</v>
+      </c>
+      <c r="J104" t="s">
+        <v>1110</v>
+      </c>
+      <c r="K104" t="s">
+        <v>395</v>
+      </c>
+      <c r="L104" t="s">
+        <v>328</v>
+      </c>
+      <c r="M104" t="s">
+        <v>397</v>
+      </c>
+      <c r="N104" t="s">
+        <v>1135</v>
+      </c>
+      <c r="P104" t="s">
+        <v>1082</v>
+      </c>
+      <c r="Q104" s="3" t="s">
+        <v>1124</v>
+      </c>
+      <c r="U104" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="105" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B105" t="s">
+        <v>263</v>
+      </c>
+      <c r="C105" t="s">
+        <v>264</v>
+      </c>
+      <c r="D105" t="s">
+        <v>1089</v>
+      </c>
+      <c r="E105" t="s">
+        <v>266</v>
+      </c>
+      <c r="F105" t="s">
+        <v>191</v>
+      </c>
+      <c r="G105" t="s">
+        <v>191</v>
+      </c>
+      <c r="H105" t="s">
+        <v>191</v>
+      </c>
+      <c r="I105" s="7" t="s">
+        <v>1101</v>
+      </c>
+      <c r="J105" t="s">
+        <v>1111</v>
+      </c>
+      <c r="K105" t="s">
+        <v>395</v>
+      </c>
+      <c r="L105" t="s">
+        <v>328</v>
+      </c>
+      <c r="M105" t="s">
+        <v>397</v>
+      </c>
+      <c r="N105" t="s">
+        <v>1135</v>
+      </c>
+      <c r="P105" t="s">
+        <v>1082</v>
+      </c>
+      <c r="Q105" s="3" t="s">
+        <v>1125</v>
+      </c>
+      <c r="U105" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="106" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B106" t="s">
+        <v>263</v>
+      </c>
+      <c r="C106" t="s">
+        <v>264</v>
+      </c>
+      <c r="D106" t="s">
+        <v>1090</v>
+      </c>
+      <c r="E106" t="s">
+        <v>266</v>
+      </c>
+      <c r="F106" t="s">
+        <v>191</v>
+      </c>
+      <c r="G106" t="s">
+        <v>191</v>
+      </c>
+      <c r="H106" t="s">
+        <v>191</v>
+      </c>
+      <c r="I106" s="7" t="s">
+        <v>1102</v>
+      </c>
+      <c r="J106" t="s">
+        <v>1112</v>
+      </c>
+      <c r="K106" t="s">
+        <v>395</v>
+      </c>
+      <c r="L106" t="s">
+        <v>328</v>
+      </c>
+      <c r="M106" t="s">
+        <v>397</v>
+      </c>
+      <c r="N106" t="s">
+        <v>1131</v>
+      </c>
+      <c r="P106" t="s">
+        <v>1082</v>
+      </c>
+      <c r="Q106" s="3" t="s">
+        <v>1126</v>
+      </c>
+      <c r="U106" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="107" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B107" t="s">
+        <v>263</v>
+      </c>
+      <c r="C107" t="s">
+        <v>264</v>
+      </c>
+      <c r="D107" t="s">
+        <v>1091</v>
+      </c>
+      <c r="E107" t="s">
+        <v>266</v>
+      </c>
+      <c r="F107" t="s">
+        <v>191</v>
+      </c>
+      <c r="G107" t="s">
+        <v>191</v>
+      </c>
+      <c r="H107" t="s">
+        <v>191</v>
+      </c>
+      <c r="I107" s="7" t="s">
+        <v>1103</v>
+      </c>
+      <c r="J107" t="s">
+        <v>1113</v>
+      </c>
+      <c r="K107" t="s">
+        <v>395</v>
+      </c>
+      <c r="L107" t="s">
+        <v>328</v>
+      </c>
+      <c r="M107" t="s">
+        <v>397</v>
+      </c>
+      <c r="N107" t="s">
+        <v>1131</v>
+      </c>
+      <c r="O107" t="s">
+        <v>1136</v>
+      </c>
+      <c r="P107" t="s">
+        <v>1082</v>
+      </c>
+      <c r="Q107" s="3" t="s">
+        <v>1119</v>
+      </c>
+      <c r="U107" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="108" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B108" t="s">
+        <v>263</v>
+      </c>
+      <c r="C108" t="s">
+        <v>264</v>
+      </c>
+      <c r="D108" t="s">
+        <v>1092</v>
+      </c>
+      <c r="E108" t="s">
+        <v>266</v>
+      </c>
+      <c r="F108" t="s">
+        <v>191</v>
+      </c>
+      <c r="G108" t="s">
+        <v>191</v>
+      </c>
+      <c r="H108" t="s">
+        <v>191</v>
+      </c>
+      <c r="I108" s="7" t="s">
+        <v>1094</v>
+      </c>
+      <c r="J108" t="s">
+        <v>1114</v>
+      </c>
+      <c r="K108" t="s">
+        <v>395</v>
+      </c>
+      <c r="L108" t="s">
+        <v>328</v>
+      </c>
+      <c r="M108" t="s">
+        <v>397</v>
+      </c>
+      <c r="N108" t="s">
+        <v>1139</v>
+      </c>
+      <c r="O108" t="s">
+        <v>1115</v>
+      </c>
+      <c r="P108" t="s">
+        <v>1082</v>
+      </c>
+      <c r="Q108" s="3" t="s">
+        <v>1120</v>
+      </c>
+      <c r="U108" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="110" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="Q110" s="3"/>
+    </row>
+    <row r="111" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="Q111" s="3"/>
+    </row>
+    <row r="112" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="Q112" s="3"/>
+    </row>
+    <row r="113" spans="17:17" x14ac:dyDescent="0.3">
+      <c r="Q113" s="3"/>
+    </row>
+    <row r="114" spans="17:17" x14ac:dyDescent="0.3">
+      <c r="Q114" s="3"/>
+    </row>
+    <row r="115" spans="17:17" x14ac:dyDescent="0.3">
+      <c r="Q115" s="3"/>
+    </row>
+    <row r="116" spans="17:17" x14ac:dyDescent="0.3">
+      <c r="Q116" s="3"/>
+    </row>
+    <row r="117" spans="17:17" x14ac:dyDescent="0.3">
+      <c r="Q117" s="3"/>
+    </row>
+    <row r="118" spans="17:17" x14ac:dyDescent="0.3">
+      <c r="Q118" s="3"/>
+    </row>
+    <row r="119" spans="17:17" x14ac:dyDescent="0.3">
+      <c r="Q119" s="3"/>
+    </row>
+    <row r="120" spans="17:17" x14ac:dyDescent="0.3">
+      <c r="Q120" s="3"/>
+    </row>
+    <row r="121" spans="17:17" x14ac:dyDescent="0.3">
+      <c r="Q121" s="3"/>
+    </row>
+    <row r="122" spans="17:17" x14ac:dyDescent="0.3">
+      <c r="Q122" s="3"/>
+    </row>
+    <row r="123" spans="17:17" x14ac:dyDescent="0.3">
+      <c r="Q123" s="3"/>
+    </row>
+    <row r="124" spans="17:17" x14ac:dyDescent="0.3">
+      <c r="Q124" s="3"/>
+    </row>
+    <row r="125" spans="17:17" x14ac:dyDescent="0.3">
+      <c r="Q125" s="3"/>
+    </row>
+    <row r="126" spans="17:17" x14ac:dyDescent="0.3">
+      <c r="Q126" s="3"/>
+    </row>
+    <row r="127" spans="17:17" x14ac:dyDescent="0.3">
+      <c r="Q127" s="3"/>
+    </row>
+    <row r="128" spans="17:17" x14ac:dyDescent="0.3">
+      <c r="Q128" s="3"/>
+    </row>
+    <row r="129" spans="17:17" x14ac:dyDescent="0.3">
+      <c r="Q129" s="3"/>
+    </row>
+    <row r="130" spans="17:17" x14ac:dyDescent="0.3">
+      <c r="Q130" s="3"/>
+    </row>
+    <row r="131" spans="17:17" x14ac:dyDescent="0.3">
+      <c r="Q131" s="3"/>
+    </row>
+    <row r="132" spans="17:17" x14ac:dyDescent="0.3">
+      <c r="Q132" s="3"/>
+    </row>
+    <row r="133" spans="17:17" x14ac:dyDescent="0.3">
+      <c r="Q133" s="3"/>
+    </row>
+    <row r="134" spans="17:17" x14ac:dyDescent="0.3">
+      <c r="Q134" s="3"/>
+    </row>
+    <row r="135" spans="17:17" x14ac:dyDescent="0.3">
+      <c r="Q135" s="3"/>
+    </row>
+    <row r="136" spans="17:17" x14ac:dyDescent="0.3">
+      <c r="Q136" s="3"/>
+    </row>
+    <row r="137" spans="17:17" x14ac:dyDescent="0.3">
+      <c r="Q137" s="3"/>
+    </row>
+    <row r="138" spans="17:17" x14ac:dyDescent="0.3">
+      <c r="Q138" s="3"/>
+    </row>
+    <row r="139" spans="17:17" x14ac:dyDescent="0.3">
+      <c r="Q139" s="3"/>
+    </row>
+    <row r="140" spans="17:17" x14ac:dyDescent="0.3">
+      <c r="Q140" s="3"/>
+    </row>
+    <row r="141" spans="17:17" x14ac:dyDescent="0.3">
+      <c r="Q141" s="3"/>
+    </row>
+    <row r="142" spans="17:17" x14ac:dyDescent="0.3">
+      <c r="Q142" s="3"/>
+    </row>
+    <row r="143" spans="17:17" x14ac:dyDescent="0.3">
+      <c r="Q143" s="3"/>
+    </row>
+    <row r="144" spans="17:17" x14ac:dyDescent="0.3">
+      <c r="Q144" s="3"/>
+    </row>
+    <row r="145" spans="17:17" x14ac:dyDescent="0.3">
+      <c r="Q145" s="3"/>
+    </row>
+    <row r="146" spans="17:17" x14ac:dyDescent="0.3">
+      <c r="Q146" s="3"/>
+    </row>
+    <row r="147" spans="17:17" x14ac:dyDescent="0.3">
+      <c r="Q147" s="3"/>
+    </row>
+    <row r="148" spans="17:17" x14ac:dyDescent="0.3">
+      <c r="Q148" s="3"/>
+    </row>
+    <row r="149" spans="17:17" x14ac:dyDescent="0.3">
+      <c r="Q149" s="3"/>
+    </row>
+    <row r="150" spans="17:17" x14ac:dyDescent="0.3">
+      <c r="Q150" s="3"/>
+    </row>
+    <row r="151" spans="17:17" x14ac:dyDescent="0.3">
+      <c r="Q151" s="3"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valore non previsto" error="Scegli un valore dal menu (Altro, Archivio, Articolo, Audio, Corrispondenza, Documento, Foto, Fotografia, Giornale, Libro, Manifesto, Opuscolo, Periodico, Rivista, Testo, Testo_bilingue, Volantino)." promptTitle="Tipo" prompt="Scegli dal menu a tendina." sqref="K2:K5000" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Altro,Archivio,Articolo,Audio,Corrispondenza,Documento,Foto,Fotografia,Giornale,Libro,Manifesto,Opuscolo,Periodico,Rivista,Testo,Testo_bilingue,Volantino"</formula1>
@@ -8959,11 +9891,22 @@
     <hyperlink ref="Q95" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
     <hyperlink ref="Q96" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
     <hyperlink ref="Q97" r:id="rId96" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
+    <hyperlink ref="Q107" r:id="rId97" xr:uid="{84EFB33B-614E-424D-A85B-52013F45CC70}"/>
+    <hyperlink ref="Q108" r:id="rId98" xr:uid="{D354A2B3-F7CC-400F-91B6-958C6DC2202E}"/>
+    <hyperlink ref="Q100" r:id="rId99" xr:uid="{023D6DEF-C997-4363-98D8-469EBE67785F}"/>
+    <hyperlink ref="Q101" r:id="rId100" xr:uid="{B92916DD-AC96-4C5B-98CB-54B2C6B8FC03}"/>
+    <hyperlink ref="Q103" r:id="rId101" xr:uid="{0626A0A1-E8BF-4830-9330-E6C52B21D359}"/>
+    <hyperlink ref="Q106" r:id="rId102" xr:uid="{8FB23791-4D7E-43F4-89B0-41A54816B954}"/>
+    <hyperlink ref="Q104" r:id="rId103" xr:uid="{C15A5608-D0DB-4EF0-9349-F45EE8F90308}"/>
+    <hyperlink ref="Q102" r:id="rId104" xr:uid="{B95ABED0-72C3-433C-A284-E9FA3C769DDB}"/>
+    <hyperlink ref="Q98" r:id="rId105" xr:uid="{ADF98019-316E-420E-AA94-2D2FBE06DF89}"/>
+    <hyperlink ref="Q99" r:id="rId106" xr:uid="{55A98A39-17A1-4E56-8B14-ED02E5A23751}"/>
+    <hyperlink ref="Q105" r:id="rId107" xr:uid="{09B963F9-4F3D-4F82-A0E7-92B1358B3997}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId97"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId108"/>
   <tableParts count="1">
-    <tablePart r:id="rId98"/>
+    <tablePart r:id="rId109"/>
   </tableParts>
 </worksheet>
 </file>
@@ -8981,275 +9924,275 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
+        <v>834</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>835</v>
+      </c>
+      <c r="C1" s="9" t="s">
         <v>836</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="D1" s="9" t="s">
         <v>837</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>838</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>839</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
+        <v>838</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>839</v>
+      </c>
+      <c r="C2" s="10" t="s">
         <v>840</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>841</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>842</v>
       </c>
       <c r="D2" s="10"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>243</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="D3" s="10"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="10"/>
       <c r="D4" s="10" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
+        <v>845</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>846</v>
+      </c>
+      <c r="C5" s="10" t="s">
         <v>847</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>848</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>849</v>
       </c>
       <c r="D5" s="10"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>260</v>
       </c>
       <c r="C6" s="10"/>
       <c r="D6" s="10" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
+        <v>850</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>851</v>
+      </c>
+      <c r="C7" s="10" t="s">
         <v>852</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>853</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>854</v>
       </c>
       <c r="D7" s="10"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="10" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="C8" s="10"/>
       <c r="D8" s="10"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="C9" s="10"/>
       <c r="D9" s="10" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="10" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="C10" s="10"/>
       <c r="D10" s="10" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="C11" s="10"/>
       <c r="D11" s="10" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="10" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="C12" s="10"/>
       <c r="D12" s="10"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="10" t="s">
+        <v>866</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>867</v>
+      </c>
+      <c r="C13" s="10" t="s">
         <v>868</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>869</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>870</v>
       </c>
       <c r="D13" s="10"/>
     </row>
     <row r="14" spans="1:4" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="10" t="s">
+        <v>869</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>870</v>
+      </c>
+      <c r="C14" s="10" t="s">
         <v>871</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>872</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>873</v>
       </c>
       <c r="D14" s="10"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="10" t="s">
+        <v>872</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>873</v>
+      </c>
+      <c r="C15" s="10" t="s">
         <v>874</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>875</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>876</v>
       </c>
       <c r="D15" s="10"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="10" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="D16" s="10"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="B17" s="10" t="s">
         <v>242</v>
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="10" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="10" t="s">
+        <v>879</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>880</v>
+      </c>
+      <c r="C18" s="10" t="s">
         <v>881</v>
-      </c>
-      <c r="B18" s="10" t="s">
-        <v>882</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>883</v>
       </c>
       <c r="D18" s="10"/>
     </row>
     <row r="19" spans="1:4" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="10" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="10" t="s">
+        <v>885</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>886</v>
+      </c>
+      <c r="C20" s="10" t="s">
         <v>887</v>
-      </c>
-      <c r="B20" s="10" t="s">
-        <v>888</v>
-      </c>
-      <c r="C20" s="10" t="s">
-        <v>889</v>
       </c>
       <c r="D20" s="10"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
+        <v>888</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>889</v>
+      </c>
+      <c r="C21" s="10" t="s">
         <v>890</v>
-      </c>
-      <c r="B21" s="10" t="s">
-        <v>891</v>
-      </c>
-      <c r="C21" s="10" t="s">
-        <v>892</v>
       </c>
       <c r="D21" s="10"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="10" t="s">
+        <v>891</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>892</v>
+      </c>
+      <c r="C22" s="10" t="s">
         <v>893</v>
-      </c>
-      <c r="B22" s="10" t="s">
-        <v>894</v>
-      </c>
-      <c r="C22" s="10" t="s">
-        <v>895</v>
       </c>
       <c r="D22" s="10"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
+        <v>894</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>895</v>
+      </c>
+      <c r="C23" s="10" t="s">
         <v>896</v>
-      </c>
-      <c r="B23" s="10" t="s">
-        <v>897</v>
-      </c>
-      <c r="C23" s="10" t="s">
-        <v>898</v>
       </c>
       <c r="D23" s="10"/>
     </row>
@@ -9283,58 +10226,58 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
+        <v>897</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>898</v>
+      </c>
+      <c r="C1" s="9" t="s">
         <v>899</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="D1" s="9" t="s">
         <v>900</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="E1" t="s">
         <v>901</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="F1" t="s">
         <v>902</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" s="9" t="s">
         <v>903</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>904</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="I1" t="s">
         <v>905</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>906</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" s="9" t="s">
         <v>907</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" s="9" t="s">
         <v>908</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="M1" s="9" t="s">
         <v>909</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="N1" s="9" t="s">
         <v>910</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="O1" s="9" t="s">
         <v>911</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="P1" s="9" t="s">
         <v>912</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="Q1" s="9" t="s">
         <v>913</v>
       </c>
-      <c r="P1" s="9" t="s">
+      <c r="R1" s="9" t="s">
         <v>914</v>
-      </c>
-      <c r="Q1" s="9" t="s">
-        <v>915</v>
-      </c>
-      <c r="R1" s="9" t="s">
-        <v>916</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
@@ -9342,22 +10285,22 @@
         <v>31</v>
       </c>
       <c r="B2" t="s">
+        <v>915</v>
+      </c>
+      <c r="C2" t="s">
+        <v>916</v>
+      </c>
+      <c r="D2" t="s">
         <v>917</v>
-      </c>
-      <c r="C2" t="s">
-        <v>918</v>
-      </c>
-      <c r="D2" t="s">
-        <v>919</v>
       </c>
       <c r="E2" t="s">
         <v>32</v>
       </c>
       <c r="F2" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="G2" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="H2">
         <v>1893</v>
@@ -9366,25 +10309,25 @@
         <v>1976</v>
       </c>
       <c r="J2" t="s">
+        <v>920</v>
+      </c>
+      <c r="M2" t="s">
+        <v>921</v>
+      </c>
+      <c r="N2" t="s">
         <v>922</v>
       </c>
-      <c r="M2" t="s">
+      <c r="O2" t="s">
         <v>923</v>
       </c>
-      <c r="N2" t="s">
+      <c r="P2" t="s">
         <v>924</v>
-      </c>
-      <c r="O2" t="s">
-        <v>925</v>
-      </c>
-      <c r="P2" t="s">
-        <v>926</v>
       </c>
       <c r="Q2" s="4">
         <v>46297</v>
       </c>
       <c r="R2" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
@@ -9392,19 +10335,19 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
+        <v>915</v>
+      </c>
+      <c r="C3" t="s">
+        <v>916</v>
+      </c>
+      <c r="D3" t="s">
         <v>917</v>
-      </c>
-      <c r="C3" t="s">
-        <v>918</v>
-      </c>
-      <c r="D3" t="s">
-        <v>919</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="H3">
         <v>1921</v>
@@ -9413,22 +10356,22 @@
         <v>1993</v>
       </c>
       <c r="J3" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="M3" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="O3" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="P3" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="Q3" s="4">
         <v>46297</v>
       </c>
       <c r="R3" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
@@ -9436,19 +10379,19 @@
         <v>17</v>
       </c>
       <c r="B4" t="s">
+        <v>915</v>
+      </c>
+      <c r="C4" t="s">
+        <v>916</v>
+      </c>
+      <c r="D4" t="s">
         <v>917</v>
-      </c>
-      <c r="C4" t="s">
-        <v>918</v>
-      </c>
-      <c r="D4" t="s">
-        <v>919</v>
       </c>
       <c r="E4" t="s">
         <v>18</v>
       </c>
       <c r="F4" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="H4">
         <v>1938</v>
@@ -9457,42 +10400,42 @@
         <v>2021</v>
       </c>
       <c r="J4" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="O4" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="P4" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="Q4" s="4">
         <v>46297</v>
       </c>
       <c r="R4" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="B5" t="s">
+        <v>915</v>
+      </c>
+      <c r="C5" t="s">
+        <v>916</v>
+      </c>
+      <c r="D5" t="s">
         <v>917</v>
-      </c>
-      <c r="C5" t="s">
-        <v>918</v>
-      </c>
-      <c r="D5" t="s">
-        <v>919</v>
       </c>
       <c r="E5" t="s">
         <v>321</v>
       </c>
       <c r="F5" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="G5" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="H5">
         <v>1931</v>
@@ -9501,42 +10444,42 @@
         <v>2005</v>
       </c>
       <c r="M5" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="N5" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="O5" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="P5" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="Q5" s="4">
         <v>46297</v>
       </c>
       <c r="R5" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>936</v>
+      </c>
+      <c r="B6" t="s">
+        <v>915</v>
+      </c>
+      <c r="C6" t="s">
+        <v>916</v>
+      </c>
+      <c r="D6" t="s">
+        <v>917</v>
+      </c>
+      <c r="E6" t="s">
+        <v>937</v>
+      </c>
+      <c r="F6" t="s">
         <v>938</v>
-      </c>
-      <c r="B6" t="s">
-        <v>917</v>
-      </c>
-      <c r="C6" t="s">
-        <v>918</v>
-      </c>
-      <c r="D6" t="s">
-        <v>919</v>
-      </c>
-      <c r="E6" t="s">
-        <v>939</v>
-      </c>
-      <c r="F6" t="s">
-        <v>940</v>
       </c>
       <c r="H6">
         <v>1960</v>
@@ -9545,16 +10488,16 @@
         <v>2023</v>
       </c>
       <c r="O6" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="P6" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="Q6" s="4">
         <v>46297</v>
       </c>
       <c r="R6" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
@@ -9562,37 +10505,37 @@
         <v>64</v>
       </c>
       <c r="B7" t="s">
+        <v>915</v>
+      </c>
+      <c r="C7" t="s">
+        <v>916</v>
+      </c>
+      <c r="D7" t="s">
         <v>917</v>
-      </c>
-      <c r="C7" t="s">
-        <v>918</v>
-      </c>
-      <c r="D7" t="s">
-        <v>919</v>
       </c>
       <c r="E7" t="s">
         <v>65</v>
       </c>
       <c r="F7" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="H7" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="I7" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="O7" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="P7" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="Q7" s="4">
         <v>46297</v>
       </c>
       <c r="R7" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
@@ -9600,63 +10543,63 @@
         <v>41</v>
       </c>
       <c r="B8" t="s">
+        <v>915</v>
+      </c>
+      <c r="C8" t="s">
+        <v>916</v>
+      </c>
+      <c r="D8" t="s">
         <v>917</v>
-      </c>
-      <c r="C8" t="s">
-        <v>918</v>
-      </c>
-      <c r="D8" t="s">
-        <v>919</v>
       </c>
       <c r="E8" t="s">
         <v>42</v>
       </c>
       <c r="F8" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="H8" t="s">
+        <v>940</v>
+      </c>
+      <c r="I8" t="s">
+        <v>940</v>
+      </c>
+      <c r="J8" t="s">
         <v>942</v>
       </c>
-      <c r="I8" t="s">
-        <v>942</v>
-      </c>
-      <c r="J8" t="s">
-        <v>944</v>
-      </c>
       <c r="O8" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="P8" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="Q8" s="4">
         <v>46297</v>
       </c>
       <c r="R8" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>943</v>
+      </c>
+      <c r="B9" t="s">
+        <v>915</v>
+      </c>
+      <c r="C9" t="s">
+        <v>916</v>
+      </c>
+      <c r="D9" t="s">
+        <v>917</v>
+      </c>
+      <c r="E9" t="s">
+        <v>805</v>
+      </c>
+      <c r="F9" t="s">
+        <v>944</v>
+      </c>
+      <c r="G9" t="s">
         <v>945</v>
-      </c>
-      <c r="B9" t="s">
-        <v>917</v>
-      </c>
-      <c r="C9" t="s">
-        <v>918</v>
-      </c>
-      <c r="D9" t="s">
-        <v>919</v>
-      </c>
-      <c r="E9" t="s">
-        <v>807</v>
-      </c>
-      <c r="F9" t="s">
-        <v>946</v>
-      </c>
-      <c r="G9" t="s">
-        <v>947</v>
       </c>
       <c r="H9">
         <v>1907</v>
@@ -9665,42 +10608,42 @@
         <v>1971</v>
       </c>
       <c r="M9" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="N9" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="O9" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="P9" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="Q9" s="4">
         <v>46297</v>
       </c>
       <c r="R9" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>948</v>
+      </c>
+      <c r="B10" t="s">
+        <v>915</v>
+      </c>
+      <c r="C10" t="s">
+        <v>916</v>
+      </c>
+      <c r="D10" t="s">
+        <v>917</v>
+      </c>
+      <c r="E10" t="s">
+        <v>949</v>
+      </c>
+      <c r="F10" t="s">
         <v>950</v>
-      </c>
-      <c r="B10" t="s">
-        <v>917</v>
-      </c>
-      <c r="C10" t="s">
-        <v>918</v>
-      </c>
-      <c r="D10" t="s">
-        <v>919</v>
-      </c>
-      <c r="E10" t="s">
-        <v>951</v>
-      </c>
-      <c r="F10" t="s">
-        <v>952</v>
       </c>
       <c r="H10">
         <v>1898</v>
@@ -9709,45 +10652,45 @@
         <v>1975</v>
       </c>
       <c r="M10" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="N10" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="O10" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="P10" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="Q10" s="4">
         <v>46297</v>
       </c>
       <c r="R10" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>953</v>
+      </c>
+      <c r="B11" t="s">
+        <v>915</v>
+      </c>
+      <c r="C11" t="s">
+        <v>916</v>
+      </c>
+      <c r="D11" t="s">
+        <v>917</v>
+      </c>
+      <c r="E11" t="s">
+        <v>954</v>
+      </c>
+      <c r="F11" t="s">
         <v>955</v>
       </c>
-      <c r="B11" t="s">
-        <v>917</v>
-      </c>
-      <c r="C11" t="s">
-        <v>918</v>
-      </c>
-      <c r="D11" t="s">
-        <v>919</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="G11" t="s">
         <v>956</v>
-      </c>
-      <c r="F11" t="s">
-        <v>957</v>
-      </c>
-      <c r="G11" t="s">
-        <v>958</v>
       </c>
       <c r="H11">
         <v>1898</v>
@@ -9756,45 +10699,45 @@
         <v>1976</v>
       </c>
       <c r="M11" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="N11" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="O11" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="P11" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="Q11" s="4">
         <v>46297</v>
       </c>
       <c r="R11" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>959</v>
+      </c>
+      <c r="B12" t="s">
+        <v>915</v>
+      </c>
+      <c r="C12" t="s">
+        <v>916</v>
+      </c>
+      <c r="D12" t="s">
+        <v>917</v>
+      </c>
+      <c r="E12" t="s">
+        <v>960</v>
+      </c>
+      <c r="F12" t="s">
         <v>961</v>
       </c>
-      <c r="B12" t="s">
-        <v>917</v>
-      </c>
-      <c r="C12" t="s">
-        <v>918</v>
-      </c>
-      <c r="D12" t="s">
-        <v>919</v>
-      </c>
-      <c r="E12" t="s">
+      <c r="G12" t="s">
         <v>962</v>
-      </c>
-      <c r="F12" t="s">
-        <v>963</v>
-      </c>
-      <c r="G12" t="s">
-        <v>964</v>
       </c>
       <c r="H12">
         <v>1904</v>
@@ -9803,45 +10746,45 @@
         <v>1989</v>
       </c>
       <c r="M12" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="N12" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="O12" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="P12" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="Q12" s="4">
         <v>46297</v>
       </c>
       <c r="R12" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>965</v>
+      </c>
+      <c r="B13" t="s">
+        <v>915</v>
+      </c>
+      <c r="C13" t="s">
+        <v>916</v>
+      </c>
+      <c r="D13" t="s">
+        <v>917</v>
+      </c>
+      <c r="E13" t="s">
+        <v>966</v>
+      </c>
+      <c r="F13" t="s">
         <v>967</v>
       </c>
-      <c r="B13" t="s">
-        <v>917</v>
-      </c>
-      <c r="C13" t="s">
-        <v>918</v>
-      </c>
-      <c r="D13" t="s">
-        <v>919</v>
-      </c>
-      <c r="E13" t="s">
+      <c r="G13" t="s">
         <v>968</v>
-      </c>
-      <c r="F13" t="s">
-        <v>969</v>
-      </c>
-      <c r="G13" t="s">
-        <v>970</v>
       </c>
       <c r="H13">
         <v>1914</v>
@@ -9850,22 +10793,22 @@
         <v>1991</v>
       </c>
       <c r="M13" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="N13" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="O13" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="P13" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="Q13" s="4">
         <v>46297</v>
       </c>
       <c r="R13" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
@@ -9873,19 +10816,19 @@
         <v>217</v>
       </c>
       <c r="B14" t="s">
+        <v>915</v>
+      </c>
+      <c r="C14" t="s">
+        <v>916</v>
+      </c>
+      <c r="D14" t="s">
         <v>917</v>
-      </c>
-      <c r="C14" t="s">
-        <v>918</v>
-      </c>
-      <c r="D14" t="s">
-        <v>919</v>
       </c>
       <c r="E14" t="s">
         <v>218</v>
       </c>
       <c r="F14" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="H14">
         <v>1920</v>
@@ -9894,22 +10837,22 @@
         <v>2004</v>
       </c>
       <c r="M14" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="N14" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="O14" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="P14" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="Q14" s="4">
         <v>46297</v>
       </c>
       <c r="R14" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
@@ -9917,19 +10860,19 @@
         <v>83</v>
       </c>
       <c r="B15" t="s">
+        <v>915</v>
+      </c>
+      <c r="C15" t="s">
+        <v>916</v>
+      </c>
+      <c r="D15" t="s">
         <v>917</v>
-      </c>
-      <c r="C15" t="s">
-        <v>918</v>
-      </c>
-      <c r="D15" t="s">
-        <v>919</v>
       </c>
       <c r="E15" t="s">
         <v>84</v>
       </c>
       <c r="F15" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="H15">
         <v>1920</v>
@@ -9938,39 +10881,39 @@
         <v>1997</v>
       </c>
       <c r="O15" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="P15" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="Q15" s="4">
         <v>46297</v>
       </c>
       <c r="R15" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="B16" t="s">
+        <v>915</v>
+      </c>
+      <c r="C16" t="s">
+        <v>916</v>
+      </c>
+      <c r="D16" t="s">
         <v>917</v>
-      </c>
-      <c r="C16" t="s">
-        <v>918</v>
-      </c>
-      <c r="D16" t="s">
-        <v>919</v>
       </c>
       <c r="E16" t="s">
         <v>632</v>
       </c>
       <c r="F16" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="G16" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="H16">
         <v>1898</v>
@@ -9979,42 +10922,42 @@
         <v>1969</v>
       </c>
       <c r="M16" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="N16" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="O16" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="P16" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="Q16" s="4">
         <v>46297</v>
       </c>
       <c r="R16" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="B17" t="s">
+        <v>915</v>
+      </c>
+      <c r="C17" t="s">
+        <v>916</v>
+      </c>
+      <c r="D17" t="s">
         <v>917</v>
-      </c>
-      <c r="C17" t="s">
-        <v>918</v>
-      </c>
-      <c r="D17" t="s">
-        <v>919</v>
       </c>
       <c r="E17" t="s">
         <v>621</v>
       </c>
       <c r="F17" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="H17">
         <v>1924</v>
@@ -10023,22 +10966,22 @@
         <v>2010</v>
       </c>
       <c r="M17" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="N17" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="O17" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="P17" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="Q17" s="4">
         <v>46297</v>
       </c>
       <c r="R17" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
@@ -10046,19 +10989,19 @@
         <v>183</v>
       </c>
       <c r="B18" t="s">
+        <v>915</v>
+      </c>
+      <c r="C18" t="s">
+        <v>916</v>
+      </c>
+      <c r="D18" t="s">
         <v>917</v>
-      </c>
-      <c r="C18" t="s">
-        <v>918</v>
-      </c>
-      <c r="D18" t="s">
-        <v>919</v>
       </c>
       <c r="E18" t="s">
         <v>184</v>
       </c>
       <c r="F18" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="H18">
         <v>1933</v>
@@ -10067,22 +11010,22 @@
         <v>1996</v>
       </c>
       <c r="M18" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="N18" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="O18" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="P18" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="Q18" s="4">
         <v>46297</v>
       </c>
       <c r="R18" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
@@ -10090,40 +11033,40 @@
         <v>107</v>
       </c>
       <c r="B19" t="s">
+        <v>915</v>
+      </c>
+      <c r="C19" t="s">
+        <v>916</v>
+      </c>
+      <c r="D19" t="s">
         <v>917</v>
-      </c>
-      <c r="C19" t="s">
-        <v>918</v>
-      </c>
-      <c r="D19" t="s">
-        <v>919</v>
       </c>
       <c r="E19" t="s">
         <v>108</v>
       </c>
       <c r="F19" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="H19">
         <v>1941</v>
       </c>
       <c r="M19" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="N19" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="O19" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="P19" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="Q19" s="4">
         <v>46299</v>
       </c>
       <c r="R19" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
@@ -10131,31 +11074,31 @@
         <v>187</v>
       </c>
       <c r="B20" t="s">
+        <v>915</v>
+      </c>
+      <c r="C20" t="s">
+        <v>916</v>
+      </c>
+      <c r="D20" t="s">
         <v>917</v>
-      </c>
-      <c r="C20" t="s">
-        <v>918</v>
-      </c>
-      <c r="D20" t="s">
-        <v>919</v>
       </c>
       <c r="E20" t="s">
         <v>188</v>
       </c>
       <c r="F20" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="O20" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="P20" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="Q20" s="4">
         <v>46299</v>
       </c>
       <c r="R20" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
@@ -10163,22 +11106,22 @@
         <v>93</v>
       </c>
       <c r="B21" t="s">
+        <v>915</v>
+      </c>
+      <c r="C21" t="s">
+        <v>916</v>
+      </c>
+      <c r="D21" t="s">
         <v>917</v>
-      </c>
-      <c r="C21" t="s">
-        <v>918</v>
-      </c>
-      <c r="D21" t="s">
-        <v>919</v>
       </c>
       <c r="E21" t="s">
         <v>94</v>
       </c>
       <c r="F21" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="G21" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="H21">
         <v>1898</v>
@@ -10187,19 +11130,19 @@
         <v>1973</v>
       </c>
       <c r="M21" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="O21" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="P21" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="Q21" s="4">
         <v>46299</v>
       </c>
       <c r="R21" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
@@ -10207,22 +11150,22 @@
         <v>100</v>
       </c>
       <c r="B22" t="s">
+        <v>915</v>
+      </c>
+      <c r="C22" t="s">
+        <v>916</v>
+      </c>
+      <c r="D22" t="s">
         <v>917</v>
-      </c>
-      <c r="C22" t="s">
-        <v>918</v>
-      </c>
-      <c r="D22" t="s">
-        <v>919</v>
       </c>
       <c r="E22" t="s">
         <v>101</v>
       </c>
       <c r="F22" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="G22" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="H22">
         <v>1927</v>
@@ -10231,16 +11174,16 @@
         <v>2009</v>
       </c>
       <c r="O22" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="P22" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="Q22" s="4">
         <v>46299</v>
       </c>
       <c r="R22" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
@@ -10248,19 +11191,19 @@
         <v>115</v>
       </c>
       <c r="B23" t="s">
+        <v>915</v>
+      </c>
+      <c r="C23" t="s">
+        <v>916</v>
+      </c>
+      <c r="D23" t="s">
         <v>917</v>
-      </c>
-      <c r="C23" t="s">
-        <v>918</v>
-      </c>
-      <c r="D23" t="s">
-        <v>919</v>
       </c>
       <c r="E23" t="s">
         <v>116</v>
       </c>
       <c r="F23" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="H23">
         <v>1936</v>
@@ -10269,22 +11212,22 @@
         <v>1994</v>
       </c>
       <c r="M23" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="N23" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="O23" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="P23" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="Q23" s="4">
         <v>46299</v>
       </c>
       <c r="R23" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
@@ -10292,34 +11235,34 @@
         <v>148</v>
       </c>
       <c r="B24" t="s">
+        <v>915</v>
+      </c>
+      <c r="C24" t="s">
+        <v>916</v>
+      </c>
+      <c r="D24" t="s">
         <v>917</v>
-      </c>
-      <c r="C24" t="s">
-        <v>918</v>
-      </c>
-      <c r="D24" t="s">
-        <v>919</v>
       </c>
       <c r="E24" t="s">
         <v>149</v>
       </c>
       <c r="F24" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="G24" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="O24" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="P24" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="Q24" s="4">
         <v>46299</v>
       </c>
       <c r="R24" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.3">
@@ -10327,31 +11270,31 @@
         <v>152</v>
       </c>
       <c r="B25" t="s">
+        <v>915</v>
+      </c>
+      <c r="C25" t="s">
+        <v>916</v>
+      </c>
+      <c r="D25" t="s">
         <v>917</v>
-      </c>
-      <c r="C25" t="s">
-        <v>918</v>
-      </c>
-      <c r="D25" t="s">
-        <v>919</v>
       </c>
       <c r="E25" t="s">
         <v>153</v>
       </c>
       <c r="F25" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="O25" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="P25" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="Q25" s="4">
         <v>46299</v>
       </c>
       <c r="R25" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.3">
@@ -10359,40 +11302,40 @@
         <v>163</v>
       </c>
       <c r="B26" t="s">
+        <v>915</v>
+      </c>
+      <c r="C26" t="s">
+        <v>916</v>
+      </c>
+      <c r="D26" t="s">
         <v>917</v>
-      </c>
-      <c r="C26" t="s">
-        <v>918</v>
-      </c>
-      <c r="D26" t="s">
-        <v>919</v>
       </c>
       <c r="E26" t="s">
         <v>164</v>
       </c>
       <c r="F26" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="H26">
         <v>1945</v>
       </c>
       <c r="M26" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="N26" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="O26" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="P26" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="Q26" s="4">
         <v>46299</v>
       </c>
       <c r="R26" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.3">
@@ -10400,31 +11343,31 @@
         <v>121</v>
       </c>
       <c r="B27" t="s">
+        <v>915</v>
+      </c>
+      <c r="C27" t="s">
+        <v>916</v>
+      </c>
+      <c r="D27" t="s">
         <v>917</v>
-      </c>
-      <c r="C27" t="s">
-        <v>918</v>
-      </c>
-      <c r="D27" t="s">
-        <v>919</v>
       </c>
       <c r="E27" t="s">
         <v>122</v>
       </c>
       <c r="F27" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="O27" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="P27" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="Q27" s="4">
         <v>46299</v>
       </c>
       <c r="R27" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
     </row>
   </sheetData>
@@ -10437,7 +11380,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:R30"/>
+  <dimension ref="A1:R31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.6640625" customWidth="1"/>
@@ -10460,58 +11403,58 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
+        <v>897</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>898</v>
+      </c>
+      <c r="C1" s="9" t="s">
         <v>899</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="D1" s="9" t="s">
         <v>900</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="E1" t="s">
         <v>901</v>
       </c>
-      <c r="D1" s="9" t="s">
-        <v>902</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="F1" s="9" t="s">
         <v>903</v>
       </c>
-      <c r="F1" s="9" t="s">
-        <v>905</v>
-      </c>
       <c r="G1" t="s">
+        <v>1007</v>
+      </c>
+      <c r="H1" t="s">
+        <v>1008</v>
+      </c>
+      <c r="I1" t="s">
         <v>1009</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
+        <v>906</v>
+      </c>
+      <c r="K1" s="9" t="s">
         <v>1010</v>
       </c>
-      <c r="I1" t="s">
-        <v>1011</v>
-      </c>
-      <c r="J1" t="s">
+      <c r="L1" s="9" t="s">
         <v>908</v>
       </c>
-      <c r="K1" s="9" t="s">
-        <v>1012</v>
-      </c>
-      <c r="L1" s="9" t="s">
+      <c r="M1" s="9" t="s">
+        <v>909</v>
+      </c>
+      <c r="N1" s="9" t="s">
         <v>910</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="O1" s="9" t="s">
         <v>911</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="P1" s="9" t="s">
         <v>912</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="Q1" s="9" t="s">
         <v>913</v>
       </c>
-      <c r="P1" s="9" t="s">
+      <c r="R1" s="9" t="s">
         <v>914</v>
-      </c>
-      <c r="Q1" s="9" t="s">
-        <v>915</v>
-      </c>
-      <c r="R1" s="9" t="s">
-        <v>916</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
@@ -10519,78 +11462,78 @@
         <v>85</v>
       </c>
       <c r="B2" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="C2" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="D2" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="E2" t="s">
         <v>86</v>
       </c>
       <c r="G2" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="H2">
         <v>1962</v>
       </c>
       <c r="I2" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="O2" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="P2" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="Q2" s="4">
         <v>46297</v>
       </c>
       <c r="R2" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="B3" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="C3" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="D3" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="E3" t="s">
         <v>267</v>
       </c>
       <c r="G3" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="H3">
         <v>1952</v>
       </c>
       <c r="M3" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="N3" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="O3" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="P3" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="Q3" s="4">
         <v>46297</v>
       </c>
       <c r="R3" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
@@ -10598,19 +11541,19 @@
         <v>96</v>
       </c>
       <c r="B4" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="C4" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="D4" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="E4" t="s">
         <v>97</v>
       </c>
       <c r="G4" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="H4">
         <v>1963</v>
@@ -10619,80 +11562,80 @@
         <v>1979</v>
       </c>
       <c r="O4" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="P4" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="Q4" s="4">
         <v>46297</v>
       </c>
       <c r="R4" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="B5" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="C5" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="D5" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="E5" t="s">
         <v>338</v>
       </c>
       <c r="F5" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="G5" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="H5">
         <v>1948</v>
       </c>
       <c r="M5" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="O5" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="P5" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="Q5" s="4">
         <v>46297</v>
       </c>
       <c r="R5" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="B6" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="C6" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="D6" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="E6" t="s">
         <v>322</v>
       </c>
       <c r="F6" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="G6" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="H6">
         <v>1958</v>
@@ -10701,22 +11644,22 @@
         <v>1988</v>
       </c>
       <c r="M6" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="N6" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="O6" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="P6" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="Q6" s="4">
         <v>46297</v>
       </c>
       <c r="R6" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
@@ -10724,22 +11667,22 @@
         <v>190</v>
       </c>
       <c r="B7" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="C7" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="D7" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="E7" t="s">
         <v>191</v>
       </c>
       <c r="F7" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="G7" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="H7">
         <v>1964</v>
@@ -10748,95 +11691,95 @@
         <v>1991</v>
       </c>
       <c r="O7" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="P7" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="Q7" s="4">
         <v>46297</v>
       </c>
       <c r="R7" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>1028</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C8" t="s">
+        <v>916</v>
+      </c>
+      <c r="D8" t="s">
+        <v>917</v>
+      </c>
+      <c r="E8" t="s">
+        <v>1029</v>
+      </c>
+      <c r="F8" t="s">
         <v>1030</v>
       </c>
-      <c r="B8" t="s">
-        <v>1013</v>
-      </c>
-      <c r="C8" t="s">
-        <v>918</v>
-      </c>
-      <c r="D8" t="s">
-        <v>919</v>
-      </c>
-      <c r="E8" t="s">
-        <v>1031</v>
-      </c>
-      <c r="F8" t="s">
-        <v>1032</v>
-      </c>
       <c r="G8" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="H8">
         <v>1956</v>
       </c>
       <c r="M8" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="O8" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="P8" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="Q8" s="4">
         <v>46297</v>
       </c>
       <c r="R8" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="B9" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="C9" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="D9" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="E9" t="s">
         <v>392</v>
       </c>
       <c r="G9" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="H9" t="s">
         <v>91</v>
       </c>
       <c r="I9" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="O9" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="P9" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="Q9" s="4">
         <v>46297</v>
       </c>
       <c r="R9" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
@@ -10844,19 +11787,19 @@
         <v>49</v>
       </c>
       <c r="B10" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="C10" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="D10" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="E10" t="s">
         <v>50</v>
       </c>
       <c r="G10" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="H10">
         <v>1966</v>
@@ -10865,16 +11808,16 @@
         <v>1991</v>
       </c>
       <c r="O10" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="P10" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="Q10" s="4">
         <v>46297</v>
       </c>
       <c r="R10" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
@@ -10882,19 +11825,19 @@
         <v>53</v>
       </c>
       <c r="B11" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="C11" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="D11" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="E11" t="s">
         <v>54</v>
       </c>
       <c r="G11" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="H11">
         <v>1968</v>
@@ -10903,16 +11846,16 @@
         <v>1972</v>
       </c>
       <c r="O11" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="P11" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="Q11" s="4">
         <v>46297</v>
       </c>
       <c r="R11" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
@@ -10920,22 +11863,22 @@
         <v>234</v>
       </c>
       <c r="B12" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="C12" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="D12" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="E12" t="s">
         <v>235</v>
       </c>
       <c r="F12" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="G12" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="H12">
         <v>1966</v>
@@ -10944,16 +11887,16 @@
         <v>1991</v>
       </c>
       <c r="O12" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="P12" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="Q12" s="4">
         <v>46297</v>
       </c>
       <c r="R12" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
@@ -10961,40 +11904,40 @@
         <v>38</v>
       </c>
       <c r="B13" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="C13" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="D13" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="E13" t="s">
         <v>39</v>
       </c>
       <c r="G13" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="H13">
         <v>1921</v>
       </c>
       <c r="M13" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="N13" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="O13" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="P13" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="Q13" s="4">
         <v>46297</v>
       </c>
       <c r="R13" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
@@ -11002,22 +11945,22 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="C14" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="D14" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="E14" t="s">
         <v>12</v>
       </c>
       <c r="F14" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="G14" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="H14">
         <v>1966</v>
@@ -11026,25 +11969,25 @@
         <v>1991</v>
       </c>
       <c r="J14" t="s">
+        <v>1042</v>
+      </c>
+      <c r="M14" t="s">
+        <v>1043</v>
+      </c>
+      <c r="N14" t="s">
         <v>1044</v>
       </c>
-      <c r="M14" t="s">
-        <v>1045</v>
-      </c>
-      <c r="N14" t="s">
-        <v>1046</v>
-      </c>
       <c r="O14" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="P14" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="Q14" s="4">
         <v>46297</v>
       </c>
       <c r="R14" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
@@ -11052,22 +11995,22 @@
         <v>55</v>
       </c>
       <c r="B15" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="C15" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="D15" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="E15" t="s">
         <v>56</v>
       </c>
       <c r="F15" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="G15" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="H15">
         <v>1968</v>
@@ -11076,25 +12019,25 @@
         <v>1972</v>
       </c>
       <c r="J15" t="s">
+        <v>1046</v>
+      </c>
+      <c r="M15" t="s">
+        <v>1047</v>
+      </c>
+      <c r="N15" t="s">
         <v>1048</v>
       </c>
-      <c r="M15" t="s">
-        <v>1049</v>
-      </c>
-      <c r="N15" t="s">
-        <v>1050</v>
-      </c>
       <c r="O15" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="P15" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="Q15" s="4">
         <v>46297</v>
       </c>
       <c r="R15" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
@@ -11102,46 +12045,46 @@
         <v>33</v>
       </c>
       <c r="B16" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="C16" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="D16" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="E16" t="s">
         <v>34</v>
       </c>
       <c r="F16" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="G16" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="H16">
         <v>1921</v>
       </c>
       <c r="J16" t="s">
+        <v>1050</v>
+      </c>
+      <c r="M16" t="s">
+        <v>1051</v>
+      </c>
+      <c r="N16" t="s">
         <v>1052</v>
       </c>
-      <c r="M16" t="s">
-        <v>1053</v>
-      </c>
-      <c r="N16" t="s">
-        <v>1054</v>
-      </c>
       <c r="O16" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="P16" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="Q16" s="4">
         <v>46297</v>
       </c>
       <c r="R16" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
@@ -11149,22 +12092,22 @@
         <v>45</v>
       </c>
       <c r="B17" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="C17" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="D17" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="E17" t="s">
         <v>46</v>
       </c>
       <c r="F17" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="G17" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="H17">
         <v>1968</v>
@@ -11173,16 +12116,16 @@
         <v>1977</v>
       </c>
       <c r="O17" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="P17" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="Q17" s="4">
         <v>46297</v>
       </c>
       <c r="R17" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
@@ -11190,22 +12133,22 @@
         <v>66</v>
       </c>
       <c r="B18" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="C18" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="D18" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="E18" t="s">
         <v>67</v>
       </c>
       <c r="F18" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="G18" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="H18">
         <v>1969</v>
@@ -11214,16 +12157,16 @@
         <v>1976</v>
       </c>
       <c r="O18" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="P18" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="Q18" s="4">
         <v>46297</v>
       </c>
       <c r="R18" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
@@ -11231,37 +12174,37 @@
         <v>117</v>
       </c>
       <c r="B19" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="C19" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="D19" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="E19" t="s">
         <v>118</v>
       </c>
       <c r="G19" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="H19">
         <v>1968</v>
       </c>
       <c r="I19" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="O19" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="P19" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="Q19" s="4">
         <v>46297</v>
       </c>
       <c r="R19" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
@@ -11269,22 +12212,22 @@
         <v>104</v>
       </c>
       <c r="B20" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="C20" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="D20" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="E20" t="s">
         <v>105</v>
       </c>
       <c r="F20" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="G20" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="H20">
         <v>1972</v>
@@ -11293,22 +12236,22 @@
         <v>1978</v>
       </c>
       <c r="M20" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="N20" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="O20" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="P20" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="Q20" s="4">
         <v>46297</v>
       </c>
       <c r="R20" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
@@ -11316,19 +12259,19 @@
         <v>220</v>
       </c>
       <c r="B21" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="C21" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="D21" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="E21" t="s">
         <v>221</v>
       </c>
       <c r="G21" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="H21">
         <v>1967</v>
@@ -11337,16 +12280,16 @@
         <v>1969</v>
       </c>
       <c r="O21" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="P21" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="Q21" s="4">
         <v>46297</v>
       </c>
       <c r="R21" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
@@ -11354,22 +12297,22 @@
         <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="C22" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="D22" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="E22" t="s">
         <v>28</v>
       </c>
       <c r="F22" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="G22" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="H22">
         <v>1977</v>
@@ -11378,19 +12321,19 @@
         <v>1984</v>
       </c>
       <c r="M22" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="O22" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="P22" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="Q22" s="4">
         <v>46297</v>
       </c>
       <c r="R22" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
@@ -11398,22 +12341,22 @@
         <v>169</v>
       </c>
       <c r="B23" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="C23" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="D23" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="E23" t="s">
         <v>170</v>
       </c>
       <c r="F23" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="G23" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="H23">
         <v>1970</v>
@@ -11422,16 +12365,16 @@
         <v>1973</v>
       </c>
       <c r="O23" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="P23" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="Q23" s="4">
         <v>46297</v>
       </c>
       <c r="R23" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
@@ -11439,19 +12382,19 @@
         <v>175</v>
       </c>
       <c r="B24" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="C24" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="D24" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="E24" t="s">
         <v>176</v>
       </c>
       <c r="G24" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="H24">
         <v>1969</v>
@@ -11460,16 +12403,16 @@
         <v>1972</v>
       </c>
       <c r="O24" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="P24" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="Q24" s="4">
         <v>46297</v>
       </c>
       <c r="R24" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.3">
@@ -11477,22 +12420,22 @@
         <v>137</v>
       </c>
       <c r="B25" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="C25" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="D25" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="E25" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="F25" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="G25" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="H25">
         <v>1973</v>
@@ -11501,16 +12444,16 @@
         <v>1977</v>
       </c>
       <c r="O25" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="P25" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="Q25" s="4">
         <v>46297</v>
       </c>
       <c r="R25" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.3">
@@ -11518,19 +12461,19 @@
         <v>165</v>
       </c>
       <c r="B26" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="C26" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="D26" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="E26" t="s">
         <v>166</v>
       </c>
       <c r="G26" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="H26">
         <v>1968</v>
@@ -11539,22 +12482,22 @@
         <v>1976</v>
       </c>
       <c r="M26" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="N26" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="O26" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="P26" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="Q26" s="4">
         <v>46297</v>
       </c>
       <c r="R26" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.3">
@@ -11562,22 +12505,22 @@
         <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="C27" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="D27" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="E27" t="s">
         <v>24</v>
       </c>
       <c r="F27" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="G27" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="H27">
         <v>1970</v>
@@ -11586,16 +12529,16 @@
         <v>1977</v>
       </c>
       <c r="O27" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="P27" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="Q27" s="4">
         <v>46297</v>
       </c>
       <c r="R27" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.3">
@@ -11603,22 +12546,22 @@
         <v>139</v>
       </c>
       <c r="B28" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="C28" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="D28" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="E28" t="s">
         <v>140</v>
       </c>
       <c r="F28" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="G28" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="H28">
         <v>1969</v>
@@ -11627,16 +12570,16 @@
         <v>1977</v>
       </c>
       <c r="O28" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="P28" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="Q28" s="4">
         <v>46297</v>
       </c>
       <c r="R28" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.3">
@@ -11644,22 +12587,22 @@
         <v>128</v>
       </c>
       <c r="B29" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="C29" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="D29" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="E29" t="s">
         <v>129</v>
       </c>
       <c r="F29" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="G29" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="H29">
         <v>1969</v>
@@ -11668,16 +12611,16 @@
         <v>1977</v>
       </c>
       <c r="O29" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="P29" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="Q29" s="4">
         <v>46297</v>
       </c>
       <c r="R29" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.3">
@@ -11685,34 +12628,73 @@
         <v>111</v>
       </c>
       <c r="B30" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="C30" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="D30" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="E30" t="s">
         <v>112</v>
       </c>
       <c r="G30" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="O30" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="P30" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="Q30" s="4">
         <v>46299</v>
       </c>
       <c r="R30" t="s">
-        <v>1016</v>
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B31" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C31" t="s">
+        <v>1117</v>
+      </c>
+      <c r="D31" t="s">
+        <v>917</v>
+      </c>
+      <c r="E31" t="s">
+        <v>1115</v>
+      </c>
+      <c r="G31" t="s">
+        <v>1033</v>
+      </c>
+      <c r="H31">
+        <v>1965</v>
+      </c>
+      <c r="I31">
+        <v>1966</v>
+      </c>
+      <c r="O31" t="s">
+        <v>923</v>
+      </c>
+      <c r="P31" t="s">
+        <v>924</v>
+      </c>
+      <c r="Q31" s="4">
+        <v>46322</v>
+      </c>
+      <c r="R31" t="s">
+        <v>1014</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
@@ -11722,7 +12704,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:H71"/>
+  <dimension ref="A1:H72"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.21875" customWidth="1"/>
@@ -12554,7 +13536,7 @@
         <v>137</v>
       </c>
       <c r="C33" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="D33" t="s">
         <v>27</v>
@@ -12684,7 +13666,7 @@
         <v>137</v>
       </c>
       <c r="E38" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="F38" t="s">
         <v>13</v>
@@ -12776,7 +13758,7 @@
         <v>137</v>
       </c>
       <c r="C42" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="D42" t="s">
         <v>11</v>
@@ -12805,7 +13787,7 @@
         <v>137</v>
       </c>
       <c r="E43" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="F43" t="s">
         <v>156</v>
@@ -13470,7 +14452,34 @@
         <v>43</v>
       </c>
     </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>1118</v>
+      </c>
+      <c r="B72" t="s">
+        <v>1116</v>
+      </c>
+      <c r="C72" t="s">
+        <v>1115</v>
+      </c>
+      <c r="D72" t="s">
+        <v>11</v>
+      </c>
+      <c r="E72" t="s">
+        <v>12</v>
+      </c>
+      <c r="F72" t="s">
+        <v>71</v>
+      </c>
+      <c r="G72" t="s">
+        <v>62</v>
+      </c>
+      <c r="H72">
+        <v>1966</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valore non previsto" error="Scegli un valore dal menu (associativa, familiare, gerarchica, temporale)." promptTitle="Categoria_ISAAR" prompt="Scegli dal menu a tendina." sqref="G2:G5000" xr:uid="{00000000-0002-0000-0400-000000000000}">
       <formula1>"associativa,familiare,gerarchica,temporale"</formula1>

--- a/data/dati.xlsx
+++ b/data/dati.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan_\Desktop\AMI\GitHub\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B5651B5-F346-42C2-A111-C9AA04AEDFF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D46DB9F3-78BF-4978-A256-66EEC3AED0D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1884" yWindow="1884" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Catalogo" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2962" uniqueCount="1150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2974" uniqueCount="1152">
   <si>
     <t>ID_relazione</t>
   </si>
@@ -3546,10 +3546,16 @@
     <t>https://archive.org/details/1985-documenti-del-iv-congresso/mode/2up</t>
   </si>
   <si>
-    <t>s.l.</t>
-  </si>
-  <si>
     <t>Nuova Unità; Unione della Gioventù Comunista d'Italia (marxista-leninista)</t>
+  </si>
+  <si>
+    <t>AMI-0110</t>
+  </si>
+  <si>
+    <t>La forza di essere comunisti: Che cosa vuole il Partito Comunista d'Italia (m-l)</t>
+  </si>
+  <si>
+    <t>https://archive.org/details/la-forza-di-essere-comunisti/mode/2up</t>
   </si>
 </sst>
 </file>
@@ -4847,7 +4853,7 @@
         <v>329</v>
       </c>
       <c r="O14" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="P14" t="s">
         <v>270</v>
@@ -9775,9 +9781,6 @@
       <c r="K110" t="s">
         <v>274</v>
       </c>
-      <c r="L110" t="s">
-        <v>1148</v>
-      </c>
       <c r="M110" t="s">
         <v>328</v>
       </c>
@@ -9792,7 +9795,51 @@
       </c>
     </row>
     <row r="111" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="Q111" s="3"/>
+      <c r="A111" t="s">
+        <v>1149</v>
+      </c>
+      <c r="B111" t="s">
+        <v>262</v>
+      </c>
+      <c r="C111" t="s">
+        <v>263</v>
+      </c>
+      <c r="D111" t="s">
+        <v>1150</v>
+      </c>
+      <c r="E111" t="s">
+        <v>265</v>
+      </c>
+      <c r="F111" t="s">
+        <v>12</v>
+      </c>
+      <c r="G111" t="s">
+        <v>10</v>
+      </c>
+      <c r="H111" t="s">
+        <v>1144</v>
+      </c>
+      <c r="I111">
+        <v>1986</v>
+      </c>
+      <c r="J111">
+        <v>1986</v>
+      </c>
+      <c r="K111" t="s">
+        <v>267</v>
+      </c>
+      <c r="L111" t="s">
+        <v>812</v>
+      </c>
+      <c r="M111" t="s">
+        <v>328</v>
+      </c>
+      <c r="P111" t="s">
+        <v>1080</v>
+      </c>
+      <c r="Q111" s="3" t="s">
+        <v>1151</v>
+      </c>
     </row>
     <row r="112" spans="1:22" x14ac:dyDescent="0.3">
       <c r="Q112" s="3"/>
@@ -10037,11 +10084,12 @@
     <hyperlink ref="Q105" r:id="rId107" xr:uid="{09B963F9-4F3D-4F82-A0E7-92B1358B3997}"/>
     <hyperlink ref="Q109" r:id="rId108" xr:uid="{DA33DC8F-848A-4B19-9DAB-DA96FA1F78B2}"/>
     <hyperlink ref="Q110" r:id="rId109" xr:uid="{54B8C84E-0C88-4EAD-825F-BFEFB5391A5A}"/>
+    <hyperlink ref="Q111" r:id="rId110" xr:uid="{987D79B4-DA9A-4321-BE42-93DC7C7ABA59}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId110"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId111"/>
   <tableParts count="1">
-    <tablePart r:id="rId111"/>
+    <tablePart r:id="rId112"/>
   </tableParts>
 </worksheet>
 </file>
